--- a/server/userPlan.xlsx
+++ b/server/userPlan.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29930"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BF4CE283-AC52-42B2-BB5E-C9191E8E7B80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6ACABEAF-C9B4-4450-9CC2-E7B88F6375EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1584" uniqueCount="415">
   <si>
     <t>id</t>
   </si>
@@ -54,30 +54,75 @@
     <t>created_at</t>
   </si>
   <si>
+    <t>AVG70261</t>
+  </si>
+  <si>
+    <t>$2200</t>
+  </si>
+  <si>
+    <t>$11</t>
+  </si>
+  <si>
+    <t>active</t>
+  </si>
+  <si>
+    <t>AVG55466</t>
+  </si>
+  <si>
+    <t>$500</t>
+  </si>
+  <si>
+    <t>$2.5</t>
+  </si>
+  <si>
+    <t>AVG71291</t>
+  </si>
+  <si>
+    <t>$3000</t>
+  </si>
+  <si>
+    <t>$15</t>
+  </si>
+  <si>
+    <t>AVG95589</t>
+  </si>
+  <si>
+    <t>$2000</t>
+  </si>
+  <si>
+    <t>$10</t>
+  </si>
+  <si>
+    <t>AVG77261</t>
+  </si>
+  <si>
+    <t>$100</t>
+  </si>
+  <si>
+    <t>$0.5</t>
+  </si>
+  <si>
+    <t>AVG35000</t>
+  </si>
+  <si>
+    <t>AVG44166</t>
+  </si>
+  <si>
+    <t>$1000</t>
+  </si>
+  <si>
+    <t>$5</t>
+  </si>
+  <si>
     <t>AVG18162</t>
   </si>
   <si>
-    <t>$1000</t>
-  </si>
-  <si>
-    <t>$5</t>
-  </si>
-  <si>
-    <t>active</t>
-  </si>
-  <si>
     <t>AVG61984</t>
   </si>
   <si>
     <t>AVG44339</t>
   </si>
   <si>
-    <t>$100</t>
-  </si>
-  <si>
-    <t>$0.5</t>
-  </si>
-  <si>
     <t>AVG76462</t>
   </si>
   <si>
@@ -99,12 +144,6 @@
     <t>AVG45681</t>
   </si>
   <si>
-    <t>$500</t>
-  </si>
-  <si>
-    <t>$2.5</t>
-  </si>
-  <si>
     <t>AVG04136</t>
   </si>
   <si>
@@ -264,12 +303,6 @@
     <t>AVG19207</t>
   </si>
   <si>
-    <t>$2000</t>
-  </si>
-  <si>
-    <t>$10</t>
-  </si>
-  <si>
     <t> AVG03021</t>
   </si>
   <si>
@@ -405,12 +438,6 @@
     <t>AVG71938</t>
   </si>
   <si>
-    <t>$3000</t>
-  </si>
-  <si>
-    <t>$15</t>
-  </si>
-  <si>
     <t> AVG21003</t>
   </si>
   <si>
@@ -733,12 +760,6 @@
   </si>
   <si>
     <t>AVG97054</t>
-  </si>
-  <si>
-    <t>$2200</t>
-  </si>
-  <si>
-    <t>$11</t>
   </si>
   <si>
     <t>AVG72593</t>
@@ -1451,7 +1472,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1502,7 +1523,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1784,8 +1810,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B9040242-A3FD-4595-BA2F-13350F718E47}" name="Table1" displayName="Table1" ref="A1:G388" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10" headerRowBorderDxfId="8" tableBorderDxfId="9" totalsRowBorderDxfId="7">
-  <autoFilter ref="A1:G388" xr:uid="{B9040242-A3FD-4595-BA2F-13350F718E47}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B9040242-A3FD-4595-BA2F-13350F718E47}" name="Table1" displayName="Table1" ref="A1:G395" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10" headerRowBorderDxfId="8" tableBorderDxfId="9" totalsRowBorderDxfId="7">
+  <autoFilter ref="A1:G395" xr:uid="{B9040242-A3FD-4595-BA2F-13350F718E47}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{F8B255F3-8561-4E75-93FC-7CD59135CCC9}" name="id" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{EE0AA50C-A116-4183-9D39-5A918AEC3F49}" name="user_code" dataDxfId="5"/>
@@ -2096,7 +2122,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K388"/>
+  <dimension ref="A1:J395"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.42578125" customWidth="1"/>
@@ -2108,7 +2134,7 @@
     <col min="7" max="7" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2131,7 +2157,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:10">
       <c r="A2" s="4"/>
       <c r="B2" s="18" t="s">
         <v>7</v>
@@ -2148,843 +2174,843 @@
       <c r="F2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="10">
+      <c r="G2" s="19">
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="4"/>
+      <c r="B3" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="5">
+        <v>3</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="19">
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="4"/>
+      <c r="B4" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="5">
+        <v>3</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="19">
+        <v>46118</v>
+      </c>
+      <c r="J4" s="17"/>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="4"/>
+      <c r="B5" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="5">
+        <v>3</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="19">
+        <v>46117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="4"/>
+      <c r="B6" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="5">
+        <v>3</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="19">
+        <v>46117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="4"/>
+      <c r="B7" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="5">
+        <v>3</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" s="10">
         <v>46116</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
-      <c r="A3" s="4"/>
-      <c r="B3" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="5">
-        <v>3</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" s="6">
+    <row r="8" spans="1:10">
+      <c r="A8" s="4"/>
+      <c r="B8" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="5">
+        <v>3</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="19">
+        <v>46116</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="4"/>
+      <c r="B9" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="5">
+        <v>3</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" s="10">
+        <v>46116</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="4"/>
+      <c r="B10" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="5">
+        <v>3</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="6">
         <v>46114</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
-      <c r="A4" s="4"/>
-      <c r="B4" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="5">
-        <v>3</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="6">
+    <row r="11" spans="1:10">
+      <c r="A11" s="4"/>
+      <c r="B11" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="5">
+        <v>3</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="6">
         <v>46114</v>
       </c>
-      <c r="K4" s="17"/>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="4"/>
-      <c r="B5" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="5">
-        <v>3</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="6">
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="4"/>
+      <c r="B12" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="5">
+        <v>3</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="6">
         <v>46113</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="4"/>
-      <c r="B6" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="5">
-        <v>3</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G6" s="6">
+    <row r="13" spans="1:10">
+      <c r="A13" s="4"/>
+      <c r="B13" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="5">
+        <v>3</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="6">
         <v>46113</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
-      <c r="A7" s="4"/>
-      <c r="B7" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" s="5">
-        <v>3</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G7" s="6">
+    <row r="14" spans="1:10">
+      <c r="A14" s="4"/>
+      <c r="B14" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="5">
+        <v>3</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="6">
         <v>46113</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
-      <c r="A8" s="4"/>
-      <c r="B8" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="5">
-        <v>3</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="10">
-        <v>46112</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" s="4"/>
-      <c r="B9" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="5">
-        <v>3</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9" s="10">
-        <v>46111</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" s="4"/>
-      <c r="B10" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="5">
-        <v>3</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="10">
-        <v>46111</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" s="4"/>
-      <c r="B11" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="5">
-        <v>3</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="10">
-        <v>46111</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" s="4"/>
-      <c r="B12" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" s="5">
-        <v>3</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G12" s="10">
-        <v>46111</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" s="4"/>
-      <c r="B13" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" s="5">
-        <v>3</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" s="10">
-        <v>46112</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" s="4"/>
-      <c r="B14" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" s="5">
-        <v>3</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G14" s="10">
-        <v>46110</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:10">
       <c r="A15" s="4"/>
       <c r="B15" s="8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C15" s="5">
         <v>3</v>
       </c>
-      <c r="D15" s="5" t="s">
-        <v>13</v>
+      <c r="D15" s="9" t="s">
+        <v>34</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G15" s="10">
-        <v>46109</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" s="4"/>
       <c r="B16" s="8" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C16" s="5">
         <v>3</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G16" s="10">
-        <v>46108</v>
+        <v>46111</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="4"/>
       <c r="B17" s="8" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C17" s="5">
         <v>3</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G17" s="10">
-        <v>46108</v>
+        <v>46111</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="4"/>
       <c r="B18" s="8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C18" s="5">
         <v>3</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G18" s="10">
-        <v>46108</v>
+        <v>46111</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="4"/>
       <c r="B19" s="8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C19" s="5">
         <v>3</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G19" s="10">
-        <v>46107</v>
+        <v>46111</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="4"/>
       <c r="B20" s="8" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C20" s="5">
         <v>3</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G20" s="10">
-        <v>46107</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="4"/>
       <c r="B21" s="8" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C21" s="5">
         <v>3</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G21" s="10">
-        <v>46107</v>
+        <v>46110</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="4"/>
       <c r="B22" s="8" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C22" s="5">
         <v>3</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G22" s="10">
-        <v>46107</v>
+        <v>46109</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="4"/>
       <c r="B23" s="8" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C23" s="5">
         <v>3</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G23" s="10">
-        <v>46107</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="4"/>
       <c r="B24" s="8" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C24" s="5">
         <v>3</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G24" s="10">
-        <v>46107</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="4"/>
       <c r="B25" s="8" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C25" s="5">
         <v>3</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G25" s="10">
-        <v>46106</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="4"/>
       <c r="B26" s="8" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C26" s="5">
         <v>3</v>
       </c>
       <c r="D26" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E26" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="F26" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G26" s="10">
-        <v>46106</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="4"/>
       <c r="B27" s="8" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C27" s="5">
         <v>3</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G27" s="10">
-        <v>46106</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" s="4"/>
       <c r="B28" s="8" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C28" s="5">
         <v>3</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G28" s="10">
-        <v>46105</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="4"/>
       <c r="B29" s="8" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C29" s="5">
         <v>3</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G29" s="10">
-        <v>46106</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="4"/>
       <c r="B30" s="8" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C30" s="5">
         <v>3</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="F30" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G30" s="10">
-        <v>46104</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="4"/>
       <c r="B31" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C31" s="5">
         <v>3</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G31" s="10">
-        <v>46101</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" s="4"/>
       <c r="B32" s="8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C32" s="5">
         <v>3</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G32" s="10">
-        <v>46102</v>
+        <v>46106</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="4"/>
       <c r="B33" s="8" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C33" s="5">
         <v>3</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F33" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G33" s="10">
-        <v>46100</v>
+        <v>46106</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="4"/>
       <c r="B34" s="8" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C34" s="5">
         <v>3</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G34" s="10">
-        <v>46111</v>
+        <v>46106</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" s="4"/>
       <c r="B35" s="8" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C35" s="5">
         <v>3</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G35" s="10">
-        <v>46099</v>
+        <v>46105</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="4"/>
       <c r="B36" s="8" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C36" s="5">
         <v>3</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G36" s="10">
-        <v>46100</v>
+        <v>46106</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="4"/>
       <c r="B37" s="8" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C37" s="5">
         <v>3</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>8</v>
+        <v>64</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G37" s="10">
-        <v>46100</v>
+        <v>46104</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="4"/>
       <c r="B38" s="8" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C38" s="5">
         <v>3</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F38" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G38" s="10">
-        <v>46099</v>
+        <v>46101</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="4"/>
       <c r="B39" s="8" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C39" s="5">
         <v>3</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="F39" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G39" s="10">
-        <v>46099</v>
+        <v>46102</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="4"/>
       <c r="B40" s="8" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C40" s="5">
         <v>3</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="F40" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G40" s="10">
-        <v>46099</v>
+        <v>46100</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="4"/>
       <c r="B41" s="8" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C41" s="5">
         <v>3</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G41" s="10">
-        <v>46099</v>
+        <v>46111</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="4"/>
       <c r="B42" s="8" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C42" s="5">
         <v>3</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="F42" s="5" t="s">
         <v>10</v>
@@ -2996,37 +3022,37 @@
     <row r="43" spans="1:7">
       <c r="A43" s="4"/>
       <c r="B43" s="8" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C43" s="5">
         <v>3</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="F43" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G43" s="10">
-        <v>46099</v>
+        <v>46100</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" s="4"/>
       <c r="B44" s="8" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C44" s="5">
         <v>3</v>
       </c>
-      <c r="D44" s="9" t="s">
-        <v>13</v>
+      <c r="D44" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F44" s="5" t="s">
         <v>10</v>
@@ -3038,16 +3064,16 @@
     <row r="45" spans="1:7">
       <c r="A45" s="4"/>
       <c r="B45" s="8" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C45" s="5">
         <v>3</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>69</v>
+        <v>25</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="F45" s="5" t="s">
         <v>10</v>
@@ -3059,37 +3085,37 @@
     <row r="46" spans="1:7">
       <c r="A46" s="4"/>
       <c r="B46" s="8" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C46" s="5">
         <v>3</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="F46" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G46" s="10">
-        <v>46098</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="4"/>
       <c r="B47" s="8" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C47" s="5">
         <v>3</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="F47" s="5" t="s">
         <v>10</v>
@@ -3101,58 +3127,58 @@
     <row r="48" spans="1:7">
       <c r="A48" s="4"/>
       <c r="B48" s="8" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C48" s="5">
         <v>3</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="F48" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G48" s="10">
-        <v>46098</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="4"/>
       <c r="B49" s="8" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C49" s="5">
         <v>3</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="F49" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G49" s="10">
-        <v>46098</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" s="4"/>
       <c r="B50" s="8" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C50" s="5">
         <v>3</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>8</v>
+        <v>64</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="F50" s="5" t="s">
         <v>10</v>
@@ -3164,58 +3190,58 @@
     <row r="51" spans="1:7">
       <c r="A51" s="4"/>
       <c r="B51" s="8" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C51" s="5">
         <v>3</v>
       </c>
-      <c r="D51" s="5" t="s">
-        <v>77</v>
+      <c r="D51" s="9" t="s">
+        <v>21</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>78</v>
+        <v>22</v>
       </c>
       <c r="F51" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G51" s="10">
-        <v>46097</v>
+        <v>46100</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="4"/>
       <c r="B52" s="8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C52" s="5">
         <v>3</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F52" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G52" s="10">
-        <v>46105</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" s="4"/>
       <c r="B53" s="8" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="C53" s="5">
         <v>3</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F53" s="5" t="s">
         <v>10</v>
@@ -3227,16 +3253,16 @@
     <row r="54" spans="1:7">
       <c r="A54" s="4"/>
       <c r="B54" s="8" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C54" s="5">
         <v>3</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>83</v>
+        <v>26</v>
       </c>
       <c r="F54" s="5" t="s">
         <v>10</v>
@@ -3248,190 +3274,190 @@
     <row r="55" spans="1:7">
       <c r="A55" s="4"/>
       <c r="B55" s="8" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C55" s="5">
         <v>3</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="F55" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G55" s="10">
-        <v>46105</v>
+        <v>46098</v>
       </c>
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="4"/>
       <c r="B56" s="8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C56" s="5">
         <v>3</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F56" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G56" s="10">
-        <v>46103</v>
+        <v>46098</v>
       </c>
     </row>
     <row r="57" spans="1:7">
       <c r="A57" s="4"/>
       <c r="B57" s="8" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C57" s="5">
         <v>3</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>85</v>
+        <v>25</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>86</v>
+        <v>26</v>
       </c>
       <c r="F57" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G57" s="10">
-        <v>46102</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="58" spans="1:7">
       <c r="A58" s="4"/>
       <c r="B58" s="8" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="C58" s="5">
         <v>3</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>87</v>
+        <v>18</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="F58" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G58" s="10">
-        <v>46099</v>
+        <v>46097</v>
       </c>
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="4"/>
       <c r="B59" s="8" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C59" s="5">
         <v>3</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="F59" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G59" s="10">
-        <v>46097</v>
+        <v>46105</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="4"/>
       <c r="B60" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C60" s="5">
         <v>3</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>91</v>
+        <v>22</v>
       </c>
       <c r="F60" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G60" s="10">
-        <v>46096</v>
+        <v>46098</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="4"/>
       <c r="B61" s="8" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C61" s="5">
         <v>3</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
       <c r="F61" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G61" s="10">
-        <v>46097</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="4"/>
       <c r="B62" s="8" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C62" s="5">
         <v>3</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="F62" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G62" s="10">
-        <v>46095</v>
+        <v>46105</v>
       </c>
     </row>
     <row r="63" spans="1:7">
       <c r="A63" s="4"/>
       <c r="B63" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C63" s="5">
         <v>3</v>
       </c>
       <c r="D63" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E63" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E63" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="F63" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G63" s="10">
-        <v>46095</v>
+        <v>46103</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -3443,115 +3469,115 @@
         <v>3</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>13</v>
+        <v>96</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>14</v>
+        <v>97</v>
       </c>
       <c r="F64" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G64" s="10">
-        <v>46106</v>
+        <v>46102</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="4"/>
       <c r="B65" s="8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C65" s="5">
         <v>3</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>51</v>
+        <v>98</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>52</v>
+        <v>99</v>
       </c>
       <c r="F65" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G65" s="10">
-        <v>46095</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="4"/>
       <c r="B66" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C66" s="5">
         <v>3</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G66" s="10">
-        <v>46101</v>
+        <v>46097</v>
       </c>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="4"/>
       <c r="B67" s="8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C67" s="5">
         <v>3</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>13</v>
+        <v>101</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>14</v>
+        <v>102</v>
       </c>
       <c r="F67" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G67" s="10">
-        <v>46095</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="4"/>
       <c r="B68" s="8" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C68" s="5">
         <v>3</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F68" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G68" s="10">
-        <v>46095</v>
+        <v>46097</v>
       </c>
     </row>
     <row r="69" spans="1:7">
       <c r="A69" s="4"/>
       <c r="B69" s="8" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C69" s="5">
         <v>3</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F69" s="5" t="s">
         <v>10</v>
@@ -3563,16 +3589,16 @@
     <row r="70" spans="1:7">
       <c r="A70" s="4"/>
       <c r="B70" s="8" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C70" s="5">
         <v>3</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F70" s="5" t="s">
         <v>10</v>
@@ -3584,226 +3610,226 @@
     <row r="71" spans="1:7">
       <c r="A71" s="4"/>
       <c r="B71" s="8" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C71" s="5">
         <v>3</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F71" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G71" s="10">
-        <v>46110</v>
+        <v>46106</v>
       </c>
     </row>
     <row r="72" spans="1:7">
       <c r="A72" s="4"/>
       <c r="B72" s="8" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C72" s="5">
         <v>3</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>103</v>
+        <v>64</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="F72" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G72" s="10">
-        <v>46098</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="73" spans="1:7">
       <c r="A73" s="4"/>
       <c r="B73" s="8" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="C73" s="5">
         <v>3</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F73" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G73" s="10">
-        <v>46095</v>
+        <v>46101</v>
       </c>
     </row>
     <row r="74" spans="1:7">
       <c r="A74" s="4"/>
       <c r="B74" s="8" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C74" s="5">
         <v>3</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>107</v>
+        <v>22</v>
       </c>
       <c r="F74" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G74" s="10">
-        <v>46094</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="75" spans="1:7">
       <c r="A75" s="4"/>
       <c r="B75" s="8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C75" s="5">
         <v>3</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="F75" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G75" s="10">
-        <v>46094</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="76" spans="1:7">
       <c r="A76" s="4"/>
       <c r="B76" s="8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C76" s="5">
         <v>3</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="F76" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G76" s="10">
-        <v>46094</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="77" spans="1:7">
       <c r="A77" s="4"/>
       <c r="B77" s="8" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C77" s="5">
         <v>3</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F77" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G77" s="10">
-        <v>46094</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="78" spans="1:7">
       <c r="A78" s="4"/>
       <c r="B78" s="8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C78" s="5">
         <v>3</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>112</v>
+        <v>12</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>113</v>
+        <v>13</v>
       </c>
       <c r="F78" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G78" s="10">
-        <v>46094</v>
+        <v>46110</v>
       </c>
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="4"/>
       <c r="B79" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="C79" s="5">
+        <v>3</v>
+      </c>
+      <c r="D79" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="C79" s="5">
-        <v>3</v>
-      </c>
-      <c r="D79" s="5" t="s">
-        <v>13</v>
-      </c>
       <c r="E79" s="5" t="s">
-        <v>14</v>
+        <v>115</v>
       </c>
       <c r="F79" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G79" s="10">
-        <v>46094</v>
+        <v>46098</v>
       </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="4"/>
       <c r="B80" s="8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C80" s="5">
         <v>3</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="F80" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G80" s="10">
-        <v>46096</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="4"/>
       <c r="B81" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C81" s="5">
         <v>3</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="F81" s="5" t="s">
         <v>10</v>
@@ -3815,37 +3841,37 @@
     <row r="82" spans="1:7">
       <c r="A82" s="4"/>
       <c r="B82" s="8" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C82" s="5">
         <v>3</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="F82" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G82" s="10">
-        <v>46097</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="4"/>
       <c r="B83" s="8" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C83" s="5">
         <v>3</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>117</v>
+        <v>25</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>118</v>
+        <v>26</v>
       </c>
       <c r="F83" s="5" t="s">
         <v>10</v>
@@ -3857,16 +3883,16 @@
     <row r="84" spans="1:7">
       <c r="A84" s="4"/>
       <c r="B84" s="8" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C84" s="5">
         <v>3</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F84" s="5" t="s">
         <v>10</v>
@@ -3878,19 +3904,19 @@
     <row r="85" spans="1:7">
       <c r="A85" s="4"/>
       <c r="B85" s="8" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C85" s="5">
         <v>3</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>51</v>
+        <v>123</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>52</v>
+        <v>124</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="G85" s="10">
         <v>46094</v>
@@ -3899,16 +3925,16 @@
     <row r="86" spans="1:7">
       <c r="A86" s="4"/>
       <c r="B86" s="8" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C86" s="5">
         <v>3</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="F86" s="5" t="s">
         <v>10</v>
@@ -3920,64 +3946,64 @@
     <row r="87" spans="1:7">
       <c r="A87" s="4"/>
       <c r="B87" s="8" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C87" s="5">
         <v>3</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="F87" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G87" s="10">
-        <v>46094</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="4"/>
       <c r="B88" s="8" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C88" s="5">
         <v>3</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>124</v>
+        <v>18</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>125</v>
+        <v>19</v>
       </c>
       <c r="F88" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G88" s="10">
-        <v>46093</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="89" spans="1:7">
       <c r="A89" s="4"/>
       <c r="B89" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C89" s="5">
         <v>3</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>9</v>
+        <v>92</v>
       </c>
       <c r="F89" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G89" s="10">
-        <v>46100</v>
+        <v>46097</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -3989,100 +4015,100 @@
         <v>3</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>45</v>
+        <v>129</v>
       </c>
       <c r="F90" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G90" s="10">
-        <v>46092</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="91" spans="1:7">
       <c r="A91" s="4"/>
       <c r="B91" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C91" s="5">
         <v>3</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>125</v>
+        <v>22</v>
       </c>
       <c r="F91" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G91" s="10">
-        <v>46093</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="4"/>
       <c r="B92" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C92" s="5">
         <v>3</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>8</v>
+        <v>64</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>10</v>
+        <v>131</v>
       </c>
       <c r="G92" s="10">
-        <v>46092</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="93" spans="1:7">
       <c r="A93" s="4"/>
       <c r="B93" s="8" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C93" s="5">
         <v>3</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F93" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G93" s="10">
-        <v>46090</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="94" spans="1:7">
       <c r="A94" s="4"/>
       <c r="B94" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C94" s="5">
         <v>3</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>132</v>
+        <v>64</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>133</v>
+        <v>65</v>
       </c>
       <c r="F94" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G94" s="10">
-        <v>46089</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -4094,16 +4120,16 @@
         <v>3</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F95" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G95" s="10">
-        <v>46089</v>
+        <v>46093</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -4115,16 +4141,16 @@
         <v>3</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F96" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G96" s="10">
-        <v>46088</v>
+        <v>46100</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4136,10 +4162,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>8</v>
+        <v>91</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>9</v>
+        <v>58</v>
       </c>
       <c r="F97" s="5" t="s">
         <v>10</v>
@@ -4157,16 +4183,16 @@
         <v>3</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F98" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G98" s="10">
-        <v>46088</v>
+        <v>46093</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4178,16 +4204,16 @@
         <v>3</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>63</v>
+        <v>26</v>
       </c>
       <c r="F99" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G99" s="10">
-        <v>46103</v>
+        <v>46092</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -4199,10 +4225,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="F100" s="5" t="s">
         <v>10</v>
@@ -4220,52 +4246,52 @@
         <v>3</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>13</v>
+        <v>141</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>14</v>
+        <v>142</v>
       </c>
       <c r="F101" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G101" s="10">
-        <v>46087</v>
+        <v>46089</v>
       </c>
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="4"/>
       <c r="B102" s="8" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C102" s="5">
         <v>3</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F102" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G102" s="10">
-        <v>46087</v>
+        <v>46089</v>
       </c>
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="4"/>
       <c r="B103" s="8" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C103" s="5">
         <v>3</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>143</v>
+        <v>46</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>144</v>
+        <v>47</v>
       </c>
       <c r="F103" s="5" t="s">
         <v>10</v>
@@ -4283,16 +4309,16 @@
         <v>3</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F104" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G104" s="10">
-        <v>46088</v>
+        <v>46092</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4304,10 +4330,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F105" s="5" t="s">
         <v>10</v>
@@ -4325,16 +4351,16 @@
         <v>3</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="F106" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G106" s="10">
-        <v>46094</v>
+        <v>46103</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4346,16 +4372,16 @@
         <v>3</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F107" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G107" s="10">
-        <v>46086</v>
+        <v>46090</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4367,16 +4393,16 @@
         <v>3</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>63</v>
+        <v>22</v>
       </c>
       <c r="F108" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G108" s="10">
-        <v>46086</v>
+        <v>46087</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4388,16 +4414,16 @@
         <v>3</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>78</v>
+        <v>22</v>
       </c>
       <c r="F109" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G109" s="10">
-        <v>46085</v>
+        <v>46087</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4409,136 +4435,136 @@
         <v>3</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="F110" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G110" s="10">
-        <v>46085</v>
+        <v>46088</v>
       </c>
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="4"/>
       <c r="B111" s="8" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C111" s="5">
         <v>3</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>153</v>
+        <v>26</v>
       </c>
       <c r="F111" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G111" s="10">
-        <v>46085</v>
+        <v>46088</v>
       </c>
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="4"/>
       <c r="B112" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C112" s="5">
         <v>3</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F112" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G112" s="10">
-        <v>46085</v>
+        <v>46088</v>
       </c>
     </row>
     <row r="113" spans="1:7">
       <c r="A113" s="4"/>
       <c r="B113" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C113" s="5">
         <v>3</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F113" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G113" s="10">
-        <v>46085</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="114" spans="1:7">
       <c r="A114" s="4"/>
       <c r="B114" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C114" s="5">
         <v>3</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>124</v>
+        <v>40</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>125</v>
+        <v>41</v>
       </c>
       <c r="F114" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G114" s="10">
-        <v>46094</v>
+        <v>46086</v>
       </c>
     </row>
     <row r="115" spans="1:7">
       <c r="A115" s="4"/>
       <c r="B115" s="8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C115" s="5">
         <v>3</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="F115" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G115" s="10">
-        <v>46085</v>
+        <v>46086</v>
       </c>
     </row>
     <row r="116" spans="1:7">
       <c r="A116" s="4"/>
       <c r="B116" s="8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C116" s="5">
         <v>3</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>78</v>
+        <v>19</v>
       </c>
       <c r="F116" s="5" t="s">
         <v>10</v>
@@ -4550,16 +4576,16 @@
     <row r="117" spans="1:7">
       <c r="A117" s="4"/>
       <c r="B117" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C117" s="5">
         <v>3</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="F117" s="5" t="s">
         <v>10</v>
@@ -4571,37 +4597,37 @@
     <row r="118" spans="1:7">
       <c r="A118" s="4"/>
       <c r="B118" s="8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C118" s="5">
         <v>3</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>14</v>
+        <v>162</v>
       </c>
       <c r="F118" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G118" s="10">
-        <v>46084</v>
+        <v>46085</v>
       </c>
     </row>
     <row r="119" spans="1:7">
       <c r="A119" s="4"/>
       <c r="B119" s="8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C119" s="5">
         <v>3</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>117</v>
+        <v>25</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>118</v>
+        <v>26</v>
       </c>
       <c r="F119" s="5" t="s">
         <v>10</v>
@@ -4613,22 +4639,22 @@
     <row r="120" spans="1:7">
       <c r="A120" s="4"/>
       <c r="B120" s="8" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C120" s="5">
         <v>3</v>
       </c>
       <c r="D120" s="5" t="s">
-        <v>163</v>
+        <v>25</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>164</v>
+        <v>26</v>
       </c>
       <c r="F120" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G120" s="10">
-        <v>46084</v>
+        <v>46085</v>
       </c>
     </row>
     <row r="121" spans="1:7">
@@ -4640,94 +4666,94 @@
         <v>3</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="F121" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G121" s="10">
-        <v>46112</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="122" spans="1:7">
       <c r="A122" s="4"/>
       <c r="B122" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C122" s="5">
         <v>3</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="F122" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G122" s="10">
-        <v>46095</v>
+        <v>46085</v>
       </c>
     </row>
     <row r="123" spans="1:7">
       <c r="A123" s="4"/>
       <c r="B123" s="8" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C123" s="5">
         <v>3</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F123" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G123" s="10">
-        <v>46084</v>
+        <v>46085</v>
       </c>
     </row>
     <row r="124" spans="1:7">
       <c r="A124" s="4"/>
       <c r="B124" s="8" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C124" s="5">
         <v>3</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>8</v>
+        <v>64</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="F124" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G124" s="10">
-        <v>46084</v>
+        <v>46085</v>
       </c>
     </row>
     <row r="125" spans="1:7">
       <c r="A125" s="4"/>
       <c r="B125" s="8" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C125" s="5">
         <v>3</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>153</v>
+        <v>22</v>
       </c>
       <c r="F125" s="5" t="s">
         <v>10</v>
@@ -4739,37 +4765,37 @@
     <row r="126" spans="1:7">
       <c r="A126" s="4"/>
       <c r="B126" s="8" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C126" s="5">
         <v>3</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>13</v>
+        <v>128</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>14</v>
+        <v>129</v>
       </c>
       <c r="F126" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G126" s="10">
-        <v>46084</v>
+        <v>46085</v>
       </c>
     </row>
     <row r="127" spans="1:7">
       <c r="A127" s="4"/>
       <c r="B127" s="8" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C127" s="5">
         <v>3</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>13</v>
+        <v>172</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>14</v>
+        <v>173</v>
       </c>
       <c r="F127" s="5" t="s">
         <v>10</v>
@@ -4781,376 +4807,376 @@
     <row r="128" spans="1:7">
       <c r="A128" s="4"/>
       <c r="B128" s="8" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C128" s="5">
         <v>3</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="F128" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G128" s="10">
-        <v>46098</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="129" spans="1:7">
       <c r="A129" s="4"/>
       <c r="B129" s="8" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C129" s="5">
         <v>3</v>
       </c>
       <c r="D129" s="5" t="s">
-        <v>8</v>
+        <v>64</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>9</v>
+        <v>65</v>
       </c>
       <c r="F129" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G129" s="10">
-        <v>46086</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="4"/>
       <c r="B130" s="8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C130" s="5">
         <v>3</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F130" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G130" s="10">
-        <v>46099</v>
+        <v>46084</v>
       </c>
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="4"/>
       <c r="B131" s="8" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C131" s="5">
         <v>3</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F131" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G131" s="10">
-        <v>46082</v>
+        <v>46084</v>
       </c>
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="4"/>
       <c r="B132" s="8" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C132" s="5">
         <v>3</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>34</v>
+        <v>162</v>
       </c>
       <c r="F132" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G132" s="10">
-        <v>46103</v>
+        <v>46084</v>
       </c>
     </row>
     <row r="133" spans="1:7">
       <c r="A133" s="4"/>
       <c r="B133" s="8" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C133" s="5">
         <v>3</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F133" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G133" s="10">
-        <v>46095</v>
+        <v>46084</v>
       </c>
     </row>
     <row r="134" spans="1:7">
       <c r="A134" s="4"/>
       <c r="B134" s="8" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C134" s="5">
         <v>3</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="F134" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G134" s="10">
-        <v>46081</v>
+        <v>46084</v>
       </c>
     </row>
     <row r="135" spans="1:7">
       <c r="A135" s="4"/>
       <c r="B135" s="8" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C135" s="5">
         <v>3</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F135" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G135" s="10">
-        <v>46080</v>
+        <v>46098</v>
       </c>
     </row>
     <row r="136" spans="1:7">
       <c r="A136" s="4"/>
       <c r="B136" s="8" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C136" s="5">
         <v>3</v>
       </c>
       <c r="D136" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F136" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G136" s="10">
-        <v>46080</v>
+        <v>46086</v>
       </c>
     </row>
     <row r="137" spans="1:7">
       <c r="A137" s="4"/>
       <c r="B137" s="8" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C137" s="5">
         <v>3</v>
       </c>
       <c r="D137" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F137" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G137" s="10">
-        <v>46080</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="138" spans="1:7">
       <c r="A138" s="4"/>
       <c r="B138" s="8" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C138" s="5">
         <v>3</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F138" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G138" s="10">
-        <v>46079</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="139" spans="1:7">
       <c r="A139" s="4"/>
       <c r="B139" s="8" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C139" s="5">
         <v>3</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="F139" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G139" s="10">
-        <v>46079</v>
+        <v>46103</v>
       </c>
     </row>
     <row r="140" spans="1:7">
       <c r="A140" s="4"/>
       <c r="B140" s="8" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C140" s="5">
         <v>3</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>125</v>
+        <v>22</v>
       </c>
       <c r="F140" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G140" s="10">
-        <v>46079</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="141" spans="1:7">
       <c r="A141" s="4"/>
       <c r="B141" s="8" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C141" s="5">
         <v>3</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>153</v>
+        <v>26</v>
       </c>
       <c r="F141" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G141" s="10">
-        <v>46079</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="142" spans="1:7">
       <c r="A142" s="4"/>
       <c r="B142" s="8" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C142" s="5">
         <v>3</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="F142" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G142" s="10">
-        <v>46079</v>
+        <v>46080</v>
       </c>
     </row>
     <row r="143" spans="1:7">
       <c r="A143" s="4"/>
       <c r="B143" s="8" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C143" s="5">
         <v>3</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>124</v>
+        <v>40</v>
       </c>
       <c r="E143" s="5" t="s">
-        <v>125</v>
+        <v>41</v>
       </c>
       <c r="F143" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G143" s="10">
-        <v>46079</v>
+        <v>46080</v>
       </c>
     </row>
     <row r="144" spans="1:7">
       <c r="A144" s="4"/>
       <c r="B144" s="8" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C144" s="5">
         <v>3</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="F144" s="5" t="s">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="G144" s="10">
-        <v>46097</v>
+        <v>46080</v>
       </c>
     </row>
     <row r="145" spans="1:7">
       <c r="A145" s="4"/>
       <c r="B145" s="8" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C145" s="5">
         <v>3</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F145" s="5" t="s">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="G145" s="10">
         <v>46079</v>
@@ -5159,16 +5185,16 @@
     <row r="146" spans="1:7">
       <c r="A146" s="4"/>
       <c r="B146" s="8" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C146" s="5">
         <v>3</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>124</v>
+        <v>18</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>125</v>
+        <v>19</v>
       </c>
       <c r="F146" s="5" t="s">
         <v>10</v>
@@ -5180,16 +5206,16 @@
     <row r="147" spans="1:7">
       <c r="A147" s="4"/>
       <c r="B147" s="8" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C147" s="5">
         <v>3</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>153</v>
+        <v>16</v>
       </c>
       <c r="F147" s="5" t="s">
         <v>10</v>
@@ -5201,16 +5227,16 @@
     <row r="148" spans="1:7">
       <c r="A148" s="4"/>
       <c r="B148" s="8" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="C148" s="5">
         <v>3</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>9</v>
+        <v>162</v>
       </c>
       <c r="F148" s="5" t="s">
         <v>10</v>
@@ -5222,16 +5248,16 @@
     <row r="149" spans="1:7">
       <c r="A149" s="4"/>
       <c r="B149" s="8" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C149" s="5">
         <v>3</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F149" s="5" t="s">
         <v>10</v>
@@ -5243,79 +5269,79 @@
     <row r="150" spans="1:7">
       <c r="A150" s="4"/>
       <c r="B150" s="8" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C150" s="5">
         <v>3</v>
       </c>
       <c r="D150" s="5" t="s">
-        <v>103</v>
+        <v>15</v>
       </c>
       <c r="E150" s="5" t="s">
-        <v>104</v>
+        <v>16</v>
       </c>
       <c r="F150" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G150" s="10">
-        <v>46111</v>
+        <v>46079</v>
       </c>
     </row>
     <row r="151" spans="1:7">
       <c r="A151" s="4"/>
       <c r="B151" s="8" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C151" s="5">
         <v>3</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="G151" s="10">
-        <v>46083</v>
+        <v>46097</v>
       </c>
     </row>
     <row r="152" spans="1:7">
       <c r="A152" s="4"/>
       <c r="B152" s="8" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C152" s="5">
         <v>3</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>10</v>
+        <v>131</v>
       </c>
       <c r="G152" s="10">
-        <v>46107</v>
+        <v>46079</v>
       </c>
     </row>
     <row r="153" spans="1:7">
       <c r="A153" s="4"/>
       <c r="B153" s="8" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="C153" s="5">
         <v>3</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F153" s="5" t="s">
         <v>10</v>
@@ -5327,37 +5353,37 @@
     <row r="154" spans="1:7">
       <c r="A154" s="4"/>
       <c r="B154" s="8" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C154" s="5">
         <v>3</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>194</v>
+        <v>34</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>195</v>
+        <v>162</v>
       </c>
       <c r="F154" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G154" s="10">
-        <v>46113</v>
+        <v>46079</v>
       </c>
     </row>
     <row r="155" spans="1:7">
       <c r="A155" s="4"/>
       <c r="B155" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C155" s="5">
         <v>3</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="F155" s="5" t="s">
         <v>10</v>
@@ -5369,43 +5395,43 @@
     <row r="156" spans="1:7">
       <c r="A156" s="4"/>
       <c r="B156" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C156" s="5">
         <v>3</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>194</v>
+        <v>25</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>195</v>
+        <v>26</v>
       </c>
       <c r="F156" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G156" s="10">
-        <v>46113</v>
+        <v>46079</v>
       </c>
     </row>
     <row r="157" spans="1:7">
       <c r="A157" s="4"/>
       <c r="B157" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C157" s="5">
         <v>3</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="F157" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G157" s="10">
-        <v>46104</v>
+        <v>46111</v>
       </c>
     </row>
     <row r="158" spans="1:7">
@@ -5417,16 +5443,16 @@
         <v>3</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="G158" s="10">
-        <v>46104</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="159" spans="1:7">
@@ -5438,37 +5464,37 @@
         <v>3</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F159" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G159" s="10">
-        <v>46078</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="160" spans="1:7">
       <c r="A160" s="4"/>
-      <c r="B160" s="11" t="s">
+      <c r="B160" s="8" t="s">
         <v>201</v>
       </c>
       <c r="C160" s="5">
         <v>3</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F160" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G160" s="10">
-        <v>46078</v>
+        <v>46079</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -5480,178 +5506,178 @@
         <v>3</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>22</v>
+        <v>203</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>23</v>
+        <v>204</v>
       </c>
       <c r="F161" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G161" s="10">
-        <v>46081</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="162" spans="1:7">
       <c r="A162" s="4"/>
       <c r="B162" s="8" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C162" s="5">
         <v>3</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>9</v>
+        <v>58</v>
       </c>
       <c r="F162" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G162" s="10">
-        <v>46077</v>
+        <v>46079</v>
       </c>
     </row>
     <row r="163" spans="1:7">
       <c r="A163" s="4"/>
       <c r="B163" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="C163" s="5">
+        <v>3</v>
+      </c>
+      <c r="D163" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="E163" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="C163" s="5">
-        <v>3</v>
-      </c>
-      <c r="D163" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E163" s="5" t="s">
-        <v>23</v>
-      </c>
       <c r="F163" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G163" s="10">
-        <v>46077</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="164" spans="1:7">
       <c r="A164" s="4"/>
       <c r="B164" s="8" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C164" s="5">
         <v>3</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>13</v>
+        <v>91</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>14</v>
+        <v>92</v>
       </c>
       <c r="F164" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G164" s="10">
-        <v>46100</v>
+        <v>46104</v>
       </c>
     </row>
     <row r="165" spans="1:7">
       <c r="A165" s="4"/>
       <c r="B165" s="8" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C165" s="5">
         <v>3</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F165" s="5" t="s">
-        <v>10</v>
+        <v>131</v>
       </c>
       <c r="G165" s="10">
-        <v>46093</v>
+        <v>46104</v>
       </c>
     </row>
     <row r="166" spans="1:7">
       <c r="A166" s="4"/>
       <c r="B166" s="8" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C166" s="5">
         <v>3</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="E166" s="5" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="F166" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G166" s="10">
-        <v>46077</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="167" spans="1:7">
       <c r="A167" s="4"/>
-      <c r="B167" s="8" t="s">
-        <v>207</v>
+      <c r="B167" s="11" t="s">
+        <v>210</v>
       </c>
       <c r="C167" s="5">
         <v>3</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F167" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G167" s="10">
-        <v>46077</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="168" spans="1:7">
       <c r="A168" s="4"/>
       <c r="B168" s="8" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C168" s="5">
         <v>3</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E168" s="5" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F168" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G168" s="10">
-        <v>46077</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="169" spans="1:7">
       <c r="A169" s="4"/>
       <c r="B169" s="8" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C169" s="5">
         <v>3</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F169" s="5" t="s">
         <v>10</v>
@@ -5663,121 +5689,121 @@
     <row r="170" spans="1:7">
       <c r="A170" s="4"/>
       <c r="B170" s="8" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C170" s="5">
         <v>3</v>
       </c>
       <c r="D170" s="5" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F170" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G170" s="10">
-        <v>46097</v>
+        <v>46077</v>
       </c>
     </row>
     <row r="171" spans="1:7">
       <c r="A171" s="4"/>
       <c r="B171" s="8" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C171" s="5">
         <v>3</v>
       </c>
       <c r="D171" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E171" s="5" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="F171" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G171" s="10">
-        <v>46079</v>
+        <v>46100</v>
       </c>
     </row>
     <row r="172" spans="1:7">
       <c r="A172" s="4"/>
       <c r="B172" s="8" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="C172" s="5">
         <v>3</v>
       </c>
       <c r="D172" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="F172" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G172" s="10">
-        <v>46076</v>
+        <v>46093</v>
       </c>
     </row>
     <row r="173" spans="1:7">
       <c r="A173" s="4"/>
       <c r="B173" s="8" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C173" s="5">
         <v>3</v>
       </c>
       <c r="D173" s="5" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="F173" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G173" s="10">
-        <v>46098</v>
+        <v>46077</v>
       </c>
     </row>
     <row r="174" spans="1:7">
       <c r="A174" s="4"/>
       <c r="B174" s="8" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C174" s="5">
         <v>3</v>
       </c>
       <c r="D174" s="5" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F174" s="5" t="s">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="G174" s="10">
-        <v>46075</v>
+        <v>46077</v>
       </c>
     </row>
     <row r="175" spans="1:7">
       <c r="A175" s="4"/>
       <c r="B175" s="8" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C175" s="5">
         <v>3</v>
       </c>
       <c r="D175" s="5" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E175" s="5" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F175" s="5" t="s">
         <v>10</v>
@@ -5789,610 +5815,610 @@
     <row r="176" spans="1:7">
       <c r="A176" s="4"/>
       <c r="B176" s="8" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C176" s="5">
         <v>3</v>
       </c>
       <c r="D176" s="5" t="s">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="F176" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G176" s="10">
-        <v>46093</v>
+        <v>46077</v>
       </c>
     </row>
     <row r="177" spans="1:7">
       <c r="A177" s="4"/>
       <c r="B177" s="8" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C177" s="5">
         <v>3</v>
       </c>
       <c r="D177" s="5" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E177" s="5" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F177" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G177" s="10">
-        <v>46078</v>
+        <v>46097</v>
       </c>
     </row>
     <row r="178" spans="1:7">
       <c r="A178" s="4"/>
       <c r="B178" s="8" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C178" s="5">
         <v>3</v>
       </c>
       <c r="D178" s="5" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="E178" s="5" t="s">
-        <v>104</v>
+        <v>26</v>
       </c>
       <c r="F178" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G178" s="10">
-        <v>46098</v>
+        <v>46079</v>
       </c>
     </row>
     <row r="179" spans="1:7">
       <c r="A179" s="4"/>
       <c r="B179" s="8" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C179" s="5">
         <v>3</v>
       </c>
       <c r="D179" s="5" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E179" s="5" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F179" s="5" t="s">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="G179" s="10">
-        <v>46098</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="180" spans="1:7">
       <c r="A180" s="4"/>
       <c r="B180" s="8" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C180" s="5">
         <v>3</v>
       </c>
-      <c r="D180" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E180" s="9" t="s">
-        <v>14</v>
+      <c r="D180" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E180" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="F180" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G180" s="10">
-        <v>46103</v>
+        <v>46098</v>
       </c>
     </row>
     <row r="181" spans="1:7">
       <c r="A181" s="4"/>
       <c r="B181" s="8" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C181" s="5">
         <v>3</v>
       </c>
-      <c r="D181" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E181" s="9" t="s">
-        <v>14</v>
+      <c r="D181" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E181" s="5" t="s">
+        <v>22</v>
       </c>
       <c r="F181" s="5" t="s">
-        <v>10</v>
+        <v>131</v>
       </c>
       <c r="G181" s="10">
-        <v>46102</v>
+        <v>46075</v>
       </c>
     </row>
     <row r="182" spans="1:7">
       <c r="A182" s="4"/>
       <c r="B182" s="8" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C182" s="5">
         <v>3</v>
       </c>
-      <c r="D182" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E182" s="9" t="s">
-        <v>14</v>
+      <c r="D182" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E182" s="5" t="s">
+        <v>47</v>
       </c>
       <c r="F182" s="5" t="s">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="G182" s="10">
-        <v>46088</v>
+        <v>46077</v>
       </c>
     </row>
     <row r="183" spans="1:7">
       <c r="A183" s="4"/>
       <c r="B183" s="8" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="C183" s="5">
         <v>3</v>
       </c>
       <c r="D183" s="5" t="s">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="E183" s="5" t="s">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="F183" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G183" s="10">
-        <v>46072</v>
+        <v>46093</v>
       </c>
     </row>
     <row r="184" spans="1:7">
       <c r="A184" s="4"/>
       <c r="B184" s="8" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C184" s="5">
         <v>3</v>
       </c>
       <c r="D184" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E184" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F184" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G184" s="10">
-        <v>46070</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="185" spans="1:7">
       <c r="A185" s="4"/>
       <c r="B185" s="8" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C185" s="5">
         <v>3</v>
       </c>
       <c r="D185" s="5" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>14</v>
+        <v>115</v>
       </c>
       <c r="F185" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G185" s="10">
-        <v>46070</v>
+        <v>46098</v>
       </c>
     </row>
     <row r="186" spans="1:7">
       <c r="A186" s="4"/>
       <c r="B186" s="8" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C186" s="5">
         <v>3</v>
       </c>
       <c r="D186" s="5" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="E186" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F186" s="5" t="s">
-        <v>10</v>
+        <v>131</v>
       </c>
       <c r="G186" s="10">
-        <v>46070</v>
+        <v>46098</v>
       </c>
     </row>
     <row r="187" spans="1:7">
       <c r="A187" s="4"/>
       <c r="B187" s="8" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C187" s="5">
         <v>3</v>
       </c>
-      <c r="D187" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="E187" s="5" t="s">
-        <v>28</v>
+      <c r="D187" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E187" s="9" t="s">
+        <v>22</v>
       </c>
       <c r="F187" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G187" s="10">
-        <v>46070</v>
+        <v>46103</v>
       </c>
     </row>
     <row r="188" spans="1:7">
       <c r="A188" s="4"/>
       <c r="B188" s="8" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C188" s="5">
         <v>3</v>
       </c>
-      <c r="D188" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E188" s="5" t="s">
-        <v>14</v>
+      <c r="D188" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E188" s="9" t="s">
+        <v>22</v>
       </c>
       <c r="F188" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G188" s="10">
-        <v>46070</v>
+        <v>46102</v>
       </c>
     </row>
     <row r="189" spans="1:7">
       <c r="A189" s="4"/>
       <c r="B189" s="8" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C189" s="5">
         <v>3</v>
       </c>
-      <c r="D189" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E189" s="5" t="s">
-        <v>14</v>
+      <c r="D189" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E189" s="9" t="s">
+        <v>22</v>
       </c>
       <c r="F189" s="5" t="s">
-        <v>10</v>
+        <v>131</v>
       </c>
       <c r="G189" s="10">
-        <v>46068</v>
+        <v>46088</v>
       </c>
     </row>
     <row r="190" spans="1:7">
       <c r="A190" s="4"/>
       <c r="B190" s="8" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C190" s="5">
         <v>3</v>
       </c>
       <c r="D190" s="5" t="s">
-        <v>112</v>
+        <v>64</v>
       </c>
       <c r="E190" s="5" t="s">
-        <v>113</v>
+        <v>65</v>
       </c>
       <c r="F190" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G190" s="10">
-        <v>46105</v>
+        <v>46072</v>
       </c>
     </row>
     <row r="191" spans="1:7">
       <c r="A191" s="4"/>
       <c r="B191" s="8" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C191" s="5">
         <v>3</v>
       </c>
       <c r="D191" s="5" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="E191" s="5" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="F191" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G191" s="10">
-        <v>46092</v>
+        <v>46070</v>
       </c>
     </row>
     <row r="192" spans="1:7">
       <c r="A192" s="4"/>
       <c r="B192" s="8" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C192" s="5">
         <v>3</v>
       </c>
       <c r="D192" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E192" s="5" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="F192" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G192" s="10">
-        <v>46075</v>
+        <v>46070</v>
       </c>
     </row>
     <row r="193" spans="1:7">
       <c r="A193" s="4"/>
       <c r="B193" s="8" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C193" s="5">
         <v>3</v>
       </c>
       <c r="D193" s="5" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="E193" s="5" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="F193" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G193" s="10">
-        <v>46072</v>
+        <v>46070</v>
       </c>
     </row>
     <row r="194" spans="1:7">
       <c r="A194" s="4"/>
       <c r="B194" s="8" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="C194" s="5">
         <v>3</v>
       </c>
       <c r="D194" s="5" t="s">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="E194" s="5" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="F194" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G194" s="10">
-        <v>46071</v>
+        <v>46070</v>
       </c>
     </row>
     <row r="195" spans="1:7">
       <c r="A195" s="4"/>
       <c r="B195" s="8" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="C195" s="5">
         <v>3</v>
       </c>
       <c r="D195" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E195" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F195" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G195" s="10">
-        <v>46072</v>
+        <v>46070</v>
       </c>
     </row>
     <row r="196" spans="1:7">
       <c r="A196" s="4"/>
       <c r="B196" s="8" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="C196" s="5">
         <v>3</v>
       </c>
       <c r="D196" s="5" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E196" s="5" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="F196" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G196" s="10">
-        <v>46107</v>
+        <v>46068</v>
       </c>
     </row>
     <row r="197" spans="1:7">
       <c r="A197" s="4"/>
       <c r="B197" s="8" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="C197" s="5">
         <v>3</v>
       </c>
       <c r="D197" s="5" t="s">
-        <v>62</v>
+        <v>123</v>
       </c>
       <c r="E197" s="5" t="s">
-        <v>63</v>
+        <v>124</v>
       </c>
       <c r="F197" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G197" s="10">
-        <v>46071</v>
+        <v>46105</v>
       </c>
     </row>
     <row r="198" spans="1:7">
       <c r="A198" s="4"/>
       <c r="B198" s="8" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="C198" s="5">
         <v>3</v>
       </c>
       <c r="D198" s="5" t="s">
-        <v>80</v>
+        <v>46</v>
       </c>
       <c r="E198" s="5" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="F198" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G198" s="10">
-        <v>46067</v>
+        <v>46092</v>
       </c>
     </row>
     <row r="199" spans="1:7">
       <c r="A199" s="4"/>
       <c r="B199" s="8" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="C199" s="5">
         <v>3</v>
       </c>
       <c r="D199" s="5" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E199" s="5" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F199" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G199" s="10">
-        <v>46079</v>
+        <v>46075</v>
       </c>
     </row>
     <row r="200" spans="1:7">
       <c r="A200" s="4"/>
       <c r="B200" s="8" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="C200" s="5">
         <v>3</v>
       </c>
       <c r="D200" s="5" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="E200" s="5" t="s">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="F200" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G200" s="10">
-        <v>46068</v>
+        <v>46072</v>
       </c>
     </row>
     <row r="201" spans="1:7">
       <c r="A201" s="4"/>
       <c r="B201" s="8" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C201" s="5">
         <v>3</v>
       </c>
       <c r="D201" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E201" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F201" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G201" s="10">
-        <v>46067</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="202" spans="1:7">
       <c r="A202" s="4"/>
       <c r="B202" s="8" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="C202" s="5">
         <v>3</v>
       </c>
       <c r="D202" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E202" s="5" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="F202" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G202" s="10">
-        <v>46096</v>
+        <v>46072</v>
       </c>
     </row>
     <row r="203" spans="1:7">
       <c r="A203" s="4"/>
       <c r="B203" s="8" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C203" s="5">
         <v>3</v>
       </c>
       <c r="D203" s="5" t="s">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="E203" s="5" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="F203" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G203" s="10">
-        <v>46083</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="204" spans="1:7">
       <c r="A204" s="4"/>
       <c r="B204" s="8" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C204" s="5">
         <v>3</v>
       </c>
       <c r="D204" s="5" t="s">
-        <v>234</v>
+        <v>75</v>
       </c>
       <c r="E204" s="5" t="s">
-        <v>235</v>
+        <v>76</v>
       </c>
       <c r="F204" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G204" s="10">
-        <v>46066</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="205" spans="1:7">
@@ -6404,142 +6430,142 @@
         <v>3</v>
       </c>
       <c r="D205" s="5" t="s">
-        <v>13</v>
+        <v>91</v>
       </c>
       <c r="E205" s="5" t="s">
-        <v>14</v>
+        <v>92</v>
       </c>
       <c r="F205" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G205" s="10">
-        <v>46107</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="206" spans="1:7">
       <c r="A206" s="4"/>
       <c r="B206" s="8" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C206" s="5">
         <v>3</v>
       </c>
       <c r="D206" s="5" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="E206" s="5" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="F206" s="5" t="s">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="G206" s="10">
-        <v>46066</v>
+        <v>46079</v>
       </c>
     </row>
     <row r="207" spans="1:7">
       <c r="A207" s="4"/>
       <c r="B207" s="8" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C207" s="5">
         <v>3</v>
       </c>
       <c r="D207" s="5" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="E207" s="5" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="F207" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G207" s="10">
-        <v>46066</v>
+        <v>46068</v>
       </c>
     </row>
     <row r="208" spans="1:7">
       <c r="A208" s="4"/>
       <c r="B208" s="8" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C208" s="5">
         <v>3</v>
       </c>
       <c r="D208" s="5" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="E208" s="5" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="F208" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G208" s="10">
-        <v>46083</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="209" spans="1:7">
       <c r="A209" s="4"/>
       <c r="B209" s="8" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C209" s="5">
         <v>3</v>
       </c>
       <c r="D209" s="5" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E209" s="5" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F209" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G209" s="10">
-        <v>46067</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="210" spans="1:7">
       <c r="A210" s="4"/>
       <c r="B210" s="8" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C210" s="5">
         <v>3</v>
       </c>
       <c r="D210" s="5" t="s">
-        <v>241</v>
+        <v>21</v>
       </c>
       <c r="E210" s="5" t="s">
-        <v>242</v>
+        <v>22</v>
       </c>
       <c r="F210" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G210" s="10">
-        <v>46087</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="211" spans="1:7">
       <c r="A211" s="4"/>
       <c r="B211" s="8" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C211" s="5">
         <v>3</v>
       </c>
       <c r="D211" s="5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E211" s="5" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F211" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G211" s="10">
-        <v>46067</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6551,142 +6577,142 @@
         <v>3</v>
       </c>
       <c r="D212" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E212" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F212" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G212" s="10">
-        <v>46067</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="213" spans="1:7">
       <c r="A213" s="4"/>
       <c r="B213" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C213" s="5">
         <v>3</v>
       </c>
       <c r="D213" s="5" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="E213" s="5" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="F213" s="5" t="s">
-        <v>10</v>
+        <v>131</v>
       </c>
       <c r="G213" s="10">
-        <v>46065</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="214" spans="1:7">
       <c r="A214" s="4"/>
       <c r="B214" s="8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C214" s="5">
         <v>3</v>
       </c>
       <c r="D214" s="5" t="s">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="E214" s="5" t="s">
-        <v>78</v>
+        <v>22</v>
       </c>
       <c r="F214" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G214" s="10">
-        <v>46065</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="215" spans="1:7">
       <c r="A215" s="4"/>
       <c r="B215" s="8" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C215" s="5">
         <v>3</v>
       </c>
       <c r="D215" s="5" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="E215" s="5" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="F215" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G215" s="10">
-        <v>46065</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="216" spans="1:7">
       <c r="A216" s="4"/>
       <c r="B216" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C216" s="5">
         <v>3</v>
       </c>
       <c r="D216" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E216" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F216" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G216" s="10">
-        <v>46071</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="217" spans="1:7">
       <c r="A217" s="4"/>
       <c r="B217" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="C217" s="5">
+        <v>3</v>
+      </c>
+      <c r="D217" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="C217" s="5">
-        <v>3</v>
-      </c>
-      <c r="D217" s="5" t="s">
-        <v>13</v>
-      </c>
       <c r="E217" s="5" t="s">
-        <v>14</v>
+        <v>249</v>
       </c>
       <c r="F217" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G217" s="10">
-        <v>46067</v>
+        <v>46087</v>
       </c>
     </row>
     <row r="218" spans="1:7">
       <c r="A218" s="4"/>
       <c r="B218" s="8" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C218" s="5">
         <v>3</v>
       </c>
       <c r="D218" s="5" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="E218" s="5" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="F218" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G218" s="10">
-        <v>46068</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="219" spans="1:7">
@@ -6698,16 +6724,16 @@
         <v>3</v>
       </c>
       <c r="D219" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E219" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F219" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G219" s="10">
-        <v>46068</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="220" spans="1:7">
@@ -6719,16 +6745,16 @@
         <v>3</v>
       </c>
       <c r="D220" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E220" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F220" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G220" s="10">
-        <v>46064</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -6740,16 +6766,16 @@
         <v>3</v>
       </c>
       <c r="D221" s="5" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="E221" s="5" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F221" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G221" s="10">
-        <v>46099</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -6761,16 +6787,16 @@
         <v>3</v>
       </c>
       <c r="D222" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E222" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F222" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G222" s="10">
-        <v>46098</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="223" spans="1:7">
@@ -6782,94 +6808,94 @@
         <v>3</v>
       </c>
       <c r="D223" s="5" t="s">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="E223" s="5" t="s">
-        <v>63</v>
+        <v>22</v>
       </c>
       <c r="F223" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G223" s="10">
-        <v>46107</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="224" spans="1:7">
       <c r="A224" s="4"/>
       <c r="B224" s="8" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C224" s="5">
         <v>3</v>
       </c>
       <c r="D224" s="5" t="s">
-        <v>194</v>
+        <v>21</v>
       </c>
       <c r="E224" s="5" t="s">
-        <v>195</v>
+        <v>22</v>
       </c>
       <c r="F224" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G224" s="10">
-        <v>46064</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="225" spans="1:7">
       <c r="A225" s="4"/>
       <c r="B225" s="8" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C225" s="5">
         <v>3</v>
       </c>
       <c r="D225" s="5" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="E225" s="5" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="F225" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G225" s="10">
-        <v>46078</v>
+        <v>46068</v>
       </c>
     </row>
     <row r="226" spans="1:7">
       <c r="A226" s="4"/>
       <c r="B226" s="8" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C226" s="5">
         <v>3</v>
       </c>
       <c r="D226" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E226" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F226" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G226" s="10">
-        <v>46064</v>
+        <v>46068</v>
       </c>
     </row>
     <row r="227" spans="1:7">
       <c r="A227" s="4"/>
       <c r="B227" s="8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C227" s="5">
         <v>3</v>
       </c>
       <c r="D227" s="5" t="s">
-        <v>62</v>
+        <v>12</v>
       </c>
       <c r="E227" s="5" t="s">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="F227" s="5" t="s">
         <v>10</v>
@@ -6881,64 +6907,64 @@
     <row r="228" spans="1:7">
       <c r="A228" s="4"/>
       <c r="B228" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C228" s="5">
         <v>3</v>
       </c>
       <c r="D228" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E228" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F228" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G228" s="10">
-        <v>46076</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="229" spans="1:7">
       <c r="A229" s="4"/>
       <c r="B229" s="8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C229" s="5">
         <v>3</v>
       </c>
       <c r="D229" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E229" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F229" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G229" s="10">
-        <v>46065</v>
+        <v>46098</v>
       </c>
     </row>
     <row r="230" spans="1:7">
       <c r="A230" s="4"/>
       <c r="B230" s="8" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C230" s="5">
         <v>3</v>
       </c>
       <c r="D230" s="5" t="s">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="E230" s="5" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="F230" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G230" s="10">
-        <v>46071</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="231" spans="1:7">
@@ -6950,16 +6976,16 @@
         <v>3</v>
       </c>
       <c r="D231" s="5" t="s">
-        <v>8</v>
+        <v>203</v>
       </c>
       <c r="E231" s="5" t="s">
-        <v>9</v>
+        <v>204</v>
       </c>
       <c r="F231" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G231" s="10">
-        <v>46076</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="232" spans="1:7">
@@ -6971,10 +6997,10 @@
         <v>3</v>
       </c>
       <c r="D232" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E232" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F232" s="5" t="s">
         <v>10</v>
@@ -6992,16 +7018,16 @@
         <v>3</v>
       </c>
       <c r="D233" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E233" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F233" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G233" s="10">
-        <v>46106</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="234" spans="1:7">
@@ -7013,16 +7039,16 @@
         <v>3</v>
       </c>
       <c r="D234" s="5" t="s">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="E234" s="5" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
       <c r="F234" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G234" s="10">
-        <v>46072</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -7034,16 +7060,16 @@
         <v>3</v>
       </c>
       <c r="D235" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E235" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F235" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G235" s="10">
-        <v>46066</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -7055,16 +7081,16 @@
         <v>3</v>
       </c>
       <c r="D236" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E236" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F236" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G236" s="10">
-        <v>46068</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -7076,16 +7102,16 @@
         <v>3</v>
       </c>
       <c r="D237" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E237" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F237" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G237" s="10">
-        <v>46067</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -7097,16 +7123,16 @@
         <v>3</v>
       </c>
       <c r="D238" s="5" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E238" s="5" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F238" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G238" s="10">
-        <v>46068</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -7118,289 +7144,289 @@
         <v>3</v>
       </c>
       <c r="D239" s="5" t="s">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="E239" s="5" t="s">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="F239" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G239" s="10">
-        <v>46096</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="240" spans="1:7">
       <c r="A240" s="4"/>
       <c r="B240" s="8" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C240" s="5">
         <v>3</v>
       </c>
       <c r="D240" s="5" t="s">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="E240" s="5" t="s">
-        <v>81</v>
+        <v>22</v>
       </c>
       <c r="F240" s="5" t="s">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="G240" s="10">
-        <v>46079</v>
+        <v>46106</v>
       </c>
     </row>
     <row r="241" spans="1:7">
       <c r="A241" s="4"/>
       <c r="B241" s="8" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C241" s="5">
         <v>3</v>
       </c>
       <c r="D241" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E241" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F241" s="5" t="s">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="G241" s="10">
-        <v>46069</v>
+        <v>46072</v>
       </c>
     </row>
     <row r="242" spans="1:7">
       <c r="A242" s="4"/>
       <c r="B242" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="C242" s="5">
         <v>3</v>
       </c>
       <c r="D242" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E242" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F242" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G242" s="10">
-        <v>46079</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="243" spans="1:7">
       <c r="A243" s="4"/>
       <c r="B243" s="8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C243" s="5">
         <v>3</v>
       </c>
       <c r="D243" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E243" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F243" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G243" s="10">
-        <v>46066</v>
+        <v>46068</v>
       </c>
     </row>
     <row r="244" spans="1:7">
       <c r="A244" s="4"/>
       <c r="B244" s="8" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="C244" s="5">
         <v>3</v>
       </c>
       <c r="D244" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E244" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F244" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G244" s="10">
-        <v>46080</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="245" spans="1:7">
       <c r="A245" s="4"/>
       <c r="B245" s="8" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C245" s="5">
         <v>3</v>
       </c>
       <c r="D245" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E245" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F245" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G245" s="10">
-        <v>46095</v>
+        <v>46068</v>
       </c>
     </row>
     <row r="246" spans="1:7">
       <c r="A246" s="4"/>
       <c r="B246" s="8" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C246" s="5">
         <v>3</v>
       </c>
       <c r="D246" s="5" t="s">
-        <v>13</v>
+        <v>91</v>
       </c>
       <c r="E246" s="5" t="s">
-        <v>14</v>
+        <v>92</v>
       </c>
       <c r="F246" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G246" s="10">
-        <v>46095</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="247" spans="1:7">
       <c r="A247" s="4"/>
       <c r="B247" s="8" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="C247" s="5">
         <v>3</v>
       </c>
       <c r="D247" s="5" t="s">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="E247" s="5" t="s">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="F247" s="5" t="s">
-        <v>10</v>
+        <v>131</v>
       </c>
       <c r="G247" s="10">
-        <v>46069</v>
+        <v>46079</v>
       </c>
     </row>
     <row r="248" spans="1:7">
       <c r="A248" s="4"/>
       <c r="B248" s="8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C248" s="5">
         <v>3</v>
       </c>
       <c r="D248" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E248" s="5" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="F248" s="5" t="s">
-        <v>10</v>
+        <v>131</v>
       </c>
       <c r="G248" s="10">
-        <v>46066</v>
+        <v>46069</v>
       </c>
     </row>
     <row r="249" spans="1:7">
       <c r="A249" s="4"/>
       <c r="B249" s="8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C249" s="5">
         <v>3</v>
       </c>
       <c r="D249" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E249" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F249" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G249" s="10">
-        <v>46076</v>
+        <v>46079</v>
       </c>
     </row>
     <row r="250" spans="1:7">
       <c r="A250" s="4"/>
       <c r="B250" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C250" s="5">
         <v>3</v>
       </c>
       <c r="D250" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E250" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F250" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G250" s="10">
-        <v>46067</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="251" spans="1:7">
       <c r="A251" s="4"/>
       <c r="B251" s="8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C251" s="5">
         <v>3</v>
       </c>
       <c r="D251" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E251" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F251" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G251" s="10">
-        <v>46095</v>
+        <v>46080</v>
       </c>
     </row>
     <row r="252" spans="1:7">
       <c r="A252" s="4"/>
       <c r="B252" s="8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C252" s="5">
         <v>3</v>
       </c>
       <c r="D252" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E252" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F252" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G252" s="10">
-        <v>46083</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="253" spans="1:7">
@@ -7412,16 +7438,16 @@
         <v>3</v>
       </c>
       <c r="D253" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E253" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F253" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G253" s="10">
-        <v>46069</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="254" spans="1:7">
@@ -7433,16 +7459,16 @@
         <v>3</v>
       </c>
       <c r="D254" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E254" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F254" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G254" s="10">
-        <v>46067</v>
+        <v>46069</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -7454,16 +7480,16 @@
         <v>3</v>
       </c>
       <c r="D255" s="5" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E255" s="5" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F255" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G255" s="10">
-        <v>46065</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -7475,16 +7501,16 @@
         <v>3</v>
       </c>
       <c r="D256" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E256" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F256" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G256" s="10">
-        <v>46066</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="257" spans="1:7">
@@ -7496,10 +7522,10 @@
         <v>3</v>
       </c>
       <c r="D257" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E257" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F257" s="5" t="s">
         <v>10</v>
@@ -7517,16 +7543,16 @@
         <v>3</v>
       </c>
       <c r="D258" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E258" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F258" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G258" s="10">
-        <v>46065</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="259" spans="1:7">
@@ -7538,16 +7564,16 @@
         <v>3</v>
       </c>
       <c r="D259" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E259" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F259" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G259" s="10">
-        <v>46095</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="260" spans="1:7">
@@ -7559,16 +7585,16 @@
         <v>3</v>
       </c>
       <c r="D260" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E260" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F260" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G260" s="10">
-        <v>46070</v>
+        <v>46069</v>
       </c>
     </row>
     <row r="261" spans="1:7">
@@ -7580,10 +7606,10 @@
         <v>3</v>
       </c>
       <c r="D261" s="5" t="s">
-        <v>22</v>
+        <v>75</v>
       </c>
       <c r="E261" s="5" t="s">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="F261" s="5" t="s">
         <v>10</v>
@@ -7601,16 +7627,16 @@
         <v>3</v>
       </c>
       <c r="D262" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E262" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F262" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G262" s="10">
-        <v>46066</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="263" spans="1:7">
@@ -7622,94 +7648,94 @@
         <v>3</v>
       </c>
       <c r="D263" s="5" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E263" s="5" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F263" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G263" s="10">
-        <v>46081</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="264" spans="1:7">
       <c r="A264" s="4"/>
       <c r="B264" s="8" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C264" s="5">
         <v>3</v>
       </c>
       <c r="D264" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E264" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E264" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="F264" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G264" s="10">
-        <v>46065</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="265" spans="1:7">
       <c r="A265" s="4"/>
       <c r="B265" s="8" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C265" s="5">
         <v>3</v>
       </c>
       <c r="D265" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E265" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F265" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G265" s="10">
-        <v>46100</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="266" spans="1:7">
       <c r="A266" s="4"/>
       <c r="B266" s="8" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C266" s="5">
         <v>3</v>
       </c>
       <c r="D266" s="5" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="E266" s="5" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="F266" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G266" s="10">
-        <v>46067</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="267" spans="1:7">
       <c r="A267" s="4"/>
       <c r="B267" s="8" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C267" s="5">
         <v>3</v>
       </c>
       <c r="D267" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E267" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F267" s="5" t="s">
         <v>10</v>
@@ -7721,16 +7747,16 @@
     <row r="268" spans="1:7">
       <c r="A268" s="4"/>
       <c r="B268" s="8" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C268" s="5">
         <v>3</v>
       </c>
       <c r="D268" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E268" s="5" t="s">
         <v>13</v>
-      </c>
-      <c r="E268" s="5" t="s">
-        <v>14</v>
       </c>
       <c r="F268" s="5" t="s">
         <v>10</v>
@@ -7742,43 +7768,43 @@
     <row r="269" spans="1:7">
       <c r="A269" s="4"/>
       <c r="B269" s="8" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C269" s="5">
         <v>3</v>
       </c>
       <c r="D269" s="5" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="E269" s="5" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="F269" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G269" s="10">
-        <v>46083</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="270" spans="1:7">
       <c r="A270" s="4"/>
       <c r="B270" s="8" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C270" s="5">
         <v>3</v>
       </c>
       <c r="D270" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E270" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E270" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="F270" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G270" s="10">
-        <v>46095</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="271" spans="1:7">
@@ -7790,16 +7816,16 @@
         <v>3</v>
       </c>
       <c r="D271" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E271" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F271" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G271" s="10">
-        <v>46098</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="272" spans="1:7">
@@ -7811,16 +7837,16 @@
         <v>3</v>
       </c>
       <c r="D272" s="5" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="E272" s="5" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="F272" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G272" s="10">
-        <v>46065</v>
+        <v>46100</v>
       </c>
     </row>
     <row r="273" spans="1:7">
@@ -7832,16 +7858,16 @@
         <v>3</v>
       </c>
       <c r="D273" s="5" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="E273" s="5" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="F273" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G273" s="10">
-        <v>46066</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="274" spans="1:7">
@@ -7853,16 +7879,16 @@
         <v>3</v>
       </c>
       <c r="D274" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E274" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F274" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G274" s="10">
-        <v>46072</v>
+        <v>46070</v>
       </c>
     </row>
     <row r="275" spans="1:7">
@@ -7874,16 +7900,16 @@
         <v>3</v>
       </c>
       <c r="D275" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E275" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F275" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G275" s="10">
-        <v>46066</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="276" spans="1:7">
@@ -7895,16 +7921,16 @@
         <v>3</v>
       </c>
       <c r="D276" s="5" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="E276" s="5" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="F276" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G276" s="10">
-        <v>46070</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="277" spans="1:7">
@@ -7916,16 +7942,16 @@
         <v>3</v>
       </c>
       <c r="D277" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E277" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F277" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G277" s="10">
-        <v>46082</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="278" spans="1:7">
@@ -7937,16 +7963,16 @@
         <v>3</v>
       </c>
       <c r="D278" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E278" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F278" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G278" s="10">
-        <v>46068</v>
+        <v>46098</v>
       </c>
     </row>
     <row r="279" spans="1:7">
@@ -7958,16 +7984,16 @@
         <v>3</v>
       </c>
       <c r="D279" s="5" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="E279" s="5" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="F279" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G279" s="10">
-        <v>46110</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="280" spans="1:7">
@@ -7979,16 +8005,16 @@
         <v>3</v>
       </c>
       <c r="D280" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E280" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F280" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G280" s="10">
-        <v>46093</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="281" spans="1:7">
@@ -8000,16 +8026,16 @@
         <v>3</v>
       </c>
       <c r="D281" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E281" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F281" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G281" s="10">
-        <v>46065</v>
+        <v>46072</v>
       </c>
     </row>
     <row r="282" spans="1:7">
@@ -8021,16 +8047,16 @@
         <v>3</v>
       </c>
       <c r="D282" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E282" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F282" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G282" s="10">
-        <v>46095</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="283" spans="1:7">
@@ -8042,16 +8068,16 @@
         <v>3</v>
       </c>
       <c r="D283" s="5" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="E283" s="5" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="F283" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G283" s="10">
-        <v>46066</v>
+        <v>46070</v>
       </c>
     </row>
     <row r="284" spans="1:7">
@@ -8063,16 +8089,16 @@
         <v>3</v>
       </c>
       <c r="D284" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E284" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F284" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G284" s="10">
-        <v>46065</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="285" spans="1:7">
@@ -8084,16 +8110,16 @@
         <v>3</v>
       </c>
       <c r="D285" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E285" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F285" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G285" s="10">
-        <v>46065</v>
+        <v>46068</v>
       </c>
     </row>
     <row r="286" spans="1:7">
@@ -8105,94 +8131,94 @@
         <v>3</v>
       </c>
       <c r="D286" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E286" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F286" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G286" s="10">
-        <v>46076</v>
+        <v>46110</v>
       </c>
     </row>
     <row r="287" spans="1:7">
       <c r="A287" s="4"/>
       <c r="B287" s="8" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C287" s="5">
         <v>3</v>
       </c>
       <c r="D287" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E287" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F287" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G287" s="10">
-        <v>46065</v>
+        <v>46093</v>
       </c>
     </row>
     <row r="288" spans="1:7">
       <c r="A288" s="4"/>
       <c r="B288" s="8" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C288" s="5">
         <v>3</v>
       </c>
       <c r="D288" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E288" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E288" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="F288" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G288" s="10">
-        <v>46076</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="289" spans="1:7">
       <c r="A289" s="4"/>
       <c r="B289" s="8" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C289" s="5">
         <v>3</v>
       </c>
       <c r="D289" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E289" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F289" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G289" s="10">
-        <v>46101</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="290" spans="1:7">
       <c r="A290" s="4"/>
       <c r="B290" s="8" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C290" s="5">
         <v>3</v>
       </c>
       <c r="D290" s="5" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="E290" s="5" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="F290" s="5" t="s">
         <v>10</v>
@@ -8204,64 +8230,64 @@
     <row r="291" spans="1:7">
       <c r="A291" s="4"/>
       <c r="B291" s="8" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C291" s="5">
         <v>3</v>
       </c>
       <c r="D291" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E291" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F291" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G291" s="10">
-        <v>46066</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="292" spans="1:7">
       <c r="A292" s="4"/>
       <c r="B292" s="8" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C292" s="5">
         <v>3</v>
       </c>
       <c r="D292" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E292" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F292" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G292" s="10">
-        <v>46081</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="293" spans="1:7">
       <c r="A293" s="4"/>
       <c r="B293" s="8" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C293" s="5">
         <v>3</v>
       </c>
       <c r="D293" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E293" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F293" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G293" s="10">
-        <v>46065</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="294" spans="1:7">
@@ -8273,16 +8299,16 @@
         <v>3</v>
       </c>
       <c r="D294" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E294" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F294" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G294" s="10">
-        <v>46069</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="295" spans="1:7">
@@ -8294,16 +8320,16 @@
         <v>3</v>
       </c>
       <c r="D295" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E295" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F295" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G295" s="10">
-        <v>46087</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="296" spans="1:7">
@@ -8315,94 +8341,94 @@
         <v>3</v>
       </c>
       <c r="D296" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E296" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F296" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G296" s="10">
-        <v>46066</v>
+        <v>46101</v>
       </c>
     </row>
     <row r="297" spans="1:7">
       <c r="A297" s="4"/>
-      <c r="B297" s="5" t="s">
+      <c r="B297" s="8" t="s">
         <v>322</v>
       </c>
       <c r="C297" s="5">
         <v>3</v>
       </c>
       <c r="D297" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E297" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F297" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G297" s="10">
-        <v>46102</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="298" spans="1:7">
       <c r="A298" s="4"/>
       <c r="B298" s="8" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C298" s="5">
         <v>3</v>
       </c>
       <c r="D298" s="5" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="E298" s="5" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="F298" s="5" t="s">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="G298" s="10">
-        <v>46094</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="299" spans="1:7">
       <c r="A299" s="4"/>
       <c r="B299" s="8" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C299" s="5">
         <v>3</v>
       </c>
       <c r="D299" s="5" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="E299" s="5" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="F299" s="5" t="s">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="G299" s="10">
-        <v>46093</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="300" spans="1:7">
       <c r="A300" s="4"/>
       <c r="B300" s="8" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C300" s="5">
         <v>3</v>
       </c>
       <c r="D300" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E300" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F300" s="5" t="s">
         <v>10</v>
@@ -8414,106 +8440,106 @@
     <row r="301" spans="1:7">
       <c r="A301" s="4"/>
       <c r="B301" s="8" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C301" s="5">
         <v>3</v>
       </c>
       <c r="D301" s="5" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="E301" s="5" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="F301" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G301" s="10">
-        <v>46079</v>
+        <v>46069</v>
       </c>
     </row>
     <row r="302" spans="1:7">
       <c r="A302" s="4"/>
       <c r="B302" s="8" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C302" s="5">
         <v>3</v>
       </c>
       <c r="D302" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E302" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F302" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G302" s="10">
-        <v>46067</v>
+        <v>46087</v>
       </c>
     </row>
     <row r="303" spans="1:7">
       <c r="A303" s="4"/>
       <c r="B303" s="8" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C303" s="5">
         <v>3</v>
       </c>
       <c r="D303" s="5" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="E303" s="5" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="F303" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G303" s="10">
-        <v>46067</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="304" spans="1:7">
       <c r="A304" s="4"/>
-      <c r="B304" s="8" t="s">
-        <v>327</v>
+      <c r="B304" s="5" t="s">
+        <v>329</v>
       </c>
       <c r="C304" s="5">
         <v>3</v>
       </c>
       <c r="D304" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E304" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F304" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G304" s="10">
-        <v>46069</v>
+        <v>46102</v>
       </c>
     </row>
     <row r="305" spans="1:7">
       <c r="A305" s="4"/>
       <c r="B305" s="8" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C305" s="5">
         <v>3</v>
       </c>
       <c r="D305" s="5" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="E305" s="5" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="F305" s="5" t="s">
-        <v>10</v>
+        <v>131</v>
       </c>
       <c r="G305" s="10">
-        <v>46064</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="306" spans="1:7">
@@ -8525,16 +8551,16 @@
         <v>3</v>
       </c>
       <c r="D306" s="5" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="E306" s="5" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="F306" s="5" t="s">
-        <v>10</v>
+        <v>131</v>
       </c>
       <c r="G306" s="10">
-        <v>46095</v>
+        <v>46093</v>
       </c>
     </row>
     <row r="307" spans="1:7">
@@ -8546,37 +8572,37 @@
         <v>3</v>
       </c>
       <c r="D307" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E307" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F307" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G307" s="10">
-        <v>46098</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="308" spans="1:7">
       <c r="A308" s="4"/>
-      <c r="B308" s="5" t="s">
+      <c r="B308" s="8" t="s">
         <v>331</v>
       </c>
       <c r="C308" s="5">
         <v>3</v>
       </c>
       <c r="D308" s="5" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="E308" s="5" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="F308" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G308" s="10">
-        <v>46077</v>
+        <v>46079</v>
       </c>
     </row>
     <row r="309" spans="1:7">
@@ -8588,10 +8614,10 @@
         <v>3</v>
       </c>
       <c r="D309" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E309" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F309" s="5" t="s">
         <v>10</v>
@@ -8609,16 +8635,16 @@
         <v>3</v>
       </c>
       <c r="D310" s="5" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="E310" s="5" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="F310" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G310" s="10">
-        <v>46066</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="311" spans="1:7">
@@ -8630,16 +8656,16 @@
         <v>3</v>
       </c>
       <c r="D311" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E311" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F311" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G311" s="10">
-        <v>46066</v>
+        <v>46069</v>
       </c>
     </row>
     <row r="312" spans="1:7">
@@ -8651,16 +8677,16 @@
         <v>3</v>
       </c>
       <c r="D312" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E312" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F312" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G312" s="10">
-        <v>46083</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="313" spans="1:7">
@@ -8672,16 +8698,16 @@
         <v>3</v>
       </c>
       <c r="D313" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E313" s="5" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="F313" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G313" s="10">
-        <v>46066</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="314" spans="1:7">
@@ -8693,94 +8719,94 @@
         <v>3</v>
       </c>
       <c r="D314" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E314" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F314" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G314" s="10">
-        <v>46097</v>
+        <v>46098</v>
       </c>
     </row>
     <row r="315" spans="1:7">
       <c r="A315" s="4"/>
-      <c r="B315" s="8" t="s">
-        <v>337</v>
+      <c r="B315" s="5" t="s">
+        <v>338</v>
       </c>
       <c r="C315" s="5">
         <v>3</v>
       </c>
       <c r="D315" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E315" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F315" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G315" s="10">
-        <v>46066</v>
+        <v>46077</v>
       </c>
     </row>
     <row r="316" spans="1:7">
       <c r="A316" s="4"/>
       <c r="B316" s="8" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C316" s="5">
         <v>3</v>
       </c>
       <c r="D316" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E316" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F316" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G316" s="10">
-        <v>46076</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="317" spans="1:7">
       <c r="A317" s="4"/>
       <c r="B317" s="8" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C317" s="5">
         <v>3</v>
       </c>
       <c r="D317" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E317" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F317" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G317" s="10">
-        <v>46065</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="318" spans="1:7">
       <c r="A318" s="4"/>
       <c r="B318" s="8" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C318" s="5">
         <v>3</v>
       </c>
       <c r="D318" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E318" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F318" s="5" t="s">
         <v>10</v>
@@ -8792,106 +8818,106 @@
     <row r="319" spans="1:7">
       <c r="A319" s="4"/>
       <c r="B319" s="8" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C319" s="5">
         <v>3</v>
       </c>
       <c r="D319" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E319" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F319" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G319" s="10">
-        <v>46094</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="320" spans="1:7">
       <c r="A320" s="4"/>
       <c r="B320" s="8" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C320" s="5">
         <v>3</v>
       </c>
       <c r="D320" s="5" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E320" s="5" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F320" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G320" s="10">
-        <v>46068</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="321" spans="1:7">
       <c r="A321" s="4"/>
       <c r="B321" s="8" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C321" s="5">
         <v>3</v>
       </c>
       <c r="D321" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E321" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F321" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G321" s="10">
-        <v>46067</v>
+        <v>46097</v>
       </c>
     </row>
     <row r="322" spans="1:7">
       <c r="A322" s="4"/>
       <c r="B322" s="8" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C322" s="5">
         <v>3</v>
       </c>
       <c r="D322" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E322" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F322" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G322" s="10">
-        <v>46079</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="323" spans="1:7">
       <c r="A323" s="4"/>
       <c r="B323" s="8" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C323" s="5">
         <v>3</v>
       </c>
       <c r="D323" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E323" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F323" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G323" s="10">
-        <v>46095</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="324" spans="1:7">
@@ -8903,184 +8929,184 @@
         <v>3</v>
       </c>
       <c r="D324" s="5" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="E324" s="5" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="F324" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G324" s="10">
-        <v>46100</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="325" spans="1:7">
       <c r="A325" s="4"/>
       <c r="B325" s="8" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C325" s="5">
         <v>3</v>
       </c>
       <c r="D325" s="5" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="E325" s="5" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="F325" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G325" s="10">
-        <v>46095</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="326" spans="1:7">
       <c r="A326" s="4"/>
       <c r="B326" s="8" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C326" s="5">
         <v>3</v>
       </c>
       <c r="D326" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E326" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F326" s="5" t="s">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="G326" s="10">
-        <v>46086</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="327" spans="1:7">
       <c r="A327" s="4"/>
       <c r="B327" s="8" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C327" s="5">
         <v>3</v>
       </c>
       <c r="D327" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E327" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F327" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G327" s="10">
-        <v>46095</v>
+        <v>46068</v>
       </c>
     </row>
     <row r="328" spans="1:7">
       <c r="A328" s="4"/>
       <c r="B328" s="8" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C328" s="5">
         <v>3</v>
       </c>
       <c r="D328" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E328" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F328" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G328" s="10">
-        <v>46099</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="329" spans="1:7">
       <c r="A329" s="4"/>
       <c r="B329" s="8" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C329" s="5">
         <v>3</v>
       </c>
       <c r="D329" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E329" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F329" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G329" s="10">
-        <v>46066</v>
+        <v>46079</v>
       </c>
     </row>
     <row r="330" spans="1:7">
       <c r="A330" s="4"/>
       <c r="B330" s="8" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C330" s="5">
         <v>3</v>
       </c>
       <c r="D330" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E330" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F330" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G330" s="10">
-        <v>46081</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="331" spans="1:7">
       <c r="A331" s="4"/>
       <c r="B331" s="8" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C331" s="5">
         <v>3</v>
       </c>
       <c r="D331" s="5" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="E331" s="5" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="F331" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G331" s="10">
-        <v>46066</v>
+        <v>46100</v>
       </c>
     </row>
     <row r="332" spans="1:7">
       <c r="A332" s="4"/>
       <c r="B332" s="8" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C332" s="5">
         <v>3</v>
       </c>
       <c r="D332" s="5" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="E332" s="5" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="F332" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G332" s="10">
-        <v>46067</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="333" spans="1:7">
@@ -9092,16 +9118,16 @@
         <v>3</v>
       </c>
       <c r="D333" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E333" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F333" s="5" t="s">
-        <v>10</v>
+        <v>131</v>
       </c>
       <c r="G333" s="10">
-        <v>46105</v>
+        <v>46086</v>
       </c>
     </row>
     <row r="334" spans="1:7">
@@ -9113,16 +9139,16 @@
         <v>3</v>
       </c>
       <c r="D334" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E334" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F334" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G334" s="10">
-        <v>46067</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="335" spans="1:7">
@@ -9134,16 +9160,16 @@
         <v>3</v>
       </c>
       <c r="D335" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E335" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F335" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G335" s="10">
-        <v>46066</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="336" spans="1:7">
@@ -9155,16 +9181,16 @@
         <v>3</v>
       </c>
       <c r="D336" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E336" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F336" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G336" s="10">
-        <v>46067</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="337" spans="1:7">
@@ -9176,16 +9202,16 @@
         <v>3</v>
       </c>
       <c r="D337" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E337" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F337" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G337" s="10">
-        <v>46066</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="338" spans="1:7">
@@ -9197,310 +9223,310 @@
         <v>3</v>
       </c>
       <c r="D338" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E338" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F338" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G338" s="10">
-        <v>46101</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="339" spans="1:7">
       <c r="A339" s="4"/>
       <c r="B339" s="8" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C339" s="5">
         <v>3</v>
       </c>
       <c r="D339" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E339" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F339" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G339" s="10">
-        <v>46080</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="340" spans="1:7">
       <c r="A340" s="4"/>
       <c r="B340" s="8" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C340" s="5">
         <v>3</v>
       </c>
       <c r="D340" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E340" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F340" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G340" s="10">
-        <v>46095</v>
+        <v>46105</v>
       </c>
     </row>
     <row r="341" spans="1:7">
       <c r="A341" s="4"/>
       <c r="B341" s="8" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C341" s="5">
         <v>3</v>
       </c>
       <c r="D341" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E341" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E341" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="F341" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G341" s="10">
-        <v>46071</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="342" spans="1:7">
       <c r="A342" s="4"/>
       <c r="B342" s="8" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C342" s="5">
         <v>3</v>
       </c>
       <c r="D342" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E342" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F342" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G342" s="10">
-        <v>46082</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="343" spans="1:7">
       <c r="A343" s="4"/>
       <c r="B343" s="8" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="C343" s="5">
         <v>3</v>
       </c>
       <c r="D343" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E343" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E343" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="F343" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G343" s="10">
-        <v>46085</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="344" spans="1:7">
       <c r="A344" s="4"/>
       <c r="B344" s="8" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C344" s="5">
         <v>3</v>
       </c>
       <c r="D344" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E344" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F344" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G344" s="10">
-        <v>46082</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="345" spans="1:7">
       <c r="A345" s="4"/>
       <c r="B345" s="8" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C345" s="5">
         <v>3</v>
       </c>
       <c r="D345" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E345" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F345" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G345" s="10">
-        <v>46077</v>
+        <v>46101</v>
       </c>
     </row>
     <row r="346" spans="1:7">
       <c r="A346" s="4"/>
       <c r="B346" s="8" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C346" s="5">
         <v>3</v>
       </c>
       <c r="D346" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E346" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F346" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G346" s="10">
-        <v>46071</v>
+        <v>46080</v>
       </c>
     </row>
     <row r="347" spans="1:7">
       <c r="A347" s="4"/>
       <c r="B347" s="8" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C347" s="5">
         <v>3</v>
       </c>
       <c r="D347" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E347" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F347" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G347" s="10">
-        <v>46079</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="348" spans="1:7">
       <c r="A348" s="4"/>
       <c r="B348" s="8" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C348" s="5">
         <v>3</v>
       </c>
       <c r="D348" s="5" t="s">
-        <v>51</v>
+        <v>21</v>
       </c>
       <c r="E348" s="5" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="F348" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G348" s="10">
-        <v>46072</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="349" spans="1:7">
       <c r="A349" s="4"/>
       <c r="B349" s="8" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C349" s="5">
         <v>3</v>
       </c>
       <c r="D349" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="E349" s="5" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="F349" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G349" s="10">
-        <v>46072</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="350" spans="1:7">
       <c r="A350" s="4"/>
       <c r="B350" s="8" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C350" s="5">
         <v>3</v>
       </c>
       <c r="D350" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E350" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F350" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G350" s="10">
-        <v>46066</v>
+        <v>46085</v>
       </c>
     </row>
     <row r="351" spans="1:7">
       <c r="A351" s="4"/>
       <c r="B351" s="8" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C351" s="5">
         <v>3</v>
       </c>
       <c r="D351" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E351" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F351" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G351" s="10">
-        <v>46070</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="352" spans="1:7">
       <c r="A352" s="4"/>
       <c r="B352" s="8" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C352" s="5">
         <v>3</v>
       </c>
       <c r="D352" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E352" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F352" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G352" s="10">
-        <v>46094</v>
+        <v>46077</v>
       </c>
     </row>
     <row r="353" spans="1:7">
@@ -9512,16 +9538,16 @@
         <v>3</v>
       </c>
       <c r="D353" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E353" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F353" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G353" s="10">
-        <v>46095</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="354" spans="1:7">
@@ -9533,16 +9559,16 @@
         <v>3</v>
       </c>
       <c r="D354" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E354" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F354" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G354" s="10">
-        <v>46064</v>
+        <v>46079</v>
       </c>
     </row>
     <row r="355" spans="1:7">
@@ -9554,16 +9580,16 @@
         <v>3</v>
       </c>
       <c r="D355" s="5" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="E355" s="5" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="F355" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G355" s="10">
-        <v>46066</v>
+        <v>46072</v>
       </c>
     </row>
     <row r="356" spans="1:7">
@@ -9575,16 +9601,16 @@
         <v>3</v>
       </c>
       <c r="D356" s="5" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="E356" s="5" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F356" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G356" s="10">
-        <v>46067</v>
+        <v>46072</v>
       </c>
     </row>
     <row r="357" spans="1:7">
@@ -9596,10 +9622,10 @@
         <v>3</v>
       </c>
       <c r="D357" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E357" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F357" s="5" t="s">
         <v>10</v>
@@ -9617,16 +9643,16 @@
         <v>3</v>
       </c>
       <c r="D358" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E358" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F358" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G358" s="10">
-        <v>46066</v>
+        <v>46070</v>
       </c>
     </row>
     <row r="359" spans="1:7">
@@ -9638,16 +9664,16 @@
         <v>3</v>
       </c>
       <c r="D359" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E359" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F359" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G359" s="10">
-        <v>46071</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="360" spans="1:7">
@@ -9659,16 +9685,16 @@
         <v>3</v>
       </c>
       <c r="D360" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E360" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F360" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G360" s="10">
-        <v>46081</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="361" spans="1:7">
@@ -9680,16 +9706,16 @@
         <v>3</v>
       </c>
       <c r="D361" s="5" t="s">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="E361" s="5" t="s">
-        <v>86</v>
+        <v>22</v>
       </c>
       <c r="F361" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G361" s="10">
-        <v>46070</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="362" spans="1:7">
@@ -9701,16 +9727,16 @@
         <v>3</v>
       </c>
       <c r="D362" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E362" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F362" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G362" s="10">
-        <v>46067</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="363" spans="1:7">
@@ -9722,10 +9748,10 @@
         <v>3</v>
       </c>
       <c r="D363" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E363" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F363" s="5" t="s">
         <v>10</v>
@@ -9743,16 +9769,16 @@
         <v>3</v>
       </c>
       <c r="D364" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E364" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E364" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="F364" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G364" s="10">
-        <v>46065</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="365" spans="1:7">
@@ -9764,163 +9790,163 @@
         <v>3</v>
       </c>
       <c r="D365" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E365" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F365" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G365" s="12" t="s">
-        <v>383</v>
+      <c r="G365" s="10">
+        <v>46066</v>
       </c>
     </row>
     <row r="366" spans="1:7">
       <c r="A366" s="4"/>
       <c r="B366" s="8" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C366" s="5">
         <v>3</v>
       </c>
       <c r="D366" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E366" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F366" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G366" s="10">
-        <v>46065</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="367" spans="1:7">
       <c r="A367" s="4"/>
       <c r="B367" s="8" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="C367" s="5">
         <v>3</v>
       </c>
       <c r="D367" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E367" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F367" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G367" s="10">
-        <v>46066</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="368" spans="1:7">
       <c r="A368" s="4"/>
       <c r="B368" s="8" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="C368" s="5">
         <v>3</v>
       </c>
       <c r="D368" s="5" t="s">
-        <v>13</v>
+        <v>96</v>
       </c>
       <c r="E368" s="5" t="s">
-        <v>14</v>
+        <v>97</v>
       </c>
       <c r="F368" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G368" s="10">
-        <v>46066</v>
+        <v>46070</v>
       </c>
     </row>
     <row r="369" spans="1:7">
       <c r="A369" s="4"/>
       <c r="B369" s="8" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C369" s="5">
         <v>3</v>
       </c>
       <c r="D369" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E369" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F369" s="5" t="s">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="G369" s="10">
-        <v>46086</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="370" spans="1:7">
       <c r="A370" s="4"/>
       <c r="B370" s="8" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C370" s="5">
         <v>3</v>
       </c>
       <c r="D370" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E370" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F370" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G370" s="10">
-        <v>46066</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="371" spans="1:7">
       <c r="A371" s="4"/>
       <c r="B371" s="8" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C371" s="5">
         <v>3</v>
       </c>
       <c r="D371" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E371" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F371" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G371" s="10">
-        <v>46068</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="372" spans="1:7">
       <c r="A372" s="4"/>
       <c r="B372" s="8" t="s">
+        <v>389</v>
+      </c>
+      <c r="C372" s="5">
+        <v>3</v>
+      </c>
+      <c r="D372" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E372" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F372" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G372" s="12" t="s">
         <v>390</v>
-      </c>
-      <c r="C372" s="5">
-        <v>3</v>
-      </c>
-      <c r="D372" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E372" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F372" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G372" s="10">
-        <v>46065</v>
       </c>
     </row>
     <row r="373" spans="1:7">
@@ -9932,16 +9958,16 @@
         <v>3</v>
       </c>
       <c r="D373" s="5" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="E373" s="5" t="s">
-        <v>125</v>
+        <v>22</v>
       </c>
       <c r="F373" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G373" s="10">
-        <v>46050</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="374" spans="1:7">
@@ -9953,16 +9979,16 @@
         <v>3</v>
       </c>
       <c r="D374" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E374" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F374" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G374" s="10">
-        <v>46099</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="375" spans="1:7">
@@ -9974,16 +10000,16 @@
         <v>3</v>
       </c>
       <c r="D375" s="5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E375" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F375" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G375" s="10">
-        <v>46071</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="376" spans="1:7">
@@ -9995,16 +10021,16 @@
         <v>3</v>
       </c>
       <c r="D376" s="5" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="E376" s="5" t="s">
-        <v>125</v>
+        <v>22</v>
       </c>
       <c r="F376" s="5" t="s">
-        <v>10</v>
+        <v>131</v>
       </c>
       <c r="G376" s="10">
-        <v>46034</v>
+        <v>46086</v>
       </c>
     </row>
     <row r="377" spans="1:7">
@@ -10016,16 +10042,16 @@
         <v>3</v>
       </c>
       <c r="D377" s="5" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="E377" s="5" t="s">
-        <v>125</v>
+        <v>22</v>
       </c>
       <c r="F377" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G377" s="10">
-        <v>46034</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="378" spans="1:7">
@@ -10037,16 +10063,16 @@
         <v>3</v>
       </c>
       <c r="D378" s="5" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="E378" s="5" t="s">
-        <v>125</v>
+        <v>22</v>
       </c>
       <c r="F378" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G378" s="10">
-        <v>46034</v>
+        <v>46068</v>
       </c>
     </row>
     <row r="379" spans="1:7">
@@ -10058,16 +10084,16 @@
         <v>3</v>
       </c>
       <c r="D379" s="5" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="E379" s="5" t="s">
-        <v>125</v>
+        <v>22</v>
       </c>
       <c r="F379" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G379" s="10">
-        <v>46034</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="380" spans="1:7">
@@ -10079,16 +10105,16 @@
         <v>3</v>
       </c>
       <c r="D380" s="5" t="s">
-        <v>124</v>
+        <v>15</v>
       </c>
       <c r="E380" s="5" t="s">
-        <v>125</v>
+        <v>16</v>
       </c>
       <c r="F380" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G380" s="10">
-        <v>46035</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="381" spans="1:7">
@@ -10100,16 +10126,16 @@
         <v>3</v>
       </c>
       <c r="D381" s="5" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="E381" s="5" t="s">
-        <v>125</v>
+        <v>22</v>
       </c>
       <c r="F381" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G381" s="10">
-        <v>46034</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="382" spans="1:7">
@@ -10121,16 +10147,16 @@
         <v>3</v>
       </c>
       <c r="D382" s="5" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="E382" s="5" t="s">
-        <v>125</v>
+        <v>22</v>
       </c>
       <c r="F382" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G382" s="10">
-        <v>46034</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="383" spans="1:7">
@@ -10142,10 +10168,10 @@
         <v>3</v>
       </c>
       <c r="D383" s="5" t="s">
-        <v>124</v>
+        <v>15</v>
       </c>
       <c r="E383" s="5" t="s">
-        <v>125</v>
+        <v>16</v>
       </c>
       <c r="F383" s="5" t="s">
         <v>10</v>
@@ -10163,10 +10189,10 @@
         <v>3</v>
       </c>
       <c r="D384" s="5" t="s">
-        <v>124</v>
+        <v>15</v>
       </c>
       <c r="E384" s="5" t="s">
-        <v>125</v>
+        <v>16</v>
       </c>
       <c r="F384" s="5" t="s">
         <v>10</v>
@@ -10184,10 +10210,10 @@
         <v>3</v>
       </c>
       <c r="D385" s="5" t="s">
-        <v>124</v>
+        <v>15</v>
       </c>
       <c r="E385" s="5" t="s">
-        <v>125</v>
+        <v>16</v>
       </c>
       <c r="F385" s="5" t="s">
         <v>10</v>
@@ -10205,10 +10231,10 @@
         <v>3</v>
       </c>
       <c r="D386" s="5" t="s">
-        <v>405</v>
+        <v>15</v>
       </c>
       <c r="E386" s="5" t="s">
-        <v>406</v>
+        <v>16</v>
       </c>
       <c r="F386" s="5" t="s">
         <v>10</v>
@@ -10220,42 +10246,189 @@
     <row r="387" spans="1:7">
       <c r="A387" s="4"/>
       <c r="B387" s="8" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C387" s="5">
         <v>3</v>
       </c>
       <c r="D387" s="5" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E387" s="5" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F387" s="5" t="s">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="G387" s="10">
+        <v>46035</v>
+      </c>
+    </row>
+    <row r="388" spans="1:7">
+      <c r="A388" s="4"/>
+      <c r="B388" s="8" t="s">
+        <v>406</v>
+      </c>
+      <c r="C388" s="5">
+        <v>3</v>
+      </c>
+      <c r="D388" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E388" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F388" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G388" s="10">
+        <v>46034</v>
+      </c>
+    </row>
+    <row r="389" spans="1:7">
+      <c r="A389" s="4"/>
+      <c r="B389" s="8" t="s">
+        <v>407</v>
+      </c>
+      <c r="C389" s="5">
+        <v>3</v>
+      </c>
+      <c r="D389" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E389" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F389" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G389" s="10">
+        <v>46034</v>
+      </c>
+    </row>
+    <row r="390" spans="1:7">
+      <c r="A390" s="4"/>
+      <c r="B390" s="8" t="s">
+        <v>408</v>
+      </c>
+      <c r="C390" s="5">
+        <v>3</v>
+      </c>
+      <c r="D390" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E390" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F390" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G390" s="10">
+        <v>46034</v>
+      </c>
+    </row>
+    <row r="391" spans="1:7">
+      <c r="A391" s="4"/>
+      <c r="B391" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="C391" s="5">
+        <v>3</v>
+      </c>
+      <c r="D391" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E391" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F391" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G391" s="10">
+        <v>46034</v>
+      </c>
+    </row>
+    <row r="392" spans="1:7">
+      <c r="A392" s="4"/>
+      <c r="B392" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="C392" s="5">
+        <v>3</v>
+      </c>
+      <c r="D392" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E392" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F392" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G392" s="10">
+        <v>46034</v>
+      </c>
+    </row>
+    <row r="393" spans="1:7">
+      <c r="A393" s="4"/>
+      <c r="B393" s="8" t="s">
+        <v>411</v>
+      </c>
+      <c r="C393" s="5">
+        <v>3</v>
+      </c>
+      <c r="D393" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="E393" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="F393" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G393" s="10">
+        <v>46034</v>
+      </c>
+    </row>
+    <row r="394" spans="1:7">
+      <c r="A394" s="4"/>
+      <c r="B394" s="8" t="s">
+        <v>411</v>
+      </c>
+      <c r="C394" s="5">
+        <v>3</v>
+      </c>
+      <c r="D394" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E394" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F394" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="G394" s="10">
         <v>46028</v>
       </c>
     </row>
-    <row r="388" spans="1:7">
-      <c r="A388" s="13"/>
-      <c r="B388" s="14" t="s">
-        <v>407</v>
-      </c>
-      <c r="C388" s="15">
-        <v>3</v>
-      </c>
-      <c r="D388" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="E388" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F388" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G388" s="16">
+    <row r="395" spans="1:7">
+      <c r="A395" s="13"/>
+      <c r="B395" s="14" t="s">
+        <v>414</v>
+      </c>
+      <c r="C395" s="15">
+        <v>3</v>
+      </c>
+      <c r="D395" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="E395" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F395" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G395" s="16">
         <v>46028</v>
       </c>
     </row>

--- a/server/userPlan.xlsx
+++ b/server/userPlan.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29930"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6ACABEAF-C9B4-4450-9CC2-E7B88F6375EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F4E3791F-B1E2-4CA0-BAD4-130A7412199E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1584" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1596" uniqueCount="418">
   <si>
     <t>id</t>
   </si>
@@ -54,6 +54,21 @@
     <t>created_at</t>
   </si>
   <si>
+    <t>AVG27912</t>
+  </si>
+  <si>
+    <t>$1000</t>
+  </si>
+  <si>
+    <t>$5</t>
+  </si>
+  <si>
+    <t>active</t>
+  </si>
+  <si>
+    <t>AVG79320</t>
+  </si>
+  <si>
     <t>AVG70261</t>
   </si>
   <si>
@@ -63,9 +78,6 @@
     <t>$11</t>
   </si>
   <si>
-    <t>active</t>
-  </si>
-  <si>
     <t>AVG55466</t>
   </si>
   <si>
@@ -108,12 +120,6 @@
     <t>AVG44166</t>
   </si>
   <si>
-    <t>$1000</t>
-  </si>
-  <si>
-    <t>$5</t>
-  </si>
-  <si>
     <t>AVG18162</t>
   </si>
   <si>
@@ -1186,6 +1192,9 @@
   </si>
   <si>
     <t>AVG16575</t>
+  </si>
+  <si>
+    <t>AVG34545</t>
   </si>
   <si>
     <t>AVG03762</t>
@@ -1810,8 +1819,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B9040242-A3FD-4595-BA2F-13350F718E47}" name="Table1" displayName="Table1" ref="A1:G395" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10" headerRowBorderDxfId="8" tableBorderDxfId="9" totalsRowBorderDxfId="7">
-  <autoFilter ref="A1:G395" xr:uid="{B9040242-A3FD-4595-BA2F-13350F718E47}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B9040242-A3FD-4595-BA2F-13350F718E47}" name="Table1" displayName="Table1" ref="A1:G398" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10" headerRowBorderDxfId="8" tableBorderDxfId="9" totalsRowBorderDxfId="7">
+  <autoFilter ref="A1:G398" xr:uid="{B9040242-A3FD-4595-BA2F-13350F718E47}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{F8B255F3-8561-4E75-93FC-7CD59135CCC9}" name="id" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{EE0AA50C-A116-4183-9D39-5A918AEC3F49}" name="user_code" dataDxfId="5"/>
@@ -2122,7 +2131,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J395"/>
+  <dimension ref="A1:J398"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.42578125" customWidth="1"/>
@@ -2187,10 +2196,10 @@
         <v>3</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>10</v>
@@ -2202,16 +2211,16 @@
     <row r="4" spans="1:10">
       <c r="A4" s="4"/>
       <c r="B4" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="5">
+        <v>3</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>14</v>
-      </c>
-      <c r="C4" s="5">
-        <v>3</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>16</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>10</v>
@@ -2224,64 +2233,64 @@
     <row r="5" spans="1:10">
       <c r="A5" s="4"/>
       <c r="B5" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="5">
+        <v>3</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="5">
-        <v>3</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>19</v>
-      </c>
       <c r="F5" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G5" s="19">
-        <v>46117</v>
+        <v>46118</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="4"/>
       <c r="B6" s="18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="5">
+        <v>3</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="5">
-        <v>3</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>22</v>
-      </c>
       <c r="F6" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G6" s="19">
-        <v>46117</v>
+        <v>46118</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="4"/>
       <c r="B7" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="5">
+        <v>3</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="5">
-        <v>3</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>22</v>
-      </c>
       <c r="F7" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="10">
-        <v>46116</v>
+      <c r="G7" s="19">
+        <v>46117</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -2302,7 +2311,7 @@
         <v>10</v>
       </c>
       <c r="G8" s="19">
-        <v>46116</v>
+        <v>46117</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -2328,44 +2337,44 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="4"/>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="18" t="s">
         <v>28</v>
       </c>
       <c r="C10" s="5">
         <v>3</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G10" s="6">
-        <v>46114</v>
+      <c r="G10" s="19">
+        <v>46116</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="4"/>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="18" t="s">
         <v>29</v>
       </c>
       <c r="C11" s="5">
         <v>3</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G11" s="6">
-        <v>46114</v>
+      <c r="G11" s="10">
+        <v>46116</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -2377,16 +2386,16 @@
         <v>3</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>26</v>
+        <v>8</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>9</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G12" s="6">
-        <v>46113</v>
+        <v>46114</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -2398,16 +2407,16 @@
         <v>3</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G13" s="6">
-        <v>46113</v>
+        <v>46114</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -2419,10 +2428,10 @@
         <v>3</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>10</v>
@@ -2433,65 +2442,65 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="4"/>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="5" t="s">
         <v>33</v>
       </c>
       <c r="C15" s="5">
         <v>3</v>
       </c>
-      <c r="D15" s="9" t="s">
-        <v>34</v>
+      <c r="D15" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G15" s="10">
-        <v>46112</v>
+      <c r="G15" s="6">
+        <v>46113</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="4"/>
-      <c r="B16" s="8" t="s">
-        <v>36</v>
+      <c r="B16" s="5" t="s">
+        <v>34</v>
       </c>
       <c r="C16" s="5">
         <v>3</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>13</v>
+        <v>8</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>9</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G16" s="10">
-        <v>46111</v>
+      <c r="G16" s="6">
+        <v>46113</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="4"/>
       <c r="B17" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="5">
+        <v>3</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E17" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="5">
-        <v>3</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>22</v>
-      </c>
       <c r="F17" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G17" s="10">
-        <v>46111</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -2503,10 +2512,10 @@
         <v>3</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>10</v>
@@ -2524,10 +2533,10 @@
         <v>3</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>10</v>
@@ -2539,43 +2548,43 @@
     <row r="20" spans="1:7">
       <c r="A20" s="4"/>
       <c r="B20" s="8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C20" s="5">
         <v>3</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G20" s="10">
-        <v>46112</v>
+        <v>46111</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="4"/>
       <c r="B21" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="5">
+        <v>3</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E21" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C21" s="5">
-        <v>3</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>22</v>
-      </c>
       <c r="F21" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G21" s="10">
-        <v>46110</v>
+        <v>46111</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -2587,16 +2596,16 @@
         <v>3</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G22" s="10">
-        <v>46109</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -2608,52 +2617,52 @@
         <v>3</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G23" s="10">
-        <v>46108</v>
+        <v>46110</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="4"/>
       <c r="B24" s="8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C24" s="5">
         <v>3</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G24" s="10">
-        <v>46108</v>
+        <v>46109</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="4"/>
       <c r="B25" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" s="5">
+        <v>3</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E25" s="5" t="s">
         <v>49</v>
-      </c>
-      <c r="C25" s="5">
-        <v>3</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>26</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>10</v>
@@ -2671,16 +2680,16 @@
         <v>3</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G26" s="10">
-        <v>46107</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -2692,16 +2701,16 @@
         <v>3</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G27" s="10">
-        <v>46107</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -2713,10 +2722,10 @@
         <v>3</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>10</v>
@@ -2755,10 +2764,10 @@
         <v>3</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F30" s="5" t="s">
         <v>10</v>
@@ -2776,10 +2785,10 @@
         <v>3</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>10</v>
@@ -2797,52 +2806,52 @@
         <v>3</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G32" s="10">
-        <v>46106</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="4"/>
       <c r="B33" s="8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C33" s="5">
         <v>3</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F33" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G33" s="10">
-        <v>46106</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="4"/>
       <c r="B34" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C34" s="5">
+        <v>3</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E34" s="5" t="s">
         <v>60</v>
-      </c>
-      <c r="C34" s="5">
-        <v>3</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>22</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>10</v>
@@ -2860,16 +2869,16 @@
         <v>3</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G35" s="10">
-        <v>46105</v>
+        <v>46106</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -2881,10 +2890,10 @@
         <v>3</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>10</v>
@@ -2902,58 +2911,58 @@
         <v>3</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G37" s="10">
-        <v>46104</v>
+        <v>46105</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" s="4"/>
       <c r="B38" s="8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C38" s="5">
         <v>3</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F38" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G38" s="10">
-        <v>46101</v>
+        <v>46106</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="4"/>
       <c r="B39" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C39" s="5">
+        <v>3</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E39" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C39" s="5">
-        <v>3</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>13</v>
-      </c>
       <c r="F39" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G39" s="10">
-        <v>46102</v>
+        <v>46104</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -2965,16 +2974,16 @@
         <v>3</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="F40" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G40" s="10">
-        <v>46100</v>
+        <v>46101</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -2986,16 +2995,16 @@
         <v>3</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G41" s="10">
-        <v>46111</v>
+        <v>46102</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -3007,16 +3016,16 @@
         <v>3</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="F42" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G42" s="10">
-        <v>46099</v>
+        <v>46100</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -3028,16 +3037,16 @@
         <v>3</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F43" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G43" s="10">
-        <v>46100</v>
+        <v>46111</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -3049,16 +3058,16 @@
         <v>3</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F44" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G44" s="10">
-        <v>46100</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -3070,16 +3079,16 @@
         <v>3</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F45" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G45" s="10">
-        <v>46099</v>
+        <v>46100</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -3091,31 +3100,31 @@
         <v>3</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>75</v>
+        <v>8</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="F46" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G46" s="10">
-        <v>46099</v>
+        <v>46100</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="4"/>
       <c r="B47" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C47" s="5">
         <v>3</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F47" s="5" t="s">
         <v>10</v>
@@ -3127,16 +3136,16 @@
     <row r="48" spans="1:7">
       <c r="A48" s="4"/>
       <c r="B48" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C48" s="5">
+        <v>3</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E48" s="5" t="s">
         <v>78</v>
-      </c>
-      <c r="C48" s="5">
-        <v>3</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>13</v>
       </c>
       <c r="F48" s="5" t="s">
         <v>10</v>
@@ -3154,10 +3163,10 @@
         <v>3</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="F49" s="5" t="s">
         <v>10</v>
@@ -3175,10 +3184,10 @@
         <v>3</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="F50" s="5" t="s">
         <v>10</v>
@@ -3195,32 +3204,32 @@
       <c r="C51" s="5">
         <v>3</v>
       </c>
-      <c r="D51" s="9" t="s">
-        <v>21</v>
+      <c r="D51" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="F51" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G51" s="10">
-        <v>46100</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="4"/>
       <c r="B52" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C52" s="5">
         <v>3</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="F52" s="5" t="s">
         <v>10</v>
@@ -3232,12 +3241,12 @@
     <row r="53" spans="1:7">
       <c r="A53" s="4"/>
       <c r="B53" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C53" s="5">
         <v>3</v>
       </c>
-      <c r="D53" s="5" t="s">
+      <c r="D53" s="9" t="s">
         <v>25</v>
       </c>
       <c r="E53" s="5" t="s">
@@ -3247,22 +3256,22 @@
         <v>10</v>
       </c>
       <c r="G53" s="10">
-        <v>46098</v>
+        <v>46100</v>
       </c>
     </row>
     <row r="54" spans="1:7">
       <c r="A54" s="4"/>
       <c r="B54" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="C54" s="5">
+        <v>3</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E54" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="C54" s="5">
-        <v>3</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E54" s="5" t="s">
-        <v>26</v>
       </c>
       <c r="F54" s="5" t="s">
         <v>10</v>
@@ -3280,10 +3289,10 @@
         <v>3</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="F55" s="5" t="s">
         <v>10</v>
@@ -3301,16 +3310,16 @@
         <v>3</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F56" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G56" s="10">
-        <v>46098</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -3322,16 +3331,16 @@
         <v>3</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="F57" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G57" s="10">
-        <v>46099</v>
+        <v>46098</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -3343,16 +3352,16 @@
         <v>3</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F58" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G58" s="10">
-        <v>46097</v>
+        <v>46098</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -3364,49 +3373,49 @@
         <v>3</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>91</v>
+        <v>8</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>92</v>
+        <v>9</v>
       </c>
       <c r="F59" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G59" s="10">
-        <v>46105</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="60" spans="1:7">
       <c r="A60" s="4"/>
       <c r="B60" s="8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C60" s="5">
         <v>3</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F60" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G60" s="10">
-        <v>46098</v>
+        <v>46097</v>
       </c>
     </row>
     <row r="61" spans="1:7">
       <c r="A61" s="4"/>
       <c r="B61" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C61" s="5">
+        <v>3</v>
+      </c>
+      <c r="D61" s="5" t="s">
         <v>93</v>
-      </c>
-      <c r="C61" s="5">
-        <v>3</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>21</v>
       </c>
       <c r="E61" s="5" t="s">
         <v>94</v>
@@ -3415,28 +3424,28 @@
         <v>10</v>
       </c>
       <c r="G61" s="10">
-        <v>46099</v>
+        <v>46105</v>
       </c>
     </row>
     <row r="62" spans="1:7">
       <c r="A62" s="4"/>
       <c r="B62" s="8" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C62" s="5">
         <v>3</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="F62" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G62" s="10">
-        <v>46105</v>
+        <v>46098</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -3448,115 +3457,115 @@
         <v>3</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>13</v>
+        <v>96</v>
       </c>
       <c r="F63" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G63" s="10">
-        <v>46103</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="4"/>
       <c r="B64" s="8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C64" s="5">
         <v>3</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>96</v>
+        <v>48</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>97</v>
+        <v>49</v>
       </c>
       <c r="F64" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G64" s="10">
-        <v>46102</v>
+        <v>46105</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="4"/>
       <c r="B65" s="8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C65" s="5">
         <v>3</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>98</v>
+        <v>16</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>99</v>
+        <v>17</v>
       </c>
       <c r="F65" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G65" s="10">
-        <v>46099</v>
+        <v>46103</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="4"/>
       <c r="B66" s="8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C66" s="5">
         <v>3</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G66" s="10">
-        <v>46097</v>
+        <v>46102</v>
       </c>
     </row>
     <row r="67" spans="1:7">
       <c r="A67" s="4"/>
       <c r="B67" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C67" s="5">
+        <v>3</v>
+      </c>
+      <c r="D67" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="C67" s="5">
-        <v>3</v>
-      </c>
-      <c r="D67" s="5" t="s">
+      <c r="E67" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="E67" s="5" t="s">
-        <v>102</v>
-      </c>
       <c r="F67" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G67" s="10">
-        <v>46096</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="68" spans="1:7">
       <c r="A68" s="4"/>
       <c r="B68" s="8" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="C68" s="5">
         <v>3</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="F68" s="5" t="s">
         <v>10</v>
@@ -3568,22 +3577,22 @@
     <row r="69" spans="1:7">
       <c r="A69" s="4"/>
       <c r="B69" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C69" s="5">
+        <v>3</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="E69" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C69" s="5">
-        <v>3</v>
-      </c>
-      <c r="D69" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E69" s="5" t="s">
-        <v>22</v>
-      </c>
       <c r="F69" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G69" s="10">
-        <v>46095</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -3595,16 +3604,16 @@
         <v>3</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F70" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G70" s="10">
-        <v>46095</v>
+        <v>46097</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -3616,16 +3625,16 @@
         <v>3</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F71" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G71" s="10">
-        <v>46106</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -3637,10 +3646,10 @@
         <v>3</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="F72" s="5" t="s">
         <v>10</v>
@@ -3658,16 +3667,16 @@
         <v>3</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F73" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G73" s="10">
-        <v>46101</v>
+        <v>46106</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -3679,10 +3688,10 @@
         <v>3</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="F74" s="5" t="s">
         <v>10</v>
@@ -3700,16 +3709,16 @@
         <v>3</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="F75" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G75" s="10">
-        <v>46095</v>
+        <v>46101</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -3721,10 +3730,10 @@
         <v>3</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F76" s="5" t="s">
         <v>10</v>
@@ -3742,10 +3751,10 @@
         <v>3</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="F77" s="5" t="s">
         <v>10</v>
@@ -3763,115 +3772,115 @@
         <v>3</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F78" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G78" s="10">
-        <v>46110</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="79" spans="1:7">
       <c r="A79" s="4"/>
       <c r="B79" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C79" s="5">
         <v>3</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>114</v>
+        <v>25</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>115</v>
+        <v>26</v>
       </c>
       <c r="F79" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G79" s="10">
-        <v>46098</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="4"/>
       <c r="B80" s="8" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C80" s="5">
         <v>3</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F80" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G80" s="10">
-        <v>46095</v>
+        <v>46110</v>
       </c>
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="4"/>
       <c r="B81" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="C81" s="5">
+        <v>3</v>
+      </c>
+      <c r="D81" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="C81" s="5">
-        <v>3</v>
-      </c>
-      <c r="D81" s="5" t="s">
+      <c r="E81" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="E81" s="5" t="s">
-        <v>118</v>
-      </c>
       <c r="F81" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G81" s="10">
-        <v>46094</v>
+        <v>46098</v>
       </c>
     </row>
     <row r="82" spans="1:7">
       <c r="A82" s="4"/>
       <c r="B82" s="8" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C82" s="5">
         <v>3</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F82" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G82" s="10">
-        <v>46094</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="83" spans="1:7">
       <c r="A83" s="4"/>
       <c r="B83" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="C83" s="5">
+        <v>3</v>
+      </c>
+      <c r="D83" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E83" s="5" t="s">
         <v>120</v>
-      </c>
-      <c r="C83" s="5">
-        <v>3</v>
-      </c>
-      <c r="D83" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E83" s="5" t="s">
-        <v>26</v>
       </c>
       <c r="F83" s="5" t="s">
         <v>10</v>
@@ -3889,10 +3898,10 @@
         <v>3</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F84" s="5" t="s">
         <v>10</v>
@@ -3910,10 +3919,10 @@
         <v>3</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>123</v>
+        <v>8</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>124</v>
+        <v>9</v>
       </c>
       <c r="F85" s="5" t="s">
         <v>10</v>
@@ -3925,16 +3934,16 @@
     <row r="86" spans="1:7">
       <c r="A86" s="4"/>
       <c r="B86" s="8" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C86" s="5">
         <v>3</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F86" s="5" t="s">
         <v>10</v>
@@ -3946,37 +3955,37 @@
     <row r="87" spans="1:7">
       <c r="A87" s="4"/>
       <c r="B87" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C87" s="5">
+        <v>3</v>
+      </c>
+      <c r="D87" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="E87" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="C87" s="5">
-        <v>3</v>
-      </c>
-      <c r="D87" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E87" s="5" t="s">
-        <v>26</v>
-      </c>
       <c r="F87" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G87" s="10">
-        <v>46096</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="88" spans="1:7">
       <c r="A88" s="4"/>
       <c r="B88" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C88" s="5">
         <v>3</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F88" s="5" t="s">
         <v>10</v>
@@ -3988,37 +3997,37 @@
     <row r="89" spans="1:7">
       <c r="A89" s="4"/>
       <c r="B89" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C89" s="5">
         <v>3</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>91</v>
+        <v>8</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>92</v>
+        <v>9</v>
       </c>
       <c r="F89" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G89" s="10">
-        <v>46097</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="90" spans="1:7">
       <c r="A90" s="4"/>
       <c r="B90" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C90" s="5">
         <v>3</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>128</v>
+        <v>22</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>129</v>
+        <v>23</v>
       </c>
       <c r="F90" s="5" t="s">
         <v>10</v>
@@ -4030,40 +4039,40 @@
     <row r="91" spans="1:7">
       <c r="A91" s="4"/>
       <c r="B91" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C91" s="5">
         <v>3</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>22</v>
+        <v>94</v>
       </c>
       <c r="F91" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G91" s="10">
-        <v>46094</v>
+        <v>46097</v>
       </c>
     </row>
     <row r="92" spans="1:7">
       <c r="A92" s="4"/>
       <c r="B92" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="C92" s="5">
+        <v>3</v>
+      </c>
+      <c r="D92" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="C92" s="5">
-        <v>3</v>
-      </c>
-      <c r="D92" s="5" t="s">
-        <v>64</v>
-      </c>
       <c r="E92" s="5" t="s">
-        <v>65</v>
+        <v>131</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>131</v>
+        <v>10</v>
       </c>
       <c r="G92" s="10">
         <v>46094</v>
@@ -4093,19 +4102,19 @@
     <row r="94" spans="1:7">
       <c r="A94" s="4"/>
       <c r="B94" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="C94" s="5">
+        <v>3</v>
+      </c>
+      <c r="D94" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E94" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F94" s="5" t="s">
         <v>133</v>
-      </c>
-      <c r="C94" s="5">
-        <v>3</v>
-      </c>
-      <c r="D94" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E94" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="F94" s="5" t="s">
-        <v>10</v>
       </c>
       <c r="G94" s="10">
         <v>46094</v>
@@ -4120,16 +4129,16 @@
         <v>3</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F95" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G95" s="10">
-        <v>46093</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -4141,16 +4150,16 @@
         <v>3</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="F96" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G96" s="10">
-        <v>46100</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -4162,16 +4171,16 @@
         <v>3</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="F97" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G97" s="10">
-        <v>46092</v>
+        <v>46093</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -4183,16 +4192,16 @@
         <v>3</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F98" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G98" s="10">
-        <v>46093</v>
+        <v>46100</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -4204,10 +4213,10 @@
         <v>3</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>25</v>
+        <v>93</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="F99" s="5" t="s">
         <v>10</v>
@@ -4225,16 +4234,16 @@
         <v>3</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F100" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G100" s="10">
-        <v>46090</v>
+        <v>46093</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -4246,58 +4255,58 @@
         <v>3</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>141</v>
+        <v>8</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>142</v>
+        <v>9</v>
       </c>
       <c r="F101" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G101" s="10">
-        <v>46089</v>
+        <v>46092</v>
       </c>
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="4"/>
       <c r="B102" s="8" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C102" s="5">
         <v>3</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F102" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G102" s="10">
-        <v>46089</v>
+        <v>46090</v>
       </c>
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="4"/>
       <c r="B103" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="C103" s="5">
+        <v>3</v>
+      </c>
+      <c r="D103" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="E103" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="C103" s="5">
-        <v>3</v>
-      </c>
-      <c r="D103" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E103" s="5" t="s">
-        <v>47</v>
-      </c>
       <c r="F103" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G103" s="10">
-        <v>46088</v>
+        <v>46089</v>
       </c>
     </row>
     <row r="104" spans="1:7">
@@ -4318,7 +4327,7 @@
         <v>10</v>
       </c>
       <c r="G104" s="10">
-        <v>46092</v>
+        <v>46089</v>
       </c>
     </row>
     <row r="105" spans="1:7">
@@ -4330,10 +4339,10 @@
         <v>3</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="F105" s="5" t="s">
         <v>10</v>
@@ -4351,16 +4360,16 @@
         <v>3</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>75</v>
+        <v>8</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="F106" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G106" s="10">
-        <v>46103</v>
+        <v>46092</v>
       </c>
     </row>
     <row r="107" spans="1:7">
@@ -4372,16 +4381,16 @@
         <v>3</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F107" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G107" s="10">
-        <v>46090</v>
+        <v>46088</v>
       </c>
     </row>
     <row r="108" spans="1:7">
@@ -4393,16 +4402,16 @@
         <v>3</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="F108" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G108" s="10">
-        <v>46087</v>
+        <v>46103</v>
       </c>
     </row>
     <row r="109" spans="1:7">
@@ -4414,16 +4423,16 @@
         <v>3</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F109" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G109" s="10">
-        <v>46087</v>
+        <v>46090</v>
       </c>
     </row>
     <row r="110" spans="1:7">
@@ -4435,22 +4444,22 @@
         <v>3</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>152</v>
+        <v>25</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>153</v>
+        <v>26</v>
       </c>
       <c r="F110" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G110" s="10">
-        <v>46088</v>
+        <v>46087</v>
       </c>
     </row>
     <row r="111" spans="1:7">
       <c r="A111" s="4"/>
       <c r="B111" s="8" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C111" s="5">
         <v>3</v>
@@ -4465,22 +4474,22 @@
         <v>10</v>
       </c>
       <c r="G111" s="10">
-        <v>46088</v>
+        <v>46087</v>
       </c>
     </row>
     <row r="112" spans="1:7">
       <c r="A112" s="4"/>
       <c r="B112" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="C112" s="5">
+        <v>3</v>
+      </c>
+      <c r="D112" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="E112" s="5" t="s">
         <v>155</v>
-      </c>
-      <c r="C112" s="5">
-        <v>3</v>
-      </c>
-      <c r="D112" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E112" s="5" t="s">
-        <v>26</v>
       </c>
       <c r="F112" s="5" t="s">
         <v>10</v>
@@ -4498,16 +4507,16 @@
         <v>3</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F113" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G113" s="10">
-        <v>46094</v>
+        <v>46088</v>
       </c>
     </row>
     <row r="114" spans="1:7">
@@ -4519,16 +4528,16 @@
         <v>3</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="F114" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G114" s="10">
-        <v>46086</v>
+        <v>46088</v>
       </c>
     </row>
     <row r="115" spans="1:7">
@@ -4540,16 +4549,16 @@
         <v>3</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>75</v>
+        <v>8</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>76</v>
+        <v>9</v>
       </c>
       <c r="F115" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G115" s="10">
-        <v>46086</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="116" spans="1:7">
@@ -4561,16 +4570,16 @@
         <v>3</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="F116" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G116" s="10">
-        <v>46085</v>
+        <v>46086</v>
       </c>
     </row>
     <row r="117" spans="1:7">
@@ -4582,16 +4591,16 @@
         <v>3</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="F117" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G117" s="10">
-        <v>46085</v>
+        <v>46086</v>
       </c>
     </row>
     <row r="118" spans="1:7">
@@ -4603,10 +4612,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>162</v>
+        <v>23</v>
       </c>
       <c r="F118" s="5" t="s">
         <v>10</v>
@@ -4618,16 +4627,16 @@
     <row r="119" spans="1:7">
       <c r="A119" s="4"/>
       <c r="B119" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C119" s="5">
         <v>3</v>
       </c>
       <c r="D119" s="5" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F119" s="5" t="s">
         <v>10</v>
@@ -4639,16 +4648,16 @@
     <row r="120" spans="1:7">
       <c r="A120" s="4"/>
       <c r="B120" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="C120" s="5">
+        <v>3</v>
+      </c>
+      <c r="D120" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E120" s="5" t="s">
         <v>164</v>
-      </c>
-      <c r="C120" s="5">
-        <v>3</v>
-      </c>
-      <c r="D120" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="E120" s="5" t="s">
-        <v>26</v>
       </c>
       <c r="F120" s="5" t="s">
         <v>10</v>
@@ -4666,16 +4675,16 @@
         <v>3</v>
       </c>
       <c r="D121" s="5" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F121" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G121" s="10">
-        <v>46094</v>
+        <v>46085</v>
       </c>
     </row>
     <row r="122" spans="1:7">
@@ -4687,10 +4696,10 @@
         <v>3</v>
       </c>
       <c r="D122" s="5" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F122" s="5" t="s">
         <v>10</v>
@@ -4708,16 +4717,16 @@
         <v>3</v>
       </c>
       <c r="D123" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F123" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G123" s="10">
-        <v>46085</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="124" spans="1:7">
@@ -4729,10 +4738,10 @@
         <v>3</v>
       </c>
       <c r="D124" s="5" t="s">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>65</v>
+        <v>9</v>
       </c>
       <c r="F124" s="5" t="s">
         <v>10</v>
@@ -4750,16 +4759,16 @@
         <v>3</v>
       </c>
       <c r="D125" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F125" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G125" s="10">
-        <v>46084</v>
+        <v>46085</v>
       </c>
     </row>
     <row r="126" spans="1:7">
@@ -4771,10 +4780,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="5" t="s">
-        <v>128</v>
+        <v>66</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>129</v>
+        <v>67</v>
       </c>
       <c r="F126" s="5" t="s">
         <v>10</v>
@@ -4792,10 +4801,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="5" t="s">
-        <v>172</v>
+        <v>25</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>173</v>
+        <v>26</v>
       </c>
       <c r="F127" s="5" t="s">
         <v>10</v>
@@ -4807,85 +4816,85 @@
     <row r="128" spans="1:7">
       <c r="A128" s="4"/>
       <c r="B128" s="8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C128" s="5">
         <v>3</v>
       </c>
       <c r="D128" s="5" t="s">
-        <v>46</v>
+        <v>130</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>47</v>
+        <v>131</v>
       </c>
       <c r="F128" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G128" s="10">
-        <v>46112</v>
+        <v>46085</v>
       </c>
     </row>
     <row r="129" spans="1:7">
       <c r="A129" s="4"/>
       <c r="B129" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C129" s="5">
+        <v>3</v>
+      </c>
+      <c r="D129" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="C129" s="5">
-        <v>3</v>
-      </c>
-      <c r="D129" s="5" t="s">
-        <v>64</v>
-      </c>
       <c r="E129" s="5" t="s">
-        <v>65</v>
+        <v>175</v>
       </c>
       <c r="F129" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G129" s="10">
-        <v>46095</v>
+        <v>46084</v>
       </c>
     </row>
     <row r="130" spans="1:7">
       <c r="A130" s="4"/>
       <c r="B130" s="8" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C130" s="5">
         <v>3</v>
       </c>
       <c r="D130" s="5" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="F130" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G130" s="10">
-        <v>46084</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="131" spans="1:7">
       <c r="A131" s="4"/>
       <c r="B131" s="8" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C131" s="5">
         <v>3</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="F131" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G131" s="10">
-        <v>46084</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="132" spans="1:7">
@@ -4897,10 +4906,10 @@
         <v>3</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>162</v>
+        <v>17</v>
       </c>
       <c r="F132" s="5" t="s">
         <v>10</v>
@@ -4918,10 +4927,10 @@
         <v>3</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F133" s="5" t="s">
         <v>10</v>
@@ -4939,10 +4948,10 @@
         <v>3</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>22</v>
+        <v>164</v>
       </c>
       <c r="F134" s="5" t="s">
         <v>10</v>
@@ -4960,16 +4969,16 @@
         <v>3</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F135" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G135" s="10">
-        <v>46098</v>
+        <v>46084</v>
       </c>
     </row>
     <row r="136" spans="1:7">
@@ -4990,7 +4999,7 @@
         <v>10</v>
       </c>
       <c r="G136" s="10">
-        <v>46086</v>
+        <v>46084</v>
       </c>
     </row>
     <row r="137" spans="1:7">
@@ -5011,7 +5020,7 @@
         <v>10</v>
       </c>
       <c r="G137" s="10">
-        <v>46099</v>
+        <v>46098</v>
       </c>
     </row>
     <row r="138" spans="1:7">
@@ -5023,16 +5032,16 @@
         <v>3</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F138" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G138" s="10">
-        <v>46082</v>
+        <v>46086</v>
       </c>
     </row>
     <row r="139" spans="1:7">
@@ -5044,58 +5053,58 @@
         <v>3</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>47</v>
+        <v>9</v>
       </c>
       <c r="F139" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G139" s="10">
-        <v>46103</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="140" spans="1:7">
       <c r="A140" s="4"/>
       <c r="B140" s="8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C140" s="5">
         <v>3</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F140" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G140" s="10">
-        <v>46095</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="141" spans="1:7">
       <c r="A141" s="4"/>
       <c r="B141" s="8" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C141" s="5">
         <v>3</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="F141" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G141" s="10">
-        <v>46081</v>
+        <v>46103</v>
       </c>
     </row>
     <row r="142" spans="1:7">
@@ -5107,16 +5116,16 @@
         <v>3</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F142" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G142" s="10">
-        <v>46080</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="143" spans="1:7">
@@ -5128,16 +5137,16 @@
         <v>3</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="E143" s="5" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="F143" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G143" s="10">
-        <v>46080</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="144" spans="1:7">
@@ -5149,10 +5158,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="F144" s="5" t="s">
         <v>10</v>
@@ -5170,16 +5179,16 @@
         <v>3</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="F145" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G145" s="10">
-        <v>46079</v>
+        <v>46080</v>
       </c>
     </row>
     <row r="146" spans="1:7">
@@ -5191,16 +5200,16 @@
         <v>3</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="F146" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G146" s="10">
-        <v>46079</v>
+        <v>46080</v>
       </c>
     </row>
     <row r="147" spans="1:7">
@@ -5212,10 +5221,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F147" s="5" t="s">
         <v>10</v>
@@ -5233,10 +5242,10 @@
         <v>3</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>162</v>
+        <v>23</v>
       </c>
       <c r="F148" s="5" t="s">
         <v>10</v>
@@ -5254,10 +5263,10 @@
         <v>3</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F149" s="5" t="s">
         <v>10</v>
@@ -5275,10 +5284,10 @@
         <v>3</v>
       </c>
       <c r="D150" s="5" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="E150" s="5" t="s">
-        <v>16</v>
+        <v>164</v>
       </c>
       <c r="F150" s="5" t="s">
         <v>10</v>
@@ -5296,34 +5305,34 @@
         <v>3</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F151" s="5" t="s">
-        <v>131</v>
+        <v>10</v>
       </c>
       <c r="G151" s="10">
-        <v>46097</v>
+        <v>46079</v>
       </c>
     </row>
     <row r="152" spans="1:7">
       <c r="A152" s="4"/>
       <c r="B152" s="8" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C152" s="5">
         <v>3</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F152" s="5" t="s">
-        <v>131</v>
+        <v>10</v>
       </c>
       <c r="G152" s="10">
         <v>46079</v>
@@ -5332,22 +5341,22 @@
     <row r="153" spans="1:7">
       <c r="A153" s="4"/>
       <c r="B153" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C153" s="5">
         <v>3</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F153" s="5" t="s">
-        <v>10</v>
+        <v>133</v>
       </c>
       <c r="G153" s="10">
-        <v>46079</v>
+        <v>46097</v>
       </c>
     </row>
     <row r="154" spans="1:7">
@@ -5359,13 +5368,13 @@
         <v>3</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>162</v>
+        <v>26</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>10</v>
+        <v>133</v>
       </c>
       <c r="G154" s="10">
         <v>46079</v>
@@ -5380,10 +5389,10 @@
         <v>3</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F155" s="5" t="s">
         <v>10</v>
@@ -5401,10 +5410,10 @@
         <v>3</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>26</v>
+        <v>164</v>
       </c>
       <c r="F156" s="5" t="s">
         <v>10</v>
@@ -5422,58 +5431,58 @@
         <v>3</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>114</v>
+        <v>8</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>115</v>
+        <v>9</v>
       </c>
       <c r="F157" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G157" s="10">
-        <v>46111</v>
+        <v>46079</v>
       </c>
     </row>
     <row r="158" spans="1:7">
       <c r="A158" s="4"/>
       <c r="B158" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C158" s="5">
         <v>3</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F158" s="5" t="s">
-        <v>131</v>
+        <v>10</v>
       </c>
       <c r="G158" s="10">
-        <v>46083</v>
+        <v>46079</v>
       </c>
     </row>
     <row r="159" spans="1:7">
       <c r="A159" s="4"/>
       <c r="B159" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C159" s="5">
         <v>3</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>21</v>
+        <v>116</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>22</v>
+        <v>117</v>
       </c>
       <c r="F159" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G159" s="10">
-        <v>46107</v>
+        <v>46111</v>
       </c>
     </row>
     <row r="160" spans="1:7">
@@ -5485,16 +5494,16 @@
         <v>3</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>10</v>
+        <v>133</v>
       </c>
       <c r="G160" s="10">
-        <v>46079</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="161" spans="1:7">
@@ -5506,31 +5515,31 @@
         <v>3</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>203</v>
+        <v>25</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>204</v>
+        <v>26</v>
       </c>
       <c r="F161" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G161" s="10">
-        <v>46113</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="162" spans="1:7">
       <c r="A162" s="4"/>
       <c r="B162" s="8" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C162" s="5">
         <v>3</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="F162" s="5" t="s">
         <v>10</v>
@@ -5542,16 +5551,16 @@
     <row r="163" spans="1:7">
       <c r="A163" s="4"/>
       <c r="B163" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="C163" s="5">
+        <v>3</v>
+      </c>
+      <c r="D163" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="E163" s="5" t="s">
         <v>206</v>
-      </c>
-      <c r="C163" s="5">
-        <v>3</v>
-      </c>
-      <c r="D163" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="E163" s="5" t="s">
-        <v>204</v>
       </c>
       <c r="F163" s="5" t="s">
         <v>10</v>
@@ -5569,16 +5578,16 @@
         <v>3</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>91</v>
+        <v>59</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="F164" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G164" s="10">
-        <v>46104</v>
+        <v>46079</v>
       </c>
     </row>
     <row r="165" spans="1:7">
@@ -5590,16 +5599,16 @@
         <v>3</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>21</v>
+        <v>205</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>22</v>
+        <v>206</v>
       </c>
       <c r="F165" s="5" t="s">
-        <v>131</v>
+        <v>10</v>
       </c>
       <c r="G165" s="10">
-        <v>46104</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="166" spans="1:7">
@@ -5611,37 +5620,37 @@
         <v>3</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="E166" s="5" t="s">
-        <v>22</v>
+        <v>94</v>
       </c>
       <c r="F166" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G166" s="10">
-        <v>46078</v>
+        <v>46104</v>
       </c>
     </row>
     <row r="167" spans="1:7">
       <c r="A167" s="4"/>
-      <c r="B167" s="11" t="s">
+      <c r="B167" s="8" t="s">
         <v>210</v>
       </c>
       <c r="C167" s="5">
         <v>3</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>10</v>
+        <v>133</v>
       </c>
       <c r="G167" s="10">
-        <v>46078</v>
+        <v>46104</v>
       </c>
     </row>
     <row r="168" spans="1:7">
@@ -5653,37 +5662,37 @@
         <v>3</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E168" s="5" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F168" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G168" s="10">
-        <v>46081</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="169" spans="1:7">
       <c r="A169" s="4"/>
-      <c r="B169" s="8" t="s">
+      <c r="B169" s="11" t="s">
         <v>212</v>
       </c>
       <c r="C169" s="5">
         <v>3</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F169" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G169" s="10">
-        <v>46077</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="170" spans="1:7">
@@ -5695,16 +5704,16 @@
         <v>3</v>
       </c>
       <c r="D170" s="5" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F170" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G170" s="10">
-        <v>46077</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="171" spans="1:7">
@@ -5716,16 +5725,16 @@
         <v>3</v>
       </c>
       <c r="D171" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E171" s="5" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F171" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G171" s="10">
-        <v>46100</v>
+        <v>46077</v>
       </c>
     </row>
     <row r="172" spans="1:7">
@@ -5737,43 +5746,43 @@
         <v>3</v>
       </c>
       <c r="D172" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F172" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G172" s="10">
-        <v>46093</v>
+        <v>46077</v>
       </c>
     </row>
     <row r="173" spans="1:7">
       <c r="A173" s="4"/>
       <c r="B173" s="8" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C173" s="5">
         <v>3</v>
       </c>
       <c r="D173" s="5" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="F173" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G173" s="10">
-        <v>46077</v>
+        <v>46100</v>
       </c>
     </row>
     <row r="174" spans="1:7">
       <c r="A174" s="4"/>
       <c r="B174" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C174" s="5">
         <v>3</v>
@@ -5788,7 +5797,7 @@
         <v>10</v>
       </c>
       <c r="G174" s="10">
-        <v>46077</v>
+        <v>46093</v>
       </c>
     </row>
     <row r="175" spans="1:7">
@@ -5800,10 +5809,10 @@
         <v>3</v>
       </c>
       <c r="D175" s="5" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="E175" s="5" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="F175" s="5" t="s">
         <v>10</v>
@@ -5821,10 +5830,10 @@
         <v>3</v>
       </c>
       <c r="D176" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F176" s="5" t="s">
         <v>10</v>
@@ -5842,22 +5851,22 @@
         <v>3</v>
       </c>
       <c r="D177" s="5" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E177" s="5" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F177" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G177" s="10">
-        <v>46097</v>
+        <v>46077</v>
       </c>
     </row>
     <row r="178" spans="1:7">
       <c r="A178" s="4"/>
       <c r="B178" s="8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C178" s="5">
         <v>3</v>
@@ -5872,49 +5881,49 @@
         <v>10</v>
       </c>
       <c r="G178" s="10">
-        <v>46079</v>
+        <v>46077</v>
       </c>
     </row>
     <row r="179" spans="1:7">
       <c r="A179" s="4"/>
       <c r="B179" s="8" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C179" s="5">
         <v>3</v>
       </c>
       <c r="D179" s="5" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E179" s="5" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F179" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G179" s="10">
-        <v>46076</v>
+        <v>46097</v>
       </c>
     </row>
     <row r="180" spans="1:7">
       <c r="A180" s="4"/>
       <c r="B180" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C180" s="5">
         <v>3</v>
       </c>
       <c r="D180" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E180" s="5" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F180" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G180" s="10">
-        <v>46098</v>
+        <v>46079</v>
       </c>
     </row>
     <row r="181" spans="1:7">
@@ -5926,16 +5935,16 @@
         <v>3</v>
       </c>
       <c r="D181" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E181" s="5" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F181" s="5" t="s">
-        <v>131</v>
+        <v>10</v>
       </c>
       <c r="G181" s="10">
-        <v>46075</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="182" spans="1:7">
@@ -5947,16 +5956,16 @@
         <v>3</v>
       </c>
       <c r="D182" s="5" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="E182" s="5" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="F182" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G182" s="10">
-        <v>46077</v>
+        <v>46098</v>
       </c>
     </row>
     <row r="183" spans="1:7">
@@ -5968,16 +5977,16 @@
         <v>3</v>
       </c>
       <c r="D183" s="5" t="s">
-        <v>91</v>
+        <v>25</v>
       </c>
       <c r="E183" s="5" t="s">
-        <v>92</v>
+        <v>26</v>
       </c>
       <c r="F183" s="5" t="s">
-        <v>10</v>
+        <v>133</v>
       </c>
       <c r="G183" s="10">
-        <v>46093</v>
+        <v>46075</v>
       </c>
     </row>
     <row r="184" spans="1:7">
@@ -5989,16 +5998,16 @@
         <v>3</v>
       </c>
       <c r="D184" s="5" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="E184" s="5" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="F184" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G184" s="10">
-        <v>46078</v>
+        <v>46077</v>
       </c>
     </row>
     <row r="185" spans="1:7">
@@ -6010,121 +6019,121 @@
         <v>3</v>
       </c>
       <c r="D185" s="5" t="s">
-        <v>114</v>
+        <v>93</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="F185" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G185" s="10">
-        <v>46098</v>
+        <v>46093</v>
       </c>
     </row>
     <row r="186" spans="1:7">
       <c r="A186" s="4"/>
       <c r="B186" s="8" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C186" s="5">
         <v>3</v>
       </c>
       <c r="D186" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E186" s="5" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F186" s="5" t="s">
-        <v>131</v>
+        <v>10</v>
       </c>
       <c r="G186" s="10">
-        <v>46098</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="187" spans="1:7">
       <c r="A187" s="4"/>
       <c r="B187" s="8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C187" s="5">
         <v>3</v>
       </c>
-      <c r="D187" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E187" s="9" t="s">
-        <v>22</v>
+      <c r="D187" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="E187" s="5" t="s">
+        <v>117</v>
       </c>
       <c r="F187" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G187" s="10">
-        <v>46103</v>
+        <v>46098</v>
       </c>
     </row>
     <row r="188" spans="1:7">
       <c r="A188" s="4"/>
       <c r="B188" s="8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C188" s="5">
         <v>3</v>
       </c>
-      <c r="D188" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E188" s="9" t="s">
-        <v>22</v>
+      <c r="D188" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E188" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="F188" s="5" t="s">
-        <v>10</v>
+        <v>133</v>
       </c>
       <c r="G188" s="10">
-        <v>46102</v>
+        <v>46098</v>
       </c>
     </row>
     <row r="189" spans="1:7">
       <c r="A189" s="4"/>
       <c r="B189" s="8" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C189" s="5">
         <v>3</v>
       </c>
       <c r="D189" s="9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E189" s="9" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F189" s="5" t="s">
-        <v>131</v>
+        <v>10</v>
       </c>
       <c r="G189" s="10">
-        <v>46088</v>
+        <v>46103</v>
       </c>
     </row>
     <row r="190" spans="1:7">
       <c r="A190" s="4"/>
       <c r="B190" s="8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C190" s="5">
         <v>3</v>
       </c>
-      <c r="D190" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E190" s="5" t="s">
-        <v>65</v>
+      <c r="D190" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E190" s="9" t="s">
+        <v>26</v>
       </c>
       <c r="F190" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G190" s="10">
-        <v>46072</v>
+        <v>46102</v>
       </c>
     </row>
     <row r="191" spans="1:7">
@@ -6135,17 +6144,17 @@
       <c r="C191" s="5">
         <v>3</v>
       </c>
-      <c r="D191" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="E191" s="5" t="s">
-        <v>41</v>
+      <c r="D191" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E191" s="9" t="s">
+        <v>26</v>
       </c>
       <c r="F191" s="5" t="s">
-        <v>10</v>
+        <v>133</v>
       </c>
       <c r="G191" s="10">
-        <v>46070</v>
+        <v>46088</v>
       </c>
     </row>
     <row r="192" spans="1:7">
@@ -6157,16 +6166,16 @@
         <v>3</v>
       </c>
       <c r="D192" s="5" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="E192" s="5" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="F192" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G192" s="10">
-        <v>46070</v>
+        <v>46072</v>
       </c>
     </row>
     <row r="193" spans="1:7">
@@ -6178,10 +6187,10 @@
         <v>3</v>
       </c>
       <c r="D193" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E193" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F193" s="5" t="s">
         <v>10</v>
@@ -6199,10 +6208,10 @@
         <v>3</v>
       </c>
       <c r="D194" s="5" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E194" s="5" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="F194" s="5" t="s">
         <v>10</v>
@@ -6220,10 +6229,10 @@
         <v>3</v>
       </c>
       <c r="D195" s="5" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E195" s="5" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="F195" s="5" t="s">
         <v>10</v>
@@ -6241,16 +6250,16 @@
         <v>3</v>
       </c>
       <c r="D196" s="5" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E196" s="5" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="F196" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G196" s="10">
-        <v>46068</v>
+        <v>46070</v>
       </c>
     </row>
     <row r="197" spans="1:7">
@@ -6262,115 +6271,115 @@
         <v>3</v>
       </c>
       <c r="D197" s="5" t="s">
-        <v>123</v>
+        <v>25</v>
       </c>
       <c r="E197" s="5" t="s">
-        <v>124</v>
+        <v>26</v>
       </c>
       <c r="F197" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G197" s="10">
-        <v>46105</v>
+        <v>46070</v>
       </c>
     </row>
     <row r="198" spans="1:7">
       <c r="A198" s="4"/>
       <c r="B198" s="8" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C198" s="5">
         <v>3</v>
       </c>
       <c r="D198" s="5" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="E198" s="5" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="F198" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G198" s="10">
-        <v>46092</v>
+        <v>46068</v>
       </c>
     </row>
     <row r="199" spans="1:7">
       <c r="A199" s="4"/>
       <c r="B199" s="8" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C199" s="5">
         <v>3</v>
       </c>
       <c r="D199" s="5" t="s">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c r="E199" s="5" t="s">
-        <v>26</v>
+        <v>126</v>
       </c>
       <c r="F199" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G199" s="10">
-        <v>46075</v>
+        <v>46105</v>
       </c>
     </row>
     <row r="200" spans="1:7">
       <c r="A200" s="4"/>
       <c r="B200" s="8" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C200" s="5">
         <v>3</v>
       </c>
       <c r="D200" s="5" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="E200" s="5" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="F200" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G200" s="10">
-        <v>46072</v>
+        <v>46092</v>
       </c>
     </row>
     <row r="201" spans="1:7">
       <c r="A201" s="4"/>
       <c r="B201" s="8" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C201" s="5">
         <v>3</v>
       </c>
       <c r="D201" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E201" s="5" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F201" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G201" s="10">
-        <v>46071</v>
+        <v>46075</v>
       </c>
     </row>
     <row r="202" spans="1:7">
       <c r="A202" s="4"/>
       <c r="B202" s="8" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C202" s="5">
         <v>3</v>
       </c>
       <c r="D202" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E202" s="5" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F202" s="5" t="s">
         <v>10</v>
@@ -6388,79 +6397,79 @@
         <v>3</v>
       </c>
       <c r="D203" s="5" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="E203" s="5" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="F203" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G203" s="10">
-        <v>46107</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="204" spans="1:7">
       <c r="A204" s="4"/>
       <c r="B204" s="8" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C204" s="5">
         <v>3</v>
       </c>
       <c r="D204" s="5" t="s">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="E204" s="5" t="s">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="F204" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G204" s="10">
-        <v>46071</v>
+        <v>46072</v>
       </c>
     </row>
     <row r="205" spans="1:7">
       <c r="A205" s="4"/>
       <c r="B205" s="8" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C205" s="5">
         <v>3</v>
       </c>
       <c r="D205" s="5" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="E205" s="5" t="s">
-        <v>92</v>
+        <v>49</v>
       </c>
       <c r="F205" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G205" s="10">
-        <v>46067</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="206" spans="1:7">
       <c r="A206" s="4"/>
       <c r="B206" s="8" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C206" s="5">
         <v>3</v>
       </c>
       <c r="D206" s="5" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="E206" s="5" t="s">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="F206" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G206" s="10">
-        <v>46079</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="207" spans="1:7">
@@ -6472,16 +6481,16 @@
         <v>3</v>
       </c>
       <c r="D207" s="5" t="s">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="E207" s="5" t="s">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="F207" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G207" s="10">
-        <v>46068</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="208" spans="1:7">
@@ -6493,16 +6502,16 @@
         <v>3</v>
       </c>
       <c r="D208" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E208" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F208" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G208" s="10">
-        <v>46067</v>
+        <v>46079</v>
       </c>
     </row>
     <row r="209" spans="1:7">
@@ -6514,16 +6523,16 @@
         <v>3</v>
       </c>
       <c r="D209" s="5" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="E209" s="5" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="F209" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G209" s="10">
-        <v>46096</v>
+        <v>46068</v>
       </c>
     </row>
     <row r="210" spans="1:7">
@@ -6535,16 +6544,16 @@
         <v>3</v>
       </c>
       <c r="D210" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E210" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F210" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G210" s="10">
-        <v>46083</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="211" spans="1:7">
@@ -6565,7 +6574,7 @@
         <v>10</v>
       </c>
       <c r="G211" s="10">
-        <v>46066</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="212" spans="1:7">
@@ -6577,34 +6586,34 @@
         <v>3</v>
       </c>
       <c r="D212" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E212" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F212" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G212" s="10">
-        <v>46107</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="213" spans="1:7">
       <c r="A213" s="4"/>
       <c r="B213" s="8" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C213" s="5">
         <v>3</v>
       </c>
       <c r="D213" s="5" t="s">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="E213" s="5" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="F213" s="5" t="s">
-        <v>131</v>
+        <v>10</v>
       </c>
       <c r="G213" s="10">
         <v>46066</v>
@@ -6613,22 +6622,22 @@
     <row r="214" spans="1:7">
       <c r="A214" s="4"/>
       <c r="B214" s="8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C214" s="5">
         <v>3</v>
       </c>
       <c r="D214" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E214" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F214" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G214" s="10">
-        <v>46066</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="215" spans="1:7">
@@ -6640,16 +6649,16 @@
         <v>3</v>
       </c>
       <c r="D215" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E215" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F215" s="5" t="s">
-        <v>10</v>
+        <v>133</v>
       </c>
       <c r="G215" s="10">
-        <v>46083</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="216" spans="1:7">
@@ -6661,16 +6670,16 @@
         <v>3</v>
       </c>
       <c r="D216" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E216" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F216" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G216" s="10">
-        <v>46067</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="217" spans="1:7">
@@ -6682,31 +6691,31 @@
         <v>3</v>
       </c>
       <c r="D217" s="5" t="s">
-        <v>248</v>
+        <v>66</v>
       </c>
       <c r="E217" s="5" t="s">
-        <v>249</v>
+        <v>67</v>
       </c>
       <c r="F217" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G217" s="10">
-        <v>46087</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="218" spans="1:7">
       <c r="A218" s="4"/>
       <c r="B218" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C218" s="5">
         <v>3</v>
       </c>
       <c r="D218" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E218" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F218" s="5" t="s">
         <v>10</v>
@@ -6718,43 +6727,43 @@
     <row r="219" spans="1:7">
       <c r="A219" s="4"/>
       <c r="B219" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="C219" s="5">
+        <v>3</v>
+      </c>
+      <c r="D219" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="C219" s="5">
-        <v>3</v>
-      </c>
-      <c r="D219" s="5" t="s">
-        <v>21</v>
-      </c>
       <c r="E219" s="5" t="s">
-        <v>22</v>
+        <v>251</v>
       </c>
       <c r="F219" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G219" s="10">
-        <v>46067</v>
+        <v>46087</v>
       </c>
     </row>
     <row r="220" spans="1:7">
       <c r="A220" s="4"/>
       <c r="B220" s="8" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C220" s="5">
         <v>3</v>
       </c>
       <c r="D220" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E220" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F220" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G220" s="10">
-        <v>46065</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="221" spans="1:7">
@@ -6766,16 +6775,16 @@
         <v>3</v>
       </c>
       <c r="D221" s="5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E221" s="5" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F221" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G221" s="10">
-        <v>46065</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="222" spans="1:7">
@@ -6787,10 +6796,10 @@
         <v>3</v>
       </c>
       <c r="D222" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E222" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F222" s="5" t="s">
         <v>10</v>
@@ -6808,16 +6817,16 @@
         <v>3</v>
       </c>
       <c r="D223" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E223" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F223" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G223" s="10">
-        <v>46071</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="224" spans="1:7">
@@ -6829,16 +6838,16 @@
         <v>3</v>
       </c>
       <c r="D224" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E224" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F224" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G224" s="10">
-        <v>46067</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="225" spans="1:7">
@@ -6850,16 +6859,16 @@
         <v>3</v>
       </c>
       <c r="D225" s="5" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="E225" s="5" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="F225" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G225" s="10">
-        <v>46068</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="226" spans="1:7">
@@ -6871,16 +6880,16 @@
         <v>3</v>
       </c>
       <c r="D226" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E226" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F226" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G226" s="10">
-        <v>46068</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="227" spans="1:7">
@@ -6892,16 +6901,16 @@
         <v>3</v>
       </c>
       <c r="D227" s="5" t="s">
-        <v>12</v>
+        <v>66</v>
       </c>
       <c r="E227" s="5" t="s">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="F227" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G227" s="10">
-        <v>46064</v>
+        <v>46068</v>
       </c>
     </row>
     <row r="228" spans="1:7">
@@ -6913,16 +6922,16 @@
         <v>3</v>
       </c>
       <c r="D228" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E228" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F228" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G228" s="10">
-        <v>46099</v>
+        <v>46068</v>
       </c>
     </row>
     <row r="229" spans="1:7">
@@ -6934,16 +6943,16 @@
         <v>3</v>
       </c>
       <c r="D229" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E229" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F229" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G229" s="10">
-        <v>46098</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="230" spans="1:7">
@@ -6955,58 +6964,58 @@
         <v>3</v>
       </c>
       <c r="D230" s="5" t="s">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="E230" s="5" t="s">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="F230" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G230" s="10">
-        <v>46107</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="231" spans="1:7">
       <c r="A231" s="4"/>
       <c r="B231" s="8" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C231" s="5">
         <v>3</v>
       </c>
       <c r="D231" s="5" t="s">
-        <v>203</v>
+        <v>25</v>
       </c>
       <c r="E231" s="5" t="s">
-        <v>204</v>
+        <v>26</v>
       </c>
       <c r="F231" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G231" s="10">
-        <v>46064</v>
+        <v>46098</v>
       </c>
     </row>
     <row r="232" spans="1:7">
       <c r="A232" s="4"/>
       <c r="B232" s="8" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C232" s="5">
         <v>3</v>
       </c>
       <c r="D232" s="5" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="E232" s="5" t="s">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="F232" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G232" s="10">
-        <v>46078</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="233" spans="1:7">
@@ -7018,10 +7027,10 @@
         <v>3</v>
       </c>
       <c r="D233" s="5" t="s">
-        <v>21</v>
+        <v>205</v>
       </c>
       <c r="E233" s="5" t="s">
-        <v>22</v>
+        <v>206</v>
       </c>
       <c r="F233" s="5" t="s">
         <v>10</v>
@@ -7039,16 +7048,16 @@
         <v>3</v>
       </c>
       <c r="D234" s="5" t="s">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="E234" s="5" t="s">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="F234" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G234" s="10">
-        <v>46064</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="235" spans="1:7">
@@ -7060,16 +7069,16 @@
         <v>3</v>
       </c>
       <c r="D235" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E235" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F235" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G235" s="10">
-        <v>46076</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="236" spans="1:7">
@@ -7081,16 +7090,16 @@
         <v>3</v>
       </c>
       <c r="D236" s="5" t="s">
-        <v>21</v>
+        <v>77</v>
       </c>
       <c r="E236" s="5" t="s">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="F236" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G236" s="10">
-        <v>46065</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="237" spans="1:7">
@@ -7102,16 +7111,16 @@
         <v>3</v>
       </c>
       <c r="D237" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E237" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F237" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G237" s="10">
-        <v>46071</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="238" spans="1:7">
@@ -7132,7 +7141,7 @@
         <v>10</v>
       </c>
       <c r="G238" s="10">
-        <v>46076</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="239" spans="1:7">
@@ -7144,16 +7153,16 @@
         <v>3</v>
       </c>
       <c r="D239" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E239" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F239" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G239" s="10">
-        <v>46078</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="240" spans="1:7">
@@ -7165,16 +7174,16 @@
         <v>3</v>
       </c>
       <c r="D240" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E240" s="5" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F240" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G240" s="10">
-        <v>46106</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="241" spans="1:7">
@@ -7186,16 +7195,16 @@
         <v>3</v>
       </c>
       <c r="D241" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E241" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F241" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G241" s="10">
-        <v>46072</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="242" spans="1:7">
@@ -7207,16 +7216,16 @@
         <v>3</v>
       </c>
       <c r="D242" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E242" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F242" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G242" s="10">
-        <v>46066</v>
+        <v>46106</v>
       </c>
     </row>
     <row r="243" spans="1:7">
@@ -7228,16 +7237,16 @@
         <v>3</v>
       </c>
       <c r="D243" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E243" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F243" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G243" s="10">
-        <v>46068</v>
+        <v>46072</v>
       </c>
     </row>
     <row r="244" spans="1:7">
@@ -7249,16 +7258,16 @@
         <v>3</v>
       </c>
       <c r="D244" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E244" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F244" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G244" s="10">
-        <v>46067</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="245" spans="1:7">
@@ -7270,10 +7279,10 @@
         <v>3</v>
       </c>
       <c r="D245" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E245" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F245" s="5" t="s">
         <v>10</v>
@@ -7291,76 +7300,76 @@
         <v>3</v>
       </c>
       <c r="D246" s="5" t="s">
-        <v>91</v>
+        <v>25</v>
       </c>
       <c r="E246" s="5" t="s">
-        <v>92</v>
+        <v>26</v>
       </c>
       <c r="F246" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G246" s="10">
-        <v>46096</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="247" spans="1:7">
       <c r="A247" s="4"/>
       <c r="B247" s="8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C247" s="5">
         <v>3</v>
       </c>
       <c r="D247" s="5" t="s">
-        <v>91</v>
+        <v>25</v>
       </c>
       <c r="E247" s="5" t="s">
-        <v>92</v>
+        <v>26</v>
       </c>
       <c r="F247" s="5" t="s">
-        <v>131</v>
+        <v>10</v>
       </c>
       <c r="G247" s="10">
-        <v>46079</v>
+        <v>46068</v>
       </c>
     </row>
     <row r="248" spans="1:7">
       <c r="A248" s="4"/>
       <c r="B248" s="8" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C248" s="5">
         <v>3</v>
       </c>
       <c r="D248" s="5" t="s">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="E248" s="5" t="s">
-        <v>22</v>
+        <v>94</v>
       </c>
       <c r="F248" s="5" t="s">
-        <v>131</v>
+        <v>10</v>
       </c>
       <c r="G248" s="10">
-        <v>46069</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="249" spans="1:7">
       <c r="A249" s="4"/>
       <c r="B249" s="8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C249" s="5">
         <v>3</v>
       </c>
       <c r="D249" s="5" t="s">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="E249" s="5" t="s">
-        <v>22</v>
+        <v>94</v>
       </c>
       <c r="F249" s="5" t="s">
-        <v>10</v>
+        <v>133</v>
       </c>
       <c r="G249" s="10">
         <v>46079</v>
@@ -7375,16 +7384,16 @@
         <v>3</v>
       </c>
       <c r="D250" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E250" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F250" s="5" t="s">
-        <v>10</v>
+        <v>133</v>
       </c>
       <c r="G250" s="10">
-        <v>46066</v>
+        <v>46069</v>
       </c>
     </row>
     <row r="251" spans="1:7">
@@ -7396,16 +7405,16 @@
         <v>3</v>
       </c>
       <c r="D251" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E251" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F251" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G251" s="10">
-        <v>46080</v>
+        <v>46079</v>
       </c>
     </row>
     <row r="252" spans="1:7">
@@ -7417,58 +7426,58 @@
         <v>3</v>
       </c>
       <c r="D252" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E252" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F252" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G252" s="10">
-        <v>46095</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="253" spans="1:7">
       <c r="A253" s="4"/>
       <c r="B253" s="8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C253" s="5">
         <v>3</v>
       </c>
       <c r="D253" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E253" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F253" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G253" s="10">
-        <v>46095</v>
+        <v>46080</v>
       </c>
     </row>
     <row r="254" spans="1:7">
       <c r="A254" s="4"/>
       <c r="B254" s="8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C254" s="5">
         <v>3</v>
       </c>
       <c r="D254" s="5" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="E254" s="5" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="F254" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G254" s="10">
-        <v>46069</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="255" spans="1:7">
@@ -7489,7 +7498,7 @@
         <v>10</v>
       </c>
       <c r="G255" s="10">
-        <v>46066</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="256" spans="1:7">
@@ -7501,16 +7510,16 @@
         <v>3</v>
       </c>
       <c r="D256" s="5" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="E256" s="5" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="F256" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G256" s="10">
-        <v>46076</v>
+        <v>46069</v>
       </c>
     </row>
     <row r="257" spans="1:7">
@@ -7522,16 +7531,16 @@
         <v>3</v>
       </c>
       <c r="D257" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E257" s="5" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F257" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G257" s="10">
-        <v>46067</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="258" spans="1:7">
@@ -7543,16 +7552,16 @@
         <v>3</v>
       </c>
       <c r="D258" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E258" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F258" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G258" s="10">
-        <v>46095</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="259" spans="1:7">
@@ -7564,16 +7573,16 @@
         <v>3</v>
       </c>
       <c r="D259" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E259" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F259" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G259" s="10">
-        <v>46083</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="260" spans="1:7">
@@ -7585,16 +7594,16 @@
         <v>3</v>
       </c>
       <c r="D260" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E260" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F260" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G260" s="10">
-        <v>46069</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="261" spans="1:7">
@@ -7606,16 +7615,16 @@
         <v>3</v>
       </c>
       <c r="D261" s="5" t="s">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="E261" s="5" t="s">
-        <v>76</v>
+        <v>26</v>
       </c>
       <c r="F261" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G261" s="10">
-        <v>46067</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="262" spans="1:7">
@@ -7627,16 +7636,16 @@
         <v>3</v>
       </c>
       <c r="D262" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E262" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F262" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G262" s="10">
-        <v>46065</v>
+        <v>46069</v>
       </c>
     </row>
     <row r="263" spans="1:7">
@@ -7648,16 +7657,16 @@
         <v>3</v>
       </c>
       <c r="D263" s="5" t="s">
-        <v>12</v>
+        <v>77</v>
       </c>
       <c r="E263" s="5" t="s">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="F263" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G263" s="10">
-        <v>46066</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="264" spans="1:7">
@@ -7669,16 +7678,16 @@
         <v>3</v>
       </c>
       <c r="D264" s="5" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E264" s="5" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F264" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G264" s="10">
-        <v>46067</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="265" spans="1:7">
@@ -7690,16 +7699,16 @@
         <v>3</v>
       </c>
       <c r="D265" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E265" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F265" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G265" s="10">
-        <v>46065</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="266" spans="1:7">
@@ -7711,16 +7720,16 @@
         <v>3</v>
       </c>
       <c r="D266" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E266" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F266" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G266" s="10">
-        <v>46095</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="267" spans="1:7">
@@ -7732,16 +7741,16 @@
         <v>3</v>
       </c>
       <c r="D267" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E267" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F267" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G267" s="10">
-        <v>46070</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="268" spans="1:7">
@@ -7753,16 +7762,16 @@
         <v>3</v>
       </c>
       <c r="D268" s="5" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E268" s="5" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F268" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G268" s="10">
-        <v>46067</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="269" spans="1:7">
@@ -7774,16 +7783,16 @@
         <v>3</v>
       </c>
       <c r="D269" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E269" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F269" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G269" s="10">
-        <v>46066</v>
+        <v>46070</v>
       </c>
     </row>
     <row r="270" spans="1:7">
@@ -7795,58 +7804,58 @@
         <v>3</v>
       </c>
       <c r="D270" s="5" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E270" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F270" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G270" s="10">
-        <v>46081</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="271" spans="1:7">
       <c r="A271" s="4"/>
       <c r="B271" s="8" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C271" s="5">
         <v>3</v>
       </c>
       <c r="D271" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E271" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F271" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G271" s="10">
-        <v>46065</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="272" spans="1:7">
       <c r="A272" s="4"/>
       <c r="B272" s="8" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C272" s="5">
         <v>3</v>
       </c>
       <c r="D272" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E272" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F272" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G272" s="10">
-        <v>46100</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="273" spans="1:7">
@@ -7858,16 +7867,16 @@
         <v>3</v>
       </c>
       <c r="D273" s="5" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="E273" s="5" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="F273" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G273" s="10">
-        <v>46067</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="274" spans="1:7">
@@ -7879,16 +7888,16 @@
         <v>3</v>
       </c>
       <c r="D274" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E274" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F274" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G274" s="10">
-        <v>46070</v>
+        <v>46100</v>
       </c>
     </row>
     <row r="275" spans="1:7">
@@ -7900,10 +7909,10 @@
         <v>3</v>
       </c>
       <c r="D275" s="5" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="E275" s="5" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="F275" s="5" t="s">
         <v>10</v>
@@ -7921,16 +7930,16 @@
         <v>3</v>
       </c>
       <c r="D276" s="5" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="E276" s="5" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="F276" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G276" s="10">
-        <v>46083</v>
+        <v>46070</v>
       </c>
     </row>
     <row r="277" spans="1:7">
@@ -7942,16 +7951,16 @@
         <v>3</v>
       </c>
       <c r="D277" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E277" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F277" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G277" s="10">
-        <v>46095</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="278" spans="1:7">
@@ -7963,16 +7972,16 @@
         <v>3</v>
       </c>
       <c r="D278" s="5" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="E278" s="5" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="F278" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G278" s="10">
-        <v>46098</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="279" spans="1:7">
@@ -7984,16 +7993,16 @@
         <v>3</v>
       </c>
       <c r="D279" s="5" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="E279" s="5" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="F279" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G279" s="10">
-        <v>46065</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="280" spans="1:7">
@@ -8005,16 +8014,16 @@
         <v>3</v>
       </c>
       <c r="D280" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E280" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F280" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G280" s="10">
-        <v>46066</v>
+        <v>46098</v>
       </c>
     </row>
     <row r="281" spans="1:7">
@@ -8026,16 +8035,16 @@
         <v>3</v>
       </c>
       <c r="D281" s="5" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="E281" s="5" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="F281" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G281" s="10">
-        <v>46072</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="282" spans="1:7">
@@ -8047,10 +8056,10 @@
         <v>3</v>
       </c>
       <c r="D282" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E282" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F282" s="5" t="s">
         <v>10</v>
@@ -8068,16 +8077,16 @@
         <v>3</v>
       </c>
       <c r="D283" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E283" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F283" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G283" s="10">
-        <v>46070</v>
+        <v>46072</v>
       </c>
     </row>
     <row r="284" spans="1:7">
@@ -8089,16 +8098,16 @@
         <v>3</v>
       </c>
       <c r="D284" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E284" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F284" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G284" s="10">
-        <v>46082</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="285" spans="1:7">
@@ -8110,16 +8119,16 @@
         <v>3</v>
       </c>
       <c r="D285" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E285" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F285" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G285" s="10">
-        <v>46068</v>
+        <v>46070</v>
       </c>
     </row>
     <row r="286" spans="1:7">
@@ -8131,16 +8140,16 @@
         <v>3</v>
       </c>
       <c r="D286" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E286" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F286" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G286" s="10">
-        <v>46110</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="287" spans="1:7">
@@ -8152,16 +8161,16 @@
         <v>3</v>
       </c>
       <c r="D287" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E287" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F287" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G287" s="10">
-        <v>46093</v>
+        <v>46068</v>
       </c>
     </row>
     <row r="288" spans="1:7">
@@ -8173,16 +8182,16 @@
         <v>3</v>
       </c>
       <c r="D288" s="5" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E288" s="5" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F288" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G288" s="10">
-        <v>46065</v>
+        <v>46110</v>
       </c>
     </row>
     <row r="289" spans="1:7">
@@ -8194,16 +8203,16 @@
         <v>3</v>
       </c>
       <c r="D289" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E289" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F289" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G289" s="10">
-        <v>46095</v>
+        <v>46093</v>
       </c>
     </row>
     <row r="290" spans="1:7">
@@ -8215,16 +8224,16 @@
         <v>3</v>
       </c>
       <c r="D290" s="5" t="s">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="E290" s="5" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="F290" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G290" s="10">
-        <v>46066</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="291" spans="1:7">
@@ -8236,16 +8245,16 @@
         <v>3</v>
       </c>
       <c r="D291" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E291" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F291" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G291" s="10">
-        <v>46065</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="292" spans="1:7">
@@ -8257,16 +8266,16 @@
         <v>3</v>
       </c>
       <c r="D292" s="5" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="E292" s="5" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="F292" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G292" s="10">
-        <v>46065</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="293" spans="1:7">
@@ -8278,31 +8287,31 @@
         <v>3</v>
       </c>
       <c r="D293" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E293" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F293" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G293" s="10">
-        <v>46076</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="294" spans="1:7">
       <c r="A294" s="4"/>
       <c r="B294" s="8" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C294" s="5">
         <v>3</v>
       </c>
       <c r="D294" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E294" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F294" s="5" t="s">
         <v>10</v>
@@ -8314,16 +8323,16 @@
     <row r="295" spans="1:7">
       <c r="A295" s="4"/>
       <c r="B295" s="8" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C295" s="5">
         <v>3</v>
       </c>
       <c r="D295" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E295" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F295" s="5" t="s">
         <v>10</v>
@@ -8341,16 +8350,16 @@
         <v>3</v>
       </c>
       <c r="D296" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E296" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F296" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G296" s="10">
-        <v>46101</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="297" spans="1:7">
@@ -8362,16 +8371,16 @@
         <v>3</v>
       </c>
       <c r="D297" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E297" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F297" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G297" s="10">
-        <v>46066</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="298" spans="1:7">
@@ -8383,16 +8392,16 @@
         <v>3</v>
       </c>
       <c r="D298" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E298" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F298" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G298" s="10">
-        <v>46066</v>
+        <v>46101</v>
       </c>
     </row>
     <row r="299" spans="1:7">
@@ -8404,16 +8413,16 @@
         <v>3</v>
       </c>
       <c r="D299" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E299" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F299" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G299" s="10">
-        <v>46081</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="300" spans="1:7">
@@ -8425,16 +8434,16 @@
         <v>3</v>
       </c>
       <c r="D300" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E300" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F300" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G300" s="10">
-        <v>46065</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="301" spans="1:7">
@@ -8446,16 +8455,16 @@
         <v>3</v>
       </c>
       <c r="D301" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E301" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F301" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G301" s="10">
-        <v>46069</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="302" spans="1:7">
@@ -8467,16 +8476,16 @@
         <v>3</v>
       </c>
       <c r="D302" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E302" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F302" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G302" s="10">
-        <v>46087</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="303" spans="1:7">
@@ -8488,100 +8497,100 @@
         <v>3</v>
       </c>
       <c r="D303" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E303" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F303" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G303" s="10">
-        <v>46066</v>
+        <v>46069</v>
       </c>
     </row>
     <row r="304" spans="1:7">
       <c r="A304" s="4"/>
-      <c r="B304" s="5" t="s">
+      <c r="B304" s="8" t="s">
         <v>329</v>
       </c>
       <c r="C304" s="5">
         <v>3</v>
       </c>
       <c r="D304" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E304" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F304" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G304" s="10">
-        <v>46102</v>
+        <v>46087</v>
       </c>
     </row>
     <row r="305" spans="1:7">
       <c r="A305" s="4"/>
       <c r="B305" s="8" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C305" s="5">
         <v>3</v>
       </c>
       <c r="D305" s="5" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="E305" s="5" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="F305" s="5" t="s">
-        <v>131</v>
+        <v>10</v>
       </c>
       <c r="G305" s="10">
-        <v>46094</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="306" spans="1:7">
       <c r="A306" s="4"/>
-      <c r="B306" s="8" t="s">
-        <v>329</v>
+      <c r="B306" s="5" t="s">
+        <v>331</v>
       </c>
       <c r="C306" s="5">
         <v>3</v>
       </c>
       <c r="D306" s="5" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="E306" s="5" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="F306" s="5" t="s">
-        <v>131</v>
+        <v>10</v>
       </c>
       <c r="G306" s="10">
-        <v>46093</v>
+        <v>46102</v>
       </c>
     </row>
     <row r="307" spans="1:7">
       <c r="A307" s="4"/>
       <c r="B307" s="8" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C307" s="5">
         <v>3</v>
       </c>
       <c r="D307" s="5" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="E307" s="5" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="F307" s="5" t="s">
-        <v>10</v>
+        <v>133</v>
       </c>
       <c r="G307" s="10">
-        <v>46065</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="308" spans="1:7">
@@ -8593,16 +8602,16 @@
         <v>3</v>
       </c>
       <c r="D308" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E308" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F308" s="5" t="s">
-        <v>10</v>
+        <v>133</v>
       </c>
       <c r="G308" s="10">
-        <v>46079</v>
+        <v>46093</v>
       </c>
     </row>
     <row r="309" spans="1:7">
@@ -8614,16 +8623,16 @@
         <v>3</v>
       </c>
       <c r="D309" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E309" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F309" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G309" s="10">
-        <v>46067</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="310" spans="1:7">
@@ -8635,16 +8644,16 @@
         <v>3</v>
       </c>
       <c r="D310" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E310" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F310" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G310" s="10">
-        <v>46067</v>
+        <v>46079</v>
       </c>
     </row>
     <row r="311" spans="1:7">
@@ -8656,16 +8665,16 @@
         <v>3</v>
       </c>
       <c r="D311" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E311" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F311" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G311" s="10">
-        <v>46069</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="312" spans="1:7">
@@ -8677,16 +8686,16 @@
         <v>3</v>
       </c>
       <c r="D312" s="5" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="E312" s="5" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="F312" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G312" s="10">
-        <v>46064</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="313" spans="1:7">
@@ -8698,16 +8707,16 @@
         <v>3</v>
       </c>
       <c r="D313" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E313" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F313" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G313" s="10">
-        <v>46095</v>
+        <v>46069</v>
       </c>
     </row>
     <row r="314" spans="1:7">
@@ -8719,37 +8728,37 @@
         <v>3</v>
       </c>
       <c r="D314" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E314" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F314" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G314" s="10">
-        <v>46098</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="315" spans="1:7">
       <c r="A315" s="4"/>
-      <c r="B315" s="5" t="s">
+      <c r="B315" s="8" t="s">
         <v>338</v>
       </c>
       <c r="C315" s="5">
         <v>3</v>
       </c>
       <c r="D315" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E315" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F315" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G315" s="10">
-        <v>46077</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="316" spans="1:7">
@@ -8761,37 +8770,37 @@
         <v>3</v>
       </c>
       <c r="D316" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E316" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F316" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G316" s="10">
-        <v>46067</v>
+        <v>46098</v>
       </c>
     </row>
     <row r="317" spans="1:7">
       <c r="A317" s="4"/>
-      <c r="B317" s="8" t="s">
+      <c r="B317" s="5" t="s">
         <v>340</v>
       </c>
       <c r="C317" s="5">
         <v>3</v>
       </c>
       <c r="D317" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E317" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F317" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G317" s="10">
-        <v>46066</v>
+        <v>46077</v>
       </c>
     </row>
     <row r="318" spans="1:7">
@@ -8803,16 +8812,16 @@
         <v>3</v>
       </c>
       <c r="D318" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E318" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F318" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G318" s="10">
-        <v>46066</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="319" spans="1:7">
@@ -8824,16 +8833,16 @@
         <v>3</v>
       </c>
       <c r="D319" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E319" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F319" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G319" s="10">
-        <v>46083</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="320" spans="1:7">
@@ -8866,31 +8875,31 @@
         <v>3</v>
       </c>
       <c r="D321" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E321" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F321" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G321" s="10">
-        <v>46097</v>
+        <v>46083</v>
       </c>
     </row>
     <row r="322" spans="1:7">
       <c r="A322" s="4"/>
       <c r="B322" s="8" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C322" s="5">
         <v>3</v>
       </c>
       <c r="D322" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E322" s="5" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F322" s="5" t="s">
         <v>10</v>
@@ -8902,64 +8911,64 @@
     <row r="323" spans="1:7">
       <c r="A323" s="4"/>
       <c r="B323" s="8" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C323" s="5">
         <v>3</v>
       </c>
       <c r="D323" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E323" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F323" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G323" s="10">
-        <v>46076</v>
+        <v>46097</v>
       </c>
     </row>
     <row r="324" spans="1:7">
       <c r="A324" s="4"/>
       <c r="B324" s="8" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C324" s="5">
         <v>3</v>
       </c>
       <c r="D324" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E324" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F324" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G324" s="10">
-        <v>46065</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="325" spans="1:7">
       <c r="A325" s="4"/>
       <c r="B325" s="8" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C325" s="5">
         <v>3</v>
       </c>
       <c r="D325" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E325" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F325" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G325" s="10">
-        <v>46066</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="326" spans="1:7">
@@ -8971,16 +8980,16 @@
         <v>3</v>
       </c>
       <c r="D326" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E326" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F326" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G326" s="10">
-        <v>46094</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="327" spans="1:7">
@@ -8992,16 +9001,16 @@
         <v>3</v>
       </c>
       <c r="D327" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E327" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F327" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G327" s="10">
-        <v>46068</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="328" spans="1:7">
@@ -9013,16 +9022,16 @@
         <v>3</v>
       </c>
       <c r="D328" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E328" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F328" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G328" s="10">
-        <v>46067</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="329" spans="1:7">
@@ -9034,16 +9043,16 @@
         <v>3</v>
       </c>
       <c r="D329" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E329" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F329" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G329" s="10">
-        <v>46079</v>
+        <v>46068</v>
       </c>
     </row>
     <row r="330" spans="1:7">
@@ -9055,16 +9064,16 @@
         <v>3</v>
       </c>
       <c r="D330" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E330" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F330" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G330" s="10">
-        <v>46095</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="331" spans="1:7">
@@ -9076,31 +9085,31 @@
         <v>3</v>
       </c>
       <c r="D331" s="5" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="E331" s="5" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="F331" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G331" s="10">
-        <v>46100</v>
+        <v>46079</v>
       </c>
     </row>
     <row r="332" spans="1:7">
       <c r="A332" s="4"/>
       <c r="B332" s="8" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C332" s="5">
         <v>3</v>
       </c>
       <c r="D332" s="5" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="E332" s="5" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="F332" s="5" t="s">
         <v>10</v>
@@ -9112,37 +9121,37 @@
     <row r="333" spans="1:7">
       <c r="A333" s="4"/>
       <c r="B333" s="8" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C333" s="5">
         <v>3</v>
       </c>
       <c r="D333" s="5" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="E333" s="5" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="F333" s="5" t="s">
-        <v>131</v>
+        <v>10</v>
       </c>
       <c r="G333" s="10">
-        <v>46086</v>
+        <v>46100</v>
       </c>
     </row>
     <row r="334" spans="1:7">
       <c r="A334" s="4"/>
       <c r="B334" s="8" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C334" s="5">
         <v>3</v>
       </c>
       <c r="D334" s="5" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="E334" s="5" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="F334" s="5" t="s">
         <v>10</v>
@@ -9160,16 +9169,16 @@
         <v>3</v>
       </c>
       <c r="D335" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E335" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F335" s="5" t="s">
-        <v>10</v>
+        <v>133</v>
       </c>
       <c r="G335" s="10">
-        <v>46099</v>
+        <v>46086</v>
       </c>
     </row>
     <row r="336" spans="1:7">
@@ -9181,16 +9190,16 @@
         <v>3</v>
       </c>
       <c r="D336" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E336" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F336" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G336" s="10">
-        <v>46066</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="337" spans="1:7">
@@ -9202,16 +9211,16 @@
         <v>3</v>
       </c>
       <c r="D337" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E337" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F337" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G337" s="10">
-        <v>46081</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="338" spans="1:7">
@@ -9223,10 +9232,10 @@
         <v>3</v>
       </c>
       <c r="D338" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E338" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F338" s="5" t="s">
         <v>10</v>
@@ -9244,16 +9253,16 @@
         <v>3</v>
       </c>
       <c r="D339" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E339" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F339" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G339" s="10">
-        <v>46067</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="340" spans="1:7">
@@ -9265,16 +9274,16 @@
         <v>3</v>
       </c>
       <c r="D340" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E340" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F340" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G340" s="10">
-        <v>46105</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="341" spans="1:7">
@@ -9286,10 +9295,10 @@
         <v>3</v>
       </c>
       <c r="D341" s="5" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E341" s="5" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F341" s="5" t="s">
         <v>10</v>
@@ -9307,16 +9316,16 @@
         <v>3</v>
       </c>
       <c r="D342" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E342" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F342" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G342" s="10">
-        <v>46066</v>
+        <v>46105</v>
       </c>
     </row>
     <row r="343" spans="1:7">
@@ -9328,10 +9337,10 @@
         <v>3</v>
       </c>
       <c r="D343" s="5" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E343" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F343" s="5" t="s">
         <v>10</v>
@@ -9349,10 +9358,10 @@
         <v>3</v>
       </c>
       <c r="D344" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E344" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F344" s="5" t="s">
         <v>10</v>
@@ -9370,58 +9379,58 @@
         <v>3</v>
       </c>
       <c r="D345" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E345" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F345" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G345" s="10">
-        <v>46101</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="346" spans="1:7">
       <c r="A346" s="4"/>
       <c r="B346" s="8" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C346" s="5">
         <v>3</v>
       </c>
       <c r="D346" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E346" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F346" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G346" s="10">
-        <v>46080</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="347" spans="1:7">
       <c r="A347" s="4"/>
       <c r="B347" s="8" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C347" s="5">
         <v>3</v>
       </c>
       <c r="D347" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E347" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F347" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G347" s="10">
-        <v>46095</v>
+        <v>46101</v>
       </c>
     </row>
     <row r="348" spans="1:7">
@@ -9433,16 +9442,16 @@
         <v>3</v>
       </c>
       <c r="D348" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E348" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F348" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G348" s="10">
-        <v>46071</v>
+        <v>46080</v>
       </c>
     </row>
     <row r="349" spans="1:7">
@@ -9454,16 +9463,16 @@
         <v>3</v>
       </c>
       <c r="D349" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E349" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F349" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G349" s="10">
-        <v>46082</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="350" spans="1:7">
@@ -9475,16 +9484,16 @@
         <v>3</v>
       </c>
       <c r="D350" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E350" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F350" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G350" s="10">
-        <v>46085</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="351" spans="1:7">
@@ -9496,10 +9505,10 @@
         <v>3</v>
       </c>
       <c r="D351" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E351" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F351" s="5" t="s">
         <v>10</v>
@@ -9517,58 +9526,58 @@
         <v>3</v>
       </c>
       <c r="D352" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E352" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F352" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G352" s="10">
-        <v>46077</v>
+        <v>46085</v>
       </c>
     </row>
     <row r="353" spans="1:7">
       <c r="A353" s="4"/>
       <c r="B353" s="8" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C353" s="5">
         <v>3</v>
       </c>
       <c r="D353" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E353" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F353" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G353" s="10">
-        <v>46071</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="354" spans="1:7">
       <c r="A354" s="4"/>
       <c r="B354" s="8" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C354" s="5">
         <v>3</v>
       </c>
       <c r="D354" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E354" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F354" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G354" s="10">
-        <v>46079</v>
+        <v>46077</v>
       </c>
     </row>
     <row r="355" spans="1:7">
@@ -9580,16 +9589,16 @@
         <v>3</v>
       </c>
       <c r="D355" s="5" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="E355" s="5" t="s">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="F355" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G355" s="10">
-        <v>46072</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="356" spans="1:7">
@@ -9610,7 +9619,7 @@
         <v>10</v>
       </c>
       <c r="G356" s="10">
-        <v>46072</v>
+        <v>46079</v>
       </c>
     </row>
     <row r="357" spans="1:7">
@@ -9622,16 +9631,16 @@
         <v>3</v>
       </c>
       <c r="D357" s="5" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="E357" s="5" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="F357" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G357" s="10">
-        <v>46066</v>
+        <v>46072</v>
       </c>
     </row>
     <row r="358" spans="1:7">
@@ -9643,16 +9652,16 @@
         <v>3</v>
       </c>
       <c r="D358" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E358" s="5" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F358" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G358" s="10">
-        <v>46070</v>
+        <v>46072</v>
       </c>
     </row>
     <row r="359" spans="1:7">
@@ -9664,16 +9673,16 @@
         <v>3</v>
       </c>
       <c r="D359" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E359" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F359" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G359" s="10">
-        <v>46094</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="360" spans="1:7">
@@ -9685,16 +9694,16 @@
         <v>3</v>
       </c>
       <c r="D360" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E360" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F360" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G360" s="10">
-        <v>46095</v>
+        <v>46070</v>
       </c>
     </row>
     <row r="361" spans="1:7">
@@ -9706,16 +9715,16 @@
         <v>3</v>
       </c>
       <c r="D361" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E361" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F361" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G361" s="10">
-        <v>46064</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="362" spans="1:7">
@@ -9727,16 +9736,16 @@
         <v>3</v>
       </c>
       <c r="D362" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E362" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F362" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G362" s="10">
-        <v>46066</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="363" spans="1:7">
@@ -9748,16 +9757,16 @@
         <v>3</v>
       </c>
       <c r="D363" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E363" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F363" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G363" s="10">
-        <v>46067</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="364" spans="1:7">
@@ -9769,10 +9778,10 @@
         <v>3</v>
       </c>
       <c r="D364" s="5" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E364" s="5" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F364" s="5" t="s">
         <v>10</v>
@@ -9790,16 +9799,16 @@
         <v>3</v>
       </c>
       <c r="D365" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E365" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F365" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G365" s="10">
-        <v>46066</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="366" spans="1:7">
@@ -9811,16 +9820,16 @@
         <v>3</v>
       </c>
       <c r="D366" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E366" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F366" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G366" s="10">
-        <v>46071</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="367" spans="1:7">
@@ -9832,16 +9841,16 @@
         <v>3</v>
       </c>
       <c r="D367" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E367" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F367" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G367" s="10">
-        <v>46081</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="368" spans="1:7">
@@ -9853,16 +9862,16 @@
         <v>3</v>
       </c>
       <c r="D368" s="5" t="s">
-        <v>96</v>
+        <v>25</v>
       </c>
       <c r="E368" s="5" t="s">
-        <v>97</v>
+        <v>26</v>
       </c>
       <c r="F368" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G368" s="10">
-        <v>46070</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="369" spans="1:7">
@@ -9874,16 +9883,16 @@
         <v>3</v>
       </c>
       <c r="D369" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E369" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F369" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G369" s="10">
-        <v>46067</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="370" spans="1:7">
@@ -9895,16 +9904,16 @@
         <v>3</v>
       </c>
       <c r="D370" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E370" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="F370" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G370" s="10">
-        <v>46067</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="371" spans="1:7">
@@ -9916,16 +9925,16 @@
         <v>3</v>
       </c>
       <c r="D371" s="5" t="s">
-        <v>21</v>
+        <v>98</v>
       </c>
       <c r="E371" s="5" t="s">
-        <v>22</v>
+        <v>99</v>
       </c>
       <c r="F371" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G371" s="10">
-        <v>46065</v>
+        <v>46070</v>
       </c>
     </row>
     <row r="372" spans="1:7">
@@ -9937,79 +9946,79 @@
         <v>3</v>
       </c>
       <c r="D372" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E372" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F372" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G372" s="12" t="s">
-        <v>390</v>
+      <c r="G372" s="10">
+        <v>46067</v>
       </c>
     </row>
     <row r="373" spans="1:7">
       <c r="A373" s="4"/>
       <c r="B373" s="8" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C373" s="5">
         <v>3</v>
       </c>
       <c r="D373" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E373" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F373" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G373" s="10">
-        <v>46065</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="374" spans="1:7">
       <c r="A374" s="4"/>
       <c r="B374" s="8" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C374" s="5">
         <v>3</v>
       </c>
       <c r="D374" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E374" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F374" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G374" s="10">
-        <v>46066</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="375" spans="1:7">
       <c r="A375" s="4"/>
       <c r="B375" s="8" t="s">
+        <v>392</v>
+      </c>
+      <c r="C375" s="5">
+        <v>3</v>
+      </c>
+      <c r="D375" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E375" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F375" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G375" s="12" t="s">
         <v>393</v>
-      </c>
-      <c r="C375" s="5">
-        <v>3</v>
-      </c>
-      <c r="D375" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E375" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="F375" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G375" s="10">
-        <v>46066</v>
       </c>
     </row>
     <row r="376" spans="1:7">
@@ -10021,16 +10030,16 @@
         <v>3</v>
       </c>
       <c r="D376" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E376" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F376" s="5" t="s">
-        <v>131</v>
+        <v>10</v>
       </c>
       <c r="G376" s="10">
-        <v>46086</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="377" spans="1:7">
@@ -10042,10 +10051,10 @@
         <v>3</v>
       </c>
       <c r="D377" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E377" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F377" s="5" t="s">
         <v>10</v>
@@ -10063,16 +10072,16 @@
         <v>3</v>
       </c>
       <c r="D378" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E378" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F378" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G378" s="10">
-        <v>46068</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="379" spans="1:7">
@@ -10084,16 +10093,16 @@
         <v>3</v>
       </c>
       <c r="D379" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E379" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F379" s="5" t="s">
-        <v>10</v>
+        <v>133</v>
       </c>
       <c r="G379" s="10">
-        <v>46065</v>
+        <v>46086</v>
       </c>
     </row>
     <row r="380" spans="1:7">
@@ -10105,16 +10114,16 @@
         <v>3</v>
       </c>
       <c r="D380" s="5" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E380" s="5" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F380" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G380" s="10">
-        <v>46050</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="381" spans="1:7">
@@ -10126,16 +10135,16 @@
         <v>3</v>
       </c>
       <c r="D381" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E381" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F381" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G381" s="10">
-        <v>46099</v>
+        <v>46068</v>
       </c>
     </row>
     <row r="382" spans="1:7">
@@ -10147,16 +10156,16 @@
         <v>3</v>
       </c>
       <c r="D382" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E382" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F382" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G382" s="10">
-        <v>46071</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="383" spans="1:7">
@@ -10168,16 +10177,16 @@
         <v>3</v>
       </c>
       <c r="D383" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E383" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F383" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G383" s="10">
-        <v>46034</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="384" spans="1:7">
@@ -10189,16 +10198,16 @@
         <v>3</v>
       </c>
       <c r="D384" s="5" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E384" s="5" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F384" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G384" s="10">
-        <v>46034</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="385" spans="1:7">
@@ -10210,16 +10219,16 @@
         <v>3</v>
       </c>
       <c r="D385" s="5" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E385" s="5" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F385" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G385" s="10">
-        <v>46034</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="386" spans="1:7">
@@ -10231,10 +10240,10 @@
         <v>3</v>
       </c>
       <c r="D386" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E386" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F386" s="5" t="s">
         <v>10</v>
@@ -10252,16 +10261,16 @@
         <v>3</v>
       </c>
       <c r="D387" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E387" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F387" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G387" s="10">
-        <v>46035</v>
+        <v>46034</v>
       </c>
     </row>
     <row r="388" spans="1:7">
@@ -10273,10 +10282,10 @@
         <v>3</v>
       </c>
       <c r="D388" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E388" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F388" s="5" t="s">
         <v>10</v>
@@ -10294,10 +10303,10 @@
         <v>3</v>
       </c>
       <c r="D389" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E389" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F389" s="5" t="s">
         <v>10</v>
@@ -10315,16 +10324,16 @@
         <v>3</v>
       </c>
       <c r="D390" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E390" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F390" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G390" s="10">
-        <v>46034</v>
+        <v>46035</v>
       </c>
     </row>
     <row r="391" spans="1:7">
@@ -10336,10 +10345,10 @@
         <v>3</v>
       </c>
       <c r="D391" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E391" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F391" s="5" t="s">
         <v>10</v>
@@ -10357,10 +10366,10 @@
         <v>3</v>
       </c>
       <c r="D392" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E392" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F392" s="5" t="s">
         <v>10</v>
@@ -10378,10 +10387,10 @@
         <v>3</v>
       </c>
       <c r="D393" s="5" t="s">
-        <v>412</v>
+        <v>19</v>
       </c>
       <c r="E393" s="5" t="s">
-        <v>413</v>
+        <v>20</v>
       </c>
       <c r="F393" s="5" t="s">
         <v>10</v>
@@ -10393,42 +10402,105 @@
     <row r="394" spans="1:7">
       <c r="A394" s="4"/>
       <c r="B394" s="8" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C394" s="5">
         <v>3</v>
       </c>
       <c r="D394" s="5" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E394" s="5" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F394" s="5" t="s">
-        <v>131</v>
+        <v>10</v>
       </c>
       <c r="G394" s="10">
+        <v>46034</v>
+      </c>
+    </row>
+    <row r="395" spans="1:7">
+      <c r="A395" s="4"/>
+      <c r="B395" s="8" t="s">
+        <v>413</v>
+      </c>
+      <c r="C395" s="5">
+        <v>3</v>
+      </c>
+      <c r="D395" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E395" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F395" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G395" s="10">
+        <v>46034</v>
+      </c>
+    </row>
+    <row r="396" spans="1:7">
+      <c r="A396" s="4"/>
+      <c r="B396" s="8" t="s">
+        <v>414</v>
+      </c>
+      <c r="C396" s="5">
+        <v>3</v>
+      </c>
+      <c r="D396" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="E396" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="F396" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G396" s="10">
+        <v>46034</v>
+      </c>
+    </row>
+    <row r="397" spans="1:7">
+      <c r="A397" s="4"/>
+      <c r="B397" s="8" t="s">
+        <v>414</v>
+      </c>
+      <c r="C397" s="5">
+        <v>3</v>
+      </c>
+      <c r="D397" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E397" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F397" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="G397" s="10">
         <v>46028</v>
       </c>
     </row>
-    <row r="395" spans="1:7">
-      <c r="A395" s="13"/>
-      <c r="B395" s="14" t="s">
-        <v>414</v>
-      </c>
-      <c r="C395" s="15">
-        <v>3</v>
-      </c>
-      <c r="D395" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="E395" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="F395" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G395" s="16">
+    <row r="398" spans="1:7">
+      <c r="A398" s="13"/>
+      <c r="B398" s="14" t="s">
+        <v>417</v>
+      </c>
+      <c r="C398" s="15">
+        <v>3</v>
+      </c>
+      <c r="D398" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E398" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F398" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="G398" s="16">
         <v>46028</v>
       </c>
     </row>

--- a/server/userPlan.xlsx
+++ b/server/userPlan.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29930"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4F8974BD-19DE-4609-8F2D-DCA841216AB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{57C6AAB2-873C-4167-B636-CC6C748C690A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1455" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1467" uniqueCount="460">
   <si>
     <t>id</t>
   </si>
@@ -54,6 +54,18 @@
     <t>created_at</t>
   </si>
   <si>
+    <t>AVG56814</t>
+  </si>
+  <si>
+    <t>$600</t>
+  </si>
+  <si>
+    <t>$3</t>
+  </si>
+  <si>
+    <t>active</t>
+  </si>
+  <si>
     <t>AVG56190</t>
   </si>
   <si>
@@ -63,9 +75,6 @@
     <t>$1</t>
   </si>
   <si>
-    <t>active</t>
-  </si>
-  <si>
     <t>AVG27912</t>
   </si>
   <si>
@@ -282,9 +291,6 @@
     <t>AVG68261</t>
   </si>
   <si>
-    <t>$600</t>
-  </si>
-  <si>
     <t>AVG07959</t>
   </si>
   <si>
@@ -490,9 +496,6 @@
   </si>
   <si>
     <t>AVG46702</t>
-  </si>
-  <si>
-    <t>$3</t>
   </si>
   <si>
     <t>AVG27381</t>
@@ -883,7 +886,7 @@
     <t>AVG04505</t>
   </si>
   <si>
-    <t>AVG46577</t>
+    <t>AVG46557</t>
   </si>
   <si>
     <t>AVG15814</t>
@@ -1394,6 +1397,9 @@
   </si>
   <si>
     <t>AVG46322</t>
+  </si>
+  <si>
+    <t>AVG97443</t>
   </si>
   <si>
     <t>AVG36108</t>
@@ -1497,7 +1503,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1520,11 +1526,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1595,6 +1627,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1881,8 +1919,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A068414D-D5DC-4F32-BF5C-C94883387B89}" name="Table1" displayName="Table1" ref="B1:G206" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" headerRowBorderDxfId="7" tableBorderDxfId="8" totalsRowBorderDxfId="6">
-  <autoFilter ref="B1:G206" xr:uid="{A068414D-D5DC-4F32-BF5C-C94883387B89}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A068414D-D5DC-4F32-BF5C-C94883387B89}" name="Table1" displayName="Table1" ref="B1:G208" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" headerRowBorderDxfId="7" tableBorderDxfId="8" totalsRowBorderDxfId="6">
+  <autoFilter ref="B1:G208" xr:uid="{A068414D-D5DC-4F32-BF5C-C94883387B89}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{0951C96C-A09F-46F0-B8A4-F44C57261DCE}" name="user_code" dataDxfId="5"/>
     <tableColumn id="2" xr3:uid="{44BDBE98-A9D7-43E3-8176-9D46CA8814FB}" name="plan_id" dataDxfId="4"/>
@@ -2192,7 +2230,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G411"/>
+  <dimension ref="A1:G414"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="4"/>
@@ -2230,7 +2268,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="1"/>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="26" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="1">
@@ -2251,13 +2289,13 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1"/>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="7" t="s">
         <v>11</v>
       </c>
       <c r="C3" s="1">
         <v>3</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>12</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -2267,7 +2305,7 @@
         <v>10</v>
       </c>
       <c r="G3" s="6">
-        <v>46118</v>
+        <v>46119</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -2278,11 +2316,11 @@
       <c r="C4" s="1">
         <v>3</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>12</v>
+      <c r="D4" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>10</v>
@@ -2294,16 +2332,16 @@
     <row r="5" spans="1:7">
       <c r="A5" s="1"/>
       <c r="B5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="1">
+        <v>3</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="1">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>10</v>
@@ -2354,7 +2392,7 @@
         <v>46118</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="14.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="1"/>
       <c r="B8" s="5" t="s">
         <v>24</v>
@@ -2371,11 +2409,12 @@
       <c r="F8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="8">
-        <v>46117</v>
+      <c r="G8" s="6">
+        <v>46118</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="14.25">
+      <c r="A9" s="1"/>
       <c r="B9" s="5" t="s">
         <v>27</v>
       </c>
@@ -2396,37 +2435,37 @@
       </c>
     </row>
     <row r="10" spans="1:7" ht="14.25">
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C10" s="1">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G10" s="8">
-        <v>46116</v>
+        <v>46117</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="14.25">
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="1">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="1">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="E11" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>10</v>
@@ -2436,17 +2475,17 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="14.25">
-      <c r="B12" s="7" t="s">
-        <v>32</v>
+      <c r="B12" s="5" t="s">
+        <v>34</v>
       </c>
       <c r="C12" s="1">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>10</v>
@@ -2457,16 +2496,16 @@
     </row>
     <row r="13" spans="1:7" ht="14.25">
       <c r="B13" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C13" s="1">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>10</v>
@@ -2477,22 +2516,22 @@
     </row>
     <row r="14" spans="1:7" ht="14.25">
       <c r="B14" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C14" s="1">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G14" s="8">
-        <v>46114</v>
+        <v>46116</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="14.25">
@@ -2503,10 +2542,10 @@
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>10</v>
@@ -2517,16 +2556,16 @@
     </row>
     <row r="16" spans="1:7" ht="14.25">
       <c r="B16" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C16" s="1">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>10</v>
@@ -2537,96 +2576,96 @@
     </row>
     <row r="17" spans="2:7" ht="14.25">
       <c r="B17" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C17" s="1">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G17" s="8">
-        <v>46113</v>
+        <v>46114</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="14.25">
       <c r="B18" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C18" s="1">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G18" s="8">
+        <v>46113</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" ht="14.25">
+      <c r="B19" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="1">
+        <v>3</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="8">
         <v>46118</v>
       </c>
     </row>
-    <row r="19" spans="2:7" ht="14.25">
-      <c r="B19" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19" s="1">
-        <v>3</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G19" s="8">
+    <row r="20" spans="2:7" ht="14.25">
+      <c r="B20" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="1">
+        <v>3</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="8">
         <v>46114</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" ht="14.25">
-      <c r="B20" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C20" s="1">
-        <v>3</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G20" s="8">
-        <v>46113</v>
       </c>
     </row>
     <row r="21" spans="2:7" ht="14.25">
       <c r="B21" s="7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C21" s="1">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>10</v>
@@ -2637,22 +2676,22 @@
     </row>
     <row r="22" spans="2:7" ht="14.25">
       <c r="B22" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C22" s="1">
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G22" s="8">
-        <v>46112</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="23" spans="2:7" ht="14.25">
@@ -2663,30 +2702,30 @@
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G23" s="8">
-        <v>46111</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="24" spans="2:7" ht="14.25">
       <c r="B24" s="7" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C24" s="1">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>10</v>
@@ -2697,16 +2736,16 @@
     </row>
     <row r="25" spans="2:7" ht="14.25">
       <c r="B25" s="7" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C25" s="1">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>10</v>
@@ -2717,16 +2756,16 @@
     </row>
     <row r="26" spans="2:7" ht="14.25">
       <c r="B26" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C26" s="1">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>10</v>
@@ -2737,85 +2776,85 @@
     </row>
     <row r="27" spans="2:7" ht="14.25">
       <c r="B27" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C27" s="1">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G27" s="8">
-        <v>46112</v>
+        <v>46111</v>
       </c>
     </row>
     <row r="28" spans="2:7" ht="14.25">
       <c r="B28" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C28" s="1">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G28" s="8">
-        <v>46110</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="29" spans="2:7" ht="14.25">
       <c r="B29" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C29" s="1">
         <v>3</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F29" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G29" s="8">
+        <v>46110</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" ht="14.25">
+      <c r="B30" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C30" s="1">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G30" s="8">
         <v>46109</v>
       </c>
     </row>
-    <row r="30" spans="2:7">
-      <c r="B30" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C30" s="1">
-        <v>3</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G30" s="9">
-        <v>46108</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7" ht="14.25">
+    <row r="31" spans="2:7">
       <c r="B31" s="7" t="s">
         <v>56</v>
       </c>
@@ -2823,30 +2862,30 @@
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G31" s="8">
+      <c r="G31" s="9">
         <v>46108</v>
       </c>
     </row>
     <row r="32" spans="2:7" ht="14.25">
       <c r="B32" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C32" s="1">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>10</v>
@@ -2857,36 +2896,36 @@
     </row>
     <row r="33" spans="2:7" ht="14.25">
       <c r="B33" s="7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C33" s="1">
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G33" s="8">
-        <v>46107</v>
+        <v>46108</v>
       </c>
     </row>
     <row r="34" spans="2:7" ht="14.25">
       <c r="B34" s="7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C34" s="1">
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>10</v>
@@ -2897,16 +2936,16 @@
     </row>
     <row r="35" spans="2:7" ht="14.25">
       <c r="B35" s="7" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C35" s="1">
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>10</v>
@@ -2917,36 +2956,36 @@
     </row>
     <row r="36" spans="2:7" ht="14.25">
       <c r="B36" s="7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C36" s="1">
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G36" s="8">
-        <v>46118</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="37" spans="2:7" ht="14.25">
       <c r="B37" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C37" s="1">
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>10</v>
@@ -2957,36 +2996,36 @@
     </row>
     <row r="38" spans="2:7" ht="14.25">
       <c r="B38" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C38" s="1">
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E38" s="1">
-        <v>5</v>
+        <v>15</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G38" s="8">
-        <v>46107</v>
+        <v>46118</v>
       </c>
     </row>
     <row r="39" spans="2:7" ht="14.25">
       <c r="B39" s="7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C39" s="1">
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>29</v>
+        <v>15</v>
+      </c>
+      <c r="E39" s="1">
+        <v>5</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>10</v>
@@ -2997,16 +3036,16 @@
     </row>
     <row r="40" spans="2:7" ht="14.25">
       <c r="B40" s="7" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C40" s="1">
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>10</v>
@@ -3017,22 +3056,22 @@
     </row>
     <row r="41" spans="2:7" ht="14.25">
       <c r="B41" s="7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C41" s="1">
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G41" s="8">
-        <v>46106</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="42" spans="2:7" ht="14.25">
@@ -3043,10 +3082,10 @@
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>28</v>
+        <v>70</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>10</v>
@@ -3057,16 +3096,16 @@
     </row>
     <row r="43" spans="2:7" ht="14.25">
       <c r="B43" s="7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C43" s="1">
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>10</v>
@@ -3077,36 +3116,36 @@
     </row>
     <row r="44" spans="2:7" ht="14.25">
       <c r="B44" s="7" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C44" s="1">
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G44" s="8">
-        <v>46105</v>
+        <v>46106</v>
       </c>
     </row>
     <row r="45" spans="2:7" ht="14.25">
       <c r="B45" s="7" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C45" s="1">
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>10</v>
@@ -3117,27 +3156,27 @@
     </row>
     <row r="46" spans="2:7" ht="14.25">
       <c r="B46" s="7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C46" s="1">
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G46" s="8">
-        <v>46104</v>
+        <v>46105</v>
       </c>
     </row>
     <row r="47" spans="2:7" ht="14.25">
       <c r="B47" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C47" s="1">
         <v>3</v>
@@ -3152,121 +3191,121 @@
         <v>10</v>
       </c>
       <c r="G47" s="8">
-        <v>46101</v>
+        <v>46104</v>
       </c>
     </row>
     <row r="48" spans="2:7" ht="14.25">
       <c r="B48" s="7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C48" s="1">
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G48" s="8">
-        <v>46102</v>
+        <v>46101</v>
       </c>
     </row>
     <row r="49" spans="2:7" ht="14.25">
       <c r="B49" s="7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C49" s="1">
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G49" s="8">
-        <v>46100</v>
+        <v>46102</v>
       </c>
     </row>
     <row r="50" spans="2:7" ht="14.25">
       <c r="B50" s="7" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C50" s="1">
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G50" s="8">
-        <v>46111</v>
+        <v>46100</v>
       </c>
     </row>
     <row r="51" spans="2:7" ht="14.25">
       <c r="B51" s="7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C51" s="1">
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G51" s="8">
-        <v>46099</v>
+        <v>46111</v>
       </c>
     </row>
     <row r="52" spans="2:7" ht="14.25">
       <c r="B52" s="7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C52" s="1">
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G52" s="8">
-        <v>46100</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="53" spans="2:7" ht="14.25">
       <c r="B53" s="7" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C53" s="1">
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>10</v>
@@ -3277,36 +3316,36 @@
     </row>
     <row r="54" spans="2:7" ht="14.25">
       <c r="B54" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C54" s="1">
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G54" s="8">
-        <v>46099</v>
+        <v>46100</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="14.25">
       <c r="B55" s="7" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C55" s="1">
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>10</v>
@@ -3317,16 +3356,16 @@
     </row>
     <row r="56" spans="2:7" ht="14.25">
       <c r="B56" s="7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C56" s="1">
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>10</v>
@@ -3337,16 +3376,16 @@
     </row>
     <row r="57" spans="2:7" ht="14.25">
       <c r="B57" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C57" s="1">
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>10</v>
@@ -3357,16 +3396,16 @@
     </row>
     <row r="58" spans="2:7" ht="14.25">
       <c r="B58" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C58" s="1">
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>10</v>
@@ -3377,16 +3416,16 @@
     </row>
     <row r="59" spans="2:7" ht="14.25">
       <c r="B59" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C59" s="1">
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>10</v>
@@ -3397,116 +3436,116 @@
     </row>
     <row r="60" spans="2:7" ht="14.25">
       <c r="B60" s="7" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C60" s="1">
         <v>3</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G60" s="8">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="61" spans="2:7" ht="14.25">
+      <c r="B61" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C61" s="1">
+        <v>3</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G61" s="8">
         <v>46100</v>
       </c>
     </row>
-    <row r="61" spans="2:7" ht="14.25">
-      <c r="B61" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="C61" s="1">
-        <v>3</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E61" s="1" t="s">
+    <row r="62" spans="2:7" ht="14.25">
+      <c r="B62" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="F61" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G61" s="8">
+      <c r="C62" s="1">
+        <v>3</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G62" s="8">
         <v>46099</v>
-      </c>
-    </row>
-    <row r="62" spans="2:7" ht="14.25">
-      <c r="B62" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C62" s="1">
-        <v>3</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G62" s="8">
-        <v>46098</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="14.25">
       <c r="B63" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C63" s="1">
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G63" s="8">
-        <v>46099</v>
+        <v>46098</v>
       </c>
     </row>
     <row r="64" spans="2:7" ht="14.25">
       <c r="B64" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C64" s="1">
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G64" s="8">
-        <v>46098</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="14.25">
       <c r="B65" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C65" s="1">
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>10</v>
@@ -3517,167 +3556,167 @@
     </row>
     <row r="66" spans="2:7" ht="14.25">
       <c r="B66" s="7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C66" s="1">
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G66" s="8">
-        <v>46099</v>
+        <v>46098</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="14.25">
       <c r="B67" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C67" s="1">
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G67" s="8">
-        <v>46097</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="68" spans="2:7" ht="14.25">
       <c r="B68" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C68" s="1">
         <v>3</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>98</v>
+        <v>28</v>
       </c>
       <c r="E68" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G68" s="8">
+        <v>46097</v>
+      </c>
+    </row>
+    <row r="69" spans="2:7" ht="14.25">
+      <c r="B69" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="F68" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G68" s="8">
+      <c r="C69" s="1">
+        <v>3</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G69" s="8">
         <v>46105</v>
       </c>
     </row>
-    <row r="69" spans="2:7" ht="14.25">
-      <c r="B69" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C69" s="1">
-        <v>3</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G69" s="8">
+    <row r="70" spans="2:7" ht="14.25">
+      <c r="B70" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C70" s="1">
+        <v>3</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G70" s="8">
         <v>46098</v>
-      </c>
-    </row>
-    <row r="70" spans="2:7" ht="14.25">
-      <c r="B70" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="C70" s="1">
-        <v>3</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G70" s="8">
-        <v>46099</v>
       </c>
     </row>
     <row r="71" spans="2:7" ht="14.25">
       <c r="B71" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C71" s="1">
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G71" s="8">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="72" spans="2:7" ht="14.25">
+      <c r="B72" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C72" s="1">
+        <v>3</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G72" s="8">
         <v>46105</v>
-      </c>
-    </row>
-    <row r="72" spans="2:7" ht="14.25">
-      <c r="B72" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="C72" s="1">
-        <v>3</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G72" s="8">
-        <v>46103</v>
       </c>
     </row>
     <row r="73" spans="2:7" ht="14.25">
       <c r="B73" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C73" s="1">
         <v>3</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>102</v>
+        <v>22</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>103</v>
+        <v>23</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G73" s="8">
-        <v>46102</v>
+        <v>46103</v>
       </c>
     </row>
     <row r="74" spans="2:7" ht="14.25">
       <c r="B74" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C74" s="1">
         <v>3</v>
@@ -3692,101 +3731,101 @@
         <v>10</v>
       </c>
       <c r="G74" s="8">
-        <v>46099</v>
+        <v>46102</v>
       </c>
     </row>
     <row r="75" spans="2:7" ht="14.25">
       <c r="B75" s="5" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C75" s="1">
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>8</v>
+        <v>106</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>9</v>
+        <v>107</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G75" s="8">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="76" spans="2:7" ht="14.25">
+      <c r="B76" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C76" s="1">
+        <v>3</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G76" s="8">
         <v>46097</v>
-      </c>
-    </row>
-    <row r="76" spans="2:7" ht="14.25">
-      <c r="B76" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="C76" s="1">
-        <v>3</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="F76" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G76" s="8">
-        <v>46096</v>
       </c>
     </row>
     <row r="77" spans="2:7" ht="14.25">
       <c r="B77" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C77" s="1">
+        <v>3</v>
+      </c>
+      <c r="D77" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="C77" s="1">
-        <v>3</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="E77" s="1" t="s">
-        <v>29</v>
+        <v>110</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G77" s="8">
-        <v>46097</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="78" spans="2:7" ht="14.25">
       <c r="B78" s="7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C78" s="1">
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G78" s="8">
-        <v>46095</v>
+        <v>46097</v>
       </c>
     </row>
     <row r="79" spans="2:7" ht="14.25">
       <c r="B79" s="7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C79" s="1">
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>10</v>
@@ -3797,96 +3836,96 @@
     </row>
     <row r="80" spans="2:7" ht="14.25">
       <c r="B80" s="7" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C80" s="1">
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G80" s="8">
-        <v>46106</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="81" spans="2:7" ht="14.25">
       <c r="B81" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C81" s="1">
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G81" s="8">
-        <v>46095</v>
+        <v>46106</v>
       </c>
     </row>
     <row r="82" spans="2:7" ht="14.25">
       <c r="B82" s="7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C82" s="1">
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G82" s="8">
-        <v>46101</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="83" spans="2:7" ht="14.25">
       <c r="B83" s="7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C83" s="1">
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G83" s="8">
-        <v>46095</v>
+        <v>46101</v>
       </c>
     </row>
     <row r="84" spans="2:7" ht="14.25">
       <c r="B84" s="7" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C84" s="1">
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>10</v>
@@ -3897,16 +3936,16 @@
     </row>
     <row r="85" spans="2:7" ht="14.25">
       <c r="B85" s="7" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C85" s="1">
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>10</v>
@@ -3917,16 +3956,16 @@
     </row>
     <row r="86" spans="2:7" ht="14.25">
       <c r="B86" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C86" s="1">
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>10</v>
@@ -3937,96 +3976,96 @@
     </row>
     <row r="87" spans="2:7" ht="14.25">
       <c r="B87" s="7" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C87" s="1">
         <v>3</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G87" s="8">
+        <v>46095</v>
+      </c>
+    </row>
+    <row r="88" spans="2:7" ht="14.25">
+      <c r="B88" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C88" s="1">
+        <v>3</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G88" s="8">
         <v>46110</v>
-      </c>
-    </row>
-    <row r="88" spans="2:7" ht="14.25">
-      <c r="B88" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="C88" s="1">
-        <v>3</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="F88" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G88" s="8">
-        <v>46098</v>
       </c>
     </row>
     <row r="89" spans="2:7" ht="14.25">
       <c r="B89" s="5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C89" s="1">
         <v>3</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>28</v>
+        <v>122</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>29</v>
+        <v>105</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G89" s="8">
+        <v>46098</v>
+      </c>
+    </row>
+    <row r="90" spans="2:7" ht="14.25">
+      <c r="B90" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C90" s="1">
+        <v>3</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G90" s="8">
         <v>46095</v>
-      </c>
-    </row>
-    <row r="90" spans="2:7" ht="14.25">
-      <c r="B90" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="C90" s="1">
-        <v>3</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="F90" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G90" s="8">
-        <v>46094</v>
       </c>
     </row>
     <row r="91" spans="2:7" ht="14.25">
       <c r="B91" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C91" s="1">
+        <v>3</v>
+      </c>
+      <c r="D91" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C91" s="1">
-        <v>3</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="E91" s="1" t="s">
-        <v>29</v>
+        <v>125</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>10</v>
@@ -4037,16 +4076,16 @@
     </row>
     <row r="92" spans="2:7" ht="14.25">
       <c r="B92" s="7" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C92" s="1">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>10</v>
@@ -4057,16 +4096,16 @@
     </row>
     <row r="93" spans="2:7" ht="14.25">
       <c r="B93" s="7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C93" s="1">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>10</v>
@@ -4077,16 +4116,16 @@
     </row>
     <row r="94" spans="2:7" ht="14.25">
       <c r="B94" s="7" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C94" s="1">
         <v>3</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>128</v>
+        <v>31</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>129</v>
+        <v>32</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>10</v>
@@ -4097,16 +4136,16 @@
     </row>
     <row r="95" spans="2:7" ht="14.25">
       <c r="B95" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="C95" s="1">
+        <v>3</v>
+      </c>
+      <c r="D95" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C95" s="1">
-        <v>3</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="E95" s="1" t="s">
-        <v>29</v>
+        <v>131</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>10</v>
@@ -4117,96 +4156,96 @@
     </row>
     <row r="96" spans="2:7" ht="14.25">
       <c r="B96" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C96" s="1">
         <v>3</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G96" s="8">
+        <v>46094</v>
+      </c>
+    </row>
+    <row r="97" spans="2:7" ht="14.25">
+      <c r="B97" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="C97" s="1">
+        <v>3</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G97" s="8">
         <v>46096</v>
       </c>
     </row>
-    <row r="97" spans="2:7" ht="14.25">
-      <c r="B97" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="C97" s="1">
-        <v>3</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="F97" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G97" s="8">
+    <row r="98" spans="2:7" ht="14.25">
+      <c r="B98" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="C98" s="1">
+        <v>3</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G98" s="8">
         <v>46094</v>
       </c>
     </row>
-    <row r="98" spans="2:7" ht="14.25">
-      <c r="B98" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="C98" s="1">
-        <v>3</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F98" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G98" s="8">
+    <row r="99" spans="2:7" ht="14.25">
+      <c r="B99" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="C99" s="1">
+        <v>3</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G99" s="8">
         <v>46097</v>
       </c>
     </row>
-    <row r="99" spans="2:7" ht="14.25">
-      <c r="B99" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="C99" s="1">
-        <v>3</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E99" s="1" t="s">
+    <row r="100" spans="2:7" ht="14.25">
+      <c r="B100" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="F99" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G99" s="8">
-        <v>46094</v>
-      </c>
-    </row>
-    <row r="100" spans="2:7" ht="14.25">
-      <c r="B100" s="7" t="s">
+      <c r="C100" s="1">
+        <v>3</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="C100" s="1">
-        <v>3</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="E100" s="1" t="s">
-        <v>29</v>
+        <v>136</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>10</v>
@@ -4216,27 +4255,27 @@
       </c>
     </row>
     <row r="101" spans="2:7" ht="14.25">
-      <c r="B101" s="5" t="s">
-        <v>135</v>
+      <c r="B101" s="7" t="s">
+        <v>137</v>
       </c>
       <c r="C101" s="1">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>136</v>
+        <v>10</v>
       </c>
       <c r="G101" s="8">
         <v>46094</v>
       </c>
     </row>
     <row r="102" spans="2:7" ht="14.25">
-      <c r="B102" s="7" t="s">
+      <c r="B102" s="5" t="s">
         <v>137</v>
       </c>
       <c r="C102" s="1">
@@ -4249,7 +4288,7 @@
         <v>13</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>10</v>
+        <v>138</v>
       </c>
       <c r="G102" s="8">
         <v>46094</v>
@@ -4257,16 +4296,16 @@
     </row>
     <row r="103" spans="2:7" ht="14.25">
       <c r="B103" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C103" s="1">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>10</v>
@@ -4277,156 +4316,156 @@
     </row>
     <row r="104" spans="2:7" ht="14.25">
       <c r="B104" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C104" s="1">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G104" s="8">
-        <v>46093</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="105" spans="2:7" ht="14.25">
       <c r="B105" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C105" s="1">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G105" s="8">
-        <v>46100</v>
+        <v>46093</v>
       </c>
     </row>
     <row r="106" spans="2:7" ht="14.25">
       <c r="B106" s="7" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C106" s="1">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G106" s="8">
-        <v>46092</v>
+        <v>46100</v>
       </c>
     </row>
     <row r="107" spans="2:7" ht="14.25">
       <c r="B107" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C107" s="1">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G107" s="8">
-        <v>46093</v>
+        <v>46092</v>
       </c>
     </row>
     <row r="108" spans="2:7" ht="14.25">
       <c r="B108" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C108" s="1">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G108" s="8">
-        <v>46092</v>
+        <v>46093</v>
       </c>
     </row>
     <row r="109" spans="2:7" ht="14.25">
       <c r="B109" s="7" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C109" s="1">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G109" s="8">
-        <v>46090</v>
+        <v>46092</v>
       </c>
     </row>
     <row r="110" spans="2:7" ht="14.25">
       <c r="B110" s="7" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C110" s="1">
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>146</v>
+        <v>31</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>147</v>
+        <v>32</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G110" s="8">
-        <v>46089</v>
+        <v>46090</v>
       </c>
     </row>
     <row r="111" spans="2:7" ht="14.25">
       <c r="B111" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C111" s="1">
+        <v>3</v>
+      </c>
+      <c r="D111" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="C111" s="1">
-        <v>3</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="E111" s="1" t="s">
-        <v>29</v>
+        <v>149</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>10</v>
@@ -4437,82 +4476,82 @@
     </row>
     <row r="112" spans="2:7" ht="14.25">
       <c r="B112" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C112" s="1">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G112" s="8">
-        <v>46088</v>
+        <v>46089</v>
       </c>
     </row>
     <row r="113" spans="2:7" ht="14.25">
       <c r="B113" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C113" s="1">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G113" s="8">
-        <v>46092</v>
+        <v>46088</v>
       </c>
     </row>
     <row r="114" spans="2:7" ht="14.25">
       <c r="B114" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C114" s="1">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G114" s="8">
-        <v>46088</v>
+        <v>46092</v>
       </c>
     </row>
     <row r="115" spans="2:7" ht="14.25">
       <c r="B115" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C115" s="1">
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>83</v>
+        <v>15</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>153</v>
+        <v>29</v>
       </c>
       <c r="F115" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G115" s="8">
-        <v>46103</v>
+        <v>46088</v>
       </c>
     </row>
     <row r="116" spans="2:7" ht="14.25">
@@ -4523,16 +4562,16 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G116" s="8">
-        <v>46090</v>
+        <v>46103</v>
       </c>
     </row>
     <row r="117" spans="2:7" ht="14.25">
@@ -4543,16 +4582,16 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G117" s="8">
-        <v>46087</v>
+        <v>46090</v>
       </c>
     </row>
     <row r="118" spans="2:7" ht="14.25">
@@ -4563,10 +4602,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>10</v>
@@ -4583,30 +4622,30 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>158</v>
+        <v>31</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>83</v>
+        <v>32</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G119" s="8">
-        <v>46088</v>
+        <v>46087</v>
       </c>
     </row>
     <row r="120" spans="2:7" ht="14.25">
       <c r="B120" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="C120" s="1">
+        <v>3</v>
+      </c>
+      <c r="D120" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="C120" s="1">
-        <v>3</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="E120" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>10</v>
@@ -4623,10 +4662,10 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>10</v>
@@ -4643,16 +4682,16 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G122" s="8">
-        <v>46094</v>
+        <v>46088</v>
       </c>
     </row>
     <row r="123" spans="2:7" ht="14.25">
@@ -4663,16 +4702,16 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G123" s="8">
-        <v>46086</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="124" spans="2:7" ht="14.25">
@@ -4683,10 +4722,10 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>153</v>
+        <v>39</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>10</v>
@@ -4703,16 +4742,16 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G125" s="8">
-        <v>46085</v>
+        <v>46086</v>
       </c>
     </row>
     <row r="126" spans="2:7" ht="14.25">
@@ -4723,10 +4762,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>10</v>
@@ -4743,10 +4782,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>10</v>
@@ -4763,10 +4802,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>10</v>
@@ -4783,10 +4822,10 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>10</v>
@@ -4803,16 +4842,16 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G130" s="8">
-        <v>46094</v>
+        <v>46085</v>
       </c>
     </row>
     <row r="131" spans="2:7" ht="14.25">
@@ -4823,16 +4862,16 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G131" s="8">
-        <v>46085</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="132" spans="2:7" ht="14.25">
@@ -4843,10 +4882,10 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>10</v>
@@ -4863,10 +4902,10 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>10</v>
@@ -4883,16 +4922,16 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G134" s="8">
-        <v>46084</v>
+        <v>46085</v>
       </c>
     </row>
     <row r="135" spans="2:7" ht="14.25">
@@ -4903,16 +4942,16 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>133</v>
+        <v>31</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>134</v>
+        <v>32</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G135" s="8">
-        <v>46085</v>
+        <v>46084</v>
       </c>
     </row>
     <row r="136" spans="2:7" ht="14.25">
@@ -4923,110 +4962,110 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>54</v>
+        <v>135</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>55</v>
+        <v>136</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G136" s="8">
+        <v>46085</v>
+      </c>
+    </row>
+    <row r="137" spans="2:7" ht="14.25">
+      <c r="B137" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="C137" s="1">
+        <v>3</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G137" s="8">
         <v>46118</v>
       </c>
     </row>
-    <row r="137" spans="2:7" ht="14.25">
-      <c r="B137" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="C137" s="1">
-        <v>3</v>
-      </c>
-      <c r="D137" s="1" t="s">
+    <row r="138" spans="2:7" ht="14.25">
+      <c r="B138" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="E137" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="F137" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G137" s="8">
+      <c r="C138" s="1">
+        <v>3</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G138" s="8">
         <v>46084</v>
       </c>
     </row>
-    <row r="138" spans="2:7" ht="14.25">
-      <c r="B138" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="C138" s="1">
-        <v>3</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E138" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F138" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G138" s="8">
+    <row r="139" spans="2:7" ht="14.25">
+      <c r="B139" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="C139" s="1">
+        <v>3</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G139" s="8">
         <v>46112</v>
-      </c>
-    </row>
-    <row r="139" spans="2:7" ht="14.25">
-      <c r="B139" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="C139" s="1">
-        <v>3</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E139" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F139" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G139" s="8">
-        <v>46095</v>
       </c>
     </row>
     <row r="140" spans="2:7" ht="14.25">
       <c r="B140" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C140" s="1">
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G140" s="8">
-        <v>46084</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="141" spans="2:7" ht="14.25">
-      <c r="B141" s="7" t="s">
+      <c r="B141" s="5" t="s">
         <v>178</v>
       </c>
       <c r="C141" s="1">
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>10</v>
@@ -5043,10 +5082,10 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>10</v>
@@ -5063,10 +5102,10 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>10</v>
@@ -5083,10 +5122,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>10</v>
@@ -5103,16 +5142,16 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G145" s="8">
-        <v>46098</v>
+        <v>46084</v>
       </c>
     </row>
     <row r="146" spans="2:7" ht="14.25">
@@ -5123,16 +5162,16 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G146" s="8">
-        <v>46086</v>
+        <v>46098</v>
       </c>
     </row>
     <row r="147" spans="2:7" ht="14.25">
@@ -5143,16 +5182,16 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G147" s="8">
-        <v>46099</v>
+        <v>46086</v>
       </c>
     </row>
     <row r="148" spans="2:7" ht="14.25">
@@ -5163,16 +5202,16 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G148" s="8">
-        <v>46082</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="149" spans="2:7" ht="14.25">
@@ -5183,56 +5222,56 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G149" s="8">
+        <v>46082</v>
+      </c>
+    </row>
+    <row r="150" spans="2:7" ht="14.25">
+      <c r="B150" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C150" s="1">
+        <v>3</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G150" s="8">
         <v>46103</v>
       </c>
     </row>
-    <row r="150" spans="2:7" ht="14.25">
-      <c r="B150" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="C150" s="1">
-        <v>3</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E150" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F150" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G150" s="8">
+    <row r="151" spans="2:7" ht="14.25">
+      <c r="B151" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="C151" s="1">
+        <v>3</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F151" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G151" s="8">
         <v>46095</v>
-      </c>
-    </row>
-    <row r="151" spans="2:7" ht="14.25">
-      <c r="B151" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="C151" s="1">
-        <v>3</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E151" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F151" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G151" s="8">
-        <v>46081</v>
       </c>
     </row>
     <row r="152" spans="2:7" ht="14.25">
@@ -5243,16 +5282,16 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G152" s="8">
-        <v>46080</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="153" spans="2:7" ht="14.25">
@@ -5263,10 +5302,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>10</v>
@@ -5283,10 +5322,10 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>10</v>
@@ -5303,16 +5342,16 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G155" s="8">
-        <v>46079</v>
+        <v>46080</v>
       </c>
     </row>
     <row r="156" spans="2:7" ht="14.25">
@@ -5323,10 +5362,10 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>10</v>
@@ -5343,10 +5382,10 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>10</v>
@@ -5363,10 +5402,10 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>10</v>
@@ -5383,10 +5422,10 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>10</v>
@@ -5403,10 +5442,10 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>10</v>
@@ -5423,73 +5462,73 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G161" s="8">
+        <v>46079</v>
+      </c>
+    </row>
+    <row r="162" spans="2:7" ht="14.25">
+      <c r="B162" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="C162" s="1">
+        <v>3</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E162" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F162" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G162" s="8">
         <v>46114</v>
-      </c>
-    </row>
-    <row r="162" spans="2:7" ht="14.25">
-      <c r="B162" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="C162" s="1">
-        <v>3</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E162" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F162" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="G162" s="8">
-        <v>46097</v>
       </c>
     </row>
     <row r="163" spans="2:7" ht="14.25">
       <c r="B163" s="5" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C163" s="1">
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G163" s="8">
-        <v>46079</v>
+        <v>46097</v>
       </c>
     </row>
     <row r="164" spans="2:7" ht="14.25">
-      <c r="B164" s="7" t="s">
+      <c r="B164" s="5" t="s">
         <v>198</v>
       </c>
       <c r="C164" s="1">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>10</v>
+        <v>138</v>
       </c>
       <c r="G164" s="8">
         <v>46079</v>
@@ -5503,10 +5542,10 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>10</v>
@@ -5523,10 +5562,10 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>10</v>
@@ -5543,10 +5582,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>10</v>
@@ -5563,56 +5602,56 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>120</v>
+        <v>15</v>
       </c>
       <c r="E168" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F168" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G168" s="8">
+        <v>46079</v>
+      </c>
+    </row>
+    <row r="169" spans="2:7" ht="14.25">
+      <c r="B169" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="F168" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G168" s="8">
+      <c r="C169" s="1">
+        <v>3</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G169" s="8">
         <v>46111</v>
       </c>
     </row>
-    <row r="169" spans="2:7" ht="14.25">
-      <c r="B169" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="C169" s="1">
-        <v>3</v>
-      </c>
-      <c r="D169" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E169" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F169" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="G169" s="8">
+    <row r="170" spans="2:7" ht="14.25">
+      <c r="B170" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="C170" s="1">
+        <v>3</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E170" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F170" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G170" s="8">
         <v>46083</v>
-      </c>
-    </row>
-    <row r="170" spans="2:7" ht="14.25">
-      <c r="B170" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="C170" s="1">
-        <v>3</v>
-      </c>
-      <c r="D170" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E170" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F170" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G170" s="8">
-        <v>46107</v>
       </c>
     </row>
     <row r="171" spans="2:7" ht="14.25">
@@ -5623,16 +5662,16 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G171" s="8">
-        <v>46079</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="172" spans="2:7" ht="14.25">
@@ -5643,36 +5682,36 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>207</v>
+        <v>31</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>208</v>
+        <v>32</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G172" s="8">
-        <v>46113</v>
+        <v>46079</v>
       </c>
     </row>
     <row r="173" spans="2:7" ht="14.25">
       <c r="B173" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="C173" s="1">
+        <v>3</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E173" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="C173" s="1">
-        <v>3</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E173" s="1" t="s">
-        <v>68</v>
-      </c>
       <c r="F173" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G173" s="8">
-        <v>46079</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="174" spans="2:7" ht="14.25">
@@ -5683,36 +5722,36 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>211</v>
+        <v>70</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>208</v>
+        <v>71</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G174" s="8">
-        <v>46113</v>
+        <v>46079</v>
       </c>
     </row>
     <row r="175" spans="2:7" ht="14.25">
       <c r="B175" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="C175" s="1">
+        <v>3</v>
+      </c>
+      <c r="D175" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C175" s="1">
-        <v>3</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>98</v>
-      </c>
       <c r="E175" s="1" t="s">
-        <v>99</v>
+        <v>209</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G175" s="8">
-        <v>46104</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="176" spans="2:7" ht="14.25">
@@ -5723,19 +5762,19 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>29</v>
+        <v>101</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>136</v>
+        <v>10</v>
       </c>
       <c r="G176" s="8">
         <v>46104</v>
       </c>
     </row>
-    <row r="177" spans="2:7" ht="14.25">
+    <row r="177" spans="2:7">
       <c r="B177" s="7" t="s">
         <v>214</v>
       </c>
@@ -5743,156 +5782,156 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>29</v>
+        <v>58</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G177" s="8">
-        <v>46078</v>
+      <c r="G177" s="27">
+        <v>46119</v>
       </c>
     </row>
     <row r="178" spans="2:7" ht="14.25">
       <c r="B178" s="7" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C178" s="1">
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>10</v>
+        <v>138</v>
       </c>
       <c r="G178" s="8">
-        <v>46078</v>
+        <v>46104</v>
       </c>
     </row>
     <row r="179" spans="2:7" ht="14.25">
       <c r="B179" s="7" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C179" s="1">
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G179" s="8">
-        <v>46081</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="180" spans="2:7" ht="14.25">
       <c r="B180" s="7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C180" s="1">
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G180" s="8">
-        <v>46077</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="181" spans="2:7" ht="14.25">
       <c r="B181" s="7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C181" s="1">
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G181" s="8">
-        <v>46077</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="182" spans="2:7" ht="14.25">
       <c r="B182" s="7" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C182" s="1">
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G182" s="8">
-        <v>46100</v>
+        <v>46077</v>
       </c>
     </row>
     <row r="183" spans="2:7" ht="14.25">
       <c r="B183" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="C183" s="1">
+        <v>3</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E183" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F183" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G183" s="8">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="184" spans="2:7" ht="14.25">
+      <c r="B184" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="C183" s="1">
-        <v>3</v>
-      </c>
-      <c r="D183" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E183" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F183" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G183" s="8">
-        <v>46093</v>
-      </c>
-    </row>
-    <row r="184" spans="2:7" ht="14.25">
-      <c r="B184" s="5" t="s">
-        <v>220</v>
-      </c>
       <c r="C184" s="1">
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G184" s="8">
-        <v>46077</v>
+        <v>46100</v>
       </c>
     </row>
     <row r="185" spans="2:7" ht="14.25">
@@ -5903,21 +5942,21 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G185" s="8">
-        <v>46077</v>
+        <v>46093</v>
       </c>
     </row>
     <row r="186" spans="2:7" ht="14.25">
-      <c r="B186" s="7" t="s">
-        <v>222</v>
+      <c r="B186" s="5" t="s">
+        <v>221</v>
       </c>
       <c r="C186" s="1">
         <v>3</v>
@@ -5937,16 +5976,16 @@
     </row>
     <row r="187" spans="2:7" ht="14.25">
       <c r="B187" s="7" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C187" s="1">
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>10</v>
@@ -5957,142 +5996,142 @@
     </row>
     <row r="188" spans="2:7" ht="14.25">
       <c r="B188" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="C188" s="1">
+        <v>3</v>
+      </c>
+      <c r="D188" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E188" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F188" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G188" s="8">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="189" spans="2:7" ht="14.25">
+      <c r="B189" s="7" t="s">
         <v>224</v>
       </c>
-      <c r="C188" s="1">
-        <v>3</v>
-      </c>
-      <c r="D188" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E188" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F188" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G188" s="8">
+      <c r="C189" s="1">
+        <v>3</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E189" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F189" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G189" s="8">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="190" spans="2:7" ht="14.25">
+      <c r="B190" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="C190" s="1">
+        <v>3</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E190" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F190" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G190" s="8">
         <v>46118</v>
-      </c>
-    </row>
-    <row r="189" spans="2:7" ht="14.25">
-      <c r="B189" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="C189" s="1">
-        <v>3</v>
-      </c>
-      <c r="D189" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E189" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F189" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G189" s="8">
-        <v>46097</v>
-      </c>
-    </row>
-    <row r="190" spans="2:7" ht="14.25">
-      <c r="B190" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="C190" s="1">
-        <v>3</v>
-      </c>
-      <c r="D190" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E190" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F190" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G190" s="8">
-        <v>46079</v>
       </c>
     </row>
     <row r="191" spans="2:7" ht="14.25">
       <c r="B191" s="5" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C191" s="1">
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G191" s="8">
+        <v>46097</v>
+      </c>
+    </row>
+    <row r="192" spans="2:7" ht="14.25">
+      <c r="B192" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="C192" s="1">
+        <v>3</v>
+      </c>
+      <c r="D192" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E192" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F192" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G192" s="8">
+        <v>46079</v>
+      </c>
+    </row>
+    <row r="193" spans="2:7" ht="14.25">
+      <c r="B193" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="C193" s="1">
+        <v>3</v>
+      </c>
+      <c r="D193" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E193" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F193" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G193" s="8">
         <v>46076</v>
       </c>
     </row>
-    <row r="192" spans="2:7" ht="14.25">
-      <c r="B192" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="C192" s="1">
-        <v>3</v>
-      </c>
-      <c r="D192" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E192" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F192" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G192" s="8">
+    <row r="194" spans="2:7" ht="14.25">
+      <c r="B194" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="C194" s="1">
+        <v>3</v>
+      </c>
+      <c r="D194" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E194" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F194" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G194" s="8">
         <v>46098</v>
-      </c>
-    </row>
-    <row r="193" spans="2:7" ht="14.25">
-      <c r="B193" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="C193" s="1">
-        <v>3</v>
-      </c>
-      <c r="D193" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E193" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F193" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G193" s="8">
-        <v>46115</v>
-      </c>
-    </row>
-    <row r="194" spans="2:7" ht="14.25">
-      <c r="B194" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="C194" s="1">
-        <v>3</v>
-      </c>
-      <c r="D194" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E194" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F194" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="G194" s="8">
-        <v>46075</v>
       </c>
     </row>
     <row r="195" spans="2:7" ht="14.25">
@@ -6103,96 +6142,96 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G195" s="8">
-        <v>46077</v>
+        <v>46115</v>
       </c>
     </row>
     <row r="196" spans="2:7" ht="14.25">
-      <c r="B196" s="7" t="s">
-        <v>228</v>
+      <c r="B196" s="5" t="s">
+        <v>227</v>
       </c>
       <c r="C196" s="1">
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>98</v>
+        <v>31</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>99</v>
+        <v>32</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>10</v>
+        <v>138</v>
       </c>
       <c r="G196" s="8">
-        <v>46093</v>
+        <v>46075</v>
       </c>
     </row>
     <row r="197" spans="2:7" ht="14.25">
       <c r="B197" s="7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C197" s="1">
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>13</v>
+        <v>58</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G197" s="8">
-        <v>46078</v>
+        <v>46077</v>
       </c>
     </row>
     <row r="198" spans="2:7" ht="14.25">
       <c r="B198" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="C198" s="1">
+        <v>3</v>
+      </c>
+      <c r="D198" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E198" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F198" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G198" s="8">
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="199" spans="2:7" ht="14.25">
+      <c r="B199" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="C198" s="1">
-        <v>3</v>
-      </c>
-      <c r="D198" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="E198" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="F198" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G198" s="8">
-        <v>46098</v>
-      </c>
-    </row>
-    <row r="199" spans="2:7" ht="14.25">
-      <c r="B199" s="5" t="s">
-        <v>230</v>
-      </c>
       <c r="C199" s="1">
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>136</v>
+        <v>10</v>
       </c>
       <c r="G199" s="8">
-        <v>46098</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="200" spans="2:7" ht="14.25">
@@ -6203,16 +6242,16 @@
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>28</v>
+        <v>122</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>29</v>
+        <v>204</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G200" s="8">
-        <v>46103</v>
+        <v>46098</v>
       </c>
     </row>
     <row r="201" spans="2:7" ht="14.25">
@@ -6223,110 +6262,110 @@
         <v>3</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>10</v>
+        <v>138</v>
       </c>
       <c r="G201" s="8">
+        <v>46098</v>
+      </c>
+    </row>
+    <row r="202" spans="2:7" ht="14.25">
+      <c r="B202" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="C202" s="1">
+        <v>3</v>
+      </c>
+      <c r="D202" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E202" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F202" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G202" s="8">
+        <v>46103</v>
+      </c>
+    </row>
+    <row r="203" spans="2:7" ht="14.25">
+      <c r="B203" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="C203" s="1">
+        <v>3</v>
+      </c>
+      <c r="D203" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E203" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F203" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G203" s="8">
         <v>46102</v>
       </c>
     </row>
-    <row r="202" spans="2:7" ht="14.25">
-      <c r="B202" s="5" t="s">
-        <v>231</v>
-      </c>
-      <c r="C202" s="1">
-        <v>3</v>
-      </c>
-      <c r="D202" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E202" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F202" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="G202" s="8">
+    <row r="204" spans="2:7" ht="14.25">
+      <c r="B204" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="C204" s="1">
+        <v>3</v>
+      </c>
+      <c r="D204" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E204" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F204" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G204" s="8">
         <v>46088</v>
-      </c>
-    </row>
-    <row r="203" spans="2:7" ht="14.25">
-      <c r="B203" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="C203" s="1">
-        <v>3</v>
-      </c>
-      <c r="D203" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E203" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="F203" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G203" s="8">
-        <v>46072</v>
-      </c>
-    </row>
-    <row r="204" spans="2:7" ht="14.25">
-      <c r="B204" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="C204" s="1">
-        <v>3</v>
-      </c>
-      <c r="D204" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E204" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F204" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G204" s="8">
-        <v>46070</v>
       </c>
     </row>
     <row r="205" spans="2:7" ht="14.25">
       <c r="B205" s="7" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C205" s="1">
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G205" s="8">
-        <v>46070</v>
+        <v>46072</v>
       </c>
     </row>
     <row r="206" spans="2:7" ht="14.25">
       <c r="B206" s="7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C206" s="1">
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>10</v>
@@ -6335,118 +6374,118 @@
         <v>46070</v>
       </c>
     </row>
-    <row r="207" spans="2:7">
-      <c r="B207" s="11" t="s">
+    <row r="207" spans="2:7" ht="14.25">
+      <c r="B207" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="C207" s="1">
+        <v>3</v>
+      </c>
+      <c r="D207" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E207" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F207" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G207" s="8">
+        <v>46070</v>
+      </c>
+    </row>
+    <row r="208" spans="2:7" ht="14.25">
+      <c r="B208" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="C207" s="10">
-        <v>3</v>
-      </c>
-      <c r="D207" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="E207" s="13">
+      <c r="C208" s="1">
+        <v>3</v>
+      </c>
+      <c r="D208" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E208" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F208" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G208" s="8">
+        <v>46070</v>
+      </c>
+    </row>
+    <row r="209" spans="2:7">
+      <c r="B209" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="C209" s="10">
+        <v>3</v>
+      </c>
+      <c r="D209" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E209" s="13">
         <v>5.5</v>
       </c>
-      <c r="F207" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G207" s="14" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="208" spans="2:7">
-      <c r="B208" s="10" t="s">
+      <c r="F209" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G209" s="14" t="s">
         <v>238</v>
       </c>
-      <c r="C208" s="10">
-        <v>3</v>
-      </c>
-      <c r="D208" s="12">
-        <v>100</v>
-      </c>
-      <c r="E208" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="F208" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G208" s="10" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="209" spans="2:7">
-      <c r="B209" s="10" t="s">
+    </row>
+    <row r="210" spans="2:7">
+      <c r="B210" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="C209" s="10">
-        <v>3</v>
-      </c>
-      <c r="D209" s="12">
-        <v>100</v>
-      </c>
-      <c r="E209" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="F209" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G209" s="10" t="s">
+      <c r="C210" s="10">
+        <v>3</v>
+      </c>
+      <c r="D210" s="12">
+        <v>100</v>
+      </c>
+      <c r="E210" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="F210" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G210" s="10" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="211" spans="2:7">
+      <c r="B211" s="10" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="210" spans="2:7">
-      <c r="B210" s="15" t="s">
+      <c r="C211" s="10">
+        <v>3</v>
+      </c>
+      <c r="D211" s="12">
+        <v>100</v>
+      </c>
+      <c r="E211" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="F211" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G211" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="C210" s="10">
-        <v>3</v>
-      </c>
-      <c r="D210" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="E210" s="16">
+    </row>
+    <row r="212" spans="2:7">
+      <c r="B212" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="C212" s="10">
+        <v>3</v>
+      </c>
+      <c r="D212" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="E212" s="16">
         <v>16</v>
-      </c>
-      <c r="F210" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G210" s="10" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="211" spans="2:7">
-      <c r="B211" s="15" t="s">
-        <v>241</v>
-      </c>
-      <c r="C211" s="10">
-        <v>3</v>
-      </c>
-      <c r="D211" s="12">
-        <v>300</v>
-      </c>
-      <c r="E211" s="13">
-        <v>1.5</v>
-      </c>
-      <c r="F211" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G211" s="17">
-        <v>46092</v>
-      </c>
-    </row>
-    <row r="212" spans="2:7">
-      <c r="B212" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="C212" s="10">
-        <v>3</v>
-      </c>
-      <c r="D212" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E212" s="12">
-        <v>5</v>
       </c>
       <c r="F212" s="10" t="s">
         <v>10</v>
@@ -6456,83 +6495,83 @@
       </c>
     </row>
     <row r="213" spans="2:7">
-      <c r="B213" s="10" t="s">
-        <v>241</v>
+      <c r="B213" s="15" t="s">
+        <v>242</v>
       </c>
       <c r="C213" s="10">
         <v>3</v>
       </c>
-      <c r="D213" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E213" s="12">
+      <c r="D213" s="12">
+        <v>300</v>
+      </c>
+      <c r="E213" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="F213" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G213" s="17">
+        <v>46092</v>
+      </c>
+    </row>
+    <row r="214" spans="2:7">
+      <c r="B214" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="C214" s="10">
+        <v>3</v>
+      </c>
+      <c r="D214" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E214" s="12">
         <v>5</v>
       </c>
-      <c r="F213" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G213" s="10" t="s">
+      <c r="F214" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G214" s="10" t="s">
         <v>244</v>
-      </c>
-    </row>
-    <row r="214" spans="2:7">
-      <c r="B214" s="15" t="s">
-        <v>241</v>
-      </c>
-      <c r="C214" s="10">
-        <v>3</v>
-      </c>
-      <c r="D214" s="12">
-        <v>100</v>
-      </c>
-      <c r="E214" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="F214" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G214" s="10" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="215" spans="2:7">
       <c r="B215" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="C215" s="10">
+        <v>3</v>
+      </c>
+      <c r="D215" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E215" s="12">
+        <v>5</v>
+      </c>
+      <c r="F215" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G215" s="10" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="216" spans="2:7">
+      <c r="B216" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="C216" s="10">
+        <v>3</v>
+      </c>
+      <c r="D216" s="12">
+        <v>100</v>
+      </c>
+      <c r="E216" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="F216" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G216" s="10" t="s">
         <v>246</v>
-      </c>
-      <c r="C215" s="10">
-        <v>3</v>
-      </c>
-      <c r="D215" s="12">
-        <v>100</v>
-      </c>
-      <c r="E215" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="F215" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G215" s="10" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="216" spans="2:7">
-      <c r="B216" s="10" t="s">
-        <v>247</v>
-      </c>
-      <c r="C216" s="10">
-        <v>3</v>
-      </c>
-      <c r="D216" s="12">
-        <v>300</v>
-      </c>
-      <c r="E216" s="13">
-        <v>1.5</v>
-      </c>
-      <c r="F216" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G216" s="10" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="217" spans="2:7">
@@ -6543,10 +6582,10 @@
         <v>3</v>
       </c>
       <c r="D217" s="12">
-        <v>600</v>
-      </c>
-      <c r="E217" s="12">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="E217" s="13">
+        <v>0.5</v>
       </c>
       <c r="F217" s="10" t="s">
         <v>10</v>
@@ -6556,17 +6595,17 @@
       </c>
     </row>
     <row r="218" spans="2:7">
-      <c r="B218" s="15" t="s">
-        <v>247</v>
+      <c r="B218" s="10" t="s">
+        <v>248</v>
       </c>
       <c r="C218" s="10">
         <v>3</v>
       </c>
       <c r="D218" s="12">
-        <v>400</v>
-      </c>
-      <c r="E218" s="12">
-        <v>2</v>
+        <v>300</v>
+      </c>
+      <c r="E218" s="13">
+        <v>1.5</v>
       </c>
       <c r="F218" s="10" t="s">
         <v>10</v>
@@ -6577,47 +6616,47 @@
     </row>
     <row r="219" spans="2:7">
       <c r="B219" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="C219" s="10">
+        <v>3</v>
+      </c>
+      <c r="D219" s="12">
+        <v>600</v>
+      </c>
+      <c r="E219" s="12">
+        <v>3</v>
+      </c>
+      <c r="F219" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G219" s="10" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="220" spans="2:7">
+      <c r="B220" s="15" t="s">
+        <v>248</v>
+      </c>
+      <c r="C220" s="10">
+        <v>3</v>
+      </c>
+      <c r="D220" s="12">
+        <v>400</v>
+      </c>
+      <c r="E220" s="12">
+        <v>2</v>
+      </c>
+      <c r="F220" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G220" s="10" t="s">
         <v>250</v>
-      </c>
-      <c r="C219" s="10">
-        <v>3</v>
-      </c>
-      <c r="D219" s="12">
-        <v>100</v>
-      </c>
-      <c r="E219" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="F219" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G219" s="10" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="220" spans="2:7">
-      <c r="B220" s="10" t="s">
-        <v>252</v>
-      </c>
-      <c r="C220" s="10">
-        <v>3</v>
-      </c>
-      <c r="D220" s="12">
-        <v>200</v>
-      </c>
-      <c r="E220" s="12">
-        <v>1</v>
-      </c>
-      <c r="F220" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G220" s="10" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="221" spans="2:7">
       <c r="B221" s="10" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C221" s="10">
         <v>3</v>
@@ -6632,92 +6671,92 @@
         <v>10</v>
       </c>
       <c r="G221" s="10" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="222" spans="2:7">
       <c r="B222" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="C222" s="10">
+        <v>3</v>
+      </c>
+      <c r="D222" s="12">
+        <v>200</v>
+      </c>
+      <c r="E222" s="12">
+        <v>1</v>
+      </c>
+      <c r="F222" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G222" s="10" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="223" spans="2:7">
+      <c r="B223" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="C222" s="10">
-        <v>3</v>
-      </c>
-      <c r="D222" s="12">
-        <v>100</v>
-      </c>
-      <c r="E222" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="F222" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G222" s="10" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="223" spans="2:7">
-      <c r="B223" s="15" t="s">
-        <v>254</v>
-      </c>
       <c r="C223" s="10">
         <v>3</v>
       </c>
-      <c r="D223" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E223" s="12">
-        <v>5</v>
+      <c r="D223" s="12">
+        <v>100</v>
+      </c>
+      <c r="E223" s="13">
+        <v>0.5</v>
       </c>
       <c r="F223" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G223" s="10" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
     </row>
     <row r="224" spans="2:7">
       <c r="B224" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="C224" s="10">
+        <v>3</v>
+      </c>
+      <c r="D224" s="12">
+        <v>100</v>
+      </c>
+      <c r="E224" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="F224" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G224" s="10" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="225" spans="2:7">
+      <c r="B225" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="C225" s="10">
+        <v>3</v>
+      </c>
+      <c r="D225" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E225" s="12">
+        <v>5</v>
+      </c>
+      <c r="F225" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G225" s="10" t="s">
         <v>257</v>
-      </c>
-      <c r="C224" s="10">
-        <v>3</v>
-      </c>
-      <c r="D224" s="12">
-        <v>100</v>
-      </c>
-      <c r="E224" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="F224" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G224" s="17">
-        <v>46056</v>
-      </c>
-    </row>
-    <row r="225" spans="2:7">
-      <c r="B225" s="10" t="s">
-        <v>258</v>
-      </c>
-      <c r="C225" s="10">
-        <v>3</v>
-      </c>
-      <c r="D225" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="E225" s="12">
-        <v>11</v>
-      </c>
-      <c r="F225" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G225" s="10" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="226" spans="2:7">
       <c r="B226" s="10" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C226" s="10">
         <v>3</v>
@@ -6731,28 +6770,28 @@
       <c r="F226" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G226" s="10" t="s">
-        <v>248</v>
+      <c r="G226" s="17">
+        <v>46056</v>
       </c>
     </row>
     <row r="227" spans="2:7">
       <c r="B227" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="C227" s="10">
+        <v>3</v>
+      </c>
+      <c r="D227" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E227" s="12">
+        <v>11</v>
+      </c>
+      <c r="F227" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G227" s="10" t="s">
         <v>260</v>
-      </c>
-      <c r="C227" s="10">
-        <v>3</v>
-      </c>
-      <c r="D227" s="12">
-        <v>200</v>
-      </c>
-      <c r="E227" s="12">
-        <v>1</v>
-      </c>
-      <c r="F227" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="G227" s="10" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="228" spans="2:7">
@@ -6772,12 +6811,12 @@
         <v>10</v>
       </c>
       <c r="G228" s="10" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
     </row>
     <row r="229" spans="2:7">
       <c r="B229" s="10" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C229" s="10">
         <v>3</v>
@@ -6789,15 +6828,15 @@
         <v>1</v>
       </c>
       <c r="F229" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G229" s="17">
-        <v>46056</v>
+        <v>138</v>
+      </c>
+      <c r="G229" s="10" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="230" spans="2:7">
       <c r="B230" s="10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C230" s="10">
         <v>3</v>
@@ -6812,27 +6851,27 @@
         <v>10</v>
       </c>
       <c r="G230" s="10" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
     </row>
     <row r="231" spans="2:7">
       <c r="B231" s="10" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C231" s="10">
         <v>3</v>
       </c>
-      <c r="D231" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="E231" s="13">
-        <v>19.5</v>
+      <c r="D231" s="12">
+        <v>200</v>
+      </c>
+      <c r="E231" s="12">
+        <v>1</v>
       </c>
       <c r="F231" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G231" s="17">
-        <v>46176</v>
+        <v>46056</v>
       </c>
     </row>
     <row r="232" spans="2:7">
@@ -6852,32 +6891,32 @@
         <v>10</v>
       </c>
       <c r="G232" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="233" spans="2:7">
       <c r="B233" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="C233" s="10">
+        <v>3</v>
+      </c>
+      <c r="D233" s="12" t="s">
         <v>266</v>
       </c>
-      <c r="C233" s="10">
-        <v>3</v>
-      </c>
-      <c r="D233" s="12">
-        <v>100</v>
-      </c>
       <c r="E233" s="13">
-        <v>0.5</v>
+        <v>19.5</v>
       </c>
       <c r="F233" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G233" s="10" t="s">
-        <v>249</v>
+      <c r="G233" s="17">
+        <v>46176</v>
       </c>
     </row>
     <row r="234" spans="2:7">
       <c r="B234" s="10" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C234" s="10">
         <v>3</v>
@@ -6891,33 +6930,33 @@
       <c r="F234" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G234" s="17">
-        <v>46065</v>
+      <c r="G234" s="10" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="235" spans="2:7">
       <c r="B235" s="10" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C235" s="10">
         <v>3</v>
       </c>
-      <c r="D235" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="E235" s="12">
-        <v>10</v>
+      <c r="D235" s="12">
+        <v>100</v>
+      </c>
+      <c r="E235" s="13">
+        <v>0.5</v>
       </c>
       <c r="F235" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G235" s="17">
-        <v>46065</v>
+      <c r="G235" s="10" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="236" spans="2:7">
       <c r="B236" s="10" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C236" s="10">
         <v>3</v>
@@ -6937,27 +6976,27 @@
     </row>
     <row r="237" spans="2:7">
       <c r="B237" s="10" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C237" s="10">
         <v>3</v>
       </c>
-      <c r="D237" s="12">
-        <v>100</v>
-      </c>
-      <c r="E237" s="13">
-        <v>0.5</v>
+      <c r="D237" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E237" s="12">
+        <v>10</v>
       </c>
       <c r="F237" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G237" s="17">
-        <v>46071</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="238" spans="2:7">
       <c r="B238" s="10" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C238" s="10">
         <v>3</v>
@@ -6971,33 +7010,33 @@
       <c r="F238" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G238" s="10" t="s">
-        <v>249</v>
+      <c r="G238" s="17">
+        <v>46065</v>
       </c>
     </row>
     <row r="239" spans="2:7">
       <c r="B239" s="10" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C239" s="10">
         <v>3</v>
       </c>
       <c r="D239" s="12">
-        <v>200</v>
-      </c>
-      <c r="E239" s="12">
-        <v>1</v>
+        <v>100</v>
+      </c>
+      <c r="E239" s="13">
+        <v>0.5</v>
       </c>
       <c r="F239" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G239" s="10" t="s">
-        <v>240</v>
+      <c r="G239" s="17">
+        <v>46071</v>
       </c>
     </row>
     <row r="240" spans="2:7">
       <c r="B240" s="10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="C240" s="10">
         <v>3</v>
@@ -7012,32 +7051,32 @@
         <v>10</v>
       </c>
       <c r="G240" s="10" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
     </row>
     <row r="241" spans="2:7">
       <c r="B241" s="10" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C241" s="10">
         <v>3</v>
       </c>
       <c r="D241" s="12">
-        <v>500</v>
-      </c>
-      <c r="E241" s="13">
-        <v>2.5</v>
+        <v>200</v>
+      </c>
+      <c r="E241" s="12">
+        <v>1</v>
       </c>
       <c r="F241" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G241" s="17">
-        <v>46064</v>
+      <c r="G241" s="10" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="242" spans="2:7">
       <c r="B242" s="10" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C242" s="10">
         <v>3</v>
@@ -7052,67 +7091,67 @@
         <v>10</v>
       </c>
       <c r="G242" s="10" t="s">
-        <v>276</v>
+        <v>241</v>
       </c>
     </row>
     <row r="243" spans="2:7">
       <c r="B243" s="10" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C243" s="10">
         <v>3</v>
       </c>
       <c r="D243" s="12">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E243" s="13">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="F243" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G243" s="10" t="s">
-        <v>278</v>
+      <c r="G243" s="17">
+        <v>46064</v>
       </c>
     </row>
     <row r="244" spans="2:7">
       <c r="B244" s="10" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C244" s="10">
         <v>3</v>
       </c>
       <c r="D244" s="12">
-        <v>600</v>
-      </c>
-      <c r="E244" s="12">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="E244" s="13">
+        <v>0.5</v>
       </c>
       <c r="F244" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G244" s="10" t="s">
-        <v>248</v>
+        <v>277</v>
       </c>
     </row>
     <row r="245" spans="2:7">
       <c r="B245" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="C245" s="10">
+        <v>3</v>
+      </c>
+      <c r="D245" s="12">
+        <v>100</v>
+      </c>
+      <c r="E245" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="F245" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G245" s="10" t="s">
         <v>279</v>
-      </c>
-      <c r="C245" s="10">
-        <v>3</v>
-      </c>
-      <c r="D245" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="E245" s="12">
-        <v>9</v>
-      </c>
-      <c r="F245" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G245" s="17">
-        <v>46064</v>
       </c>
     </row>
     <row r="246" spans="2:7">
@@ -7123,30 +7162,30 @@
         <v>3</v>
       </c>
       <c r="D246" s="12">
-        <v>100</v>
-      </c>
-      <c r="E246" s="13">
-        <v>0.5</v>
+        <v>600</v>
+      </c>
+      <c r="E246" s="12">
+        <v>3</v>
       </c>
       <c r="F246" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G246" s="10" t="s">
-        <v>281</v>
+        <v>249</v>
       </c>
     </row>
     <row r="247" spans="2:7">
       <c r="B247" s="10" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C247" s="10">
         <v>3</v>
       </c>
-      <c r="D247" s="12">
-        <v>100</v>
-      </c>
-      <c r="E247" s="13">
-        <v>0.5</v>
+      <c r="D247" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="E247" s="12">
+        <v>9</v>
       </c>
       <c r="F247" s="10" t="s">
         <v>10</v>
@@ -7157,27 +7196,27 @@
     </row>
     <row r="248" spans="2:7">
       <c r="B248" s="10" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C248" s="10">
         <v>3</v>
       </c>
       <c r="D248" s="12">
-        <v>600</v>
-      </c>
-      <c r="E248" s="12">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="E248" s="13">
+        <v>0.5</v>
       </c>
       <c r="F248" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G248" s="17">
-        <v>46328</v>
+      <c r="G248" s="10" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="249" spans="2:7">
       <c r="B249" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C249" s="10">
         <v>3</v>
@@ -7191,33 +7230,33 @@
       <c r="F249" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G249" s="10" t="s">
-        <v>285</v>
+      <c r="G249" s="17">
+        <v>46064</v>
       </c>
     </row>
     <row r="250" spans="2:7">
       <c r="B250" s="10" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C250" s="10">
         <v>3</v>
       </c>
       <c r="D250" s="12">
-        <v>100</v>
-      </c>
-      <c r="E250" s="13">
-        <v>0.5</v>
+        <v>600</v>
+      </c>
+      <c r="E250" s="12">
+        <v>3</v>
       </c>
       <c r="F250" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G250" s="17">
-        <v>46065</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="251" spans="2:7">
       <c r="B251" s="10" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C251" s="10">
         <v>3</v>
@@ -7232,32 +7271,32 @@
         <v>10</v>
       </c>
       <c r="G251" s="10" t="s">
-        <v>245</v>
+        <v>286</v>
       </c>
     </row>
     <row r="252" spans="2:7">
       <c r="B252" s="10" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C252" s="10">
         <v>3</v>
       </c>
-      <c r="D252" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E252" s="12">
-        <v>5</v>
+      <c r="D252" s="12">
+        <v>100</v>
+      </c>
+      <c r="E252" s="13">
+        <v>0.5</v>
       </c>
       <c r="F252" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G252" s="10" t="s">
-        <v>285</v>
+      <c r="G252" s="17">
+        <v>46065</v>
       </c>
     </row>
     <row r="253" spans="2:7">
       <c r="B253" s="10" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C253" s="10">
         <v>3</v>
@@ -7271,33 +7310,33 @@
       <c r="F253" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G253" s="18" t="s">
-        <v>281</v>
+      <c r="G253" s="10" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="254" spans="2:7">
       <c r="B254" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C254" s="10">
         <v>3</v>
       </c>
-      <c r="D254" s="12">
-        <v>100</v>
-      </c>
-      <c r="E254" s="13">
-        <v>0.5</v>
+      <c r="D254" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E254" s="12">
+        <v>5</v>
       </c>
       <c r="F254" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G254" s="10" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
     </row>
     <row r="255" spans="2:7">
       <c r="B255" s="10" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C255" s="10">
         <v>3</v>
@@ -7311,13 +7350,13 @@
       <c r="F255" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G255" s="10" t="s">
-        <v>244</v>
+      <c r="G255" s="18" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="256" spans="2:7">
       <c r="B256" s="10" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="C256" s="10">
         <v>3</v>
@@ -7331,13 +7370,13 @@
       <c r="F256" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G256" s="18" t="s">
-        <v>259</v>
+      <c r="G256" s="10" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="257" spans="2:7">
       <c r="B257" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C257" s="10">
         <v>3</v>
@@ -7352,12 +7391,12 @@
         <v>10</v>
       </c>
       <c r="G257" s="10" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
     </row>
     <row r="258" spans="2:7">
       <c r="B258" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C258" s="10">
         <v>3</v>
@@ -7371,13 +7410,13 @@
       <c r="F258" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G258" s="10" t="s">
-        <v>249</v>
+      <c r="G258" s="18" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="259" spans="2:7">
       <c r="B259" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C259" s="10">
         <v>3</v>
@@ -7392,27 +7431,27 @@
         <v>10</v>
       </c>
       <c r="G259" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="260" spans="2:7">
       <c r="B260" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C260" s="10">
         <v>3</v>
       </c>
       <c r="D260" s="12">
-        <v>400</v>
-      </c>
-      <c r="E260" s="10">
-        <v>2</v>
+        <v>100</v>
+      </c>
+      <c r="E260" s="13">
+        <v>0.5</v>
       </c>
       <c r="F260" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G260" s="10" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
     </row>
     <row r="261" spans="2:7">
@@ -7423,61 +7462,61 @@
         <v>3</v>
       </c>
       <c r="D261" s="12">
-        <v>400</v>
-      </c>
-      <c r="E261" s="10">
-        <v>2</v>
+        <v>100</v>
+      </c>
+      <c r="E261" s="13">
+        <v>0.5</v>
       </c>
       <c r="F261" s="10" t="s">
-        <v>136</v>
+        <v>10</v>
       </c>
       <c r="G261" s="10" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
     </row>
     <row r="262" spans="2:7">
       <c r="B262" s="10" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C262" s="10">
         <v>3</v>
       </c>
       <c r="D262" s="12">
-        <v>100</v>
-      </c>
-      <c r="E262" s="13">
-        <v>0.5</v>
+        <v>400</v>
+      </c>
+      <c r="E262" s="10">
+        <v>2</v>
       </c>
       <c r="F262" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="G262" s="18" t="s">
-        <v>298</v>
+        <v>10</v>
+      </c>
+      <c r="G262" s="10" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="263" spans="2:7">
       <c r="B263" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C263" s="10">
         <v>3</v>
       </c>
       <c r="D263" s="12">
-        <v>100</v>
-      </c>
-      <c r="E263" s="13">
-        <v>0.5</v>
+        <v>400</v>
+      </c>
+      <c r="E263" s="10">
+        <v>2</v>
       </c>
       <c r="F263" s="10" t="s">
-        <v>10</v>
+        <v>138</v>
       </c>
       <c r="G263" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="264" spans="2:7">
       <c r="B264" s="10" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C264" s="10">
         <v>3</v>
@@ -7489,15 +7528,15 @@
         <v>0.5</v>
       </c>
       <c r="F264" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G264" s="10" t="s">
-        <v>259</v>
+        <v>138</v>
+      </c>
+      <c r="G264" s="18" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="265" spans="2:7">
       <c r="B265" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C265" s="10">
         <v>3</v>
@@ -7512,12 +7551,12 @@
         <v>10</v>
       </c>
       <c r="G265" s="10" t="s">
-        <v>302</v>
+        <v>252</v>
       </c>
     </row>
     <row r="266" spans="2:7">
       <c r="B266" s="10" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="C266" s="10">
         <v>3</v>
@@ -7532,92 +7571,92 @@
         <v>10</v>
       </c>
       <c r="G266" s="10" t="s">
-        <v>304</v>
+        <v>260</v>
       </c>
     </row>
     <row r="267" spans="2:7">
       <c r="B267" s="10" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C267" s="10">
         <v>3</v>
       </c>
       <c r="D267" s="12">
-        <v>200</v>
-      </c>
-      <c r="E267" s="12">
-        <v>1</v>
+        <v>100</v>
+      </c>
+      <c r="E267" s="13">
+        <v>0.5</v>
       </c>
       <c r="F267" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G267" s="10" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
     </row>
     <row r="268" spans="2:7">
       <c r="B268" s="10" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C268" s="10">
         <v>3</v>
       </c>
-      <c r="D268" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E268" s="12">
-        <v>5</v>
+      <c r="D268" s="12">
+        <v>100</v>
+      </c>
+      <c r="E268" s="13">
+        <v>0.5</v>
       </c>
       <c r="F268" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G268" s="10" t="s">
-        <v>259</v>
+        <v>305</v>
       </c>
     </row>
     <row r="269" spans="2:7">
       <c r="B269" s="10" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C269" s="10">
         <v>3</v>
       </c>
       <c r="D269" s="12">
-        <v>100</v>
-      </c>
-      <c r="E269" s="13">
-        <v>0.5</v>
+        <v>200</v>
+      </c>
+      <c r="E269" s="12">
+        <v>1</v>
       </c>
       <c r="F269" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G269" s="10" t="s">
-        <v>285</v>
+        <v>299</v>
       </c>
     </row>
     <row r="270" spans="2:7">
       <c r="B270" s="10" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C270" s="10">
         <v>3</v>
       </c>
-      <c r="D270" s="12">
-        <v>100</v>
-      </c>
-      <c r="E270" s="13">
-        <v>0.5</v>
+      <c r="D270" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E270" s="12">
+        <v>5</v>
       </c>
       <c r="F270" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G270" s="10" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
     </row>
     <row r="271" spans="2:7">
       <c r="B271" s="10" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="C271" s="10">
         <v>3</v>
@@ -7632,12 +7671,12 @@
         <v>10</v>
       </c>
       <c r="G271" s="10" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
     </row>
     <row r="272" spans="2:7">
       <c r="B272" s="10" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C272" s="10">
         <v>3</v>
@@ -7651,13 +7690,13 @@
       <c r="F272" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G272" s="17">
-        <v>46056</v>
+      <c r="G272" s="10" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="273" spans="2:7">
       <c r="B273" s="10" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C273" s="10">
         <v>3</v>
@@ -7671,33 +7710,33 @@
       <c r="F273" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G273" s="18" t="s">
-        <v>298</v>
+      <c r="G273" s="10" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="274" spans="2:7">
       <c r="B274" s="10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C274" s="10">
         <v>3</v>
       </c>
       <c r="D274" s="12">
-        <v>600</v>
-      </c>
-      <c r="E274" s="12">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="E274" s="13">
+        <v>0.5</v>
       </c>
       <c r="F274" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G274" s="18" t="s">
-        <v>249</v>
+      <c r="G274" s="17">
+        <v>46056</v>
       </c>
     </row>
     <row r="275" spans="2:7">
       <c r="B275" s="10" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C275" s="10">
         <v>3</v>
@@ -7711,93 +7750,93 @@
       <c r="F275" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G275" s="17">
-        <v>46065</v>
+      <c r="G275" s="18" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="276" spans="2:7">
       <c r="B276" s="10" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C276" s="10">
         <v>3</v>
       </c>
       <c r="D276" s="12">
-        <v>500</v>
-      </c>
-      <c r="E276" s="13">
-        <v>2.5</v>
+        <v>600</v>
+      </c>
+      <c r="E276" s="12">
+        <v>3</v>
       </c>
       <c r="F276" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G276" s="18" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
     </row>
     <row r="277" spans="2:7">
       <c r="B277" s="10" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="C277" s="10">
         <v>3</v>
       </c>
       <c r="D277" s="12">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="E277" s="13">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="F277" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G277" s="10" t="s">
-        <v>249</v>
+      <c r="G277" s="17">
+        <v>46065</v>
       </c>
     </row>
     <row r="278" spans="2:7">
       <c r="B278" s="10" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C278" s="10">
         <v>3</v>
       </c>
       <c r="D278" s="12">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E278" s="13">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="F278" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G278" s="17">
-        <v>46065</v>
+      <c r="G278" s="18" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="279" spans="2:7">
       <c r="B279" s="10" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C279" s="10">
         <v>3</v>
       </c>
       <c r="D279" s="12">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E279" s="13">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="F279" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G279" s="10" t="s">
-        <v>304</v>
+        <v>250</v>
       </c>
     </row>
     <row r="280" spans="2:7">
       <c r="B280" s="10" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C280" s="10">
         <v>3</v>
@@ -7811,33 +7850,33 @@
       <c r="F280" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G280" s="17" t="s">
-        <v>237</v>
+      <c r="G280" s="17">
+        <v>46065</v>
       </c>
     </row>
     <row r="281" spans="2:7">
       <c r="B281" s="10" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C281" s="10">
         <v>3</v>
       </c>
       <c r="D281" s="12">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="E281" s="13">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="F281" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G281" s="10" t="s">
-        <v>249</v>
+        <v>305</v>
       </c>
     </row>
     <row r="282" spans="2:7">
       <c r="B282" s="10" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C282" s="10">
         <v>3</v>
@@ -7851,13 +7890,13 @@
       <c r="F282" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G282" s="10" t="s">
-        <v>259</v>
+      <c r="G282" s="17" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="283" spans="2:7">
       <c r="B283" s="10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C283" s="10">
         <v>3</v>
@@ -7871,8 +7910,8 @@
       <c r="F283" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G283" s="18" t="s">
-        <v>322</v>
+      <c r="G283" s="10" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="284" spans="2:7">
@@ -7891,53 +7930,53 @@
       <c r="F284" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G284" s="17">
-        <v>46065</v>
+      <c r="G284" s="10" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="285" spans="2:7">
       <c r="B285" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="C285" s="10">
+        <v>3</v>
+      </c>
+      <c r="D285" s="12">
+        <v>500</v>
+      </c>
+      <c r="E285" s="13">
+        <v>2.5</v>
+      </c>
+      <c r="F285" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G285" s="18" t="s">
         <v>323</v>
-      </c>
-      <c r="C285" s="10">
-        <v>3</v>
-      </c>
-      <c r="D285" s="12">
-        <v>100</v>
-      </c>
-      <c r="E285" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="F285" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G285" s="10" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="286" spans="2:7">
       <c r="B286" s="10" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C286" s="10">
         <v>3</v>
       </c>
       <c r="D286" s="12">
-        <v>200</v>
-      </c>
-      <c r="E286" s="12">
-        <v>1</v>
+        <v>100</v>
+      </c>
+      <c r="E286" s="13">
+        <v>0.5</v>
       </c>
       <c r="F286" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G286" s="10" t="s">
-        <v>249</v>
+      <c r="G286" s="17">
+        <v>46065</v>
       </c>
     </row>
     <row r="287" spans="2:7">
       <c r="B287" s="10" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C287" s="10">
         <v>3</v>
@@ -7951,53 +7990,53 @@
       <c r="F287" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G287" s="17" t="s">
-        <v>237</v>
+      <c r="G287" s="10" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="288" spans="2:7">
       <c r="B288" s="10" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C288" s="10">
         <v>3</v>
       </c>
       <c r="D288" s="12">
-        <v>100</v>
-      </c>
-      <c r="E288" s="13">
-        <v>0.5</v>
+        <v>200</v>
+      </c>
+      <c r="E288" s="12">
+        <v>1</v>
       </c>
       <c r="F288" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G288" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="289" spans="2:7">
       <c r="B289" s="10" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C289" s="10">
         <v>3</v>
       </c>
       <c r="D289" s="12">
-        <v>200</v>
-      </c>
-      <c r="E289" s="12">
-        <v>1</v>
+        <v>100</v>
+      </c>
+      <c r="E289" s="13">
+        <v>0.5</v>
       </c>
       <c r="F289" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G289" s="17">
-        <v>46056</v>
+      <c r="G289" s="17" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="290" spans="2:7">
       <c r="B290" s="10" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C290" s="10">
         <v>3</v>
@@ -8012,112 +8051,112 @@
         <v>10</v>
       </c>
       <c r="G290" s="10" t="s">
-        <v>304</v>
+        <v>250</v>
       </c>
     </row>
     <row r="291" spans="2:7">
       <c r="B291" s="10" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C291" s="10">
         <v>3</v>
       </c>
       <c r="D291" s="12">
-        <v>100</v>
-      </c>
-      <c r="E291" s="13">
-        <v>0.5</v>
+        <v>200</v>
+      </c>
+      <c r="E291" s="12">
+        <v>1</v>
       </c>
       <c r="F291" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G291" s="10" t="s">
-        <v>278</v>
+      <c r="G291" s="17">
+        <v>46056</v>
       </c>
     </row>
     <row r="292" spans="2:7">
       <c r="B292" s="10" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C292" s="10">
         <v>3</v>
       </c>
-      <c r="D292" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E292" s="12">
-        <v>5</v>
+      <c r="D292" s="12">
+        <v>100</v>
+      </c>
+      <c r="E292" s="13">
+        <v>0.5</v>
       </c>
       <c r="F292" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G292" s="17">
-        <v>46177</v>
+      <c r="G292" s="10" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="293" spans="2:7">
       <c r="B293" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C293" s="10">
         <v>3</v>
       </c>
       <c r="D293" s="12">
-        <v>200</v>
-      </c>
-      <c r="E293" s="12">
-        <v>1</v>
+        <v>100</v>
+      </c>
+      <c r="E293" s="13">
+        <v>0.5</v>
       </c>
       <c r="F293" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G293" s="17">
-        <v>46065</v>
+      <c r="G293" s="10" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="294" spans="2:7">
       <c r="B294" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C294" s="10">
         <v>3</v>
       </c>
-      <c r="D294" s="12">
-        <v>100</v>
-      </c>
-      <c r="E294" s="13">
-        <v>0.5</v>
+      <c r="D294" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E294" s="12">
+        <v>5</v>
       </c>
       <c r="F294" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G294" s="10" t="s">
-        <v>259</v>
+      <c r="G294" s="17">
+        <v>46118</v>
       </c>
     </row>
     <row r="295" spans="2:7">
       <c r="B295" s="10" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C295" s="10">
         <v>3</v>
       </c>
       <c r="D295" s="12">
-        <v>100</v>
-      </c>
-      <c r="E295" s="13">
-        <v>0.5</v>
+        <v>200</v>
+      </c>
+      <c r="E295" s="12">
+        <v>1</v>
       </c>
       <c r="F295" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G295" s="10" t="s">
-        <v>244</v>
+      <c r="G295" s="17">
+        <v>46065</v>
       </c>
     </row>
     <row r="296" spans="2:7">
       <c r="B296" s="10" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C296" s="10">
         <v>3</v>
@@ -8132,12 +8171,12 @@
         <v>10</v>
       </c>
       <c r="G296" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="297" spans="2:7">
       <c r="B297" s="10" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C297" s="10">
         <v>3</v>
@@ -8151,13 +8190,13 @@
       <c r="F297" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G297" s="17" t="s">
-        <v>237</v>
+      <c r="G297" s="10" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="298" spans="2:7">
       <c r="B298" s="10" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="C298" s="10">
         <v>3</v>
@@ -8171,13 +8210,13 @@
       <c r="F298" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G298" s="17">
-        <v>46025</v>
+      <c r="G298" s="10" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="299" spans="2:7">
       <c r="B299" s="10" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C299" s="10">
         <v>3</v>
@@ -8192,12 +8231,12 @@
         <v>10</v>
       </c>
       <c r="G299" s="17" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="300" spans="2:7">
       <c r="B300" s="10" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C300" s="10">
         <v>3</v>
@@ -8211,13 +8250,13 @@
       <c r="F300" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G300" s="17" t="s">
-        <v>340</v>
+      <c r="G300" s="17">
+        <v>46025</v>
       </c>
     </row>
     <row r="301" spans="2:7">
       <c r="B301" s="10" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C301" s="10">
         <v>3</v>
@@ -8231,33 +8270,33 @@
       <c r="F301" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G301" s="17">
-        <v>46093</v>
+      <c r="G301" s="17" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="302" spans="2:7">
       <c r="B302" s="10" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C302" s="10">
         <v>3</v>
       </c>
       <c r="D302" s="12">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="E302" s="13">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="F302" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G302" s="19">
-        <v>46065</v>
+      <c r="G302" s="17" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="303" spans="2:7">
       <c r="B303" s="10" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C303" s="10">
         <v>3</v>
@@ -8272,32 +8311,32 @@
         <v>10</v>
       </c>
       <c r="G303" s="17">
-        <v>46095</v>
+        <v>46093</v>
       </c>
     </row>
     <row r="304" spans="2:7">
       <c r="B304" s="10" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C304" s="10">
         <v>3</v>
       </c>
       <c r="D304" s="12">
-        <v>200</v>
-      </c>
-      <c r="E304" s="12">
-        <v>1</v>
+        <v>500</v>
+      </c>
+      <c r="E304" s="13">
+        <v>2.5</v>
       </c>
       <c r="F304" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G304" s="17">
-        <v>46066</v>
+      <c r="G304" s="19">
+        <v>46065</v>
       </c>
     </row>
     <row r="305" spans="2:7">
       <c r="B305" s="10" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C305" s="10">
         <v>3</v>
@@ -8311,33 +8350,33 @@
       <c r="F305" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G305" s="19">
-        <v>46065</v>
+      <c r="G305" s="17">
+        <v>46095</v>
       </c>
     </row>
     <row r="306" spans="2:7">
       <c r="B306" s="10" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C306" s="10">
         <v>3</v>
       </c>
       <c r="D306" s="12">
-        <v>100</v>
-      </c>
-      <c r="E306" s="13">
-        <v>0.5</v>
+        <v>200</v>
+      </c>
+      <c r="E306" s="12">
+        <v>1</v>
       </c>
       <c r="F306" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G306" s="19">
-        <v>46065</v>
+      <c r="G306" s="17">
+        <v>46066</v>
       </c>
     </row>
     <row r="307" spans="2:7">
       <c r="B307" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C307" s="10">
         <v>3</v>
@@ -8352,7 +8391,7 @@
         <v>10</v>
       </c>
       <c r="G307" s="19">
-        <v>46076</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="308" spans="2:7">
@@ -8397,7 +8436,7 @@
     </row>
     <row r="310" spans="2:7">
       <c r="B310" s="10" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C310" s="10">
         <v>3</v>
@@ -8411,13 +8450,13 @@
       <c r="F310" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G310" s="19" t="s">
-        <v>350</v>
+      <c r="G310" s="19">
+        <v>46065</v>
       </c>
     </row>
     <row r="311" spans="2:7">
       <c r="B311" s="10" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C311" s="10">
         <v>3</v>
@@ -8431,13 +8470,13 @@
       <c r="F311" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G311" s="19" t="s">
-        <v>259</v>
+      <c r="G311" s="19">
+        <v>46076</v>
       </c>
     </row>
     <row r="312" spans="2:7">
       <c r="B312" s="10" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C312" s="10">
         <v>3</v>
@@ -8452,32 +8491,32 @@
         <v>10</v>
       </c>
       <c r="G312" s="19" t="s">
-        <v>259</v>
+        <v>351</v>
       </c>
     </row>
     <row r="313" spans="2:7">
       <c r="B313" s="10" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C313" s="10">
         <v>3</v>
       </c>
-      <c r="D313" s="20">
-        <v>100</v>
-      </c>
-      <c r="E313" s="21">
-        <v>0.5</v>
-      </c>
-      <c r="F313" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="G313" s="23" t="s">
-        <v>322</v>
+      <c r="D313" s="12">
+        <v>100</v>
+      </c>
+      <c r="E313" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="F313" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G313" s="19" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="314" spans="2:7">
       <c r="B314" s="10" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C314" s="10">
         <v>3</v>
@@ -8491,33 +8530,33 @@
       <c r="F314" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G314" s="19">
-        <v>46065</v>
+      <c r="G314" s="19" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="315" spans="2:7">
       <c r="B315" s="10" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C315" s="10">
         <v>3</v>
       </c>
-      <c r="D315" s="12">
-        <v>100</v>
-      </c>
-      <c r="E315" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="F315" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G315" s="19">
-        <v>46069</v>
+      <c r="D315" s="20">
+        <v>100</v>
+      </c>
+      <c r="E315" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="F315" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="G315" s="23" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="316" spans="2:7">
       <c r="B316" s="10" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C316" s="10">
         <v>3</v>
@@ -8532,12 +8571,12 @@
         <v>10</v>
       </c>
       <c r="G316" s="19">
-        <v>46087</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="317" spans="2:7">
       <c r="B317" s="10" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C317" s="10">
         <v>3</v>
@@ -8551,13 +8590,13 @@
       <c r="F317" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G317" s="19" t="s">
-        <v>259</v>
+      <c r="G317" s="19">
+        <v>46069</v>
       </c>
     </row>
     <row r="318" spans="2:7">
       <c r="B318" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C318" s="10">
         <v>3</v>
@@ -8571,8 +8610,8 @@
       <c r="F318" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G318" s="24" t="s">
-        <v>359</v>
+      <c r="G318" s="19">
+        <v>46087</v>
       </c>
     </row>
     <row r="319" spans="2:7">
@@ -8583,61 +8622,61 @@
         <v>3</v>
       </c>
       <c r="D319" s="12">
-        <v>200</v>
-      </c>
-      <c r="E319" s="12">
-        <v>1</v>
+        <v>100</v>
+      </c>
+      <c r="E319" s="13">
+        <v>0.5</v>
       </c>
       <c r="F319" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="G319" s="17" t="s">
-        <v>360</v>
+        <v>10</v>
+      </c>
+      <c r="G319" s="19" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="320" spans="2:7">
       <c r="B320" s="10" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C320" s="10">
         <v>3</v>
       </c>
       <c r="D320" s="12">
-        <v>200</v>
-      </c>
-      <c r="E320" s="12">
-        <v>1</v>
+        <v>100</v>
+      </c>
+      <c r="E320" s="13">
+        <v>0.5</v>
       </c>
       <c r="F320" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="G320" s="17">
-        <v>46093</v>
+        <v>10</v>
+      </c>
+      <c r="G320" s="24" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="321" spans="2:7">
       <c r="B321" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="C321" s="10">
+        <v>3</v>
+      </c>
+      <c r="D321" s="12">
+        <v>200</v>
+      </c>
+      <c r="E321" s="12">
+        <v>1</v>
+      </c>
+      <c r="F321" s="10" t="s">
+        <v>138</v>
+      </c>
+      <c r="G321" s="17" t="s">
         <v>361</v>
-      </c>
-      <c r="C321" s="10">
-        <v>3</v>
-      </c>
-      <c r="D321" s="12">
-        <v>100</v>
-      </c>
-      <c r="E321" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="F321" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G321" s="17">
-        <v>46065</v>
       </c>
     </row>
     <row r="322" spans="2:7">
       <c r="B322" s="10" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C322" s="10">
         <v>3</v>
@@ -8649,15 +8688,15 @@
         <v>1</v>
       </c>
       <c r="F322" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G322" s="18" t="s">
-        <v>251</v>
+        <v>138</v>
+      </c>
+      <c r="G322" s="17">
+        <v>46093</v>
       </c>
     </row>
     <row r="323" spans="2:7">
       <c r="B323" s="10" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C323" s="10">
         <v>3</v>
@@ -8671,13 +8710,13 @@
       <c r="F323" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G323" s="17" t="s">
-        <v>249</v>
+      <c r="G323" s="17">
+        <v>46065</v>
       </c>
     </row>
     <row r="324" spans="2:7">
       <c r="B324" s="10" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C324" s="10">
         <v>3</v>
@@ -8692,12 +8731,12 @@
         <v>10</v>
       </c>
       <c r="G324" s="18" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
     </row>
     <row r="325" spans="2:7">
       <c r="B325" s="10" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C325" s="10">
         <v>3</v>
@@ -8712,32 +8751,32 @@
         <v>10</v>
       </c>
       <c r="G325" s="17" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="326" spans="2:7">
       <c r="B326" s="10" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C326" s="10">
         <v>3</v>
       </c>
       <c r="D326" s="12">
-        <v>100</v>
-      </c>
-      <c r="E326" s="13">
-        <v>0.5</v>
+        <v>200</v>
+      </c>
+      <c r="E326" s="12">
+        <v>1</v>
       </c>
       <c r="F326" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G326" s="17">
-        <v>46064</v>
+      <c r="G326" s="18" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="327" spans="2:7">
       <c r="B327" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C327" s="10">
         <v>3</v>
@@ -8751,13 +8790,13 @@
       <c r="F327" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G327" s="19" t="s">
-        <v>304</v>
+      <c r="G327" s="17" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="328" spans="2:7">
       <c r="B328" s="10" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C328" s="10">
         <v>3</v>
@@ -8771,13 +8810,13 @@
       <c r="F328" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G328" s="19" t="s">
-        <v>278</v>
+      <c r="G328" s="17">
+        <v>46064</v>
       </c>
     </row>
     <row r="329" spans="2:7">
       <c r="B329" s="10" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C329" s="10">
         <v>3</v>
@@ -8791,13 +8830,13 @@
       <c r="F329" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G329" s="17" t="s">
-        <v>370</v>
+      <c r="G329" s="19" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="330" spans="2:7">
       <c r="B330" s="10" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C330" s="10">
         <v>3</v>
@@ -8811,13 +8850,13 @@
       <c r="F330" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G330" s="17" t="s">
-        <v>249</v>
+      <c r="G330" s="19" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="331" spans="2:7">
       <c r="B331" s="10" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C331" s="10">
         <v>3</v>
@@ -8831,8 +8870,8 @@
       <c r="F331" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G331" s="19">
-        <v>46057</v>
+      <c r="G331" s="17" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="332" spans="2:7">
@@ -8851,8 +8890,8 @@
       <c r="F332" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G332" s="10" t="s">
-        <v>259</v>
+      <c r="G332" s="17" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="333" spans="2:7">
@@ -8871,13 +8910,13 @@
       <c r="F333" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G333" s="10" t="s">
-        <v>259</v>
+      <c r="G333" s="19">
+        <v>46057</v>
       </c>
     </row>
     <row r="334" spans="2:7">
       <c r="B334" s="10" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C334" s="10">
         <v>3</v>
@@ -8891,33 +8930,33 @@
       <c r="F334" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G334" s="19">
-        <v>46056</v>
+      <c r="G334" s="10" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="335" spans="2:7">
       <c r="B335" s="10" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C335" s="10">
         <v>3</v>
       </c>
-      <c r="D335" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E335" s="12">
-        <v>5</v>
+      <c r="D335" s="12">
+        <v>100</v>
+      </c>
+      <c r="E335" s="13">
+        <v>0.5</v>
       </c>
       <c r="F335" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G335" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="336" spans="2:7">
       <c r="B336" s="10" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C336" s="10">
         <v>3</v>
@@ -8931,8 +8970,8 @@
       <c r="F336" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G336" s="19" t="s">
-        <v>377</v>
+      <c r="G336" s="19">
+        <v>46056</v>
       </c>
     </row>
     <row r="337" spans="2:7">
@@ -8942,22 +8981,22 @@
       <c r="C337" s="10">
         <v>3</v>
       </c>
-      <c r="D337" s="12">
-        <v>100</v>
-      </c>
-      <c r="E337" s="13">
-        <v>0.5</v>
+      <c r="D337" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E337" s="12">
+        <v>5</v>
       </c>
       <c r="F337" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G337" s="17" t="s">
-        <v>378</v>
+      <c r="G337" s="10" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="338" spans="2:7">
       <c r="B338" s="10" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C338" s="10">
         <v>3</v>
@@ -8971,28 +9010,28 @@
       <c r="F338" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G338" s="18" t="s">
-        <v>285</v>
+      <c r="G338" s="19" t="s">
+        <v>378</v>
       </c>
     </row>
     <row r="339" spans="2:7">
       <c r="B339" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="C339" s="10">
+        <v>3</v>
+      </c>
+      <c r="D339" s="12">
+        <v>100</v>
+      </c>
+      <c r="E339" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="F339" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G339" s="17" t="s">
         <v>379</v>
-      </c>
-      <c r="C339" s="10">
-        <v>3</v>
-      </c>
-      <c r="D339" s="12">
-        <v>100</v>
-      </c>
-      <c r="E339" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="F339" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G339" s="17">
-        <v>46065</v>
       </c>
     </row>
     <row r="340" spans="2:7">
@@ -9011,13 +9050,13 @@
       <c r="F340" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G340" s="17" t="s">
-        <v>378</v>
+      <c r="G340" s="18" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="341" spans="2:7">
       <c r="B341" s="10" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C341" s="10">
         <v>3</v>
@@ -9031,13 +9070,13 @@
       <c r="F341" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G341" s="17" t="s">
-        <v>382</v>
+      <c r="G341" s="17">
+        <v>46065</v>
       </c>
     </row>
     <row r="342" spans="2:7">
       <c r="B342" s="10" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C342" s="10">
         <v>3</v>
@@ -9052,12 +9091,12 @@
         <v>10</v>
       </c>
       <c r="G342" s="17" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="343" spans="2:7">
       <c r="B343" s="10" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C343" s="10">
         <v>3</v>
@@ -9072,12 +9111,12 @@
         <v>10</v>
       </c>
       <c r="G343" s="17" t="s">
-        <v>249</v>
+        <v>383</v>
       </c>
     </row>
     <row r="344" spans="2:7">
       <c r="B344" s="10" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C344" s="10">
         <v>3</v>
@@ -9091,13 +9130,13 @@
       <c r="F344" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G344" s="18" t="s">
-        <v>251</v>
+      <c r="G344" s="17" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="345" spans="2:7">
       <c r="B345" s="10" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C345" s="10">
         <v>3</v>
@@ -9111,28 +9150,28 @@
       <c r="F345" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G345" s="19" t="s">
-        <v>304</v>
+      <c r="G345" s="17" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="346" spans="2:7">
       <c r="B346" s="10" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C346" s="10">
         <v>3</v>
       </c>
       <c r="D346" s="12">
-        <v>200</v>
-      </c>
-      <c r="E346" s="12">
-        <v>1</v>
+        <v>100</v>
+      </c>
+      <c r="E346" s="13">
+        <v>0.5</v>
       </c>
       <c r="F346" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G346" s="18" t="s">
-        <v>324</v>
+        <v>252</v>
       </c>
     </row>
     <row r="347" spans="2:7">
@@ -9143,36 +9182,36 @@
         <v>3</v>
       </c>
       <c r="D347" s="12">
-        <v>200</v>
-      </c>
-      <c r="E347" s="12">
-        <v>1</v>
+        <v>100</v>
+      </c>
+      <c r="E347" s="13">
+        <v>0.5</v>
       </c>
       <c r="F347" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G347" s="10" t="s">
-        <v>304</v>
+      <c r="G347" s="19" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="348" spans="2:7">
       <c r="B348" s="10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C348" s="10">
         <v>3</v>
       </c>
       <c r="D348" s="12">
-        <v>100</v>
-      </c>
-      <c r="E348" s="13">
-        <v>0.5</v>
+        <v>200</v>
+      </c>
+      <c r="E348" s="12">
+        <v>1</v>
       </c>
       <c r="F348" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="G348" s="17">
-        <v>46145</v>
+        <v>10</v>
+      </c>
+      <c r="G348" s="18" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="349" spans="2:7">
@@ -9183,21 +9222,21 @@
         <v>3</v>
       </c>
       <c r="D349" s="12">
-        <v>100</v>
-      </c>
-      <c r="E349" s="13">
-        <v>0.5</v>
+        <v>200</v>
+      </c>
+      <c r="E349" s="12">
+        <v>1</v>
       </c>
       <c r="F349" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G349" s="19" t="s">
-        <v>304</v>
+      <c r="G349" s="10" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="350" spans="2:7">
       <c r="B350" s="10" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="C350" s="10">
         <v>3</v>
@@ -9209,95 +9248,95 @@
         <v>0.5</v>
       </c>
       <c r="F350" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G350" s="17" t="s">
-        <v>391</v>
+        <v>138</v>
+      </c>
+      <c r="G350" s="17">
+        <v>46145</v>
       </c>
     </row>
     <row r="351" spans="2:7">
       <c r="B351" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="C351" s="10">
+        <v>3</v>
+      </c>
+      <c r="D351" s="12">
+        <v>100</v>
+      </c>
+      <c r="E351" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="F351" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G351" s="19" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="352" spans="2:7">
+      <c r="B352" s="10" t="s">
+        <v>391</v>
+      </c>
+      <c r="C352" s="10">
+        <v>3</v>
+      </c>
+      <c r="D352" s="12">
+        <v>100</v>
+      </c>
+      <c r="E352" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="F352" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G352" s="17" t="s">
         <v>392</v>
-      </c>
-      <c r="C351" s="10">
-        <v>3</v>
-      </c>
-      <c r="D351" s="12">
-        <v>100</v>
-      </c>
-      <c r="E351" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="F351" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G351" s="17" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="352" spans="2:7">
-      <c r="B352" s="11" t="s">
-        <v>393</v>
-      </c>
-      <c r="C352" s="10">
-        <v>3</v>
-      </c>
-      <c r="D352" s="12">
-        <v>100</v>
-      </c>
-      <c r="E352" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="F352" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G352" s="17" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="353" spans="2:7">
       <c r="B353" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C353" s="10">
+        <v>3</v>
+      </c>
+      <c r="D353" s="12">
+        <v>100</v>
+      </c>
+      <c r="E353" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="F353" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G353" s="17" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="354" spans="2:7">
+      <c r="B354" s="11" t="s">
+        <v>394</v>
+      </c>
+      <c r="C354" s="10">
+        <v>3</v>
+      </c>
+      <c r="D354" s="12">
+        <v>100</v>
+      </c>
+      <c r="E354" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="F354" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G354" s="17" t="s">
         <v>395</v>
-      </c>
-      <c r="C353" s="10">
-        <v>3</v>
-      </c>
-      <c r="D353" s="12">
-        <v>100</v>
-      </c>
-      <c r="E353" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="F353" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G353" s="17" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="354" spans="2:7">
-      <c r="B354" s="10" t="s">
-        <v>396</v>
-      </c>
-      <c r="C354" s="10">
-        <v>3</v>
-      </c>
-      <c r="D354" s="12">
-        <v>100</v>
-      </c>
-      <c r="E354" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="F354" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G354" s="17" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="355" spans="2:7">
       <c r="B355" s="10" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C355" s="10">
         <v>3</v>
@@ -9311,33 +9350,33 @@
       <c r="F355" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G355" s="24" t="s">
-        <v>242</v>
+      <c r="G355" s="17" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="356" spans="2:7">
       <c r="B356" s="10" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C356" s="10">
         <v>3</v>
       </c>
       <c r="D356" s="12">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="E356" s="13">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="F356" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G356" s="19" t="s">
-        <v>249</v>
+      <c r="G356" s="17" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="357" spans="2:7">
       <c r="B357" s="10" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C357" s="10">
         <v>3</v>
@@ -9351,13 +9390,13 @@
       <c r="F357" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G357" s="17" t="s">
-        <v>378</v>
+      <c r="G357" s="24" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="358" spans="2:7">
       <c r="B358" s="10" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C358" s="10">
         <v>3</v>
@@ -9372,12 +9411,12 @@
         <v>10</v>
       </c>
       <c r="G358" s="19" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="359" spans="2:7">
       <c r="B359" s="10" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C359" s="10">
         <v>3</v>
@@ -9392,27 +9431,27 @@
         <v>10</v>
       </c>
       <c r="G359" s="17" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="360" spans="2:7">
       <c r="B360" s="10" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C360" s="10">
         <v>3</v>
       </c>
       <c r="D360" s="12">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E360" s="13">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="F360" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G360" s="17" t="s">
-        <v>403</v>
+      <c r="G360" s="19" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="361" spans="2:7">
@@ -9431,33 +9470,33 @@
       <c r="F361" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G361" s="10" t="s">
-        <v>302</v>
+      <c r="G361" s="17" t="s">
+        <v>379</v>
       </c>
     </row>
     <row r="362" spans="2:7">
       <c r="B362" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="C362" s="10">
+        <v>3</v>
+      </c>
+      <c r="D362" s="12">
+        <v>100</v>
+      </c>
+      <c r="E362" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="F362" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G362" s="17" t="s">
         <v>404</v>
-      </c>
-      <c r="C362" s="10">
-        <v>3</v>
-      </c>
-      <c r="D362" s="12">
-        <v>100</v>
-      </c>
-      <c r="E362" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="F362" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G362" s="19" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="363" spans="2:7">
       <c r="B363" s="10" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C363" s="10">
         <v>3</v>
@@ -9471,13 +9510,13 @@
       <c r="F363" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G363" s="17" t="s">
-        <v>245</v>
+      <c r="G363" s="10" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="364" spans="2:7">
       <c r="B364" s="10" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C364" s="10">
         <v>3</v>
@@ -9491,13 +9530,13 @@
       <c r="F364" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G364" s="17" t="s">
-        <v>407</v>
+      <c r="G364" s="19" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="365" spans="2:7">
       <c r="B365" s="10" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C365" s="10">
         <v>3</v>
@@ -9512,12 +9551,12 @@
         <v>10</v>
       </c>
       <c r="G365" s="17" t="s">
-        <v>409</v>
+        <v>246</v>
       </c>
     </row>
     <row r="366" spans="2:7">
       <c r="B366" s="10" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="C366" s="10">
         <v>3</v>
@@ -9532,12 +9571,12 @@
         <v>10</v>
       </c>
       <c r="G366" s="17" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="367" spans="2:7">
       <c r="B367" s="10" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C367" s="10">
         <v>3</v>
@@ -9551,8 +9590,8 @@
       <c r="F367" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G367" s="10" t="s">
-        <v>370</v>
+      <c r="G367" s="17" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="368" spans="2:7">
@@ -9572,7 +9611,7 @@
         <v>10</v>
       </c>
       <c r="G368" s="17" t="s">
-        <v>245</v>
+        <v>408</v>
       </c>
     </row>
     <row r="369" spans="2:7">
@@ -9592,201 +9631,201 @@
         <v>10</v>
       </c>
       <c r="G369" s="10" t="s">
-        <v>251</v>
+        <v>371</v>
       </c>
     </row>
     <row r="370" spans="2:7">
       <c r="B370" s="10" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C370" s="10">
         <v>3</v>
       </c>
       <c r="D370" s="12">
-        <v>200</v>
-      </c>
-      <c r="E370" s="12">
-        <v>1</v>
+        <v>100</v>
+      </c>
+      <c r="E370" s="13">
+        <v>0.5</v>
       </c>
       <c r="F370" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G370" s="18" t="s">
-        <v>244</v>
+      <c r="G370" s="17" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="371" spans="2:7">
       <c r="B371" s="10" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C371" s="10">
         <v>3</v>
       </c>
-      <c r="D371" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E371" s="12">
-        <v>5</v>
+      <c r="D371" s="12">
+        <v>100</v>
+      </c>
+      <c r="E371" s="13">
+        <v>0.5</v>
       </c>
       <c r="F371" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G371" s="18" t="s">
-        <v>244</v>
+      <c r="G371" s="10" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="372" spans="2:7">
       <c r="B372" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="C372" s="10">
+        <v>3</v>
+      </c>
+      <c r="D372" s="12">
+        <v>200</v>
+      </c>
+      <c r="E372" s="12">
+        <v>1</v>
+      </c>
+      <c r="F372" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G372" s="18" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="373" spans="2:7">
+      <c r="B373" s="10" t="s">
         <v>415</v>
       </c>
-      <c r="C372" s="10">
-        <v>3</v>
-      </c>
-      <c r="D372" s="12">
-        <v>100</v>
-      </c>
-      <c r="E372" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="F372" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G372" s="17" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="373" spans="2:7">
-      <c r="B373" s="7" t="s">
+      <c r="C373" s="10">
+        <v>3</v>
+      </c>
+      <c r="D373" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="E373" s="12">
+        <v>5</v>
+      </c>
+      <c r="F373" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G373" s="18" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="374" spans="2:7">
+      <c r="B374" s="10" t="s">
         <v>416</v>
       </c>
-      <c r="C373" s="10">
-        <v>3</v>
-      </c>
-      <c r="D373" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E373" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F373" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="G373" s="24" t="s">
+      <c r="C374" s="10">
+        <v>3</v>
+      </c>
+      <c r="D374" s="12">
+        <v>100</v>
+      </c>
+      <c r="E374" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="F374" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G374" s="17" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="375" spans="2:7">
+      <c r="B375" s="7" t="s">
         <v>417</v>
       </c>
-    </row>
-    <row r="374" spans="2:7" ht="14.25">
-      <c r="B374" s="7" t="s">
+      <c r="C375" s="10">
+        <v>3</v>
+      </c>
+      <c r="D375" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E375" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F375" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="G375" s="24" t="s">
         <v>418</v>
-      </c>
-      <c r="C374" s="10">
-        <v>3</v>
-      </c>
-      <c r="D374" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E374" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F374" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="G374" s="8">
-        <v>46094</v>
-      </c>
-    </row>
-    <row r="375" spans="2:7" ht="14.25">
-      <c r="B375" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="C375" s="10">
-        <v>3</v>
-      </c>
-      <c r="D375" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E375" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F375" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="G375" s="8">
-        <v>46095</v>
       </c>
     </row>
     <row r="376" spans="2:7" ht="14.25">
       <c r="B376" s="7" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C376" s="10">
         <v>3</v>
       </c>
       <c r="D376" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E376" s="4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F376" s="25" t="s">
         <v>10</v>
       </c>
       <c r="G376" s="8">
-        <v>46064</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="377" spans="2:7" ht="14.25">
       <c r="B377" s="7" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C377" s="10">
         <v>3</v>
       </c>
       <c r="D377" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E377" s="4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F377" s="25" t="s">
         <v>10</v>
       </c>
       <c r="G377" s="8">
-        <v>46066</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="378" spans="2:7" ht="14.25">
       <c r="B378" s="7" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="C378" s="10">
         <v>3</v>
       </c>
       <c r="D378" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E378" s="4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F378" s="25" t="s">
         <v>10</v>
       </c>
       <c r="G378" s="8">
-        <v>46067</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="379" spans="2:7" ht="14.25">
       <c r="B379" s="7" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C379" s="10">
         <v>3</v>
       </c>
       <c r="D379" s="4" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="E379" s="4" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F379" s="25" t="s">
         <v>10</v>
@@ -9797,196 +9836,196 @@
     </row>
     <row r="380" spans="2:7" ht="14.25">
       <c r="B380" s="7" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C380" s="10">
         <v>3</v>
       </c>
       <c r="D380" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E380" s="4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F380" s="25" t="s">
         <v>10</v>
       </c>
       <c r="G380" s="8">
-        <v>46066</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="381" spans="2:7" ht="14.25">
       <c r="B381" s="7" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C381" s="10">
         <v>3</v>
       </c>
       <c r="D381" s="4" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E381" s="4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F381" s="25" t="s">
         <v>10</v>
       </c>
       <c r="G381" s="8">
-        <v>46071</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="382" spans="2:7" ht="14.25">
       <c r="B382" s="7" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C382" s="10">
         <v>3</v>
       </c>
       <c r="D382" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E382" s="4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F382" s="25" t="s">
         <v>10</v>
       </c>
       <c r="G382" s="8">
-        <v>46081</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="383" spans="2:7" ht="14.25">
       <c r="B383" s="7" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C383" s="10">
         <v>3</v>
       </c>
       <c r="D383" s="4" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="E383" s="4" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="F383" s="25" t="s">
         <v>10</v>
       </c>
       <c r="G383" s="8">
-        <v>46066</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="384" spans="2:7" ht="14.25">
       <c r="B384" s="7" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C384" s="10">
         <v>3</v>
       </c>
       <c r="D384" s="4" t="s">
-        <v>102</v>
+        <v>31</v>
       </c>
       <c r="E384" s="4" t="s">
-        <v>103</v>
+        <v>32</v>
       </c>
       <c r="F384" s="25" t="s">
         <v>10</v>
       </c>
       <c r="G384" s="8">
-        <v>46070</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="385" spans="2:7" ht="14.25">
       <c r="B385" s="7" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C385" s="10">
         <v>3</v>
       </c>
       <c r="D385" s="4" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E385" s="4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F385" s="25" t="s">
         <v>10</v>
       </c>
       <c r="G385" s="8">
-        <v>46067</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="386" spans="2:7" ht="14.25">
       <c r="B386" s="7" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C386" s="10">
         <v>3</v>
       </c>
       <c r="D386" s="4" t="s">
-        <v>28</v>
+        <v>104</v>
       </c>
       <c r="E386" s="4" t="s">
-        <v>29</v>
+        <v>105</v>
       </c>
       <c r="F386" s="25" t="s">
         <v>10</v>
       </c>
       <c r="G386" s="8">
-        <v>46067</v>
+        <v>46070</v>
       </c>
     </row>
     <row r="387" spans="2:7" ht="14.25">
       <c r="B387" s="7" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C387" s="10">
         <v>3</v>
       </c>
       <c r="D387" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E387" s="4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F387" s="25" t="s">
         <v>10</v>
       </c>
       <c r="G387" s="8">
-        <v>46065</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="388" spans="2:7" ht="14.25">
       <c r="B388" s="7" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C388" s="10">
         <v>3</v>
       </c>
       <c r="D388" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E388" s="4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F388" s="25" t="s">
         <v>10</v>
       </c>
       <c r="G388" s="8">
-        <v>46065</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="389" spans="2:7" ht="14.25">
       <c r="B389" s="7" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C389" s="10">
         <v>3</v>
       </c>
       <c r="D389" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E389" s="4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F389" s="25" t="s">
         <v>10</v>
@@ -9997,98 +10036,98 @@
     </row>
     <row r="390" spans="2:7" ht="14.25">
       <c r="B390" s="7" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C390" s="10">
         <v>3</v>
       </c>
       <c r="D390" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E390" s="4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F390" s="25" t="s">
         <v>10</v>
       </c>
       <c r="G390" s="8">
-        <v>46115</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="391" spans="2:7" ht="14.25">
       <c r="B391" s="7" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C391" s="10">
         <v>3</v>
       </c>
       <c r="D391" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E391" s="4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F391" s="25" t="s">
         <v>10</v>
       </c>
       <c r="G391" s="8">
-        <v>46066</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="392" spans="2:7" ht="14.25">
       <c r="B392" s="7" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C392" s="10">
         <v>3</v>
       </c>
       <c r="D392" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E392" s="4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F392" s="25" t="s">
         <v>10</v>
       </c>
       <c r="G392" s="8">
-        <v>46066</v>
+        <v>46115</v>
       </c>
     </row>
     <row r="393" spans="2:7" ht="14.25">
       <c r="B393" s="7" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C393" s="10">
         <v>3</v>
       </c>
       <c r="D393" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E393" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F393" s="4" t="s">
-        <v>136</v>
+        <v>32</v>
+      </c>
+      <c r="F393" s="25" t="s">
+        <v>10</v>
       </c>
       <c r="G393" s="8">
-        <v>46086</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="394" spans="2:7" ht="14.25">
       <c r="B394" s="7" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C394" s="10">
         <v>3</v>
       </c>
       <c r="D394" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E394" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F394" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F394" s="25" t="s">
         <v>10</v>
       </c>
       <c r="G394" s="8">
@@ -10097,156 +10136,156 @@
     </row>
     <row r="395" spans="2:7" ht="14.25">
       <c r="B395" s="7" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C395" s="10">
         <v>3</v>
       </c>
       <c r="D395" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E395" s="4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F395" s="4" t="s">
-        <v>10</v>
+        <v>138</v>
       </c>
       <c r="G395" s="8">
-        <v>46068</v>
+        <v>46086</v>
       </c>
     </row>
     <row r="396" spans="2:7" ht="14.25">
       <c r="B396" s="7" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C396" s="10">
         <v>3</v>
       </c>
       <c r="D396" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E396" s="4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F396" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G396" s="8">
-        <v>46065</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="397" spans="2:7" ht="14.25">
       <c r="B397" s="7" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C397" s="10">
         <v>3</v>
       </c>
       <c r="D397" s="4" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="E397" s="4" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F397" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G397" s="8">
-        <v>46050</v>
+        <v>46068</v>
       </c>
     </row>
     <row r="398" spans="2:7" ht="14.25">
       <c r="B398" s="7" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C398" s="10">
         <v>3</v>
       </c>
       <c r="D398" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E398" s="4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F398" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G398" s="8">
-        <v>46099</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="399" spans="2:7" ht="14.25">
       <c r="B399" s="7" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C399" s="10">
         <v>3</v>
       </c>
       <c r="D399" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E399" s="4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F399" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G399" s="8">
-        <v>46071</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="400" spans="2:7" ht="14.25">
       <c r="B400" s="7" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C400" s="10">
         <v>3</v>
       </c>
       <c r="D400" s="4" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="E400" s="4" t="s">
-        <v>445</v>
+        <v>32</v>
       </c>
       <c r="F400" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G400" s="8">
-        <v>46034</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="401" spans="2:7" ht="14.25">
       <c r="B401" s="7" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C401" s="10">
         <v>3</v>
       </c>
       <c r="D401" s="4" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="E401" s="4" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F401" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G401" s="8">
-        <v>46034</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="402" spans="2:7" ht="14.25">
       <c r="B402" s="7" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C402" s="10">
         <v>3</v>
       </c>
       <c r="D402" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E402" s="4" t="s">
-        <v>23</v>
+        <v>446</v>
       </c>
       <c r="F402" s="4" t="s">
         <v>10</v>
@@ -10257,16 +10296,16 @@
     </row>
     <row r="403" spans="2:7" ht="14.25">
       <c r="B403" s="7" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C403" s="10">
         <v>3</v>
       </c>
       <c r="D403" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E403" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F403" s="4" t="s">
         <v>10</v>
@@ -10277,36 +10316,36 @@
     </row>
     <row r="404" spans="2:7" ht="14.25">
       <c r="B404" s="7" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C404" s="10">
         <v>3</v>
       </c>
       <c r="D404" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E404" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F404" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G404" s="8">
-        <v>46035</v>
+        <v>46034</v>
       </c>
     </row>
     <row r="405" spans="2:7" ht="14.25">
       <c r="B405" s="7" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C405" s="10">
         <v>3</v>
       </c>
       <c r="D405" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E405" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F405" s="4" t="s">
         <v>10</v>
@@ -10317,36 +10356,36 @@
     </row>
     <row r="406" spans="2:7" ht="14.25">
       <c r="B406" s="7" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C406" s="10">
         <v>3</v>
       </c>
       <c r="D406" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E406" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F406" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G406" s="8">
-        <v>46034</v>
+        <v>46035</v>
       </c>
     </row>
     <row r="407" spans="2:7" ht="14.25">
       <c r="B407" s="7" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C407" s="10">
         <v>3</v>
       </c>
       <c r="D407" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E407" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F407" s="4" t="s">
         <v>10</v>
@@ -10357,16 +10396,16 @@
     </row>
     <row r="408" spans="2:7" ht="14.25">
       <c r="B408" s="7" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C408" s="10">
         <v>3</v>
       </c>
       <c r="D408" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E408" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F408" s="4" t="s">
         <v>10</v>
@@ -10377,16 +10416,16 @@
     </row>
     <row r="409" spans="2:7" ht="14.25">
       <c r="B409" s="7" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C409" s="10">
         <v>3</v>
       </c>
       <c r="D409" s="4" t="s">
-        <v>455</v>
+        <v>25</v>
       </c>
       <c r="E409" s="4" t="s">
-        <v>456</v>
+        <v>26</v>
       </c>
       <c r="F409" s="4" t="s">
         <v>10</v>
@@ -10403,35 +10442,95 @@
         <v>3</v>
       </c>
       <c r="D410" s="4" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E410" s="4" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F410" s="4" t="s">
-        <v>136</v>
+        <v>10</v>
       </c>
       <c r="G410" s="8">
-        <v>46028</v>
+        <v>46034</v>
       </c>
     </row>
     <row r="411" spans="2:7" ht="14.25">
       <c r="B411" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="C411" s="10">
+        <v>3</v>
+      </c>
+      <c r="D411" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E411" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F411" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G411" s="8">
+        <v>46034</v>
+      </c>
+    </row>
+    <row r="412" spans="2:7" ht="14.25">
+      <c r="B412" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="C412" s="10">
+        <v>3</v>
+      </c>
+      <c r="D412" s="4" t="s">
         <v>457</v>
       </c>
-      <c r="C411" s="10">
-        <v>3</v>
-      </c>
-      <c r="D411" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E411" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F411" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G411" s="8">
+      <c r="E412" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="F412" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G412" s="8">
+        <v>46034</v>
+      </c>
+    </row>
+    <row r="413" spans="2:7" ht="14.25">
+      <c r="B413" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="C413" s="10">
+        <v>3</v>
+      </c>
+      <c r="D413" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E413" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F413" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="G413" s="8">
+        <v>46028</v>
+      </c>
+    </row>
+    <row r="414" spans="2:7" ht="14.25">
+      <c r="B414" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="C414" s="10">
+        <v>3</v>
+      </c>
+      <c r="D414" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E414" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F414" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G414" s="8">
         <v>46028</v>
       </c>
     </row>

--- a/server/userPlan.xlsx
+++ b/server/userPlan.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29930"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30002"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{57C6AAB2-873C-4167-B636-CC6C748C690A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{05AD72BD-47C7-4EF0-96D4-2A0E2EBDC7CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1467" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1455" uniqueCount="457">
   <si>
     <t>id</t>
   </si>
@@ -54,450 +54,447 @@
     <t>created_at</t>
   </si>
   <si>
-    <t>AVG56814</t>
+    <t>AVG56190</t>
+  </si>
+  <si>
+    <t>$200</t>
+  </si>
+  <si>
+    <t>$1</t>
+  </si>
+  <si>
+    <t>active</t>
+  </si>
+  <si>
+    <t>AVG27912</t>
+  </si>
+  <si>
+    <t>$1000</t>
+  </si>
+  <si>
+    <t>$5</t>
+  </si>
+  <si>
+    <t>AVG79320</t>
+  </si>
+  <si>
+    <t>AVG70261</t>
+  </si>
+  <si>
+    <t>$2200</t>
+  </si>
+  <si>
+    <t>$11</t>
+  </si>
+  <si>
+    <t>AVG55466</t>
+  </si>
+  <si>
+    <t>$500</t>
+  </si>
+  <si>
+    <t>$2.5</t>
+  </si>
+  <si>
+    <t>AVG71291</t>
+  </si>
+  <si>
+    <t>$3000</t>
+  </si>
+  <si>
+    <t>$15</t>
+  </si>
+  <si>
+    <t>AVG95589</t>
+  </si>
+  <si>
+    <t>$2000</t>
+  </si>
+  <si>
+    <t>$10</t>
+  </si>
+  <si>
+    <t>AVG77261</t>
+  </si>
+  <si>
+    <t>$100</t>
+  </si>
+  <si>
+    <t>$0.5</t>
+  </si>
+  <si>
+    <t>AVG35000</t>
+  </si>
+  <si>
+    <t>AVG44166</t>
+  </si>
+  <si>
+    <t>AVG41212</t>
+  </si>
+  <si>
+    <t>AVG18162</t>
+  </si>
+  <si>
+    <t>AVG44793</t>
+  </si>
+  <si>
+    <t>$1100</t>
+  </si>
+  <si>
+    <t>$5.5</t>
+  </si>
+  <si>
+    <t>AVG61984</t>
+  </si>
+  <si>
+    <t>AVG43359</t>
+  </si>
+  <si>
+    <t>AVG76462</t>
+  </si>
+  <si>
+    <t>AVG06662</t>
+  </si>
+  <si>
+    <t>AVG25998</t>
+  </si>
+  <si>
+    <t>AVG85139</t>
+  </si>
+  <si>
+    <t>AVG08399</t>
+  </si>
+  <si>
+    <t>$4000</t>
+  </si>
+  <si>
+    <t>$20</t>
+  </si>
+  <si>
+    <t>AVG45681</t>
+  </si>
+  <si>
+    <t>AVG04136</t>
+  </si>
+  <si>
+    <t>AVG97943</t>
+  </si>
+  <si>
+    <t>AVG36115</t>
+  </si>
+  <si>
+    <t>AVG02471</t>
+  </si>
+  <si>
+    <t>AVG91234</t>
+  </si>
+  <si>
+    <t>AVG51289</t>
+  </si>
+  <si>
+    <t>AVG08663</t>
+  </si>
+  <si>
+    <t>$300</t>
+  </si>
+  <si>
+    <t>$1.5</t>
+  </si>
+  <si>
+    <t>AVG93836</t>
+  </si>
+  <si>
+    <t>AVG37270</t>
+  </si>
+  <si>
+    <t>AVG39529</t>
+  </si>
+  <si>
+    <t>AVG45996</t>
+  </si>
+  <si>
+    <t>AVG38726</t>
+  </si>
+  <si>
+    <t>AVG32588</t>
+  </si>
+  <si>
+    <t>AVG04770</t>
+  </si>
+  <si>
+    <t>AVG52284</t>
+  </si>
+  <si>
+    <t>AVG62854</t>
+  </si>
+  <si>
+    <t>AVG66823</t>
+  </si>
+  <si>
+    <t>AVG96905</t>
+  </si>
+  <si>
+    <t>$800</t>
+  </si>
+  <si>
+    <t>$4</t>
+  </si>
+  <si>
+    <t>AVG13952</t>
+  </si>
+  <si>
+    <t>AVG06726</t>
+  </si>
+  <si>
+    <t>AVG32973</t>
+  </si>
+  <si>
+    <t>AVG47615</t>
+  </si>
+  <si>
+    <t>AVG60570</t>
+  </si>
+  <si>
+    <t>AVG60594</t>
+  </si>
+  <si>
+    <t>AVG35889</t>
+  </si>
+  <si>
+    <t>AVG82579</t>
+  </si>
+  <si>
+    <t>AVG43886</t>
+  </si>
+  <si>
+    <t>AVG86176</t>
+  </si>
+  <si>
+    <t>AVG92069</t>
+  </si>
+  <si>
+    <t>AVG54350</t>
+  </si>
+  <si>
+    <t>AVG50211</t>
+  </si>
+  <si>
+    <t>AVG68261</t>
   </si>
   <si>
     <t>$600</t>
   </si>
   <si>
+    <t>AVG07959</t>
+  </si>
+  <si>
+    <t>AVG70278</t>
+  </si>
+  <si>
+    <t>AVG17583</t>
+  </si>
+  <si>
+    <t>AVG82389</t>
+  </si>
+  <si>
+    <t>AVG77981</t>
+  </si>
+  <si>
+    <t>$1600</t>
+  </si>
+  <si>
+    <t>$8</t>
+  </si>
+  <si>
+    <t>AVG65835</t>
+  </si>
+  <si>
+    <t>AVG75028</t>
+  </si>
+  <si>
+    <t>AVG54104</t>
+  </si>
+  <si>
+    <t>AVG36821</t>
+  </si>
+  <si>
+    <t>AVG23956</t>
+  </si>
+  <si>
+    <t>AVG19207</t>
+  </si>
+  <si>
+    <t>AVG03021</t>
+  </si>
+  <si>
+    <t>$400</t>
+  </si>
+  <si>
+    <t>$2</t>
+  </si>
+  <si>
+    <t>AVG14937</t>
+  </si>
+  <si>
+    <t>AVG37301</t>
+  </si>
+  <si>
+    <t>$700</t>
+  </si>
+  <si>
+    <t>$3.5</t>
+  </si>
+  <si>
+    <t>$1300</t>
+  </si>
+  <si>
+    <t>$6.5</t>
+  </si>
+  <si>
+    <t>AVG01831</t>
+  </si>
+  <si>
+    <t>$4400</t>
+  </si>
+  <si>
+    <t>$22</t>
+  </si>
+  <si>
+    <t>AVG64196</t>
+  </si>
+  <si>
+    <t>AVG78761</t>
+  </si>
+  <si>
+    <t>AVG93843</t>
+  </si>
+  <si>
+    <t>AVG85148</t>
+  </si>
+  <si>
+    <t>AVG26928</t>
+  </si>
+  <si>
+    <t>AVG42880</t>
+  </si>
+  <si>
+    <t>AVG65391</t>
+  </si>
+  <si>
+    <t>AVG02556</t>
+  </si>
+  <si>
+    <t>AVG35295</t>
+  </si>
+  <si>
+    <t>AVG95291</t>
+  </si>
+  <si>
+    <t>AVG04303</t>
+  </si>
+  <si>
+    <t>$900</t>
+  </si>
+  <si>
+    <t>AVG44516</t>
+  </si>
+  <si>
+    <t>$1900</t>
+  </si>
+  <si>
+    <t>$9.5</t>
+  </si>
+  <si>
+    <t>AVG76224</t>
+  </si>
+  <si>
+    <t>AVG25093</t>
+  </si>
+  <si>
+    <t>AVG80256</t>
+  </si>
+  <si>
+    <t>AVG94123</t>
+  </si>
+  <si>
+    <t>$3200</t>
+  </si>
+  <si>
+    <t>$16</t>
+  </si>
+  <si>
+    <t>AVG71865</t>
+  </si>
+  <si>
+    <t>AVG53601</t>
+  </si>
+  <si>
+    <t>AVG21368</t>
+  </si>
+  <si>
+    <t>$3300</t>
+  </si>
+  <si>
+    <t>$16.5</t>
+  </si>
+  <si>
+    <t>AVG40579</t>
+  </si>
+  <si>
+    <t>completed</t>
+  </si>
+  <si>
+    <t>AVG02038</t>
+  </si>
+  <si>
+    <t>AVG13619</t>
+  </si>
+  <si>
+    <t>AVG71938</t>
+  </si>
+  <si>
+    <t>AVG21003</t>
+  </si>
+  <si>
+    <t>AVG97326</t>
+  </si>
+  <si>
+    <t>AVG28384</t>
+  </si>
+  <si>
+    <t>AVG98351</t>
+  </si>
+  <si>
+    <t>AVG89351</t>
+  </si>
+  <si>
+    <t>AVG99875</t>
+  </si>
+  <si>
+    <t>$1700</t>
+  </si>
+  <si>
+    <t>$8.5</t>
+  </si>
+  <si>
+    <t>AVG25194</t>
+  </si>
+  <si>
+    <t>AVG54499</t>
+  </si>
+  <si>
+    <t>AVG76082</t>
+  </si>
+  <si>
+    <t>AVG39779</t>
+  </si>
+  <si>
+    <t>AVG46702</t>
+  </si>
+  <si>
     <t>$3</t>
   </si>
   <si>
-    <t>active</t>
-  </si>
-  <si>
-    <t>AVG56190</t>
-  </si>
-  <si>
-    <t>$200</t>
-  </si>
-  <si>
-    <t>$1</t>
-  </si>
-  <si>
-    <t>AVG27912</t>
-  </si>
-  <si>
-    <t>$1000</t>
-  </si>
-  <si>
-    <t>$5</t>
-  </si>
-  <si>
-    <t>AVG79320</t>
-  </si>
-  <si>
-    <t>AVG70261</t>
-  </si>
-  <si>
-    <t>$2200</t>
-  </si>
-  <si>
-    <t>$11</t>
-  </si>
-  <si>
-    <t>AVG55466</t>
-  </si>
-  <si>
-    <t>$500</t>
-  </si>
-  <si>
-    <t>$2.5</t>
-  </si>
-  <si>
-    <t>AVG71291</t>
-  </si>
-  <si>
-    <t>$3000</t>
-  </si>
-  <si>
-    <t>$15</t>
-  </si>
-  <si>
-    <t>AVG95589</t>
-  </si>
-  <si>
-    <t>$2000</t>
-  </si>
-  <si>
-    <t>$10</t>
-  </si>
-  <si>
-    <t>AVG77261</t>
-  </si>
-  <si>
-    <t>$100</t>
-  </si>
-  <si>
-    <t>$0.5</t>
-  </si>
-  <si>
-    <t>AVG35000</t>
-  </si>
-  <si>
-    <t>AVG44166</t>
-  </si>
-  <si>
-    <t>AVG41212</t>
-  </si>
-  <si>
-    <t>AVG18162</t>
-  </si>
-  <si>
-    <t>AVG44793</t>
-  </si>
-  <si>
-    <t>$1100</t>
-  </si>
-  <si>
-    <t>$5.5</t>
-  </si>
-  <si>
-    <t>AVG61984</t>
-  </si>
-  <si>
-    <t>AVG43359</t>
-  </si>
-  <si>
-    <t>AVG76462</t>
-  </si>
-  <si>
-    <t>AVG06662</t>
-  </si>
-  <si>
-    <t>AVG25998</t>
-  </si>
-  <si>
-    <t>AVG85139</t>
-  </si>
-  <si>
-    <t>AVG08399</t>
-  </si>
-  <si>
-    <t>$4000</t>
-  </si>
-  <si>
-    <t>$20</t>
-  </si>
-  <si>
-    <t>AVG45681</t>
-  </si>
-  <si>
-    <t>AVG04136</t>
-  </si>
-  <si>
-    <t>AVG97943</t>
-  </si>
-  <si>
-    <t>AVG36115</t>
-  </si>
-  <si>
-    <t>AVG02471</t>
-  </si>
-  <si>
-    <t>AVG91234</t>
-  </si>
-  <si>
-    <t>AVG51289</t>
-  </si>
-  <si>
-    <t>AVG08663</t>
-  </si>
-  <si>
-    <t>$300</t>
-  </si>
-  <si>
-    <t>$1.5</t>
-  </si>
-  <si>
-    <t>AVG93836</t>
-  </si>
-  <si>
-    <t>AVG37270</t>
-  </si>
-  <si>
-    <t>AVG39529</t>
-  </si>
-  <si>
-    <t>AVG45996</t>
-  </si>
-  <si>
-    <t>AVG38726</t>
-  </si>
-  <si>
-    <t>AVG32588</t>
-  </si>
-  <si>
-    <t>AVG04770</t>
-  </si>
-  <si>
-    <t>AVG52284</t>
-  </si>
-  <si>
-    <t>AVG62854</t>
-  </si>
-  <si>
-    <t>AVG66823</t>
-  </si>
-  <si>
-    <t>AVG96905</t>
-  </si>
-  <si>
-    <t>$800</t>
-  </si>
-  <si>
-    <t>$4</t>
-  </si>
-  <si>
-    <t>AVG13952</t>
-  </si>
-  <si>
-    <t>AVG06726</t>
-  </si>
-  <si>
-    <t>AVG32973</t>
-  </si>
-  <si>
-    <t>AVG47615</t>
-  </si>
-  <si>
-    <t>AVG60570</t>
-  </si>
-  <si>
-    <t>AVG60594</t>
-  </si>
-  <si>
-    <t>AVG35889</t>
-  </si>
-  <si>
-    <t>AVG82579</t>
-  </si>
-  <si>
-    <t>AVG43886</t>
-  </si>
-  <si>
-    <t>AVG86176</t>
-  </si>
-  <si>
-    <t>AVG92069</t>
-  </si>
-  <si>
-    <t>AVG54350</t>
-  </si>
-  <si>
-    <t>AVG50211</t>
-  </si>
-  <si>
-    <t>AVG68261</t>
-  </si>
-  <si>
-    <t>AVG07959</t>
-  </si>
-  <si>
-    <t>AVG70278</t>
-  </si>
-  <si>
-    <t>AVG17583</t>
-  </si>
-  <si>
-    <t>AVG82389</t>
-  </si>
-  <si>
-    <t>AVG77981</t>
-  </si>
-  <si>
-    <t>$1600</t>
-  </si>
-  <si>
-    <t>$8</t>
-  </si>
-  <si>
-    <t>AVG65835</t>
-  </si>
-  <si>
-    <t>AVG75028</t>
-  </si>
-  <si>
-    <t>AVG54104</t>
-  </si>
-  <si>
-    <t>AVG36821</t>
-  </si>
-  <si>
-    <t>AVG23956</t>
-  </si>
-  <si>
-    <t>AVG19207</t>
-  </si>
-  <si>
-    <t>AVG03021</t>
-  </si>
-  <si>
-    <t>$400</t>
-  </si>
-  <si>
-    <t>$2</t>
-  </si>
-  <si>
-    <t>AVG14937</t>
-  </si>
-  <si>
-    <t>AVG37301</t>
-  </si>
-  <si>
-    <t>$700</t>
-  </si>
-  <si>
-    <t>$3.5</t>
-  </si>
-  <si>
-    <t>$1300</t>
-  </si>
-  <si>
-    <t>$6.5</t>
-  </si>
-  <si>
-    <t>AVG01831</t>
-  </si>
-  <si>
-    <t>$4400</t>
-  </si>
-  <si>
-    <t>$22</t>
-  </si>
-  <si>
-    <t>AVG64196</t>
-  </si>
-  <si>
-    <t>AVG78761</t>
-  </si>
-  <si>
-    <t>AVG93843</t>
-  </si>
-  <si>
-    <t>AVG85148</t>
-  </si>
-  <si>
-    <t>AVG26928</t>
-  </si>
-  <si>
-    <t>AVG42880</t>
-  </si>
-  <si>
-    <t>AVG65391</t>
-  </si>
-  <si>
-    <t>AVG02556</t>
-  </si>
-  <si>
-    <t>AVG35295</t>
-  </si>
-  <si>
-    <t>AVG95291</t>
-  </si>
-  <si>
-    <t>AVG04303</t>
-  </si>
-  <si>
-    <t>$900</t>
-  </si>
-  <si>
-    <t>AVG44516</t>
-  </si>
-  <si>
-    <t>$1900</t>
-  </si>
-  <si>
-    <t>$9.5</t>
-  </si>
-  <si>
-    <t>AVG76224</t>
-  </si>
-  <si>
-    <t>AVG25093</t>
-  </si>
-  <si>
-    <t>AVG80256</t>
-  </si>
-  <si>
-    <t>AVG94123</t>
-  </si>
-  <si>
-    <t>$3200</t>
-  </si>
-  <si>
-    <t>$16</t>
-  </si>
-  <si>
-    <t>AVG71865</t>
-  </si>
-  <si>
-    <t>AVG53601</t>
-  </si>
-  <si>
-    <t>AVG21368</t>
-  </si>
-  <si>
-    <t>$3300</t>
-  </si>
-  <si>
-    <t>$16.5</t>
-  </si>
-  <si>
-    <t>AVG40579</t>
-  </si>
-  <si>
-    <t>completed</t>
-  </si>
-  <si>
-    <t>AVG02038</t>
-  </si>
-  <si>
-    <t>AVG13619</t>
-  </si>
-  <si>
-    <t>AVG71938</t>
-  </si>
-  <si>
-    <t>AVG21003</t>
-  </si>
-  <si>
-    <t>AVG97326</t>
-  </si>
-  <si>
-    <t>AVG28384</t>
-  </si>
-  <si>
-    <t>AVG98351</t>
-  </si>
-  <si>
-    <t>AVG89351</t>
-  </si>
-  <si>
-    <t>AVG99875</t>
-  </si>
-  <si>
-    <t>$1700</t>
-  </si>
-  <si>
-    <t>$8.5</t>
-  </si>
-  <si>
-    <t>AVG25194</t>
-  </si>
-  <si>
-    <t>AVG54499</t>
-  </si>
-  <si>
-    <t>AVG76082</t>
-  </si>
-  <si>
-    <t>AVG39779</t>
-  </si>
-  <si>
-    <t>AVG46702</t>
-  </si>
-  <si>
     <t>AVG27381</t>
   </si>
   <si>
@@ -667,9 +664,6 @@
   </si>
   <si>
     <t>AVG66419</t>
-  </si>
-  <si>
-    <t>$18000</t>
   </si>
   <si>
     <t>AVG19194</t>
@@ -886,7 +880,7 @@
     <t>AVG04505</t>
   </si>
   <si>
-    <t>AVG46557</t>
+    <t>AVG46577</t>
   </si>
   <si>
     <t>AVG15814</t>
@@ -1397,9 +1391,6 @@
   </si>
   <si>
     <t>AVG46322</t>
-  </si>
-  <si>
-    <t>AVG97443</t>
   </si>
   <si>
     <t>AVG36108</t>
@@ -1503,7 +1494,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1526,37 +1517,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1627,12 +1592,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1919,8 +1878,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A068414D-D5DC-4F32-BF5C-C94883387B89}" name="Table1" displayName="Table1" ref="B1:G208" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" headerRowBorderDxfId="7" tableBorderDxfId="8" totalsRowBorderDxfId="6">
-  <autoFilter ref="B1:G208" xr:uid="{A068414D-D5DC-4F32-BF5C-C94883387B89}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A068414D-D5DC-4F32-BF5C-C94883387B89}" name="Table1" displayName="Table1" ref="B1:G206" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" headerRowBorderDxfId="7" tableBorderDxfId="8" totalsRowBorderDxfId="6">
+  <autoFilter ref="B1:G206" xr:uid="{A068414D-D5DC-4F32-BF5C-C94883387B89}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{0951C96C-A09F-46F0-B8A4-F44C57261DCE}" name="user_code" dataDxfId="5"/>
     <tableColumn id="2" xr3:uid="{44BDBE98-A9D7-43E3-8176-9D46CA8814FB}" name="plan_id" dataDxfId="4"/>
@@ -2230,7 +2189,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G414"/>
+  <dimension ref="A1:G411"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="4"/>
@@ -2268,7 +2227,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="1"/>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="1">
@@ -2289,13 +2248,13 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1"/>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C3" s="1">
         <v>3</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>12</v>
       </c>
       <c r="E3" s="1" t="s">
@@ -2305,7 +2264,7 @@
         <v>10</v>
       </c>
       <c r="G3" s="6">
-        <v>46119</v>
+        <v>46118</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -2316,11 +2275,11 @@
       <c r="C4" s="1">
         <v>3</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>15</v>
+      <c r="D4" s="3" t="s">
+        <v>12</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>10</v>
@@ -2332,16 +2291,16 @@
     <row r="5" spans="1:7">
       <c r="A5" s="1"/>
       <c r="B5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="1">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="C5" s="1">
-        <v>3</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>10</v>
@@ -2392,7 +2351,7 @@
         <v>46118</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" ht="14.25">
       <c r="A8" s="1"/>
       <c r="B8" s="5" t="s">
         <v>24</v>
@@ -2409,12 +2368,11 @@
       <c r="F8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="6">
-        <v>46118</v>
+      <c r="G8" s="8">
+        <v>46117</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="14.25">
-      <c r="A9" s="1"/>
       <c r="B9" s="5" t="s">
         <v>27</v>
       </c>
@@ -2435,37 +2393,37 @@
       </c>
     </row>
     <row r="10" spans="1:7" ht="14.25">
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="7" t="s">
         <v>30</v>
       </c>
       <c r="C10" s="1">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="8">
+        <v>46116</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="14.25">
+      <c r="B11" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10" s="8">
-        <v>46117</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="14.25">
-      <c r="B11" s="7" t="s">
-        <v>33</v>
-      </c>
       <c r="C11" s="1">
         <v>3</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>10</v>
@@ -2475,17 +2433,17 @@
       </c>
     </row>
     <row r="12" spans="1:7" ht="14.25">
-      <c r="B12" s="5" t="s">
-        <v>34</v>
+      <c r="B12" s="7" t="s">
+        <v>32</v>
       </c>
       <c r="C12" s="1">
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>10</v>
@@ -2496,16 +2454,16 @@
     </row>
     <row r="13" spans="1:7" ht="14.25">
       <c r="B13" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C13" s="1">
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>10</v>
@@ -2516,22 +2474,22 @@
     </row>
     <row r="14" spans="1:7" ht="14.25">
       <c r="B14" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="1">
+        <v>3</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="1">
-        <v>3</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="F14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G14" s="8">
-        <v>46116</v>
+        <v>46114</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="14.25">
@@ -2542,10 +2500,10 @@
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>10</v>
@@ -2556,16 +2514,16 @@
     </row>
     <row r="16" spans="1:7" ht="14.25">
       <c r="B16" s="7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C16" s="1">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>10</v>
@@ -2576,96 +2534,96 @@
     </row>
     <row r="17" spans="2:7" ht="14.25">
       <c r="B17" s="7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C17" s="1">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G17" s="8">
-        <v>46114</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="14.25">
       <c r="B18" s="7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C18" s="1">
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G18" s="8">
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" ht="14.25">
+      <c r="B19" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="1">
+        <v>3</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="8">
+        <v>46114</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" ht="14.25">
+      <c r="B20" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="1">
+        <v>3</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" s="8">
         <v>46113</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" ht="14.25">
-      <c r="B19" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C19" s="1">
-        <v>3</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G19" s="8">
-        <v>46118</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" ht="14.25">
-      <c r="B20" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" s="1">
-        <v>3</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G20" s="8">
-        <v>46114</v>
       </c>
     </row>
     <row r="21" spans="2:7" ht="14.25">
       <c r="B21" s="7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C21" s="1">
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>10</v>
@@ -2676,22 +2634,22 @@
     </row>
     <row r="22" spans="2:7" ht="14.25">
       <c r="B22" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" s="1">
+        <v>3</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E22" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C22" s="1">
-        <v>3</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="F22" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G22" s="8">
-        <v>46113</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="23" spans="2:7" ht="14.25">
@@ -2702,30 +2660,30 @@
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G23" s="8">
-        <v>46112</v>
+        <v>46111</v>
       </c>
     </row>
     <row r="24" spans="2:7" ht="14.25">
       <c r="B24" s="7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C24" s="1">
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>10</v>
@@ -2736,16 +2694,16 @@
     </row>
     <row r="25" spans="2:7" ht="14.25">
       <c r="B25" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C25" s="1">
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>10</v>
@@ -2756,16 +2714,16 @@
     </row>
     <row r="26" spans="2:7" ht="14.25">
       <c r="B26" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C26" s="1">
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>10</v>
@@ -2776,85 +2734,85 @@
     </row>
     <row r="27" spans="2:7" ht="14.25">
       <c r="B27" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C27" s="1">
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G27" s="8">
-        <v>46111</v>
+        <v>46112</v>
       </c>
     </row>
     <row r="28" spans="2:7" ht="14.25">
       <c r="B28" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C28" s="1">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F28" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G28" s="8">
-        <v>46112</v>
+        <v>46110</v>
       </c>
     </row>
     <row r="29" spans="2:7" ht="14.25">
       <c r="B29" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C29" s="1">
+        <v>3</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29" s="8">
+        <v>46109</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7">
+      <c r="B30" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C30" s="1">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C29" s="1">
-        <v>3</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G29" s="8">
-        <v>46110</v>
-      </c>
-    </row>
-    <row r="30" spans="2:7" ht="14.25">
-      <c r="B30" s="7" t="s">
+      <c r="E30" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C30" s="1">
-        <v>3</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="F30" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G30" s="8">
-        <v>46109</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7">
+      <c r="G30" s="9">
+        <v>46108</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" ht="14.25">
       <c r="B31" s="7" t="s">
         <v>56</v>
       </c>
@@ -2862,30 +2820,30 @@
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G31" s="9">
+      <c r="G31" s="8">
         <v>46108</v>
       </c>
     </row>
     <row r="32" spans="2:7" ht="14.25">
       <c r="B32" s="7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C32" s="1">
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>10</v>
@@ -2896,36 +2854,36 @@
     </row>
     <row r="33" spans="2:7" ht="14.25">
       <c r="B33" s="7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C33" s="1">
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G33" s="8">
-        <v>46108</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="34" spans="2:7" ht="14.25">
       <c r="B34" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C34" s="1">
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>10</v>
@@ -2936,16 +2894,16 @@
     </row>
     <row r="35" spans="2:7" ht="14.25">
       <c r="B35" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C35" s="1">
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>10</v>
@@ -2956,36 +2914,36 @@
     </row>
     <row r="36" spans="2:7" ht="14.25">
       <c r="B36" s="7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C36" s="1">
         <v>3</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G36" s="8">
-        <v>46107</v>
+        <v>46118</v>
       </c>
     </row>
     <row r="37" spans="2:7" ht="14.25">
       <c r="B37" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C37" s="1">
         <v>3</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>10</v>
@@ -2996,36 +2954,36 @@
     </row>
     <row r="38" spans="2:7" ht="14.25">
       <c r="B38" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C38" s="1">
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
+      </c>
+      <c r="E38" s="1">
+        <v>5</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G38" s="8">
-        <v>46118</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="39" spans="2:7" ht="14.25">
       <c r="B39" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C39" s="1">
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E39" s="1">
-        <v>5</v>
+        <v>28</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>10</v>
@@ -3036,16 +2994,16 @@
     </row>
     <row r="40" spans="2:7" ht="14.25">
       <c r="B40" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C40" s="1">
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>10</v>
@@ -3056,22 +3014,22 @@
     </row>
     <row r="41" spans="2:7" ht="14.25">
       <c r="B41" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C41" s="1">
+        <v>3</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C41" s="1">
-        <v>3</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="F41" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G41" s="8">
-        <v>46107</v>
+        <v>46106</v>
       </c>
     </row>
     <row r="42" spans="2:7" ht="14.25">
@@ -3082,10 +3040,10 @@
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>71</v>
+        <v>29</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>10</v>
@@ -3096,16 +3054,16 @@
     </row>
     <row r="43" spans="2:7" ht="14.25">
       <c r="B43" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C43" s="1">
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>10</v>
@@ -3116,36 +3074,36 @@
     </row>
     <row r="44" spans="2:7" ht="14.25">
       <c r="B44" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C44" s="1">
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G44" s="8">
-        <v>46106</v>
+        <v>46105</v>
       </c>
     </row>
     <row r="45" spans="2:7" ht="14.25">
       <c r="B45" s="7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C45" s="1">
         <v>3</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>10</v>
@@ -3156,27 +3114,27 @@
     </row>
     <row r="46" spans="2:7" ht="14.25">
       <c r="B46" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C46" s="1">
         <v>3</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G46" s="8">
-        <v>46105</v>
+        <v>46104</v>
       </c>
     </row>
     <row r="47" spans="2:7" ht="14.25">
       <c r="B47" s="7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C47" s="1">
         <v>3</v>
@@ -3191,121 +3149,121 @@
         <v>10</v>
       </c>
       <c r="G47" s="8">
-        <v>46104</v>
+        <v>46101</v>
       </c>
     </row>
     <row r="48" spans="2:7" ht="14.25">
       <c r="B48" s="7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C48" s="1">
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G48" s="8">
-        <v>46101</v>
+        <v>46102</v>
       </c>
     </row>
     <row r="49" spans="2:7" ht="14.25">
       <c r="B49" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C49" s="1">
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G49" s="8">
-        <v>46102</v>
+        <v>46100</v>
       </c>
     </row>
     <row r="50" spans="2:7" ht="14.25">
       <c r="B50" s="7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C50" s="1">
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G50" s="8">
-        <v>46100</v>
+        <v>46111</v>
       </c>
     </row>
     <row r="51" spans="2:7" ht="14.25">
       <c r="B51" s="7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C51" s="1">
         <v>3</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G51" s="8">
-        <v>46111</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="52" spans="2:7" ht="14.25">
       <c r="B52" s="7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C52" s="1">
         <v>3</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G52" s="8">
-        <v>46099</v>
+        <v>46100</v>
       </c>
     </row>
     <row r="53" spans="2:7" ht="14.25">
       <c r="B53" s="7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C53" s="1">
         <v>3</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>10</v>
@@ -3316,36 +3274,36 @@
     </row>
     <row r="54" spans="2:7" ht="14.25">
       <c r="B54" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C54" s="1">
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G54" s="8">
-        <v>46100</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="55" spans="2:7" ht="14.25">
       <c r="B55" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C55" s="1">
         <v>3</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>15</v>
+        <v>83</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>16</v>
+        <v>54</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>10</v>
@@ -3356,16 +3314,16 @@
     </row>
     <row r="56" spans="2:7" ht="14.25">
       <c r="B56" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C56" s="1">
         <v>3</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>57</v>
+        <v>29</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>10</v>
@@ -3376,16 +3334,16 @@
     </row>
     <row r="57" spans="2:7" ht="14.25">
       <c r="B57" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C57" s="1">
         <v>3</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>10</v>
@@ -3396,16 +3354,16 @@
     </row>
     <row r="58" spans="2:7" ht="14.25">
       <c r="B58" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C58" s="1">
         <v>3</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>10</v>
@@ -3416,16 +3374,16 @@
     </row>
     <row r="59" spans="2:7" ht="14.25">
       <c r="B59" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C59" s="1">
         <v>3</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>10</v>
@@ -3436,116 +3394,116 @@
     </row>
     <row r="60" spans="2:7" ht="14.25">
       <c r="B60" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="C60" s="1">
+        <v>3</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G60" s="8">
+        <v>46100</v>
+      </c>
+    </row>
+    <row r="61" spans="2:7" ht="14.25">
+      <c r="B61" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C61" s="1">
+        <v>3</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C60" s="1">
-        <v>3</v>
-      </c>
-      <c r="D60" s="1" t="s">
+      <c r="E61" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G61" s="8">
+        <v>46099</v>
+      </c>
+    </row>
+    <row r="62" spans="2:7" ht="14.25">
+      <c r="B62" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C62" s="1">
+        <v>3</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E60" s="1" t="s">
+      <c r="E62" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F60" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G60" s="8">
-        <v>46099</v>
-      </c>
-    </row>
-    <row r="61" spans="2:7" ht="14.25">
-      <c r="B61" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C61" s="1">
-        <v>3</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G61" s="8">
-        <v>46100</v>
-      </c>
-    </row>
-    <row r="62" spans="2:7" ht="14.25">
-      <c r="B62" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="C62" s="1">
-        <v>3</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>92</v>
-      </c>
       <c r="F62" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G62" s="8">
-        <v>46099</v>
+        <v>46098</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="14.25">
       <c r="B63" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C63" s="1">
         <v>3</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G63" s="8">
-        <v>46098</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="64" spans="2:7" ht="14.25">
       <c r="B64" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C64" s="1">
         <v>3</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G64" s="8">
-        <v>46099</v>
+        <v>46098</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="14.25">
       <c r="B65" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C65" s="1">
         <v>3</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="F65" s="1" t="s">
         <v>10</v>
@@ -3556,167 +3514,167 @@
     </row>
     <row r="66" spans="2:7" ht="14.25">
       <c r="B66" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C66" s="1">
         <v>3</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G66" s="8">
-        <v>46098</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="67" spans="2:7" ht="14.25">
       <c r="B67" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C67" s="1">
         <v>3</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G67" s="8">
-        <v>46099</v>
+        <v>46097</v>
       </c>
     </row>
     <row r="68" spans="2:7" ht="14.25">
       <c r="B68" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C68" s="1">
+        <v>3</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="C68" s="1">
-        <v>3</v>
-      </c>
-      <c r="D68" s="1" t="s">
+      <c r="E68" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G68" s="8">
+        <v>46105</v>
+      </c>
+    </row>
+    <row r="69" spans="2:7" ht="14.25">
+      <c r="B69" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C69" s="1">
+        <v>3</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E68" s="1" t="s">
+      <c r="E69" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F68" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G68" s="8">
-        <v>46097</v>
-      </c>
-    </row>
-    <row r="69" spans="2:7" ht="14.25">
-      <c r="B69" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="C69" s="1">
-        <v>3</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>101</v>
-      </c>
       <c r="F69" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G69" s="8">
-        <v>46105</v>
+        <v>46098</v>
       </c>
     </row>
     <row r="70" spans="2:7" ht="14.25">
-      <c r="B70" s="5" t="s">
-        <v>99</v>
+      <c r="B70" s="7" t="s">
+        <v>100</v>
       </c>
       <c r="C70" s="1">
         <v>3</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G70" s="8">
-        <v>46098</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="71" spans="2:7" ht="14.25">
       <c r="B71" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C71" s="1">
         <v>3</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G71" s="8">
-        <v>46099</v>
+        <v>46105</v>
       </c>
     </row>
     <row r="72" spans="2:7" ht="14.25">
-      <c r="B72" s="7" t="s">
-        <v>103</v>
+      <c r="B72" s="5" t="s">
+        <v>101</v>
       </c>
       <c r="C72" s="1">
         <v>3</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G72" s="8">
-        <v>46105</v>
+        <v>46103</v>
       </c>
     </row>
     <row r="73" spans="2:7" ht="14.25">
       <c r="B73" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C73" s="1">
+        <v>3</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E73" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="C73" s="1">
-        <v>3</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="F73" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G73" s="8">
-        <v>46103</v>
+        <v>46102</v>
       </c>
     </row>
     <row r="74" spans="2:7" ht="14.25">
       <c r="B74" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C74" s="1">
         <v>3</v>
@@ -3731,101 +3689,101 @@
         <v>10</v>
       </c>
       <c r="G74" s="8">
-        <v>46102</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="75" spans="2:7" ht="14.25">
       <c r="B75" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C75" s="1">
         <v>3</v>
       </c>
       <c r="D75" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G75" s="8">
+        <v>46097</v>
+      </c>
+    </row>
+    <row r="76" spans="2:7" ht="14.25">
+      <c r="B76" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="E75" s="1" t="s">
+      <c r="C76" s="1">
+        <v>3</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="F75" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G75" s="8">
-        <v>46099</v>
-      </c>
-    </row>
-    <row r="76" spans="2:7" ht="14.25">
-      <c r="B76" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="C76" s="1">
-        <v>3</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="E76" s="1" t="s">
-        <v>13</v>
+        <v>108</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G76" s="8">
-        <v>46097</v>
+        <v>46096</v>
       </c>
     </row>
     <row r="77" spans="2:7" ht="14.25">
       <c r="B77" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C77" s="1">
         <v>3</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>109</v>
+        <v>28</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>110</v>
+        <v>29</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G77" s="8">
-        <v>46096</v>
+        <v>46097</v>
       </c>
     </row>
     <row r="78" spans="2:7" ht="14.25">
       <c r="B78" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C78" s="1">
         <v>3</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G78" s="8">
-        <v>46097</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="79" spans="2:7" ht="14.25">
       <c r="B79" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C79" s="1">
         <v>3</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>10</v>
@@ -3836,96 +3794,96 @@
     </row>
     <row r="80" spans="2:7" ht="14.25">
       <c r="B80" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C80" s="1">
         <v>3</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G80" s="8">
-        <v>46095</v>
+        <v>46106</v>
       </c>
     </row>
     <row r="81" spans="2:7" ht="14.25">
       <c r="B81" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C81" s="1">
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G81" s="8">
-        <v>46106</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="82" spans="2:7" ht="14.25">
       <c r="B82" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C82" s="1">
         <v>3</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G82" s="8">
-        <v>46095</v>
+        <v>46101</v>
       </c>
     </row>
     <row r="83" spans="2:7" ht="14.25">
       <c r="B83" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C83" s="1">
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G83" s="8">
-        <v>46101</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="84" spans="2:7" ht="14.25">
       <c r="B84" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C84" s="1">
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>10</v>
@@ -3936,16 +3894,16 @@
     </row>
     <row r="85" spans="2:7" ht="14.25">
       <c r="B85" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C85" s="1">
         <v>3</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>10</v>
@@ -3956,16 +3914,16 @@
     </row>
     <row r="86" spans="2:7" ht="14.25">
       <c r="B86" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C86" s="1">
         <v>3</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>10</v>
@@ -3976,96 +3934,96 @@
     </row>
     <row r="87" spans="2:7" ht="14.25">
       <c r="B87" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C87" s="1">
+        <v>3</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G87" s="8">
+        <v>46110</v>
+      </c>
+    </row>
+    <row r="88" spans="2:7" ht="14.25">
+      <c r="B88" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C88" s="1">
+        <v>3</v>
+      </c>
+      <c r="D88" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C87" s="1">
-        <v>3</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F87" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G87" s="8">
-        <v>46095</v>
-      </c>
-    </row>
-    <row r="88" spans="2:7" ht="14.25">
-      <c r="B88" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="C88" s="1">
-        <v>3</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="E88" s="1" t="s">
-        <v>23</v>
+        <v>103</v>
       </c>
       <c r="F88" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G88" s="8">
-        <v>46110</v>
+        <v>46098</v>
       </c>
     </row>
     <row r="89" spans="2:7" ht="14.25">
       <c r="B89" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C89" s="1">
+        <v>3</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G89" s="8">
+        <v>46095</v>
+      </c>
+    </row>
+    <row r="90" spans="2:7" ht="14.25">
+      <c r="B90" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C89" s="1">
-        <v>3</v>
-      </c>
-      <c r="D89" s="1" t="s">
+      <c r="C90" s="1">
+        <v>3</v>
+      </c>
+      <c r="D90" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="E89" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="F89" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G89" s="8">
-        <v>46098</v>
-      </c>
-    </row>
-    <row r="90" spans="2:7" ht="14.25">
-      <c r="B90" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="C90" s="1">
-        <v>3</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="E90" s="1" t="s">
-        <v>32</v>
+        <v>123</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G90" s="8">
-        <v>46095</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="91" spans="2:7" ht="14.25">
       <c r="B91" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C91" s="1">
         <v>3</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>125</v>
+        <v>29</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>10</v>
@@ -4076,16 +4034,16 @@
     </row>
     <row r="92" spans="2:7" ht="14.25">
       <c r="B92" s="7" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C92" s="1">
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>10</v>
@@ -4096,16 +4054,16 @@
     </row>
     <row r="93" spans="2:7" ht="14.25">
       <c r="B93" s="7" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C93" s="1">
         <v>3</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>10</v>
@@ -4116,16 +4074,16 @@
     </row>
     <row r="94" spans="2:7" ht="14.25">
       <c r="B94" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C94" s="1">
+        <v>3</v>
+      </c>
+      <c r="D94" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C94" s="1">
-        <v>3</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="E94" s="1" t="s">
-        <v>32</v>
+        <v>129</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>10</v>
@@ -4136,16 +4094,16 @@
     </row>
     <row r="95" spans="2:7" ht="14.25">
       <c r="B95" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C95" s="1">
         <v>3</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>130</v>
+        <v>28</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>131</v>
+        <v>29</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>10</v>
@@ -4156,96 +4114,96 @@
     </row>
     <row r="96" spans="2:7" ht="14.25">
       <c r="B96" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C96" s="1">
+        <v>3</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G96" s="8">
+        <v>46096</v>
+      </c>
+    </row>
+    <row r="97" spans="2:7" ht="14.25">
+      <c r="B97" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C97" s="1">
+        <v>3</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G97" s="8">
+        <v>46094</v>
+      </c>
+    </row>
+    <row r="98" spans="2:7" ht="14.25">
+      <c r="B98" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="C96" s="1">
-        <v>3</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F96" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G96" s="8">
+      <c r="C98" s="1">
+        <v>3</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G98" s="8">
+        <v>46097</v>
+      </c>
+    </row>
+    <row r="99" spans="2:7" ht="14.25">
+      <c r="B99" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="C99" s="1">
+        <v>3</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G99" s="8">
         <v>46094</v>
       </c>
     </row>
-    <row r="97" spans="2:7" ht="14.25">
-      <c r="B97" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="C97" s="1">
-        <v>3</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F97" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G97" s="8">
-        <v>46096</v>
-      </c>
-    </row>
-    <row r="98" spans="2:7" ht="14.25">
-      <c r="B98" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="C98" s="1">
-        <v>3</v>
-      </c>
-      <c r="D98" s="1" t="s">
+    <row r="100" spans="2:7" ht="14.25">
+      <c r="B100" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="C100" s="1">
+        <v>3</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E98" s="1" t="s">
+      <c r="E100" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="F98" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G98" s="8">
-        <v>46094</v>
-      </c>
-    </row>
-    <row r="99" spans="2:7" ht="14.25">
-      <c r="B99" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="C99" s="1">
-        <v>3</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="F99" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G99" s="8">
-        <v>46097</v>
-      </c>
-    </row>
-    <row r="100" spans="2:7" ht="14.25">
-      <c r="B100" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="C100" s="1">
-        <v>3</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>136</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>10</v>
@@ -4255,27 +4213,27 @@
       </c>
     </row>
     <row r="101" spans="2:7" ht="14.25">
-      <c r="B101" s="7" t="s">
-        <v>137</v>
+      <c r="B101" s="5" t="s">
+        <v>135</v>
       </c>
       <c r="C101" s="1">
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>10</v>
+        <v>136</v>
       </c>
       <c r="G101" s="8">
         <v>46094</v>
       </c>
     </row>
     <row r="102" spans="2:7" ht="14.25">
-      <c r="B102" s="5" t="s">
+      <c r="B102" s="7" t="s">
         <v>137</v>
       </c>
       <c r="C102" s="1">
@@ -4288,7 +4246,7 @@
         <v>13</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>138</v>
+        <v>10</v>
       </c>
       <c r="G102" s="8">
         <v>46094</v>
@@ -4296,16 +4254,16 @@
     </row>
     <row r="103" spans="2:7" ht="14.25">
       <c r="B103" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C103" s="1">
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>10</v>
@@ -4316,156 +4274,156 @@
     </row>
     <row r="104" spans="2:7" ht="14.25">
       <c r="B104" s="7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C104" s="1">
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G104" s="8">
-        <v>46094</v>
+        <v>46093</v>
       </c>
     </row>
     <row r="105" spans="2:7" ht="14.25">
       <c r="B105" s="7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C105" s="1">
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G105" s="8">
-        <v>46093</v>
+        <v>46100</v>
       </c>
     </row>
     <row r="106" spans="2:7" ht="14.25">
       <c r="B106" s="7" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C106" s="1">
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G106" s="8">
-        <v>46100</v>
+        <v>46092</v>
       </c>
     </row>
     <row r="107" spans="2:7" ht="14.25">
       <c r="B107" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C107" s="1">
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G107" s="8">
-        <v>46092</v>
+        <v>46093</v>
       </c>
     </row>
     <row r="108" spans="2:7" ht="14.25">
       <c r="B108" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C108" s="1">
         <v>3</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G108" s="8">
-        <v>46093</v>
+        <v>46092</v>
       </c>
     </row>
     <row r="109" spans="2:7" ht="14.25">
       <c r="B109" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C109" s="1">
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G109" s="8">
-        <v>46092</v>
+        <v>46090</v>
       </c>
     </row>
     <row r="110" spans="2:7" ht="14.25">
       <c r="B110" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="C110" s="1">
+        <v>3</v>
+      </c>
+      <c r="D110" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="C110" s="1">
-        <v>3</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="E110" s="1" t="s">
-        <v>32</v>
+        <v>147</v>
       </c>
       <c r="F110" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G110" s="8">
-        <v>46090</v>
+        <v>46089</v>
       </c>
     </row>
     <row r="111" spans="2:7" ht="14.25">
       <c r="B111" s="7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C111" s="1">
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>148</v>
+        <v>28</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>149</v>
+        <v>29</v>
       </c>
       <c r="F111" s="1" t="s">
         <v>10</v>
@@ -4476,82 +4434,82 @@
     </row>
     <row r="112" spans="2:7" ht="14.25">
       <c r="B112" s="7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C112" s="1">
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G112" s="8">
-        <v>46089</v>
+        <v>46088</v>
       </c>
     </row>
     <row r="113" spans="2:7" ht="14.25">
       <c r="B113" s="7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C113" s="1">
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="F113" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G113" s="8">
-        <v>46088</v>
+        <v>46092</v>
       </c>
     </row>
     <row r="114" spans="2:7" ht="14.25">
       <c r="B114" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C114" s="1">
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G114" s="8">
-        <v>46092</v>
+        <v>46088</v>
       </c>
     </row>
     <row r="115" spans="2:7" ht="14.25">
       <c r="B115" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="C115" s="1">
+        <v>3</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E115" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="C115" s="1">
-        <v>3</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="F115" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G115" s="8">
-        <v>46088</v>
+        <v>46103</v>
       </c>
     </row>
     <row r="116" spans="2:7" ht="14.25">
@@ -4562,16 +4520,16 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G116" s="8">
-        <v>46103</v>
+        <v>46090</v>
       </c>
     </row>
     <row r="117" spans="2:7" ht="14.25">
@@ -4582,16 +4540,16 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G117" s="8">
-        <v>46090</v>
+        <v>46087</v>
       </c>
     </row>
     <row r="118" spans="2:7" ht="14.25">
@@ -4602,10 +4560,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>10</v>
@@ -4622,30 +4580,30 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>31</v>
+        <v>158</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G119" s="8">
-        <v>46087</v>
+        <v>46088</v>
       </c>
     </row>
     <row r="120" spans="2:7" ht="14.25">
       <c r="B120" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C120" s="1">
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>159</v>
+        <v>12</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>10</v>
@@ -4662,10 +4620,10 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>10</v>
@@ -4682,16 +4640,16 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G122" s="8">
-        <v>46088</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="123" spans="2:7" ht="14.25">
@@ -4702,16 +4660,16 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G123" s="8">
-        <v>46094</v>
+        <v>46086</v>
       </c>
     </row>
     <row r="124" spans="2:7" ht="14.25">
@@ -4722,10 +4680,10 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>39</v>
+        <v>153</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>10</v>
@@ -4742,16 +4700,16 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="F125" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G125" s="8">
-        <v>46086</v>
+        <v>46085</v>
       </c>
     </row>
     <row r="126" spans="2:7" ht="14.25">
@@ -4762,10 +4720,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>10</v>
@@ -4782,10 +4740,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>10</v>
@@ -4802,10 +4760,10 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>10</v>
@@ -4822,10 +4780,10 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>10</v>
@@ -4842,16 +4800,16 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G130" s="8">
-        <v>46085</v>
+        <v>46094</v>
       </c>
     </row>
     <row r="131" spans="2:7" ht="14.25">
@@ -4862,16 +4820,16 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G131" s="8">
-        <v>46094</v>
+        <v>46085</v>
       </c>
     </row>
     <row r="132" spans="2:7" ht="14.25">
@@ -4882,10 +4840,10 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>10</v>
@@ -4902,10 +4860,10 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>10</v>
@@ -4922,16 +4880,16 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G134" s="8">
-        <v>46085</v>
+        <v>46084</v>
       </c>
     </row>
     <row r="135" spans="2:7" ht="14.25">
@@ -4942,16 +4900,16 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>31</v>
+        <v>133</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>32</v>
+        <v>134</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G135" s="8">
-        <v>46084</v>
+        <v>46085</v>
       </c>
     </row>
     <row r="136" spans="2:7" ht="14.25">
@@ -4962,110 +4920,110 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>135</v>
+        <v>54</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>136</v>
+        <v>55</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G136" s="8">
-        <v>46085</v>
+        <v>46118</v>
       </c>
     </row>
     <row r="137" spans="2:7" ht="14.25">
-      <c r="B137" s="7" t="s">
+      <c r="B137" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="C137" s="1">
+        <v>3</v>
+      </c>
+      <c r="D137" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="C137" s="1">
-        <v>3</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>57</v>
-      </c>
       <c r="E137" s="1" t="s">
-        <v>58</v>
+        <v>134</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G137" s="8">
-        <v>46118</v>
+        <v>46084</v>
       </c>
     </row>
     <row r="138" spans="2:7" ht="14.25">
-      <c r="B138" s="5" t="s">
-        <v>176</v>
+      <c r="B138" s="7" t="s">
+        <v>177</v>
       </c>
       <c r="C138" s="1">
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G138" s="8">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="139" spans="2:7" ht="14.25">
+      <c r="B139" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="E138" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="F138" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G138" s="8">
-        <v>46084</v>
-      </c>
-    </row>
-    <row r="139" spans="2:7" ht="14.25">
-      <c r="B139" s="7" t="s">
-        <v>178</v>
-      </c>
       <c r="C139" s="1">
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G139" s="8">
-        <v>46112</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="140" spans="2:7" ht="14.25">
       <c r="B140" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="C140" s="1">
+        <v>3</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G140" s="8">
+        <v>46084</v>
+      </c>
+    </row>
+    <row r="141" spans="2:7" ht="14.25">
+      <c r="B141" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="C140" s="1">
-        <v>3</v>
-      </c>
-      <c r="D140" s="1" t="s">
+      <c r="C141" s="1">
+        <v>3</v>
+      </c>
+      <c r="D141" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E140" s="1" t="s">
+      <c r="E141" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="F140" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G140" s="8">
-        <v>46095</v>
-      </c>
-    </row>
-    <row r="141" spans="2:7" ht="14.25">
-      <c r="B141" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="C141" s="1">
-        <v>3</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E141" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>10</v>
@@ -5082,10 +5040,10 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>10</v>
@@ -5102,10 +5060,10 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>10</v>
@@ -5122,10 +5080,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>10</v>
@@ -5142,16 +5100,16 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G145" s="8">
-        <v>46084</v>
+        <v>46098</v>
       </c>
     </row>
     <row r="146" spans="2:7" ht="14.25">
@@ -5162,16 +5120,16 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G146" s="8">
-        <v>46098</v>
+        <v>46086</v>
       </c>
     </row>
     <row r="147" spans="2:7" ht="14.25">
@@ -5182,16 +5140,16 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G147" s="8">
-        <v>46086</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="148" spans="2:7" ht="14.25">
@@ -5202,16 +5160,16 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G148" s="8">
-        <v>46099</v>
+        <v>46082</v>
       </c>
     </row>
     <row r="149" spans="2:7" ht="14.25">
@@ -5222,56 +5180,56 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="F149" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G149" s="8">
-        <v>46082</v>
+        <v>46103</v>
       </c>
     </row>
     <row r="150" spans="2:7" ht="14.25">
-      <c r="B150" s="7" t="s">
+      <c r="B150" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="C150" s="1">
+        <v>3</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F150" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G150" s="8">
+        <v>46095</v>
+      </c>
+    </row>
+    <row r="151" spans="2:7" ht="14.25">
+      <c r="B151" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="C150" s="1">
-        <v>3</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E150" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F150" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G150" s="8">
-        <v>46103</v>
-      </c>
-    </row>
-    <row r="151" spans="2:7" ht="14.25">
-      <c r="B151" s="5" t="s">
-        <v>187</v>
-      </c>
       <c r="C151" s="1">
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G151" s="8">
-        <v>46095</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="152" spans="2:7" ht="14.25">
@@ -5282,16 +5240,16 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F152" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G152" s="8">
-        <v>46081</v>
+        <v>46080</v>
       </c>
     </row>
     <row r="153" spans="2:7" ht="14.25">
@@ -5302,10 +5260,10 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F153" s="1" t="s">
         <v>10</v>
@@ -5322,10 +5280,10 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>10</v>
@@ -5342,16 +5300,16 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G155" s="8">
-        <v>46080</v>
+        <v>46079</v>
       </c>
     </row>
     <row r="156" spans="2:7" ht="14.25">
@@ -5362,10 +5320,10 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>10</v>
@@ -5382,10 +5340,10 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>10</v>
@@ -5402,10 +5360,10 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>10</v>
@@ -5422,10 +5380,10 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>10</v>
@@ -5442,10 +5400,10 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>10</v>
@@ -5462,73 +5420,73 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G161" s="8">
-        <v>46079</v>
+        <v>46114</v>
       </c>
     </row>
     <row r="162" spans="2:7" ht="14.25">
-      <c r="B162" s="7" t="s">
-        <v>198</v>
+      <c r="B162" s="5" t="s">
+        <v>197</v>
       </c>
       <c r="C162" s="1">
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>10</v>
+        <v>136</v>
       </c>
       <c r="G162" s="8">
-        <v>46114</v>
+        <v>46097</v>
       </c>
     </row>
     <row r="163" spans="2:7" ht="14.25">
       <c r="B163" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="C163" s="1">
+        <v>3</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F163" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="G163" s="8">
+        <v>46079</v>
+      </c>
+    </row>
+    <row r="164" spans="2:7" ht="14.25">
+      <c r="B164" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="C163" s="1">
-        <v>3</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E163" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F163" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="G163" s="8">
-        <v>46097</v>
-      </c>
-    </row>
-    <row r="164" spans="2:7" ht="14.25">
-      <c r="B164" s="5" t="s">
-        <v>198</v>
-      </c>
       <c r="C164" s="1">
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>138</v>
+        <v>10</v>
       </c>
       <c r="G164" s="8">
         <v>46079</v>
@@ -5542,10 +5500,10 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>10</v>
@@ -5562,10 +5520,10 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>10</v>
@@ -5582,10 +5540,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>10</v>
@@ -5602,56 +5560,56 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>16</v>
+        <v>203</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G168" s="8">
-        <v>46079</v>
+        <v>46111</v>
       </c>
     </row>
     <row r="169" spans="2:7" ht="14.25">
-      <c r="B169" s="7" t="s">
-        <v>203</v>
+      <c r="B169" s="5" t="s">
+        <v>202</v>
       </c>
       <c r="C169" s="1">
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>122</v>
+        <v>28</v>
       </c>
       <c r="E169" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F169" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="G169" s="8">
+        <v>46083</v>
+      </c>
+    </row>
+    <row r="170" spans="2:7" ht="14.25">
+      <c r="B170" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="F169" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G169" s="8">
-        <v>46111</v>
-      </c>
-    </row>
-    <row r="170" spans="2:7" ht="14.25">
-      <c r="B170" s="5" t="s">
-        <v>203</v>
-      </c>
       <c r="C170" s="1">
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>138</v>
+        <v>10</v>
       </c>
       <c r="G170" s="8">
-        <v>46083</v>
+        <v>46107</v>
       </c>
     </row>
     <row r="171" spans="2:7" ht="14.25">
@@ -5662,16 +5620,16 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G171" s="8">
-        <v>46107</v>
+        <v>46079</v>
       </c>
     </row>
     <row r="172" spans="2:7" ht="14.25">
@@ -5682,36 +5640,36 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>31</v>
+        <v>207</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>32</v>
+        <v>208</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G172" s="8">
-        <v>46079</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="173" spans="2:7" ht="14.25">
       <c r="B173" s="7" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C173" s="1">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>208</v>
+        <v>67</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>209</v>
+        <v>68</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G173" s="8">
-        <v>46113</v>
+        <v>46079</v>
       </c>
     </row>
     <row r="174" spans="2:7" ht="14.25">
@@ -5722,16 +5680,16 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>70</v>
+        <v>207</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>71</v>
+        <v>208</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G174" s="8">
-        <v>46079</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="175" spans="2:7" ht="14.25">
@@ -5742,56 +5700,56 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>212</v>
+        <v>98</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>209</v>
+        <v>99</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G175" s="8">
-        <v>46113</v>
+        <v>46104</v>
       </c>
     </row>
     <row r="176" spans="2:7" ht="14.25">
       <c r="B176" s="7" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C176" s="1">
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>101</v>
+        <v>29</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>10</v>
+        <v>136</v>
       </c>
       <c r="G176" s="8">
         <v>46104</v>
       </c>
     </row>
-    <row r="177" spans="2:7">
+    <row r="177" spans="2:7" ht="14.25">
       <c r="B177" s="7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C177" s="1">
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G177" s="27">
-        <v>46119</v>
+      <c r="G177" s="8">
+        <v>46078</v>
       </c>
     </row>
     <row r="178" spans="2:7" ht="14.25">
@@ -5802,16 +5760,16 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>138</v>
+        <v>10</v>
       </c>
       <c r="G178" s="8">
-        <v>46104</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="179" spans="2:7" ht="14.25">
@@ -5822,16 +5780,16 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G179" s="8">
-        <v>46078</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="180" spans="2:7" ht="14.25">
@@ -5842,16 +5800,16 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G180" s="8">
-        <v>46078</v>
+        <v>46077</v>
       </c>
     </row>
     <row r="181" spans="2:7" ht="14.25">
@@ -5862,16 +5820,16 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G181" s="8">
-        <v>46081</v>
+        <v>46077</v>
       </c>
     </row>
     <row r="182" spans="2:7" ht="14.25">
@@ -5882,16 +5840,16 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G182" s="8">
-        <v>46077</v>
+        <v>46100</v>
       </c>
     </row>
     <row r="183" spans="2:7" ht="14.25">
@@ -5902,60 +5860,60 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G183" s="8">
+        <v>46093</v>
+      </c>
+    </row>
+    <row r="184" spans="2:7" ht="14.25">
+      <c r="B184" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="C184" s="1">
+        <v>3</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E184" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F184" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G184" s="8">
         <v>46077</v>
-      </c>
-    </row>
-    <row r="184" spans="2:7" ht="14.25">
-      <c r="B184" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="C184" s="1">
-        <v>3</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E184" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F184" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G184" s="8">
-        <v>46100</v>
       </c>
     </row>
     <row r="185" spans="2:7" ht="14.25">
       <c r="B185" s="7" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C185" s="1">
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G185" s="8">
-        <v>46093</v>
+        <v>46077</v>
       </c>
     </row>
     <row r="186" spans="2:7" ht="14.25">
-      <c r="B186" s="5" t="s">
+      <c r="B186" s="7" t="s">
         <v>221</v>
       </c>
       <c r="C186" s="1">
@@ -5982,10 +5940,10 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>10</v>
@@ -6002,176 +5960,176 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G188" s="8">
-        <v>46077</v>
+        <v>46118</v>
       </c>
     </row>
     <row r="189" spans="2:7" ht="14.25">
-      <c r="B189" s="7" t="s">
-        <v>224</v>
+      <c r="B189" s="5" t="s">
+        <v>223</v>
       </c>
       <c r="C189" s="1">
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G189" s="8">
-        <v>46077</v>
+        <v>46097</v>
       </c>
     </row>
     <row r="190" spans="2:7" ht="14.25">
-      <c r="B190" s="7" t="s">
-        <v>225</v>
+      <c r="B190" s="5" t="s">
+        <v>223</v>
       </c>
       <c r="C190" s="1">
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G190" s="8">
-        <v>46118</v>
+        <v>46079</v>
       </c>
     </row>
     <row r="191" spans="2:7" ht="14.25">
       <c r="B191" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="C191" s="1">
+        <v>3</v>
+      </c>
+      <c r="D191" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E191" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F191" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G191" s="8">
+        <v>46076</v>
+      </c>
+    </row>
+    <row r="192" spans="2:7" ht="14.25">
+      <c r="B192" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="C192" s="1">
+        <v>3</v>
+      </c>
+      <c r="D192" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E192" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F192" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G192" s="8">
+        <v>46098</v>
+      </c>
+    </row>
+    <row r="193" spans="2:7" ht="14.25">
+      <c r="B193" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="C191" s="1">
-        <v>3</v>
-      </c>
-      <c r="D191" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E191" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F191" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G191" s="8">
-        <v>46097</v>
-      </c>
-    </row>
-    <row r="192" spans="2:7" ht="14.25">
-      <c r="B192" s="5" t="s">
+      <c r="C193" s="1">
+        <v>3</v>
+      </c>
+      <c r="D193" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E193" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F193" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G193" s="8">
+        <v>46115</v>
+      </c>
+    </row>
+    <row r="194" spans="2:7" ht="14.25">
+      <c r="B194" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="C192" s="1">
-        <v>3</v>
-      </c>
-      <c r="D192" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E192" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F192" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G192" s="8">
-        <v>46079</v>
-      </c>
-    </row>
-    <row r="193" spans="2:7" ht="14.25">
-      <c r="B193" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="C193" s="1">
-        <v>3</v>
-      </c>
-      <c r="D193" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E193" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F193" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G193" s="8">
-        <v>46076</v>
-      </c>
-    </row>
-    <row r="194" spans="2:7" ht="14.25">
-      <c r="B194" s="7" t="s">
-        <v>226</v>
-      </c>
       <c r="C194" s="1">
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>10</v>
+        <v>136</v>
       </c>
       <c r="G194" s="8">
-        <v>46098</v>
+        <v>46075</v>
       </c>
     </row>
     <row r="195" spans="2:7" ht="14.25">
       <c r="B195" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="C195" s="1">
+        <v>3</v>
+      </c>
+      <c r="D195" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E195" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F195" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G195" s="8">
+        <v>46077</v>
+      </c>
+    </row>
+    <row r="196" spans="2:7" ht="14.25">
+      <c r="B196" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="C195" s="1">
-        <v>3</v>
-      </c>
-      <c r="D195" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E195" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F195" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G195" s="8">
-        <v>46115</v>
-      </c>
-    </row>
-    <row r="196" spans="2:7" ht="14.25">
-      <c r="B196" s="5" t="s">
-        <v>227</v>
-      </c>
       <c r="C196" s="1">
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>31</v>
+        <v>98</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>138</v>
+        <v>10</v>
       </c>
       <c r="G196" s="8">
-        <v>46075</v>
+        <v>46093</v>
       </c>
     </row>
     <row r="197" spans="2:7" ht="14.25">
@@ -6182,16 +6140,16 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>57</v>
+        <v>12</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G197" s="8">
-        <v>46077</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="198" spans="2:7" ht="14.25">
@@ -6202,136 +6160,136 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>101</v>
+        <v>203</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G198" s="8">
-        <v>46093</v>
+        <v>46098</v>
       </c>
     </row>
     <row r="199" spans="2:7" ht="14.25">
-      <c r="B199" s="7" t="s">
-        <v>230</v>
+      <c r="B199" s="5" t="s">
+        <v>229</v>
       </c>
       <c r="C199" s="1">
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>10</v>
+        <v>136</v>
       </c>
       <c r="G199" s="8">
-        <v>46078</v>
+        <v>46098</v>
       </c>
     </row>
     <row r="200" spans="2:7" ht="14.25">
       <c r="B200" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C200" s="1">
         <v>3</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>122</v>
+        <v>28</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>204</v>
+        <v>29</v>
       </c>
       <c r="F200" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G200" s="8">
-        <v>46098</v>
+        <v>46103</v>
       </c>
     </row>
     <row r="201" spans="2:7" ht="14.25">
       <c r="B201" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="C201" s="1">
+        <v>3</v>
+      </c>
+      <c r="D201" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E201" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F201" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G201" s="8">
+        <v>46102</v>
+      </c>
+    </row>
+    <row r="202" spans="2:7" ht="14.25">
+      <c r="B202" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="C202" s="1">
+        <v>3</v>
+      </c>
+      <c r="D202" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E202" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F202" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="G202" s="8">
+        <v>46088</v>
+      </c>
+    </row>
+    <row r="203" spans="2:7" ht="14.25">
+      <c r="B203" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="C201" s="1">
-        <v>3</v>
-      </c>
-      <c r="D201" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E201" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F201" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="G201" s="8">
-        <v>46098</v>
-      </c>
-    </row>
-    <row r="202" spans="2:7" ht="14.25">
-      <c r="B202" s="7" t="s">
+      <c r="C203" s="1">
+        <v>3</v>
+      </c>
+      <c r="D203" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E203" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F203" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G203" s="8">
+        <v>46072</v>
+      </c>
+    </row>
+    <row r="204" spans="2:7" ht="14.25">
+      <c r="B204" s="7" t="s">
         <v>232</v>
       </c>
-      <c r="C202" s="1">
-        <v>3</v>
-      </c>
-      <c r="D202" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E202" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F202" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G202" s="8">
-        <v>46103</v>
-      </c>
-    </row>
-    <row r="203" spans="2:7" ht="14.25">
-      <c r="B203" s="5" t="s">
-        <v>232</v>
-      </c>
-      <c r="C203" s="1">
-        <v>3</v>
-      </c>
-      <c r="D203" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E203" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F203" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G203" s="8">
-        <v>46102</v>
-      </c>
-    </row>
-    <row r="204" spans="2:7" ht="14.25">
-      <c r="B204" s="5" t="s">
-        <v>232</v>
-      </c>
       <c r="C204" s="1">
         <v>3</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>138</v>
+        <v>10</v>
       </c>
       <c r="G204" s="8">
-        <v>46088</v>
+        <v>46070</v>
       </c>
     </row>
     <row r="205" spans="2:7" ht="14.25">
@@ -6342,16 +6300,16 @@
         <v>3</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G205" s="8">
-        <v>46072</v>
+        <v>46070</v>
       </c>
     </row>
     <row r="206" spans="2:7" ht="14.25">
@@ -6362,10 +6320,10 @@
         <v>3</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>10</v>
@@ -6374,158 +6332,158 @@
         <v>46070</v>
       </c>
     </row>
-    <row r="207" spans="2:7" ht="14.25">
-      <c r="B207" s="7" t="s">
+    <row r="207" spans="2:7">
+      <c r="B207" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="C207" s="1">
-        <v>3</v>
-      </c>
-      <c r="D207" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E207" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F207" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G207" s="8">
-        <v>46070</v>
-      </c>
-    </row>
-    <row r="208" spans="2:7" ht="14.25">
-      <c r="B208" s="7" t="s">
+      <c r="C207" s="10">
+        <v>3</v>
+      </c>
+      <c r="D207" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="E207" s="13">
+        <v>5.5</v>
+      </c>
+      <c r="F207" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G207" s="14" t="s">
         <v>236</v>
       </c>
-      <c r="C208" s="1">
-        <v>3</v>
-      </c>
-      <c r="D208" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E208" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F208" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G208" s="8">
-        <v>46070</v>
+    </row>
+    <row r="208" spans="2:7">
+      <c r="B208" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="C208" s="10">
+        <v>3</v>
+      </c>
+      <c r="D208" s="12">
+        <v>100</v>
+      </c>
+      <c r="E208" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="F208" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G208" s="10" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="209" spans="2:7">
-      <c r="B209" s="11" t="s">
-        <v>237</v>
+      <c r="B209" s="10" t="s">
+        <v>238</v>
       </c>
       <c r="C209" s="10">
         <v>3</v>
       </c>
-      <c r="D209" s="12" t="s">
-        <v>38</v>
+      <c r="D209" s="12">
+        <v>100</v>
       </c>
       <c r="E209" s="13">
-        <v>5.5</v>
+        <v>0.5</v>
       </c>
       <c r="F209" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G209" s="14" t="s">
-        <v>238</v>
+      <c r="G209" s="10" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="210" spans="2:7">
-      <c r="B210" s="10" t="s">
-        <v>239</v>
+      <c r="B210" s="15" t="s">
+        <v>240</v>
       </c>
       <c r="C210" s="10">
         <v>3</v>
       </c>
-      <c r="D210" s="12">
-        <v>100</v>
-      </c>
-      <c r="E210" s="13">
-        <v>0.5</v>
+      <c r="D210" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="E210" s="16">
+        <v>16</v>
       </c>
       <c r="F210" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G210" s="10" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
     </row>
     <row r="211" spans="2:7">
-      <c r="B211" s="10" t="s">
+      <c r="B211" s="15" t="s">
         <v>240</v>
       </c>
       <c r="C211" s="10">
         <v>3</v>
       </c>
       <c r="D211" s="12">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E211" s="13">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="F211" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G211" s="10" t="s">
-        <v>241</v>
+      <c r="G211" s="17">
+        <v>46092</v>
       </c>
     </row>
     <row r="212" spans="2:7">
-      <c r="B212" s="15" t="s">
+      <c r="B212" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="C212" s="10">
+        <v>3</v>
+      </c>
+      <c r="D212" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E212" s="12">
+        <v>5</v>
+      </c>
+      <c r="F212" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G212" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="C212" s="10">
-        <v>3</v>
-      </c>
-      <c r="D212" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="E212" s="16">
-        <v>16</v>
-      </c>
-      <c r="F212" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G212" s="10" t="s">
+    </row>
+    <row r="213" spans="2:7">
+      <c r="B213" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="C213" s="10">
+        <v>3</v>
+      </c>
+      <c r="D213" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E213" s="12">
+        <v>5</v>
+      </c>
+      <c r="F213" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G213" s="10" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="213" spans="2:7">
-      <c r="B213" s="15" t="s">
-        <v>242</v>
-      </c>
-      <c r="C213" s="10">
-        <v>3</v>
-      </c>
-      <c r="D213" s="12">
-        <v>300</v>
-      </c>
-      <c r="E213" s="13">
-        <v>1.5</v>
-      </c>
-      <c r="F213" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G213" s="17">
-        <v>46092</v>
-      </c>
-    </row>
     <row r="214" spans="2:7">
-      <c r="B214" s="10" t="s">
-        <v>242</v>
+      <c r="B214" s="15" t="s">
+        <v>240</v>
       </c>
       <c r="C214" s="10">
         <v>3</v>
       </c>
-      <c r="D214" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="E214" s="12">
-        <v>5</v>
+      <c r="D214" s="12">
+        <v>100</v>
+      </c>
+      <c r="E214" s="13">
+        <v>0.5</v>
       </c>
       <c r="F214" s="10" t="s">
         <v>10</v>
@@ -6536,127 +6494,127 @@
     </row>
     <row r="215" spans="2:7">
       <c r="B215" s="10" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C215" s="10">
         <v>3</v>
       </c>
-      <c r="D215" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="E215" s="12">
-        <v>5</v>
+      <c r="D215" s="12">
+        <v>100</v>
+      </c>
+      <c r="E215" s="13">
+        <v>0.5</v>
       </c>
       <c r="F215" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G215" s="10" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="216" spans="2:7">
-      <c r="B216" s="15" t="s">
-        <v>242</v>
+      <c r="B216" s="10" t="s">
+        <v>246</v>
       </c>
       <c r="C216" s="10">
         <v>3</v>
       </c>
       <c r="D216" s="12">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="E216" s="13">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="F216" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G216" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="217" spans="2:7">
       <c r="B217" s="10" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C217" s="10">
         <v>3</v>
       </c>
       <c r="D217" s="12">
-        <v>100</v>
-      </c>
-      <c r="E217" s="13">
-        <v>0.5</v>
+        <v>600</v>
+      </c>
+      <c r="E217" s="12">
+        <v>3</v>
       </c>
       <c r="F217" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G217" s="10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="218" spans="2:7">
-      <c r="B218" s="10" t="s">
+      <c r="B218" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="C218" s="10">
+        <v>3</v>
+      </c>
+      <c r="D218" s="12">
+        <v>400</v>
+      </c>
+      <c r="E218" s="12">
+        <v>2</v>
+      </c>
+      <c r="F218" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G218" s="10" t="s">
         <v>248</v>
-      </c>
-      <c r="C218" s="10">
-        <v>3</v>
-      </c>
-      <c r="D218" s="12">
-        <v>300</v>
-      </c>
-      <c r="E218" s="13">
-        <v>1.5</v>
-      </c>
-      <c r="F218" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G218" s="10" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="219" spans="2:7">
       <c r="B219" s="10" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C219" s="10">
         <v>3</v>
       </c>
       <c r="D219" s="12">
-        <v>600</v>
-      </c>
-      <c r="E219" s="12">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="E219" s="13">
+        <v>0.5</v>
       </c>
       <c r="F219" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G219" s="10" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="220" spans="2:7">
-      <c r="B220" s="15" t="s">
-        <v>248</v>
+      <c r="B220" s="10" t="s">
+        <v>251</v>
       </c>
       <c r="C220" s="10">
         <v>3</v>
       </c>
       <c r="D220" s="12">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="E220" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F220" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G220" s="10" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
     </row>
     <row r="221" spans="2:7">
       <c r="B221" s="10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C221" s="10">
         <v>3</v>
@@ -6671,7 +6629,7 @@
         <v>10</v>
       </c>
       <c r="G221" s="10" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="222" spans="2:7">
@@ -6682,41 +6640,41 @@
         <v>3</v>
       </c>
       <c r="D222" s="12">
-        <v>200</v>
-      </c>
-      <c r="E222" s="12">
-        <v>1</v>
+        <v>100</v>
+      </c>
+      <c r="E222" s="13">
+        <v>0.5</v>
       </c>
       <c r="F222" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G222" s="10" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
     </row>
     <row r="223" spans="2:7">
-      <c r="B223" s="10" t="s">
-        <v>254</v>
+      <c r="B223" s="15" t="s">
+        <v>253</v>
       </c>
       <c r="C223" s="10">
         <v>3</v>
       </c>
-      <c r="D223" s="12">
-        <v>100</v>
-      </c>
-      <c r="E223" s="13">
-        <v>0.5</v>
+      <c r="D223" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E223" s="12">
+        <v>5</v>
       </c>
       <c r="F223" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G223" s="10" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
     </row>
     <row r="224" spans="2:7">
       <c r="B224" s="10" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C224" s="10">
         <v>3</v>
@@ -6730,33 +6688,33 @@
       <c r="F224" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G224" s="10" t="s">
-        <v>256</v>
+      <c r="G224" s="17">
+        <v>46056</v>
       </c>
     </row>
     <row r="225" spans="2:7">
-      <c r="B225" s="15" t="s">
-        <v>255</v>
+      <c r="B225" s="10" t="s">
+        <v>257</v>
       </c>
       <c r="C225" s="10">
         <v>3</v>
       </c>
       <c r="D225" s="12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E225" s="12">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F225" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G225" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="226" spans="2:7">
       <c r="B226" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C226" s="10">
         <v>3</v>
@@ -6770,8 +6728,8 @@
       <c r="F226" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G226" s="17">
-        <v>46056</v>
+      <c r="G226" s="10" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="227" spans="2:7">
@@ -6781,22 +6739,22 @@
       <c r="C227" s="10">
         <v>3</v>
       </c>
-      <c r="D227" s="12" t="s">
-        <v>19</v>
+      <c r="D227" s="12">
+        <v>200</v>
       </c>
       <c r="E227" s="12">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F227" s="10" t="s">
-        <v>10</v>
+        <v>136</v>
       </c>
       <c r="G227" s="10" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="228" spans="2:7">
       <c r="B228" s="10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C228" s="10">
         <v>3</v>
@@ -6811,7 +6769,7 @@
         <v>10</v>
       </c>
       <c r="G228" s="10" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
     </row>
     <row r="229" spans="2:7">
@@ -6828,10 +6786,10 @@
         <v>1</v>
       </c>
       <c r="F229" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="G229" s="10" t="s">
-        <v>260</v>
+        <v>10</v>
+      </c>
+      <c r="G229" s="17">
+        <v>46056</v>
       </c>
     </row>
     <row r="230" spans="2:7">
@@ -6851,7 +6809,7 @@
         <v>10</v>
       </c>
       <c r="G230" s="10" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
     </row>
     <row r="231" spans="2:7">
@@ -6861,22 +6819,22 @@
       <c r="C231" s="10">
         <v>3</v>
       </c>
-      <c r="D231" s="12">
-        <v>200</v>
-      </c>
-      <c r="E231" s="12">
-        <v>1</v>
+      <c r="D231" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="E231" s="13">
+        <v>19.5</v>
       </c>
       <c r="F231" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G231" s="17">
-        <v>46056</v>
+        <v>46176</v>
       </c>
     </row>
     <row r="232" spans="2:7">
       <c r="B232" s="10" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C232" s="10">
         <v>3</v>
@@ -6891,7 +6849,7 @@
         <v>10</v>
       </c>
       <c r="G232" s="10" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="233" spans="2:7">
@@ -6901,22 +6859,22 @@
       <c r="C233" s="10">
         <v>3</v>
       </c>
-      <c r="D233" s="12" t="s">
-        <v>266</v>
+      <c r="D233" s="12">
+        <v>100</v>
       </c>
       <c r="E233" s="13">
-        <v>19.5</v>
+        <v>0.5</v>
       </c>
       <c r="F233" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G233" s="17">
-        <v>46176</v>
+      <c r="G233" s="10" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="234" spans="2:7">
       <c r="B234" s="10" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C234" s="10">
         <v>3</v>
@@ -6930,8 +6888,8 @@
       <c r="F234" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G234" s="10" t="s">
-        <v>250</v>
+      <c r="G234" s="17">
+        <v>46065</v>
       </c>
     </row>
     <row r="235" spans="2:7">
@@ -6941,17 +6899,17 @@
       <c r="C235" s="10">
         <v>3</v>
       </c>
-      <c r="D235" s="12">
-        <v>100</v>
-      </c>
-      <c r="E235" s="13">
-        <v>0.5</v>
+      <c r="D235" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E235" s="12">
+        <v>10</v>
       </c>
       <c r="F235" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G235" s="10" t="s">
-        <v>250</v>
+      <c r="G235" s="17">
+        <v>46065</v>
       </c>
     </row>
     <row r="236" spans="2:7">
@@ -6981,17 +6939,17 @@
       <c r="C237" s="10">
         <v>3</v>
       </c>
-      <c r="D237" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="E237" s="12">
-        <v>10</v>
+      <c r="D237" s="12">
+        <v>100</v>
+      </c>
+      <c r="E237" s="13">
+        <v>0.5</v>
       </c>
       <c r="F237" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G237" s="17">
-        <v>46065</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="238" spans="2:7">
@@ -7010,8 +6968,8 @@
       <c r="F238" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G238" s="17">
-        <v>46065</v>
+      <c r="G238" s="10" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="239" spans="2:7">
@@ -7022,16 +6980,16 @@
         <v>3</v>
       </c>
       <c r="D239" s="12">
-        <v>100</v>
-      </c>
-      <c r="E239" s="13">
-        <v>0.5</v>
+        <v>200</v>
+      </c>
+      <c r="E239" s="12">
+        <v>1</v>
       </c>
       <c r="F239" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G239" s="17">
-        <v>46071</v>
+      <c r="G239" s="10" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="240" spans="2:7">
@@ -7051,7 +7009,7 @@
         <v>10</v>
       </c>
       <c r="G240" s="10" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
     </row>
     <row r="241" spans="2:7">
@@ -7062,16 +7020,16 @@
         <v>3</v>
       </c>
       <c r="D241" s="12">
-        <v>200</v>
-      </c>
-      <c r="E241" s="12">
-        <v>1</v>
+        <v>500</v>
+      </c>
+      <c r="E241" s="13">
+        <v>2.5</v>
       </c>
       <c r="F241" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G241" s="10" t="s">
-        <v>241</v>
+      <c r="G241" s="17">
+        <v>46064</v>
       </c>
     </row>
     <row r="242" spans="2:7">
@@ -7091,47 +7049,47 @@
         <v>10</v>
       </c>
       <c r="G242" s="10" t="s">
-        <v>241</v>
+        <v>275</v>
       </c>
     </row>
     <row r="243" spans="2:7">
       <c r="B243" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C243" s="10">
         <v>3</v>
       </c>
       <c r="D243" s="12">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="E243" s="13">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="F243" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G243" s="17">
-        <v>46064</v>
+      <c r="G243" s="10" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="244" spans="2:7">
       <c r="B244" s="10" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C244" s="10">
         <v>3</v>
       </c>
       <c r="D244" s="12">
-        <v>100</v>
-      </c>
-      <c r="E244" s="13">
-        <v>0.5</v>
+        <v>600</v>
+      </c>
+      <c r="E244" s="12">
+        <v>3</v>
       </c>
       <c r="F244" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G244" s="10" t="s">
-        <v>277</v>
+        <v>247</v>
       </c>
     </row>
     <row r="245" spans="2:7">
@@ -7141,51 +7099,51 @@
       <c r="C245" s="10">
         <v>3</v>
       </c>
-      <c r="D245" s="12">
-        <v>100</v>
-      </c>
-      <c r="E245" s="13">
-        <v>0.5</v>
+      <c r="D245" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="E245" s="12">
+        <v>9</v>
       </c>
       <c r="F245" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G245" s="10" t="s">
-        <v>279</v>
+      <c r="G245" s="17">
+        <v>46064</v>
       </c>
     </row>
     <row r="246" spans="2:7">
       <c r="B246" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="C246" s="10">
+        <v>3</v>
+      </c>
+      <c r="D246" s="12">
+        <v>100</v>
+      </c>
+      <c r="E246" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="F246" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G246" s="10" t="s">
         <v>280</v>
-      </c>
-      <c r="C246" s="10">
-        <v>3</v>
-      </c>
-      <c r="D246" s="12">
-        <v>600</v>
-      </c>
-      <c r="E246" s="12">
-        <v>3</v>
-      </c>
-      <c r="F246" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G246" s="10" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="247" spans="2:7">
       <c r="B247" s="10" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C247" s="10">
         <v>3</v>
       </c>
-      <c r="D247" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="E247" s="12">
-        <v>9</v>
+      <c r="D247" s="12">
+        <v>100</v>
+      </c>
+      <c r="E247" s="13">
+        <v>0.5</v>
       </c>
       <c r="F247" s="10" t="s">
         <v>10</v>
@@ -7196,22 +7154,22 @@
     </row>
     <row r="248" spans="2:7">
       <c r="B248" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C248" s="10">
         <v>3</v>
       </c>
       <c r="D248" s="12">
-        <v>100</v>
-      </c>
-      <c r="E248" s="13">
-        <v>0.5</v>
+        <v>600</v>
+      </c>
+      <c r="E248" s="12">
+        <v>3</v>
       </c>
       <c r="F248" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G248" s="10" t="s">
-        <v>282</v>
+      <c r="G248" s="17">
+        <v>46328</v>
       </c>
     </row>
     <row r="249" spans="2:7">
@@ -7230,33 +7188,33 @@
       <c r="F249" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G249" s="17">
-        <v>46064</v>
+      <c r="G249" s="10" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="250" spans="2:7">
       <c r="B250" s="10" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C250" s="10">
         <v>3</v>
       </c>
       <c r="D250" s="12">
-        <v>600</v>
-      </c>
-      <c r="E250" s="12">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="E250" s="13">
+        <v>0.5</v>
       </c>
       <c r="F250" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G250" s="17">
-        <v>46064</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="251" spans="2:7">
       <c r="B251" s="10" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C251" s="10">
         <v>3</v>
@@ -7271,7 +7229,7 @@
         <v>10</v>
       </c>
       <c r="G251" s="10" t="s">
-        <v>286</v>
+        <v>244</v>
       </c>
     </row>
     <row r="252" spans="2:7">
@@ -7281,17 +7239,17 @@
       <c r="C252" s="10">
         <v>3</v>
       </c>
-      <c r="D252" s="12">
-        <v>100</v>
-      </c>
-      <c r="E252" s="13">
-        <v>0.5</v>
+      <c r="D252" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E252" s="12">
+        <v>5</v>
       </c>
       <c r="F252" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G252" s="17">
-        <v>46065</v>
+      <c r="G252" s="10" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="253" spans="2:7">
@@ -7310,8 +7268,8 @@
       <c r="F253" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G253" s="10" t="s">
-        <v>246</v>
+      <c r="G253" s="18" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="254" spans="2:7">
@@ -7321,22 +7279,22 @@
       <c r="C254" s="10">
         <v>3</v>
       </c>
-      <c r="D254" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="E254" s="12">
-        <v>5</v>
+      <c r="D254" s="12">
+        <v>100</v>
+      </c>
+      <c r="E254" s="13">
+        <v>0.5</v>
       </c>
       <c r="F254" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G254" s="10" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="255" spans="2:7">
       <c r="B255" s="10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C255" s="10">
         <v>3</v>
@@ -7350,13 +7308,13 @@
       <c r="F255" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G255" s="18" t="s">
-        <v>282</v>
+      <c r="G255" s="10" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="256" spans="2:7">
       <c r="B256" s="10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C256" s="10">
         <v>3</v>
@@ -7370,8 +7328,8 @@
       <c r="F256" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G256" s="10" t="s">
-        <v>292</v>
+      <c r="G256" s="18" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="257" spans="2:7">
@@ -7391,7 +7349,7 @@
         <v>10</v>
       </c>
       <c r="G257" s="10" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
     </row>
     <row r="258" spans="2:7">
@@ -7410,8 +7368,8 @@
       <c r="F258" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G258" s="18" t="s">
-        <v>260</v>
+      <c r="G258" s="10" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="259" spans="2:7">
@@ -7431,7 +7389,7 @@
         <v>10</v>
       </c>
       <c r="G259" s="10" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="260" spans="2:7">
@@ -7442,56 +7400,56 @@
         <v>3</v>
       </c>
       <c r="D260" s="12">
-        <v>100</v>
-      </c>
-      <c r="E260" s="13">
-        <v>0.5</v>
+        <v>400</v>
+      </c>
+      <c r="E260" s="10">
+        <v>2</v>
       </c>
       <c r="F260" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G260" s="10" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
     </row>
     <row r="261" spans="2:7">
       <c r="B261" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C261" s="10">
         <v>3</v>
       </c>
       <c r="D261" s="12">
-        <v>100</v>
-      </c>
-      <c r="E261" s="13">
-        <v>0.5</v>
+        <v>400</v>
+      </c>
+      <c r="E261" s="10">
+        <v>2</v>
       </c>
       <c r="F261" s="10" t="s">
-        <v>10</v>
+        <v>136</v>
       </c>
       <c r="G261" s="10" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
     </row>
     <row r="262" spans="2:7">
       <c r="B262" s="10" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C262" s="10">
         <v>3</v>
       </c>
       <c r="D262" s="12">
-        <v>400</v>
-      </c>
-      <c r="E262" s="10">
-        <v>2</v>
+        <v>100</v>
+      </c>
+      <c r="E262" s="13">
+        <v>0.5</v>
       </c>
       <c r="F262" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G262" s="10" t="s">
-        <v>257</v>
+        <v>136</v>
+      </c>
+      <c r="G262" s="18" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="263" spans="2:7">
@@ -7502,21 +7460,21 @@
         <v>3</v>
       </c>
       <c r="D263" s="12">
-        <v>400</v>
-      </c>
-      <c r="E263" s="10">
-        <v>2</v>
+        <v>100</v>
+      </c>
+      <c r="E263" s="13">
+        <v>0.5</v>
       </c>
       <c r="F263" s="10" t="s">
-        <v>138</v>
+        <v>10</v>
       </c>
       <c r="G263" s="10" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="264" spans="2:7">
       <c r="B264" s="10" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C264" s="10">
         <v>3</v>
@@ -7528,10 +7486,10 @@
         <v>0.5</v>
       </c>
       <c r="F264" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="G264" s="18" t="s">
-        <v>299</v>
+        <v>10</v>
+      </c>
+      <c r="G264" s="10" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="265" spans="2:7">
@@ -7551,12 +7509,12 @@
         <v>10</v>
       </c>
       <c r="G265" s="10" t="s">
-        <v>252</v>
+        <v>301</v>
       </c>
     </row>
     <row r="266" spans="2:7">
       <c r="B266" s="10" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C266" s="10">
         <v>3</v>
@@ -7571,47 +7529,47 @@
         <v>10</v>
       </c>
       <c r="G266" s="10" t="s">
-        <v>260</v>
+        <v>303</v>
       </c>
     </row>
     <row r="267" spans="2:7">
       <c r="B267" s="10" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C267" s="10">
         <v>3</v>
       </c>
       <c r="D267" s="12">
-        <v>100</v>
-      </c>
-      <c r="E267" s="13">
-        <v>0.5</v>
+        <v>200</v>
+      </c>
+      <c r="E267" s="12">
+        <v>1</v>
       </c>
       <c r="F267" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G267" s="10" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
     </row>
     <row r="268" spans="2:7">
       <c r="B268" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C268" s="10">
         <v>3</v>
       </c>
-      <c r="D268" s="12">
-        <v>100</v>
-      </c>
-      <c r="E268" s="13">
-        <v>0.5</v>
+      <c r="D268" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E268" s="12">
+        <v>5</v>
       </c>
       <c r="F268" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G268" s="10" t="s">
-        <v>305</v>
+        <v>258</v>
       </c>
     </row>
     <row r="269" spans="2:7">
@@ -7622,16 +7580,16 @@
         <v>3</v>
       </c>
       <c r="D269" s="12">
-        <v>200</v>
-      </c>
-      <c r="E269" s="12">
-        <v>1</v>
+        <v>100</v>
+      </c>
+      <c r="E269" s="13">
+        <v>0.5</v>
       </c>
       <c r="F269" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G269" s="10" t="s">
-        <v>299</v>
+        <v>284</v>
       </c>
     </row>
     <row r="270" spans="2:7">
@@ -7641,17 +7599,17 @@
       <c r="C270" s="10">
         <v>3</v>
       </c>
-      <c r="D270" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="E270" s="12">
-        <v>5</v>
+      <c r="D270" s="12">
+        <v>100</v>
+      </c>
+      <c r="E270" s="13">
+        <v>0.5</v>
       </c>
       <c r="F270" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G270" s="10" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
     </row>
     <row r="271" spans="2:7">
@@ -7671,7 +7629,7 @@
         <v>10</v>
       </c>
       <c r="G271" s="10" t="s">
-        <v>286</v>
+        <v>303</v>
       </c>
     </row>
     <row r="272" spans="2:7">
@@ -7690,8 +7648,8 @@
       <c r="F272" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G272" s="10" t="s">
-        <v>250</v>
+      <c r="G272" s="17">
+        <v>46056</v>
       </c>
     </row>
     <row r="273" spans="2:7">
@@ -7710,8 +7668,8 @@
       <c r="F273" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G273" s="10" t="s">
-        <v>305</v>
+      <c r="G273" s="18" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="274" spans="2:7">
@@ -7722,16 +7680,16 @@
         <v>3</v>
       </c>
       <c r="D274" s="12">
-        <v>100</v>
-      </c>
-      <c r="E274" s="13">
-        <v>0.5</v>
+        <v>600</v>
+      </c>
+      <c r="E274" s="12">
+        <v>3</v>
       </c>
       <c r="F274" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G274" s="17">
-        <v>46056</v>
+      <c r="G274" s="18" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="275" spans="2:7">
@@ -7750,8 +7708,8 @@
       <c r="F275" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G275" s="18" t="s">
-        <v>299</v>
+      <c r="G275" s="17">
+        <v>46065</v>
       </c>
     </row>
     <row r="276" spans="2:7">
@@ -7762,16 +7720,16 @@
         <v>3</v>
       </c>
       <c r="D276" s="12">
-        <v>600</v>
-      </c>
-      <c r="E276" s="12">
-        <v>3</v>
+        <v>500</v>
+      </c>
+      <c r="E276" s="13">
+        <v>2.5</v>
       </c>
       <c r="F276" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G276" s="18" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
     </row>
     <row r="277" spans="2:7">
@@ -7782,16 +7740,16 @@
         <v>3</v>
       </c>
       <c r="D277" s="12">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E277" s="13">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="F277" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G277" s="17">
-        <v>46065</v>
+      <c r="G277" s="10" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="278" spans="2:7">
@@ -7802,16 +7760,16 @@
         <v>3</v>
       </c>
       <c r="D278" s="12">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="E278" s="13">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="F278" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G278" s="18" t="s">
-        <v>260</v>
+      <c r="G278" s="17">
+        <v>46065</v>
       </c>
     </row>
     <row r="279" spans="2:7">
@@ -7822,16 +7780,16 @@
         <v>3</v>
       </c>
       <c r="D279" s="12">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="E279" s="13">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="F279" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G279" s="10" t="s">
-        <v>250</v>
+        <v>303</v>
       </c>
     </row>
     <row r="280" spans="2:7">
@@ -7850,8 +7808,8 @@
       <c r="F280" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G280" s="17">
-        <v>46065</v>
+      <c r="G280" s="17" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="281" spans="2:7">
@@ -7862,16 +7820,16 @@
         <v>3</v>
       </c>
       <c r="D281" s="12">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E281" s="13">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="F281" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G281" s="10" t="s">
-        <v>305</v>
+        <v>248</v>
       </c>
     </row>
     <row r="282" spans="2:7">
@@ -7890,8 +7848,8 @@
       <c r="F282" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G282" s="17" t="s">
-        <v>238</v>
+      <c r="G282" s="10" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="283" spans="2:7">
@@ -7910,13 +7868,13 @@
       <c r="F283" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G283" s="10" t="s">
-        <v>250</v>
+      <c r="G283" s="18" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="284" spans="2:7">
       <c r="B284" s="10" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C284" s="10">
         <v>3</v>
@@ -7930,8 +7888,8 @@
       <c r="F284" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G284" s="10" t="s">
-        <v>260</v>
+      <c r="G284" s="17">
+        <v>46065</v>
       </c>
     </row>
     <row r="285" spans="2:7">
@@ -7942,41 +7900,41 @@
         <v>3</v>
       </c>
       <c r="D285" s="12">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="E285" s="13">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="F285" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G285" s="18" t="s">
+      <c r="G285" s="10" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="286" spans="2:7">
       <c r="B286" s="10" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C286" s="10">
         <v>3</v>
       </c>
       <c r="D286" s="12">
-        <v>100</v>
-      </c>
-      <c r="E286" s="13">
-        <v>0.5</v>
+        <v>200</v>
+      </c>
+      <c r="E286" s="12">
+        <v>1</v>
       </c>
       <c r="F286" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G286" s="17">
-        <v>46065</v>
+      <c r="G286" s="10" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="287" spans="2:7">
       <c r="B287" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C287" s="10">
         <v>3</v>
@@ -7990,8 +7948,8 @@
       <c r="F287" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G287" s="10" t="s">
-        <v>325</v>
+      <c r="G287" s="17" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="288" spans="2:7">
@@ -8002,16 +7960,16 @@
         <v>3</v>
       </c>
       <c r="D288" s="12">
-        <v>200</v>
-      </c>
-      <c r="E288" s="12">
-        <v>1</v>
+        <v>100</v>
+      </c>
+      <c r="E288" s="13">
+        <v>0.5</v>
       </c>
       <c r="F288" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G288" s="10" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="289" spans="2:7">
@@ -8022,16 +7980,16 @@
         <v>3</v>
       </c>
       <c r="D289" s="12">
-        <v>100</v>
-      </c>
-      <c r="E289" s="13">
-        <v>0.5</v>
+        <v>200</v>
+      </c>
+      <c r="E289" s="12">
+        <v>1</v>
       </c>
       <c r="F289" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G289" s="17" t="s">
-        <v>238</v>
+      <c r="G289" s="17">
+        <v>46056</v>
       </c>
     </row>
     <row r="290" spans="2:7">
@@ -8051,7 +8009,7 @@
         <v>10</v>
       </c>
       <c r="G290" s="10" t="s">
-        <v>250</v>
+        <v>303</v>
       </c>
     </row>
     <row r="291" spans="2:7">
@@ -8062,16 +8020,16 @@
         <v>3</v>
       </c>
       <c r="D291" s="12">
-        <v>200</v>
-      </c>
-      <c r="E291" s="12">
-        <v>1</v>
+        <v>100</v>
+      </c>
+      <c r="E291" s="13">
+        <v>0.5</v>
       </c>
       <c r="F291" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G291" s="17">
-        <v>46056</v>
+      <c r="G291" s="10" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="292" spans="2:7">
@@ -8081,17 +8039,17 @@
       <c r="C292" s="10">
         <v>3</v>
       </c>
-      <c r="D292" s="12">
-        <v>100</v>
-      </c>
-      <c r="E292" s="13">
-        <v>0.5</v>
+      <c r="D292" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E292" s="12">
+        <v>5</v>
       </c>
       <c r="F292" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G292" s="10" t="s">
-        <v>305</v>
+      <c r="G292" s="17">
+        <v>46177</v>
       </c>
     </row>
     <row r="293" spans="2:7">
@@ -8102,16 +8060,16 @@
         <v>3</v>
       </c>
       <c r="D293" s="12">
-        <v>100</v>
-      </c>
-      <c r="E293" s="13">
-        <v>0.5</v>
+        <v>200</v>
+      </c>
+      <c r="E293" s="12">
+        <v>1</v>
       </c>
       <c r="F293" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G293" s="10" t="s">
-        <v>279</v>
+      <c r="G293" s="17">
+        <v>46065</v>
       </c>
     </row>
     <row r="294" spans="2:7">
@@ -8121,17 +8079,17 @@
       <c r="C294" s="10">
         <v>3</v>
       </c>
-      <c r="D294" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="E294" s="12">
-        <v>5</v>
+      <c r="D294" s="12">
+        <v>100</v>
+      </c>
+      <c r="E294" s="13">
+        <v>0.5</v>
       </c>
       <c r="F294" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G294" s="17">
-        <v>46118</v>
+      <c r="G294" s="10" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="295" spans="2:7">
@@ -8142,16 +8100,16 @@
         <v>3</v>
       </c>
       <c r="D295" s="12">
-        <v>200</v>
-      </c>
-      <c r="E295" s="12">
-        <v>1</v>
+        <v>100</v>
+      </c>
+      <c r="E295" s="13">
+        <v>0.5</v>
       </c>
       <c r="F295" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G295" s="17">
-        <v>46065</v>
+      <c r="G295" s="10" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="296" spans="2:7">
@@ -8171,7 +8129,7 @@
         <v>10</v>
       </c>
       <c r="G296" s="10" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="297" spans="2:7">
@@ -8190,8 +8148,8 @@
       <c r="F297" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G297" s="10" t="s">
-        <v>245</v>
+      <c r="G297" s="17" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="298" spans="2:7">
@@ -8210,8 +8168,8 @@
       <c r="F298" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G298" s="10" t="s">
-        <v>260</v>
+      <c r="G298" s="17">
+        <v>46025</v>
       </c>
     </row>
     <row r="299" spans="2:7">
@@ -8231,7 +8189,7 @@
         <v>10</v>
       </c>
       <c r="G299" s="17" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="300" spans="2:7">
@@ -8250,13 +8208,13 @@
       <c r="F300" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G300" s="17">
-        <v>46025</v>
+      <c r="G300" s="17" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="301" spans="2:7">
       <c r="B301" s="10" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C301" s="10">
         <v>3</v>
@@ -8270,28 +8228,28 @@
       <c r="F301" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G301" s="17" t="s">
-        <v>241</v>
+      <c r="G301" s="17">
+        <v>46093</v>
       </c>
     </row>
     <row r="302" spans="2:7">
       <c r="B302" s="10" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C302" s="10">
         <v>3</v>
       </c>
       <c r="D302" s="12">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E302" s="13">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="F302" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G302" s="17" t="s">
-        <v>341</v>
+      <c r="G302" s="19">
+        <v>46065</v>
       </c>
     </row>
     <row r="303" spans="2:7">
@@ -8311,7 +8269,7 @@
         <v>10</v>
       </c>
       <c r="G303" s="17">
-        <v>46093</v>
+        <v>46095</v>
       </c>
     </row>
     <row r="304" spans="2:7">
@@ -8322,16 +8280,16 @@
         <v>3</v>
       </c>
       <c r="D304" s="12">
-        <v>500</v>
-      </c>
-      <c r="E304" s="13">
-        <v>2.5</v>
+        <v>200</v>
+      </c>
+      <c r="E304" s="12">
+        <v>1</v>
       </c>
       <c r="F304" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G304" s="19">
-        <v>46065</v>
+      <c r="G304" s="17">
+        <v>46066</v>
       </c>
     </row>
     <row r="305" spans="2:7">
@@ -8350,8 +8308,8 @@
       <c r="F305" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G305" s="17">
-        <v>46095</v>
+      <c r="G305" s="19">
+        <v>46065</v>
       </c>
     </row>
     <row r="306" spans="2:7">
@@ -8362,16 +8320,16 @@
         <v>3</v>
       </c>
       <c r="D306" s="12">
-        <v>200</v>
-      </c>
-      <c r="E306" s="12">
-        <v>1</v>
+        <v>100</v>
+      </c>
+      <c r="E306" s="13">
+        <v>0.5</v>
       </c>
       <c r="F306" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G306" s="17">
-        <v>46066</v>
+      <c r="G306" s="19">
+        <v>46065</v>
       </c>
     </row>
     <row r="307" spans="2:7">
@@ -8391,12 +8349,12 @@
         <v>10</v>
       </c>
       <c r="G307" s="19">
-        <v>46065</v>
+        <v>46076</v>
       </c>
     </row>
     <row r="308" spans="2:7">
       <c r="B308" s="10" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C308" s="10">
         <v>3</v>
@@ -8416,7 +8374,7 @@
     </row>
     <row r="309" spans="2:7">
       <c r="B309" s="10" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C309" s="10">
         <v>3</v>
@@ -8450,13 +8408,13 @@
       <c r="F310" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G310" s="19">
-        <v>46065</v>
+      <c r="G310" s="19" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="311" spans="2:7">
       <c r="B311" s="10" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C311" s="10">
         <v>3</v>
@@ -8470,13 +8428,13 @@
       <c r="F311" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G311" s="19">
-        <v>46076</v>
+      <c r="G311" s="19" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="312" spans="2:7">
       <c r="B312" s="10" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C312" s="10">
         <v>3</v>
@@ -8491,7 +8449,7 @@
         <v>10</v>
       </c>
       <c r="G312" s="19" t="s">
-        <v>351</v>
+        <v>258</v>
       </c>
     </row>
     <row r="313" spans="2:7">
@@ -8501,17 +8459,17 @@
       <c r="C313" s="10">
         <v>3</v>
       </c>
-      <c r="D313" s="12">
-        <v>100</v>
-      </c>
-      <c r="E313" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="F313" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G313" s="19" t="s">
-        <v>260</v>
+      <c r="D313" s="20">
+        <v>100</v>
+      </c>
+      <c r="E313" s="21">
+        <v>0.5</v>
+      </c>
+      <c r="F313" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="G313" s="23" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="314" spans="2:7">
@@ -8530,8 +8488,8 @@
       <c r="F314" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G314" s="19" t="s">
-        <v>260</v>
+      <c r="G314" s="19">
+        <v>46065</v>
       </c>
     </row>
     <row r="315" spans="2:7">
@@ -8541,17 +8499,17 @@
       <c r="C315" s="10">
         <v>3</v>
       </c>
-      <c r="D315" s="20">
-        <v>100</v>
-      </c>
-      <c r="E315" s="21">
-        <v>0.5</v>
-      </c>
-      <c r="F315" s="22" t="s">
-        <v>10</v>
-      </c>
-      <c r="G315" s="23" t="s">
-        <v>323</v>
+      <c r="D315" s="12">
+        <v>100</v>
+      </c>
+      <c r="E315" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="F315" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G315" s="19">
+        <v>46069</v>
       </c>
     </row>
     <row r="316" spans="2:7">
@@ -8571,7 +8529,7 @@
         <v>10</v>
       </c>
       <c r="G316" s="19">
-        <v>46065</v>
+        <v>46087</v>
       </c>
     </row>
     <row r="317" spans="2:7">
@@ -8590,8 +8548,8 @@
       <c r="F317" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G317" s="19">
-        <v>46069</v>
+      <c r="G317" s="19" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="318" spans="2:7">
@@ -8610,73 +8568,73 @@
       <c r="F318" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G318" s="19">
-        <v>46087</v>
+      <c r="G318" s="24" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="319" spans="2:7">
       <c r="B319" s="10" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C319" s="10">
         <v>3</v>
       </c>
       <c r="D319" s="12">
-        <v>100</v>
-      </c>
-      <c r="E319" s="13">
-        <v>0.5</v>
+        <v>200</v>
+      </c>
+      <c r="E319" s="12">
+        <v>1</v>
       </c>
       <c r="F319" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G319" s="19" t="s">
-        <v>260</v>
+        <v>136</v>
+      </c>
+      <c r="G319" s="17" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="320" spans="2:7">
       <c r="B320" s="10" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C320" s="10">
         <v>3</v>
       </c>
       <c r="D320" s="12">
-        <v>100</v>
-      </c>
-      <c r="E320" s="13">
-        <v>0.5</v>
+        <v>200</v>
+      </c>
+      <c r="E320" s="12">
+        <v>1</v>
       </c>
       <c r="F320" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G320" s="24" t="s">
-        <v>360</v>
+        <v>136</v>
+      </c>
+      <c r="G320" s="17">
+        <v>46093</v>
       </c>
     </row>
     <row r="321" spans="2:7">
       <c r="B321" s="10" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C321" s="10">
         <v>3</v>
       </c>
       <c r="D321" s="12">
-        <v>200</v>
-      </c>
-      <c r="E321" s="12">
-        <v>1</v>
+        <v>100</v>
+      </c>
+      <c r="E321" s="13">
+        <v>0.5</v>
       </c>
       <c r="F321" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="G321" s="17" t="s">
-        <v>361</v>
+        <v>10</v>
+      </c>
+      <c r="G321" s="17">
+        <v>46065</v>
       </c>
     </row>
     <row r="322" spans="2:7">
       <c r="B322" s="10" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C322" s="10">
         <v>3</v>
@@ -8688,10 +8646,10 @@
         <v>1</v>
       </c>
       <c r="F322" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="G322" s="17">
-        <v>46093</v>
+        <v>10</v>
+      </c>
+      <c r="G322" s="18" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="323" spans="2:7">
@@ -8710,8 +8668,8 @@
       <c r="F323" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G323" s="17">
-        <v>46065</v>
+      <c r="G323" s="17" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="324" spans="2:7">
@@ -8731,7 +8689,7 @@
         <v>10</v>
       </c>
       <c r="G324" s="18" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="325" spans="2:7">
@@ -8751,7 +8709,7 @@
         <v>10</v>
       </c>
       <c r="G325" s="17" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="326" spans="2:7">
@@ -8762,16 +8720,16 @@
         <v>3</v>
       </c>
       <c r="D326" s="12">
-        <v>200</v>
-      </c>
-      <c r="E326" s="12">
-        <v>1</v>
+        <v>100</v>
+      </c>
+      <c r="E326" s="13">
+        <v>0.5</v>
       </c>
       <c r="F326" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G326" s="18" t="s">
-        <v>250</v>
+      <c r="G326" s="17">
+        <v>46064</v>
       </c>
     </row>
     <row r="327" spans="2:7">
@@ -8790,8 +8748,8 @@
       <c r="F327" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G327" s="17" t="s">
-        <v>250</v>
+      <c r="G327" s="19" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="328" spans="2:7">
@@ -8810,8 +8768,8 @@
       <c r="F328" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G328" s="17">
-        <v>46064</v>
+      <c r="G328" s="19" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="329" spans="2:7">
@@ -8830,13 +8788,13 @@
       <c r="F329" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G329" s="19" t="s">
-        <v>305</v>
+      <c r="G329" s="17" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="330" spans="2:7">
       <c r="B330" s="10" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C330" s="10">
         <v>3</v>
@@ -8850,13 +8808,13 @@
       <c r="F330" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G330" s="19" t="s">
-        <v>279</v>
+      <c r="G330" s="17" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="331" spans="2:7">
       <c r="B331" s="10" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C331" s="10">
         <v>3</v>
@@ -8870,13 +8828,13 @@
       <c r="F331" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G331" s="17" t="s">
-        <v>371</v>
+      <c r="G331" s="19">
+        <v>46057</v>
       </c>
     </row>
     <row r="332" spans="2:7">
       <c r="B332" s="10" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C332" s="10">
         <v>3</v>
@@ -8890,13 +8848,13 @@
       <c r="F332" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G332" s="17" t="s">
-        <v>250</v>
+      <c r="G332" s="10" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="333" spans="2:7">
       <c r="B333" s="10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C333" s="10">
         <v>3</v>
@@ -8910,8 +8868,8 @@
       <c r="F333" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G333" s="19">
-        <v>46057</v>
+      <c r="G333" s="10" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="334" spans="2:7">
@@ -8930,8 +8888,8 @@
       <c r="F334" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G334" s="10" t="s">
-        <v>260</v>
+      <c r="G334" s="19">
+        <v>46056</v>
       </c>
     </row>
     <row r="335" spans="2:7">
@@ -8941,17 +8899,17 @@
       <c r="C335" s="10">
         <v>3</v>
       </c>
-      <c r="D335" s="12">
-        <v>100</v>
-      </c>
-      <c r="E335" s="13">
-        <v>0.5</v>
+      <c r="D335" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E335" s="12">
+        <v>5</v>
       </c>
       <c r="F335" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G335" s="10" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="336" spans="2:7">
@@ -8970,33 +8928,33 @@
       <c r="F336" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G336" s="19">
-        <v>46056</v>
+      <c r="G336" s="19" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="337" spans="2:7">
       <c r="B337" s="10" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C337" s="10">
         <v>3</v>
       </c>
-      <c r="D337" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="E337" s="12">
-        <v>5</v>
+      <c r="D337" s="12">
+        <v>100</v>
+      </c>
+      <c r="E337" s="13">
+        <v>0.5</v>
       </c>
       <c r="F337" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G337" s="10" t="s">
-        <v>260</v>
+      <c r="G337" s="17" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="338" spans="2:7">
       <c r="B338" s="10" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C338" s="10">
         <v>3</v>
@@ -9010,13 +8968,13 @@
       <c r="F338" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G338" s="19" t="s">
-        <v>378</v>
+      <c r="G338" s="18" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="339" spans="2:7">
       <c r="B339" s="10" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C339" s="10">
         <v>3</v>
@@ -9030,13 +8988,13 @@
       <c r="F339" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G339" s="17" t="s">
-        <v>379</v>
+      <c r="G339" s="17">
+        <v>46065</v>
       </c>
     </row>
     <row r="340" spans="2:7">
       <c r="B340" s="10" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C340" s="10">
         <v>3</v>
@@ -9050,8 +9008,8 @@
       <c r="F340" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G340" s="18" t="s">
-        <v>286</v>
+      <c r="G340" s="17" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="341" spans="2:7">
@@ -9070,13 +9028,13 @@
       <c r="F341" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G341" s="17">
-        <v>46065</v>
+      <c r="G341" s="17" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="342" spans="2:7">
       <c r="B342" s="10" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C342" s="10">
         <v>3</v>
@@ -9091,12 +9049,12 @@
         <v>10</v>
       </c>
       <c r="G342" s="17" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="343" spans="2:7">
       <c r="B343" s="10" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C343" s="10">
         <v>3</v>
@@ -9111,12 +9069,12 @@
         <v>10</v>
       </c>
       <c r="G343" s="17" t="s">
-        <v>383</v>
+        <v>248</v>
       </c>
     </row>
     <row r="344" spans="2:7">
       <c r="B344" s="10" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C344" s="10">
         <v>3</v>
@@ -9130,8 +9088,8 @@
       <c r="F344" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G344" s="17" t="s">
-        <v>385</v>
+      <c r="G344" s="18" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="345" spans="2:7">
@@ -9150,8 +9108,8 @@
       <c r="F345" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G345" s="17" t="s">
-        <v>250</v>
+      <c r="G345" s="19" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="346" spans="2:7">
@@ -9162,76 +9120,76 @@
         <v>3</v>
       </c>
       <c r="D346" s="12">
-        <v>100</v>
-      </c>
-      <c r="E346" s="13">
-        <v>0.5</v>
+        <v>200</v>
+      </c>
+      <c r="E346" s="12">
+        <v>1</v>
       </c>
       <c r="F346" s="10" t="s">
         <v>10</v>
       </c>
       <c r="G346" s="18" t="s">
-        <v>252</v>
+        <v>323</v>
       </c>
     </row>
     <row r="347" spans="2:7">
       <c r="B347" s="10" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C347" s="10">
         <v>3</v>
       </c>
       <c r="D347" s="12">
-        <v>100</v>
-      </c>
-      <c r="E347" s="13">
-        <v>0.5</v>
+        <v>200</v>
+      </c>
+      <c r="E347" s="12">
+        <v>1</v>
       </c>
       <c r="F347" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G347" s="19" t="s">
-        <v>305</v>
+      <c r="G347" s="10" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="348" spans="2:7">
       <c r="B348" s="10" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C348" s="10">
         <v>3</v>
       </c>
       <c r="D348" s="12">
-        <v>200</v>
-      </c>
-      <c r="E348" s="12">
-        <v>1</v>
+        <v>100</v>
+      </c>
+      <c r="E348" s="13">
+        <v>0.5</v>
       </c>
       <c r="F348" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G348" s="18" t="s">
-        <v>325</v>
+        <v>136</v>
+      </c>
+      <c r="G348" s="17">
+        <v>46145</v>
       </c>
     </row>
     <row r="349" spans="2:7">
       <c r="B349" s="10" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C349" s="10">
         <v>3</v>
       </c>
       <c r="D349" s="12">
-        <v>200</v>
-      </c>
-      <c r="E349" s="12">
-        <v>1</v>
+        <v>100</v>
+      </c>
+      <c r="E349" s="13">
+        <v>0.5</v>
       </c>
       <c r="F349" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G349" s="10" t="s">
-        <v>305</v>
+      <c r="G349" s="19" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="350" spans="2:7">
@@ -9248,15 +9206,15 @@
         <v>0.5</v>
       </c>
       <c r="F350" s="10" t="s">
-        <v>138</v>
-      </c>
-      <c r="G350" s="17">
-        <v>46145</v>
+        <v>10</v>
+      </c>
+      <c r="G350" s="17" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="351" spans="2:7">
       <c r="B351" s="10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C351" s="10">
         <v>3</v>
@@ -9270,13 +9228,13 @@
       <c r="F351" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G351" s="19" t="s">
-        <v>305</v>
+      <c r="G351" s="17" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="352" spans="2:7">
-      <c r="B352" s="10" t="s">
-        <v>391</v>
+      <c r="B352" s="11" t="s">
+        <v>392</v>
       </c>
       <c r="C352" s="10">
         <v>3</v>
@@ -9291,12 +9249,12 @@
         <v>10</v>
       </c>
       <c r="G352" s="17" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="353" spans="2:7">
       <c r="B353" s="10" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C353" s="10">
         <v>3</v>
@@ -9311,12 +9269,12 @@
         <v>10</v>
       </c>
       <c r="G353" s="17" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="354" spans="2:7">
-      <c r="B354" s="11" t="s">
-        <v>394</v>
+      <c r="B354" s="10" t="s">
+        <v>395</v>
       </c>
       <c r="C354" s="10">
         <v>3</v>
@@ -9331,7 +9289,7 @@
         <v>10</v>
       </c>
       <c r="G354" s="17" t="s">
-        <v>395</v>
+        <v>248</v>
       </c>
     </row>
     <row r="355" spans="2:7">
@@ -9350,8 +9308,8 @@
       <c r="F355" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G355" s="17" t="s">
-        <v>379</v>
+      <c r="G355" s="24" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="356" spans="2:7">
@@ -9362,16 +9320,16 @@
         <v>3</v>
       </c>
       <c r="D356" s="12">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="E356" s="13">
-        <v>0.5</v>
+        <v>2.5</v>
       </c>
       <c r="F356" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G356" s="17" t="s">
-        <v>250</v>
+      <c r="G356" s="19" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="357" spans="2:7">
@@ -9390,8 +9348,8 @@
       <c r="F357" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G357" s="24" t="s">
-        <v>243</v>
+      <c r="G357" s="17" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="358" spans="2:7">
@@ -9411,7 +9369,7 @@
         <v>10</v>
       </c>
       <c r="G358" s="19" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="359" spans="2:7">
@@ -9431,7 +9389,7 @@
         <v>10</v>
       </c>
       <c r="G359" s="17" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="360" spans="2:7">
@@ -9442,21 +9400,21 @@
         <v>3</v>
       </c>
       <c r="D360" s="12">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="E360" s="13">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="F360" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G360" s="19" t="s">
-        <v>250</v>
+      <c r="G360" s="17" t="s">
+        <v>402</v>
       </c>
     </row>
     <row r="361" spans="2:7">
       <c r="B361" s="10" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C361" s="10">
         <v>3</v>
@@ -9470,8 +9428,8 @@
       <c r="F361" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G361" s="17" t="s">
-        <v>379</v>
+      <c r="G361" s="10" t="s">
+        <v>301</v>
       </c>
     </row>
     <row r="362" spans="2:7">
@@ -9490,13 +9448,13 @@
       <c r="F362" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G362" s="17" t="s">
-        <v>404</v>
+      <c r="G362" s="19" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="363" spans="2:7">
       <c r="B363" s="10" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C363" s="10">
         <v>3</v>
@@ -9510,8 +9468,8 @@
       <c r="F363" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G363" s="10" t="s">
-        <v>303</v>
+      <c r="G363" s="17" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="364" spans="2:7">
@@ -9530,13 +9488,13 @@
       <c r="F364" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G364" s="19" t="s">
-        <v>305</v>
+      <c r="G364" s="17" t="s">
+        <v>406</v>
       </c>
     </row>
     <row r="365" spans="2:7">
       <c r="B365" s="10" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C365" s="10">
         <v>3</v>
@@ -9551,12 +9509,12 @@
         <v>10</v>
       </c>
       <c r="G365" s="17" t="s">
-        <v>246</v>
+        <v>408</v>
       </c>
     </row>
     <row r="366" spans="2:7">
       <c r="B366" s="10" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C366" s="10">
         <v>3</v>
@@ -9571,12 +9529,12 @@
         <v>10</v>
       </c>
       <c r="G366" s="17" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="367" spans="2:7">
       <c r="B367" s="10" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C367" s="10">
         <v>3</v>
@@ -9590,13 +9548,13 @@
       <c r="F367" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G367" s="17" t="s">
-        <v>410</v>
+      <c r="G367" s="10" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="368" spans="2:7">
       <c r="B368" s="10" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C368" s="10">
         <v>3</v>
@@ -9611,12 +9569,12 @@
         <v>10</v>
       </c>
       <c r="G368" s="17" t="s">
-        <v>408</v>
+        <v>244</v>
       </c>
     </row>
     <row r="369" spans="2:7">
       <c r="B369" s="10" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C369" s="10">
         <v>3</v>
@@ -9631,7 +9589,7 @@
         <v>10</v>
       </c>
       <c r="G369" s="10" t="s">
-        <v>371</v>
+        <v>250</v>
       </c>
     </row>
     <row r="370" spans="2:7">
@@ -9642,16 +9600,16 @@
         <v>3</v>
       </c>
       <c r="D370" s="12">
-        <v>100</v>
-      </c>
-      <c r="E370" s="13">
-        <v>0.5</v>
+        <v>200</v>
+      </c>
+      <c r="E370" s="12">
+        <v>1</v>
       </c>
       <c r="F370" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G370" s="17" t="s">
-        <v>246</v>
+      <c r="G370" s="18" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="371" spans="2:7">
@@ -9661,17 +9619,17 @@
       <c r="C371" s="10">
         <v>3</v>
       </c>
-      <c r="D371" s="12">
-        <v>100</v>
-      </c>
-      <c r="E371" s="13">
-        <v>0.5</v>
+      <c r="D371" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E371" s="12">
+        <v>5</v>
       </c>
       <c r="F371" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G371" s="10" t="s">
-        <v>252</v>
+      <c r="G371" s="18" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="372" spans="2:7">
@@ -9682,76 +9640,76 @@
         <v>3</v>
       </c>
       <c r="D372" s="12">
-        <v>200</v>
-      </c>
-      <c r="E372" s="12">
-        <v>1</v>
+        <v>100</v>
+      </c>
+      <c r="E372" s="13">
+        <v>0.5</v>
       </c>
       <c r="F372" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G372" s="18" t="s">
-        <v>245</v>
+      <c r="G372" s="17" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="373" spans="2:7">
-      <c r="B373" s="10" t="s">
+      <c r="B373" s="7" t="s">
         <v>415</v>
       </c>
       <c r="C373" s="10">
         <v>3</v>
       </c>
-      <c r="D373" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="E373" s="12">
-        <v>5</v>
-      </c>
-      <c r="F373" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G373" s="18" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="374" spans="2:7">
-      <c r="B374" s="10" t="s">
+      <c r="D373" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E373" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F373" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="G373" s="24" t="s">
         <v>416</v>
       </c>
+    </row>
+    <row r="374" spans="2:7" ht="14.25">
+      <c r="B374" s="7" t="s">
+        <v>417</v>
+      </c>
       <c r="C374" s="10">
         <v>3</v>
       </c>
-      <c r="D374" s="12">
-        <v>100</v>
-      </c>
-      <c r="E374" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="F374" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G374" s="17" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="375" spans="2:7">
+      <c r="D374" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E374" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F374" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="G374" s="8">
+        <v>46094</v>
+      </c>
+    </row>
+    <row r="375" spans="2:7" ht="14.25">
       <c r="B375" s="7" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C375" s="10">
         <v>3</v>
       </c>
       <c r="D375" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E375" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F375" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="G375" s="24" t="s">
-        <v>418</v>
+      <c r="G375" s="8">
+        <v>46095</v>
       </c>
     </row>
     <row r="376" spans="2:7" ht="14.25">
@@ -9762,16 +9720,16 @@
         <v>3</v>
       </c>
       <c r="D376" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E376" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F376" s="25" t="s">
         <v>10</v>
       </c>
       <c r="G376" s="8">
-        <v>46094</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="377" spans="2:7" ht="14.25">
@@ -9782,16 +9740,16 @@
         <v>3</v>
       </c>
       <c r="D377" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E377" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F377" s="25" t="s">
         <v>10</v>
       </c>
       <c r="G377" s="8">
-        <v>46095</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="378" spans="2:7" ht="14.25">
@@ -9802,16 +9760,16 @@
         <v>3</v>
       </c>
       <c r="D378" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E378" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F378" s="25" t="s">
         <v>10</v>
       </c>
       <c r="G378" s="8">
-        <v>46064</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="379" spans="2:7" ht="14.25">
@@ -9822,10 +9780,10 @@
         <v>3</v>
       </c>
       <c r="D379" s="4" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="E379" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F379" s="25" t="s">
         <v>10</v>
@@ -9842,16 +9800,16 @@
         <v>3</v>
       </c>
       <c r="D380" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E380" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F380" s="25" t="s">
         <v>10</v>
       </c>
       <c r="G380" s="8">
-        <v>46067</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="381" spans="2:7" ht="14.25">
@@ -9862,16 +9820,16 @@
         <v>3</v>
       </c>
       <c r="D381" s="4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E381" s="4" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F381" s="25" t="s">
         <v>10</v>
       </c>
       <c r="G381" s="8">
-        <v>46066</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="382" spans="2:7" ht="14.25">
@@ -9882,16 +9840,16 @@
         <v>3</v>
       </c>
       <c r="D382" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E382" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F382" s="25" t="s">
         <v>10</v>
       </c>
       <c r="G382" s="8">
-        <v>46066</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="383" spans="2:7" ht="14.25">
@@ -9902,16 +9860,16 @@
         <v>3</v>
       </c>
       <c r="D383" s="4" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="E383" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F383" s="25" t="s">
         <v>10</v>
       </c>
       <c r="G383" s="8">
-        <v>46071</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="384" spans="2:7" ht="14.25">
@@ -9922,16 +9880,16 @@
         <v>3</v>
       </c>
       <c r="D384" s="4" t="s">
-        <v>31</v>
+        <v>102</v>
       </c>
       <c r="E384" s="4" t="s">
-        <v>32</v>
+        <v>103</v>
       </c>
       <c r="F384" s="25" t="s">
         <v>10</v>
       </c>
       <c r="G384" s="8">
-        <v>46081</v>
+        <v>46070</v>
       </c>
     </row>
     <row r="385" spans="2:7" ht="14.25">
@@ -9942,16 +9900,16 @@
         <v>3</v>
       </c>
       <c r="D385" s="4" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E385" s="4" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F385" s="25" t="s">
         <v>10</v>
       </c>
       <c r="G385" s="8">
-        <v>46066</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="386" spans="2:7" ht="14.25">
@@ -9962,16 +9920,16 @@
         <v>3</v>
       </c>
       <c r="D386" s="4" t="s">
-        <v>104</v>
+        <v>28</v>
       </c>
       <c r="E386" s="4" t="s">
-        <v>105</v>
+        <v>29</v>
       </c>
       <c r="F386" s="25" t="s">
         <v>10</v>
       </c>
       <c r="G386" s="8">
-        <v>46070</v>
+        <v>46067</v>
       </c>
     </row>
     <row r="387" spans="2:7" ht="14.25">
@@ -9982,16 +9940,16 @@
         <v>3</v>
       </c>
       <c r="D387" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E387" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F387" s="25" t="s">
         <v>10</v>
       </c>
       <c r="G387" s="8">
-        <v>46067</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="388" spans="2:7" ht="14.25">
@@ -10002,16 +9960,16 @@
         <v>3</v>
       </c>
       <c r="D388" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E388" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F388" s="25" t="s">
         <v>10</v>
       </c>
       <c r="G388" s="8">
-        <v>46067</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="389" spans="2:7" ht="14.25">
@@ -10022,10 +9980,10 @@
         <v>3</v>
       </c>
       <c r="D389" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E389" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F389" s="25" t="s">
         <v>10</v>
@@ -10042,16 +10000,16 @@
         <v>3</v>
       </c>
       <c r="D390" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E390" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F390" s="25" t="s">
         <v>10</v>
       </c>
       <c r="G390" s="8">
-        <v>46065</v>
+        <v>46115</v>
       </c>
     </row>
     <row r="391" spans="2:7" ht="14.25">
@@ -10062,16 +10020,16 @@
         <v>3</v>
       </c>
       <c r="D391" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E391" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F391" s="25" t="s">
         <v>10</v>
       </c>
       <c r="G391" s="8">
-        <v>46065</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="392" spans="2:7" ht="14.25">
@@ -10082,16 +10040,16 @@
         <v>3</v>
       </c>
       <c r="D392" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E392" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F392" s="25" t="s">
         <v>10</v>
       </c>
       <c r="G392" s="8">
-        <v>46115</v>
+        <v>46066</v>
       </c>
     </row>
     <row r="393" spans="2:7" ht="14.25">
@@ -10102,16 +10060,16 @@
         <v>3</v>
       </c>
       <c r="D393" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E393" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F393" s="25" t="s">
-        <v>10</v>
+        <v>29</v>
+      </c>
+      <c r="F393" s="4" t="s">
+        <v>136</v>
       </c>
       <c r="G393" s="8">
-        <v>46066</v>
+        <v>46086</v>
       </c>
     </row>
     <row r="394" spans="2:7" ht="14.25">
@@ -10122,12 +10080,12 @@
         <v>3</v>
       </c>
       <c r="D394" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E394" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F394" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="F394" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G394" s="8">
@@ -10142,16 +10100,16 @@
         <v>3</v>
       </c>
       <c r="D395" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E395" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F395" s="4" t="s">
-        <v>138</v>
+        <v>10</v>
       </c>
       <c r="G395" s="8">
-        <v>46086</v>
+        <v>46068</v>
       </c>
     </row>
     <row r="396" spans="2:7" ht="14.25">
@@ -10162,16 +10120,16 @@
         <v>3</v>
       </c>
       <c r="D396" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E396" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F396" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G396" s="8">
-        <v>46066</v>
+        <v>46065</v>
       </c>
     </row>
     <row r="397" spans="2:7" ht="14.25">
@@ -10182,16 +10140,16 @@
         <v>3</v>
       </c>
       <c r="D397" s="4" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E397" s="4" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F397" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G397" s="8">
-        <v>46068</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="398" spans="2:7" ht="14.25">
@@ -10202,16 +10160,16 @@
         <v>3</v>
       </c>
       <c r="D398" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E398" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F398" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G398" s="8">
-        <v>46065</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="399" spans="2:7" ht="14.25">
@@ -10222,16 +10180,16 @@
         <v>3</v>
       </c>
       <c r="D399" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E399" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F399" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G399" s="8">
-        <v>46050</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="400" spans="2:7" ht="14.25">
@@ -10242,50 +10200,50 @@
         <v>3</v>
       </c>
       <c r="D400" s="4" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E400" s="4" t="s">
-        <v>32</v>
+        <v>444</v>
       </c>
       <c r="F400" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G400" s="8">
-        <v>46099</v>
+        <v>46034</v>
       </c>
     </row>
     <row r="401" spans="2:7" ht="14.25">
       <c r="B401" s="7" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C401" s="10">
         <v>3</v>
       </c>
       <c r="D401" s="4" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E401" s="4" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F401" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G401" s="8">
-        <v>46071</v>
+        <v>46034</v>
       </c>
     </row>
     <row r="402" spans="2:7" ht="14.25">
       <c r="B402" s="7" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C402" s="10">
         <v>3</v>
       </c>
       <c r="D402" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E402" s="4" t="s">
-        <v>446</v>
+        <v>23</v>
       </c>
       <c r="F402" s="4" t="s">
         <v>10</v>
@@ -10302,10 +10260,10 @@
         <v>3</v>
       </c>
       <c r="D403" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E403" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F403" s="4" t="s">
         <v>10</v>
@@ -10322,16 +10280,16 @@
         <v>3</v>
       </c>
       <c r="D404" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E404" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F404" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G404" s="8">
-        <v>46034</v>
+        <v>46035</v>
       </c>
     </row>
     <row r="405" spans="2:7" ht="14.25">
@@ -10342,10 +10300,10 @@
         <v>3</v>
       </c>
       <c r="D405" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E405" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F405" s="4" t="s">
         <v>10</v>
@@ -10362,16 +10320,16 @@
         <v>3</v>
       </c>
       <c r="D406" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E406" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F406" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G406" s="8">
-        <v>46035</v>
+        <v>46034</v>
       </c>
     </row>
     <row r="407" spans="2:7" ht="14.25">
@@ -10382,10 +10340,10 @@
         <v>3</v>
       </c>
       <c r="D407" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E407" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F407" s="4" t="s">
         <v>10</v>
@@ -10402,10 +10360,10 @@
         <v>3</v>
       </c>
       <c r="D408" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="E408" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F408" s="4" t="s">
         <v>10</v>
@@ -10422,10 +10380,10 @@
         <v>3</v>
       </c>
       <c r="D409" s="4" t="s">
-        <v>25</v>
+        <v>454</v>
       </c>
       <c r="E409" s="4" t="s">
-        <v>26</v>
+        <v>455</v>
       </c>
       <c r="F409" s="4" t="s">
         <v>10</v>
@@ -10436,101 +10394,41 @@
     </row>
     <row r="410" spans="2:7" ht="14.25">
       <c r="B410" s="7" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="C410" s="10">
         <v>3</v>
       </c>
       <c r="D410" s="4" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="E410" s="4" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="F410" s="4" t="s">
-        <v>10</v>
+        <v>136</v>
       </c>
       <c r="G410" s="8">
-        <v>46034</v>
+        <v>46028</v>
       </c>
     </row>
     <row r="411" spans="2:7" ht="14.25">
       <c r="B411" s="7" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C411" s="10">
         <v>3</v>
       </c>
       <c r="D411" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E411" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F411" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G411" s="8">
-        <v>46034</v>
-      </c>
-    </row>
-    <row r="412" spans="2:7" ht="14.25">
-      <c r="B412" s="7" t="s">
-        <v>456</v>
-      </c>
-      <c r="C412" s="10">
-        <v>3</v>
-      </c>
-      <c r="D412" s="4" t="s">
-        <v>457</v>
-      </c>
-      <c r="E412" s="4" t="s">
-        <v>458</v>
-      </c>
-      <c r="F412" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G412" s="8">
-        <v>46034</v>
-      </c>
-    </row>
-    <row r="413" spans="2:7" ht="14.25">
-      <c r="B413" s="7" t="s">
-        <v>456</v>
-      </c>
-      <c r="C413" s="10">
-        <v>3</v>
-      </c>
-      <c r="D413" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E413" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F413" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="G413" s="8">
-        <v>46028</v>
-      </c>
-    </row>
-    <row r="414" spans="2:7" ht="14.25">
-      <c r="B414" s="7" t="s">
-        <v>459</v>
-      </c>
-      <c r="C414" s="10">
-        <v>3</v>
-      </c>
-      <c r="D414" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E414" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F414" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G414" s="8">
         <v>46028</v>
       </c>
     </row>

--- a/server/userPlan.xlsx
+++ b/server/userPlan.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30002"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30006"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E7D4B851-04A1-4B92-B678-4A89F73E5990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD6560E2-5666-4365-8BA0-14BAF8880782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9410,7 +9410,7 @@
         <v>143</v>
       </c>
       <c r="G356" s="17">
-        <v>46145</v>
+        <v>46086</v>
       </c>
     </row>
     <row r="357" spans="2:7">
